--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.32985</v>
+        <v>3.31794</v>
       </c>
       <c r="C2" t="n">
-        <v>3.82001</v>
+        <v>4.76365</v>
       </c>
       <c r="D2" t="n">
-        <v>5.45415</v>
+        <v>5.4241</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89096</v>
+        <v>3.89045</v>
       </c>
       <c r="F2" t="n">
-        <v>3.96948</v>
+        <v>4.00366</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.35604</v>
+        <v>3.33237</v>
       </c>
       <c r="C3" t="n">
-        <v>3.88141</v>
+        <v>4.77802</v>
       </c>
       <c r="D3" t="n">
-        <v>5.81161</v>
+        <v>5.67153</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9047</v>
+        <v>3.9074</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0123</v>
+        <v>4.00392</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.3805</v>
+        <v>3.35431</v>
       </c>
       <c r="C4" t="n">
-        <v>3.93107</v>
+        <v>4.81749</v>
       </c>
       <c r="D4" t="n">
-        <v>6.12063</v>
+        <v>6.08561</v>
       </c>
       <c r="E4" t="n">
-        <v>3.92394</v>
+        <v>3.93549</v>
       </c>
       <c r="F4" t="n">
-        <v>4.03532</v>
+        <v>4.07958</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.40395</v>
+        <v>3.39528</v>
       </c>
       <c r="C5" t="n">
-        <v>3.96325</v>
+        <v>4.86858</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49892</v>
+        <v>6.33702</v>
       </c>
       <c r="E5" t="n">
-        <v>3.94427</v>
+        <v>3.95003</v>
       </c>
       <c r="F5" t="n">
-        <v>4.07052</v>
+        <v>4.11674</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.43384</v>
+        <v>3.41402</v>
       </c>
       <c r="C6" t="n">
-        <v>4.00211</v>
+        <v>4.9007</v>
       </c>
       <c r="D6" t="n">
-        <v>6.85698</v>
+        <v>6.68646</v>
       </c>
       <c r="E6" t="n">
-        <v>3.97338</v>
+        <v>4.00183</v>
       </c>
       <c r="F6" t="n">
-        <v>4.12174</v>
+        <v>4.1324</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.45262</v>
+        <v>3.45389</v>
       </c>
       <c r="C7" t="n">
-        <v>4.05181</v>
+        <v>4.95857</v>
       </c>
       <c r="D7" t="n">
-        <v>5.19155</v>
+        <v>5.10777</v>
       </c>
       <c r="E7" t="n">
-        <v>4.01201</v>
+        <v>4.04834</v>
       </c>
       <c r="F7" t="n">
-        <v>4.18214</v>
+        <v>4.2056</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.50091</v>
+        <v>3.50374</v>
       </c>
       <c r="C8" t="n">
-        <v>4.08859</v>
+        <v>4.94559</v>
       </c>
       <c r="D8" t="n">
-        <v>5.33073</v>
+        <v>5.22568</v>
       </c>
       <c r="E8" t="n">
-        <v>4.13881</v>
+        <v>4.09875</v>
       </c>
       <c r="F8" t="n">
-        <v>4.34374</v>
+        <v>4.3716</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.55459</v>
+        <v>3.53876</v>
       </c>
       <c r="C9" t="n">
-        <v>4.17295</v>
+        <v>4.95898</v>
       </c>
       <c r="D9" t="n">
-        <v>5.55314</v>
+        <v>5.4482</v>
       </c>
       <c r="E9" t="n">
-        <v>3.94576</v>
+        <v>3.95581</v>
       </c>
       <c r="F9" t="n">
-        <v>4.13747</v>
+        <v>4.12473</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.95079</v>
+        <v>3.95916</v>
       </c>
       <c r="C10" t="n">
-        <v>4.34802</v>
+        <v>4.97773</v>
       </c>
       <c r="D10" t="n">
-        <v>5.79258</v>
+        <v>5.65386</v>
       </c>
       <c r="E10" t="n">
-        <v>3.96099</v>
+        <v>3.97518</v>
       </c>
       <c r="F10" t="n">
-        <v>4.12262</v>
+        <v>4.15416</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.95044</v>
+        <v>3.96882</v>
       </c>
       <c r="C11" t="n">
-        <v>4.35265</v>
+        <v>4.9724</v>
       </c>
       <c r="D11" t="n">
-        <v>6.01887</v>
+        <v>5.93209</v>
       </c>
       <c r="E11" t="n">
-        <v>3.98451</v>
+        <v>3.98035</v>
       </c>
       <c r="F11" t="n">
-        <v>4.14298</v>
+        <v>4.16431</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.98316</v>
+        <v>3.98272</v>
       </c>
       <c r="C12" t="n">
-        <v>4.36145</v>
+        <v>4.98444</v>
       </c>
       <c r="D12" t="n">
-        <v>6.29261</v>
+        <v>6.20719</v>
       </c>
       <c r="E12" t="n">
-        <v>4.00957</v>
+        <v>4.00968</v>
       </c>
       <c r="F12" t="n">
-        <v>4.17245</v>
+        <v>4.19475</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.998</v>
+        <v>3.98197</v>
       </c>
       <c r="C13" t="n">
-        <v>4.38488</v>
+        <v>5.04367</v>
       </c>
       <c r="D13" t="n">
-        <v>6.58815</v>
+        <v>6.44222</v>
       </c>
       <c r="E13" t="n">
-        <v>4.02768</v>
+        <v>4.02703</v>
       </c>
       <c r="F13" t="n">
-        <v>4.20227</v>
+        <v>4.22254</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.02179</v>
+        <v>4.01148</v>
       </c>
       <c r="C14" t="n">
-        <v>4.38434</v>
+        <v>5.02499</v>
       </c>
       <c r="D14" t="n">
-        <v>6.89716</v>
+        <v>6.75954</v>
       </c>
       <c r="E14" t="n">
-        <v>4.03628</v>
+        <v>4.06337</v>
       </c>
       <c r="F14" t="n">
-        <v>4.22386</v>
+        <v>4.21977</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.0316</v>
+        <v>4.00692</v>
       </c>
       <c r="C15" t="n">
-        <v>4.40905</v>
+        <v>5.07107</v>
       </c>
       <c r="D15" t="n">
-        <v>7.12783</v>
+        <v>6.98275</v>
       </c>
       <c r="E15" t="n">
-        <v>4.08105</v>
+        <v>4.10122</v>
       </c>
       <c r="F15" t="n">
-        <v>4.27901</v>
+        <v>4.29756</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.0433</v>
+        <v>4.04735</v>
       </c>
       <c r="C16" t="n">
-        <v>4.45245</v>
+        <v>5.0498</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3565</v>
+        <v>7.28489</v>
       </c>
       <c r="E16" t="n">
-        <v>4.09683</v>
+        <v>4.12328</v>
       </c>
       <c r="F16" t="n">
-        <v>4.30769</v>
+        <v>4.29287</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.05315</v>
+        <v>4.04602</v>
       </c>
       <c r="C17" t="n">
-        <v>4.45053</v>
+        <v>5.08608</v>
       </c>
       <c r="D17" t="n">
-        <v>7.65433</v>
+        <v>7.53422</v>
       </c>
       <c r="E17" t="n">
-        <v>4.12553</v>
+        <v>4.14838</v>
       </c>
       <c r="F17" t="n">
-        <v>4.31633</v>
+        <v>4.33545</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.08906</v>
+        <v>4.09512</v>
       </c>
       <c r="C18" t="n">
-        <v>4.48614</v>
+        <v>5.12976</v>
       </c>
       <c r="D18" t="n">
-        <v>7.93731</v>
+        <v>7.79069</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1525</v>
+        <v>4.19932</v>
       </c>
       <c r="F18" t="n">
-        <v>4.34936</v>
+        <v>4.35276</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.11013</v>
+        <v>4.1012</v>
       </c>
       <c r="C19" t="n">
-        <v>4.51711</v>
+        <v>5.18735</v>
       </c>
       <c r="D19" t="n">
-        <v>8.21086</v>
+        <v>8.09314</v>
       </c>
       <c r="E19" t="n">
-        <v>4.20276</v>
+        <v>4.23844</v>
       </c>
       <c r="F19" t="n">
-        <v>4.40376</v>
+        <v>4.40607</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.13157</v>
+        <v>4.13286</v>
       </c>
       <c r="C20" t="n">
-        <v>4.5602</v>
+        <v>5.2332</v>
       </c>
       <c r="D20" t="n">
-        <v>8.487819999999999</v>
+        <v>8.336880000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>4.26777</v>
+        <v>4.31618</v>
       </c>
       <c r="F20" t="n">
-        <v>4.51644</v>
+        <v>4.5058</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.21011</v>
+        <v>4.20552</v>
       </c>
       <c r="C21" t="n">
-        <v>4.58005</v>
+        <v>5.33434</v>
       </c>
       <c r="D21" t="n">
-        <v>6.30335</v>
+        <v>6.22504</v>
       </c>
       <c r="E21" t="n">
-        <v>4.34485</v>
+        <v>4.43236</v>
       </c>
       <c r="F21" t="n">
-        <v>4.57559</v>
+        <v>4.62554</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.26231</v>
+        <v>4.27979</v>
       </c>
       <c r="C22" t="n">
-        <v>4.67356</v>
+        <v>5.28735</v>
       </c>
       <c r="D22" t="n">
-        <v>6.49181</v>
+        <v>6.41485</v>
       </c>
       <c r="E22" t="n">
-        <v>4.67123</v>
+        <v>4.73212</v>
       </c>
       <c r="F22" t="n">
-        <v>4.96257</v>
+        <v>4.93637</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.40895</v>
+        <v>4.44727</v>
       </c>
       <c r="C23" t="n">
-        <v>4.80675</v>
+        <v>5.26797</v>
       </c>
       <c r="D23" t="n">
-        <v>6.71573</v>
+        <v>6.61999</v>
       </c>
       <c r="E23" t="n">
-        <v>4.21387</v>
+        <v>4.20728</v>
       </c>
       <c r="F23" t="n">
-        <v>4.54209</v>
+        <v>4.54648</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.47287</v>
+        <v>4.4841</v>
       </c>
       <c r="C24" t="n">
-        <v>5.08306</v>
+        <v>5.3065</v>
       </c>
       <c r="D24" t="n">
-        <v>6.95637</v>
+        <v>6.88551</v>
       </c>
       <c r="E24" t="n">
-        <v>4.22334</v>
+        <v>4.25208</v>
       </c>
       <c r="F24" t="n">
-        <v>4.55736</v>
+        <v>4.5876</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.4799</v>
+        <v>4.50227</v>
       </c>
       <c r="C25" t="n">
-        <v>5.09707</v>
+        <v>5.3439</v>
       </c>
       <c r="D25" t="n">
-        <v>7.21843</v>
+        <v>7.11891</v>
       </c>
       <c r="E25" t="n">
-        <v>4.23443</v>
+        <v>4.24847</v>
       </c>
       <c r="F25" t="n">
-        <v>4.58057</v>
+        <v>4.61822</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.48725</v>
+        <v>4.50197</v>
       </c>
       <c r="C26" t="n">
-        <v>5.08965</v>
+        <v>5.30047</v>
       </c>
       <c r="D26" t="n">
-        <v>7.42691</v>
+        <v>7.32707</v>
       </c>
       <c r="E26" t="n">
-        <v>4.29039</v>
+        <v>4.26719</v>
       </c>
       <c r="F26" t="n">
-        <v>4.61509</v>
+        <v>4.63073</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.48252</v>
+        <v>4.50998</v>
       </c>
       <c r="C27" t="n">
-        <v>5.10527</v>
+        <v>5.3971</v>
       </c>
       <c r="D27" t="n">
-        <v>7.71231</v>
+        <v>7.58458</v>
       </c>
       <c r="E27" t="n">
-        <v>4.32169</v>
+        <v>4.29646</v>
       </c>
       <c r="F27" t="n">
-        <v>4.63806</v>
+        <v>4.65281</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.50652</v>
+        <v>4.5099</v>
       </c>
       <c r="C28" t="n">
-        <v>5.12043</v>
+        <v>5.38477</v>
       </c>
       <c r="D28" t="n">
-        <v>7.9508</v>
+        <v>7.83901</v>
       </c>
       <c r="E28" t="n">
-        <v>4.35744</v>
+        <v>4.35181</v>
       </c>
       <c r="F28" t="n">
-        <v>4.66939</v>
+        <v>4.70615</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.51703</v>
+        <v>4.53529</v>
       </c>
       <c r="C29" t="n">
-        <v>5.14778</v>
+        <v>5.4466</v>
       </c>
       <c r="D29" t="n">
-        <v>8.245850000000001</v>
+        <v>8.101129999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>4.36072</v>
+        <v>4.37746</v>
       </c>
       <c r="F29" t="n">
-        <v>4.70559</v>
+        <v>4.71672</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.53897</v>
+        <v>4.53756</v>
       </c>
       <c r="C30" t="n">
-        <v>5.15745</v>
+        <v>5.43717</v>
       </c>
       <c r="D30" t="n">
-        <v>8.516439999999999</v>
+        <v>8.35074</v>
       </c>
       <c r="E30" t="n">
-        <v>4.40095</v>
+        <v>4.42109</v>
       </c>
       <c r="F30" t="n">
-        <v>4.74202</v>
+        <v>4.76556</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.55229</v>
+        <v>4.55538</v>
       </c>
       <c r="C31" t="n">
-        <v>5.1802</v>
+        <v>5.47086</v>
       </c>
       <c r="D31" t="n">
-        <v>8.737170000000001</v>
+        <v>8.57939</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4626</v>
+        <v>4.46178</v>
       </c>
       <c r="F31" t="n">
-        <v>4.80036</v>
+        <v>4.81022</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.57334</v>
+        <v>4.583</v>
       </c>
       <c r="C32" t="n">
-        <v>5.21317</v>
+        <v>5.49596</v>
       </c>
       <c r="D32" t="n">
-        <v>8.97301</v>
+        <v>8.791550000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>4.46151</v>
+        <v>4.49244</v>
       </c>
       <c r="F32" t="n">
-        <v>4.83482</v>
+        <v>4.85219</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.61216</v>
+        <v>4.61309</v>
       </c>
       <c r="C33" t="n">
-        <v>5.25777</v>
+        <v>5.53762</v>
       </c>
       <c r="D33" t="n">
-        <v>9.222709999999999</v>
+        <v>9.088469999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>4.58346</v>
+        <v>4.55537</v>
       </c>
       <c r="F33" t="n">
-        <v>4.90293</v>
+        <v>4.91851</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.64976</v>
+        <v>4.63718</v>
       </c>
       <c r="C34" t="n">
-        <v>5.27667</v>
+        <v>5.5572</v>
       </c>
       <c r="D34" t="n">
-        <v>9.44913</v>
+        <v>9.31734</v>
       </c>
       <c r="E34" t="n">
-        <v>4.62758</v>
+        <v>4.62069</v>
       </c>
       <c r="F34" t="n">
-        <v>4.99377</v>
+        <v>5.00543</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.71085</v>
+        <v>4.70093</v>
       </c>
       <c r="C35" t="n">
-        <v>5.33843</v>
+        <v>5.70652</v>
       </c>
       <c r="D35" t="n">
-        <v>6.80691</v>
+        <v>6.71466</v>
       </c>
       <c r="E35" t="n">
-        <v>4.86586</v>
+        <v>4.8246</v>
       </c>
       <c r="F35" t="n">
-        <v>5.19216</v>
+        <v>5.20781</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.81483</v>
+        <v>4.80858</v>
       </c>
       <c r="C36" t="n">
-        <v>5.42439</v>
+        <v>5.74492</v>
       </c>
       <c r="D36" t="n">
-        <v>6.98313</v>
+        <v>6.87544</v>
       </c>
       <c r="E36" t="n">
-        <v>5.23935</v>
+        <v>5.29876</v>
       </c>
       <c r="F36" t="n">
-        <v>5.66849</v>
+        <v>5.68268</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.99562</v>
+        <v>5.02668</v>
       </c>
       <c r="C37" t="n">
-        <v>5.65041</v>
+        <v>5.57315</v>
       </c>
       <c r="D37" t="n">
-        <v>7.16779</v>
+        <v>7.03779</v>
       </c>
       <c r="E37" t="n">
-        <v>4.54384</v>
+        <v>4.54924</v>
       </c>
       <c r="F37" t="n">
-        <v>4.88167</v>
+        <v>4.86132</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.75495</v>
+        <v>4.77637</v>
       </c>
       <c r="C38" t="n">
-        <v>5.65181</v>
+        <v>5.64714</v>
       </c>
       <c r="D38" t="n">
-        <v>7.38668</v>
+        <v>7.2738</v>
       </c>
       <c r="E38" t="n">
-        <v>4.5279</v>
+        <v>4.57137</v>
       </c>
       <c r="F38" t="n">
-        <v>4.89863</v>
+        <v>4.89559</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.78218</v>
+        <v>4.75192</v>
       </c>
       <c r="C39" t="n">
-        <v>5.66303</v>
+        <v>5.64039</v>
       </c>
       <c r="D39" t="n">
-        <v>7.60108</v>
+        <v>7.465</v>
       </c>
       <c r="E39" t="n">
-        <v>4.59782</v>
+        <v>4.59968</v>
       </c>
       <c r="F39" t="n">
-        <v>4.91653</v>
+        <v>4.954</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.78489</v>
+        <v>4.77323</v>
       </c>
       <c r="C40" t="n">
-        <v>5.65581</v>
+        <v>5.64333</v>
       </c>
       <c r="D40" t="n">
-        <v>7.85553</v>
+        <v>7.71468</v>
       </c>
       <c r="E40" t="n">
-        <v>4.63193</v>
+        <v>4.63611</v>
       </c>
       <c r="F40" t="n">
-        <v>4.96846</v>
+        <v>4.99617</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.78124</v>
+        <v>4.80782</v>
       </c>
       <c r="C41" t="n">
-        <v>5.65998</v>
+        <v>5.65119</v>
       </c>
       <c r="D41" t="n">
-        <v>8.098039999999999</v>
+        <v>7.93763</v>
       </c>
       <c r="E41" t="n">
-        <v>4.68184</v>
+        <v>4.68349</v>
       </c>
       <c r="F41" t="n">
-        <v>4.97927</v>
+        <v>5.01901</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.7597</v>
+        <v>4.82279</v>
       </c>
       <c r="C42" t="n">
-        <v>5.66681</v>
+        <v>5.67358</v>
       </c>
       <c r="D42" t="n">
-        <v>8.339079999999999</v>
+        <v>8.189220000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>4.69815</v>
+        <v>4.71019</v>
       </c>
       <c r="F42" t="n">
-        <v>5.01284</v>
+        <v>5.02115</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.83092</v>
+        <v>4.84411</v>
       </c>
       <c r="C43" t="n">
-        <v>5.70702</v>
+        <v>5.7146</v>
       </c>
       <c r="D43" t="n">
-        <v>8.59967</v>
+        <v>8.437049999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>4.76061</v>
+        <v>4.75207</v>
       </c>
       <c r="F43" t="n">
-        <v>5.06457</v>
+        <v>5.10715</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.80283</v>
+        <v>4.78989</v>
       </c>
       <c r="C44" t="n">
-        <v>5.67781</v>
+        <v>5.74409</v>
       </c>
       <c r="D44" t="n">
-        <v>8.88278</v>
+        <v>8.70862</v>
       </c>
       <c r="E44" t="n">
-        <v>4.80912</v>
+        <v>4.78838</v>
       </c>
       <c r="F44" t="n">
-        <v>5.10145</v>
+        <v>5.1042</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.79359</v>
+        <v>4.86715</v>
       </c>
       <c r="C45" t="n">
-        <v>5.71845</v>
+        <v>5.7478</v>
       </c>
       <c r="D45" t="n">
-        <v>9.122389999999999</v>
+        <v>8.971640000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>4.80352</v>
+        <v>4.83668</v>
       </c>
       <c r="F45" t="n">
-        <v>5.1851</v>
+        <v>5.13324</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.87704</v>
+        <v>4.90325</v>
       </c>
       <c r="C46" t="n">
-        <v>5.80143</v>
+        <v>5.83841</v>
       </c>
       <c r="D46" t="n">
-        <v>9.35988</v>
+        <v>9.20862</v>
       </c>
       <c r="E46" t="n">
-        <v>4.89798</v>
+        <v>4.90202</v>
       </c>
       <c r="F46" t="n">
-        <v>5.17918</v>
+        <v>5.2072</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.91821</v>
+        <v>4.94866</v>
       </c>
       <c r="C47" t="n">
-        <v>5.77287</v>
+        <v>5.85105</v>
       </c>
       <c r="D47" t="n">
-        <v>9.59192</v>
+        <v>9.41907</v>
       </c>
       <c r="E47" t="n">
-        <v>4.97752</v>
+        <v>4.95063</v>
       </c>
       <c r="F47" t="n">
-        <v>5.28523</v>
+        <v>5.31325</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.96188</v>
+        <v>4.98484</v>
       </c>
       <c r="C48" t="n">
-        <v>5.83878</v>
+        <v>5.95949</v>
       </c>
       <c r="D48" t="n">
-        <v>9.829879999999999</v>
+        <v>9.68717</v>
       </c>
       <c r="E48" t="n">
-        <v>5.08973</v>
+        <v>5.1578</v>
       </c>
       <c r="F48" t="n">
-        <v>5.45068</v>
+        <v>5.49836</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.03459</v>
+        <v>5.04927</v>
       </c>
       <c r="C49" t="n">
-        <v>5.89424</v>
+        <v>6.06013</v>
       </c>
       <c r="D49" t="n">
-        <v>10.0918</v>
+        <v>9.883979999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>5.38746</v>
+        <v>5.39089</v>
       </c>
       <c r="F49" t="n">
-        <v>5.72293</v>
+        <v>5.75709</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.08681</v>
+        <v>5.12731</v>
       </c>
       <c r="C50" t="n">
-        <v>6.06878</v>
+        <v>6.17605</v>
       </c>
       <c r="D50" t="n">
-        <v>7.09736</v>
+        <v>6.99021</v>
       </c>
       <c r="E50" t="n">
-        <v>5.69451</v>
+        <v>5.74499</v>
       </c>
       <c r="F50" t="n">
-        <v>6.11088</v>
+        <v>6.13893</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.36063</v>
+        <v>5.34924</v>
       </c>
       <c r="C51" t="n">
-        <v>6.30749</v>
+        <v>6.03601</v>
       </c>
       <c r="D51" t="n">
-        <v>7.28055</v>
+        <v>7.13186</v>
       </c>
       <c r="E51" t="n">
-        <v>4.90775</v>
+        <v>4.92101</v>
       </c>
       <c r="F51" t="n">
-        <v>5.14114</v>
+        <v>5.18287</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.72646</v>
+        <v>5.75188</v>
       </c>
       <c r="C52" t="n">
-        <v>6.74657</v>
+        <v>6.0289</v>
       </c>
       <c r="D52" t="n">
-        <v>7.4762</v>
+        <v>7.35949</v>
       </c>
       <c r="E52" t="n">
-        <v>4.94748</v>
+        <v>4.95507</v>
       </c>
       <c r="F52" t="n">
-        <v>5.16513</v>
+        <v>5.20379</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.46969</v>
+        <v>5.42004</v>
       </c>
       <c r="C53" t="n">
-        <v>6.28083</v>
+        <v>6.05719</v>
       </c>
       <c r="D53" t="n">
-        <v>7.70735</v>
+        <v>7.56591</v>
       </c>
       <c r="E53" t="n">
-        <v>4.96571</v>
+        <v>4.99232</v>
       </c>
       <c r="F53" t="n">
-        <v>5.158</v>
+        <v>5.23377</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.45245</v>
+        <v>5.44496</v>
       </c>
       <c r="C54" t="n">
-        <v>6.28733</v>
+        <v>6.03004</v>
       </c>
       <c r="D54" t="n">
-        <v>7.95201</v>
+        <v>7.80524</v>
       </c>
       <c r="E54" t="n">
-        <v>4.99126</v>
+        <v>5.01523</v>
       </c>
       <c r="F54" t="n">
-        <v>5.2435</v>
+        <v>5.2442</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.43782</v>
+        <v>5.43784</v>
       </c>
       <c r="C55" t="n">
-        <v>6.31524</v>
+        <v>6.0382</v>
       </c>
       <c r="D55" t="n">
-        <v>8.204359999999999</v>
+        <v>8.035399999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>5.04895</v>
+        <v>5.0641</v>
       </c>
       <c r="F55" t="n">
-        <v>5.26493</v>
+        <v>5.28607</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.50684</v>
+        <v>5.46473</v>
       </c>
       <c r="C56" t="n">
-        <v>6.25813</v>
+        <v>6.04286</v>
       </c>
       <c r="D56" t="n">
-        <v>8.459860000000001</v>
+        <v>8.29152</v>
       </c>
       <c r="E56" t="n">
-        <v>5.06087</v>
+        <v>5.08963</v>
       </c>
       <c r="F56" t="n">
-        <v>5.30416</v>
+        <v>5.34673</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.4861</v>
+        <v>5.46827</v>
       </c>
       <c r="C57" t="n">
-        <v>6.33846</v>
+        <v>6.12842</v>
       </c>
       <c r="D57" t="n">
-        <v>8.71777</v>
+        <v>8.550240000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>5.125</v>
+        <v>5.13583</v>
       </c>
       <c r="F57" t="n">
-        <v>5.36684</v>
+        <v>5.34947</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.50358</v>
+        <v>5.4753</v>
       </c>
       <c r="C58" t="n">
-        <v>6.34736</v>
+        <v>6.12976</v>
       </c>
       <c r="D58" t="n">
-        <v>8.97284</v>
+        <v>8.831759999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>5.17314</v>
+        <v>5.19503</v>
       </c>
       <c r="F58" t="n">
-        <v>5.40301</v>
+        <v>5.41944</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.5272</v>
+        <v>5.49401</v>
       </c>
       <c r="C59" t="n">
-        <v>6.34843</v>
+        <v>6.19291</v>
       </c>
       <c r="D59" t="n">
-        <v>9.2074</v>
+        <v>9.04702</v>
       </c>
       <c r="E59" t="n">
-        <v>5.24171</v>
+        <v>5.26697</v>
       </c>
       <c r="F59" t="n">
-        <v>5.45341</v>
+        <v>5.48505</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.5335</v>
+        <v>5.51592</v>
       </c>
       <c r="C60" t="n">
-        <v>6.39073</v>
+        <v>6.23902</v>
       </c>
       <c r="D60" t="n">
-        <v>9.443440000000001</v>
+        <v>9.299709999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>5.30667</v>
+        <v>5.32715</v>
       </c>
       <c r="F60" t="n">
-        <v>5.54702</v>
+        <v>5.56995</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.57258</v>
+        <v>5.52623</v>
       </c>
       <c r="C61" t="n">
-        <v>6.41876</v>
+        <v>6.29338</v>
       </c>
       <c r="D61" t="n">
-        <v>9.72465</v>
+        <v>9.57081</v>
       </c>
       <c r="E61" t="n">
-        <v>5.4439</v>
+        <v>5.46713</v>
       </c>
       <c r="F61" t="n">
-        <v>5.67932</v>
+        <v>5.71495</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.563</v>
+        <v>5.61194</v>
       </c>
       <c r="C62" t="n">
-        <v>6.47905</v>
+        <v>6.3329</v>
       </c>
       <c r="D62" t="n">
-        <v>9.980779999999999</v>
+        <v>9.806340000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>5.59968</v>
+        <v>5.6157</v>
       </c>
       <c r="F62" t="n">
-        <v>5.8369</v>
+        <v>5.85856</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.68615</v>
+        <v>5.68467</v>
       </c>
       <c r="C63" t="n">
-        <v>6.55891</v>
+        <v>6.45387</v>
       </c>
       <c r="D63" t="n">
-        <v>10.2221</v>
+        <v>10.0449</v>
       </c>
       <c r="E63" t="n">
-        <v>5.79351</v>
+        <v>5.83336</v>
       </c>
       <c r="F63" t="n">
-        <v>6.11946</v>
+        <v>6.13838</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.77711</v>
+        <v>5.78317</v>
       </c>
       <c r="C64" t="n">
-        <v>6.67325</v>
+        <v>6.5651</v>
       </c>
       <c r="D64" t="n">
-        <v>7.34226</v>
+        <v>7.27413</v>
       </c>
       <c r="E64" t="n">
-        <v>6.14113</v>
+        <v>6.134</v>
       </c>
       <c r="F64" t="n">
-        <v>6.4498</v>
+        <v>6.46419</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.99196</v>
+        <v>5.98566</v>
       </c>
       <c r="C65" t="n">
-        <v>6.87289</v>
+        <v>6.28723</v>
       </c>
       <c r="D65" t="n">
-        <v>7.55589</v>
+        <v>7.47771</v>
       </c>
       <c r="E65" t="n">
-        <v>6.60175</v>
+        <v>6.61928</v>
       </c>
       <c r="F65" t="n">
-        <v>6.95418</v>
+        <v>7.00328</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.21902</v>
+        <v>6.27279</v>
       </c>
       <c r="C66" t="n">
-        <v>7.21829</v>
+        <v>6.31836</v>
       </c>
       <c r="D66" t="n">
-        <v>7.80166</v>
+        <v>7.67785</v>
       </c>
       <c r="E66" t="n">
-        <v>5.24699</v>
+        <v>5.25099</v>
       </c>
       <c r="F66" t="n">
-        <v>5.4227</v>
+        <v>5.46354</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>6.37408</v>
+        <v>6.11859</v>
       </c>
       <c r="C67" t="n">
-        <v>6.88251</v>
+        <v>6.321</v>
       </c>
       <c r="D67" t="n">
-        <v>8.104710000000001</v>
+        <v>7.94071</v>
       </c>
       <c r="E67" t="n">
-        <v>5.27569</v>
+        <v>5.28847</v>
       </c>
       <c r="F67" t="n">
-        <v>5.43502</v>
+        <v>5.51601</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>6.4129</v>
+        <v>6.16827</v>
       </c>
       <c r="C68" t="n">
-        <v>7.03103</v>
+        <v>6.32401</v>
       </c>
       <c r="D68" t="n">
-        <v>8.34581</v>
+        <v>8.2256</v>
       </c>
       <c r="E68" t="n">
-        <v>5.31296</v>
+        <v>5.30953</v>
       </c>
       <c r="F68" t="n">
-        <v>5.62311</v>
+        <v>5.5452</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>6.40825</v>
+        <v>6.15326</v>
       </c>
       <c r="C69" t="n">
-        <v>7.0653</v>
+        <v>6.35547</v>
       </c>
       <c r="D69" t="n">
-        <v>8.68496</v>
+        <v>8.47653</v>
       </c>
       <c r="E69" t="n">
-        <v>5.33902</v>
+        <v>5.36386</v>
       </c>
       <c r="F69" t="n">
-        <v>5.56191</v>
+        <v>5.65178</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>6.46424</v>
+        <v>6.16497</v>
       </c>
       <c r="C70" t="n">
-        <v>7.03886</v>
+        <v>6.35085</v>
       </c>
       <c r="D70" t="n">
-        <v>8.996639999999999</v>
+        <v>8.780570000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>5.35128</v>
+        <v>5.39195</v>
       </c>
       <c r="F70" t="n">
-        <v>5.84376</v>
+        <v>5.98629</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>6.38113</v>
+        <v>6.16206</v>
       </c>
       <c r="C71" t="n">
-        <v>7.63107</v>
+        <v>6.39579</v>
       </c>
       <c r="D71" t="n">
-        <v>9.30161</v>
+        <v>9.166499999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>5.42252</v>
+        <v>5.42527</v>
       </c>
       <c r="F71" t="n">
-        <v>6.09736</v>
+        <v>6.27215</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>6.43024</v>
+        <v>6.19846</v>
       </c>
       <c r="C72" t="n">
-        <v>7.8477</v>
+        <v>6.4027</v>
       </c>
       <c r="D72" t="n">
-        <v>9.74489</v>
+        <v>9.44122</v>
       </c>
       <c r="E72" t="n">
-        <v>5.45241</v>
+        <v>5.487</v>
       </c>
       <c r="F72" t="n">
-        <v>6.74977</v>
+        <v>6.99469</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>6.4565</v>
+        <v>6.19484</v>
       </c>
       <c r="C73" t="n">
-        <v>8.91433</v>
+        <v>6.46156</v>
       </c>
       <c r="D73" t="n">
-        <v>10.25</v>
+        <v>10.0766</v>
       </c>
       <c r="E73" t="n">
-        <v>5.51757</v>
+        <v>5.55073</v>
       </c>
       <c r="F73" t="n">
-        <v>7.16293</v>
+        <v>7.33621</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>6.49299</v>
+        <v>6.20509</v>
       </c>
       <c r="C74" t="n">
-        <v>9.54175</v>
+        <v>6.47409</v>
       </c>
       <c r="D74" t="n">
-        <v>10.8487</v>
+        <v>10.6354</v>
       </c>
       <c r="E74" t="n">
-        <v>5.60529</v>
+        <v>5.63203</v>
       </c>
       <c r="F74" t="n">
-        <v>8.10131</v>
+        <v>8.22148</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>6.51586</v>
+        <v>6.2633</v>
       </c>
       <c r="C75" t="n">
-        <v>10.2205</v>
+        <v>6.5435</v>
       </c>
       <c r="D75" t="n">
-        <v>11.3207</v>
+        <v>11.2684</v>
       </c>
       <c r="E75" t="n">
-        <v>5.72371</v>
+        <v>5.74075</v>
       </c>
       <c r="F75" t="n">
-        <v>8.854010000000001</v>
+        <v>9.022460000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>6.59603</v>
+        <v>6.27207</v>
       </c>
       <c r="C76" t="n">
-        <v>10.4227</v>
+        <v>6.62333</v>
       </c>
       <c r="D76" t="n">
-        <v>12.1695</v>
+        <v>11.9033</v>
       </c>
       <c r="E76" t="n">
-        <v>5.86452</v>
+        <v>5.89504</v>
       </c>
       <c r="F76" t="n">
-        <v>9.6532</v>
+        <v>9.849959999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.63954</v>
+        <v>6.3706</v>
       </c>
       <c r="C77" t="n">
-        <v>11.2775</v>
+        <v>6.70232</v>
       </c>
       <c r="D77" t="n">
-        <v>13.0734</v>
+        <v>12.7822</v>
       </c>
       <c r="E77" t="n">
-        <v>6.0579</v>
+        <v>6.08512</v>
       </c>
       <c r="F77" t="n">
-        <v>10.2616</v>
+        <v>10.423</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>6.72317</v>
+        <v>6.49419</v>
       </c>
       <c r="C78" t="n">
-        <v>11.6813</v>
+        <v>6.8564</v>
       </c>
       <c r="D78" t="n">
-        <v>14.9465</v>
+        <v>14.7937</v>
       </c>
       <c r="E78" t="n">
-        <v>6.3359</v>
+        <v>6.36761</v>
       </c>
       <c r="F78" t="n">
-        <v>10.8214</v>
+        <v>11.048</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>6.89732</v>
+        <v>6.64509</v>
       </c>
       <c r="C79" t="n">
-        <v>12.2145</v>
+        <v>13.945</v>
       </c>
       <c r="D79" t="n">
-        <v>15.7083</v>
+        <v>15.547</v>
       </c>
       <c r="E79" t="n">
-        <v>6.73346</v>
+        <v>6.77701</v>
       </c>
       <c r="F79" t="n">
-        <v>11.5551</v>
+        <v>11.7533</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>7.07828</v>
+        <v>6.91512</v>
       </c>
       <c r="C80" t="n">
-        <v>12.5896</v>
+        <v>14.184</v>
       </c>
       <c r="D80" t="n">
-        <v>16.4874</v>
+        <v>16.3078</v>
       </c>
       <c r="E80" t="n">
-        <v>6.69425</v>
+        <v>6.80174</v>
       </c>
       <c r="F80" t="n">
-        <v>11.9314</v>
+        <v>12.0879</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>15.0167</v>
+        <v>14.9115</v>
       </c>
       <c r="C81" t="n">
-        <v>14.865</v>
+        <v>14.2613</v>
       </c>
       <c r="D81" t="n">
-        <v>17.1989</v>
+        <v>17.0633</v>
       </c>
       <c r="E81" t="n">
-        <v>6.80841</v>
+        <v>7.06881</v>
       </c>
       <c r="F81" t="n">
-        <v>12.1239</v>
+        <v>12.1143</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>15.1417</v>
+        <v>14.9978</v>
       </c>
       <c r="C82" t="n">
-        <v>14.9583</v>
+        <v>14.3081</v>
       </c>
       <c r="D82" t="n">
-        <v>17.9127</v>
+        <v>17.8235</v>
       </c>
       <c r="E82" t="n">
-        <v>6.93889</v>
+        <v>7.17802</v>
       </c>
       <c r="F82" t="n">
-        <v>12.1787</v>
+        <v>12.3215</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>15.2844</v>
+        <v>14.9717</v>
       </c>
       <c r="C83" t="n">
-        <v>14.9119</v>
+        <v>14.4013</v>
       </c>
       <c r="D83" t="n">
-        <v>18.5699</v>
+        <v>18.5266</v>
       </c>
       <c r="E83" t="n">
-        <v>7.22795</v>
+        <v>7.21777</v>
       </c>
       <c r="F83" t="n">
-        <v>12.2545</v>
+        <v>12.2577</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>15.3083</v>
+        <v>15.2691</v>
       </c>
       <c r="C84" t="n">
-        <v>15.0231</v>
+        <v>14.5023</v>
       </c>
       <c r="D84" t="n">
-        <v>19.2846</v>
+        <v>19.117</v>
       </c>
       <c r="E84" t="n">
-        <v>7.21041</v>
+        <v>7.57872</v>
       </c>
       <c r="F84" t="n">
-        <v>12.3046</v>
+        <v>12.4721</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>15.2468</v>
+        <v>15.3424</v>
       </c>
       <c r="C85" t="n">
-        <v>15.0211</v>
+        <v>14.4316</v>
       </c>
       <c r="D85" t="n">
-        <v>19.9685</v>
+        <v>19.8608</v>
       </c>
       <c r="E85" t="n">
-        <v>7.4866</v>
+        <v>7.65809</v>
       </c>
       <c r="F85" t="n">
-        <v>12.4389</v>
+        <v>12.5879</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>15.2597</v>
+        <v>15.2923</v>
       </c>
       <c r="C86" t="n">
-        <v>15.0376</v>
+        <v>14.5302</v>
       </c>
       <c r="D86" t="n">
-        <v>20.5645</v>
+        <v>20.4742</v>
       </c>
       <c r="E86" t="n">
-        <v>7.59157</v>
+        <v>7.86494</v>
       </c>
       <c r="F86" t="n">
-        <v>12.4187</v>
+        <v>12.7378</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>15.3632</v>
+        <v>15.4717</v>
       </c>
       <c r="C87" t="n">
-        <v>15.2275</v>
+        <v>14.6833</v>
       </c>
       <c r="D87" t="n">
-        <v>21.2513</v>
+        <v>21.0575</v>
       </c>
       <c r="E87" t="n">
-        <v>7.9185</v>
+        <v>7.87536</v>
       </c>
       <c r="F87" t="n">
-        <v>12.6151</v>
+        <v>12.7995</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.5326</v>
+        <v>15.4269</v>
       </c>
       <c r="C88" t="n">
-        <v>15.3163</v>
+        <v>14.8051</v>
       </c>
       <c r="D88" t="n">
-        <v>21.8633</v>
+        <v>21.7643</v>
       </c>
       <c r="E88" t="n">
-        <v>8.02392</v>
+        <v>8.09305</v>
       </c>
       <c r="F88" t="n">
-        <v>12.7492</v>
+        <v>12.957</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>15.5933</v>
+        <v>15.4303</v>
       </c>
       <c r="C89" t="n">
-        <v>15.3889</v>
+        <v>14.7431</v>
       </c>
       <c r="D89" t="n">
-        <v>22.6732</v>
+        <v>22.384</v>
       </c>
       <c r="E89" t="n">
-        <v>8.2256</v>
+        <v>8.419029999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>12.9521</v>
+        <v>13.1266</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>15.6106</v>
+        <v>15.5465</v>
       </c>
       <c r="C90" t="n">
-        <v>15.5894</v>
+        <v>14.8043</v>
       </c>
       <c r="D90" t="n">
-        <v>23.341</v>
+        <v>23.1407</v>
       </c>
       <c r="E90" t="n">
-        <v>8.47236</v>
+        <v>8.67634</v>
       </c>
       <c r="F90" t="n">
-        <v>13.0986</v>
+        <v>13.3805</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>15.68</v>
+        <v>15.5704</v>
       </c>
       <c r="C91" t="n">
-        <v>15.6837</v>
+        <v>14.7828</v>
       </c>
       <c r="D91" t="n">
-        <v>24.0771</v>
+        <v>23.904</v>
       </c>
       <c r="E91" t="n">
-        <v>8.729570000000001</v>
+        <v>8.844620000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>13.4134</v>
+        <v>13.5019</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>15.5682</v>
+        <v>15.6958</v>
       </c>
       <c r="C92" t="n">
-        <v>15.9619</v>
+        <v>14.8459</v>
       </c>
       <c r="D92" t="n">
-        <v>24.0525</v>
+        <v>23.9405</v>
       </c>
       <c r="E92" t="n">
-        <v>8.97555</v>
+        <v>9.134270000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>13.8009</v>
+        <v>13.8639</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>15.7084</v>
+        <v>15.7782</v>
       </c>
       <c r="C93" t="n">
-        <v>16.2242</v>
+        <v>14.8226</v>
       </c>
       <c r="D93" t="n">
-        <v>24.5057</v>
+        <v>24.4112</v>
       </c>
       <c r="E93" t="n">
-        <v>9.36218</v>
+        <v>9.451309999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>14.2836</v>
+        <v>14.3728</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.8779</v>
+        <v>15.9339</v>
       </c>
       <c r="C94" t="n">
-        <v>16.6073</v>
+        <v>23.5421</v>
       </c>
       <c r="D94" t="n">
-        <v>25.0184</v>
+        <v>24.922</v>
       </c>
       <c r="E94" t="n">
-        <v>17.0487</v>
+        <v>17.0013</v>
       </c>
       <c r="F94" t="n">
-        <v>20.1489</v>
+        <v>20.1999</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.1764</v>
+        <v>22.9437</v>
       </c>
       <c r="C95" t="n">
-        <v>24.4726</v>
+        <v>23.5011</v>
       </c>
       <c r="D95" t="n">
-        <v>25.6383</v>
+        <v>25.3897</v>
       </c>
       <c r="E95" t="n">
-        <v>17.2901</v>
+        <v>17.2146</v>
       </c>
       <c r="F95" t="n">
-        <v>20.218</v>
+        <v>20.3144</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.2029</v>
+        <v>23.2131</v>
       </c>
       <c r="C96" t="n">
-        <v>24.5898</v>
+        <v>23.5472</v>
       </c>
       <c r="D96" t="n">
-        <v>26.1642</v>
+        <v>25.9065</v>
       </c>
       <c r="E96" t="n">
-        <v>17.4724</v>
+        <v>17.3683</v>
       </c>
       <c r="F96" t="n">
-        <v>20.318</v>
+        <v>20.3918</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.2175</v>
+        <v>23.1197</v>
       </c>
       <c r="C97" t="n">
-        <v>24.5864</v>
+        <v>23.5338</v>
       </c>
       <c r="D97" t="n">
-        <v>26.5954</v>
+        <v>26.4135</v>
       </c>
       <c r="E97" t="n">
-        <v>17.6089</v>
+        <v>17.5597</v>
       </c>
       <c r="F97" t="n">
-        <v>20.4504</v>
+        <v>20.466</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>23.2226</v>
+        <v>23.153</v>
       </c>
       <c r="C98" t="n">
-        <v>24.4764</v>
+        <v>23.5479</v>
       </c>
       <c r="D98" t="n">
-        <v>27.2079</v>
+        <v>27.0562</v>
       </c>
       <c r="E98" t="n">
-        <v>17.7412</v>
+        <v>17.7589</v>
       </c>
       <c r="F98" t="n">
-        <v>20.5175</v>
+        <v>20.592</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>23.2273</v>
+        <v>23.1036</v>
       </c>
       <c r="C99" t="n">
-        <v>24.593</v>
+        <v>23.6972</v>
       </c>
       <c r="D99" t="n">
-        <v>27.8913</v>
+        <v>27.6846</v>
       </c>
       <c r="E99" t="n">
-        <v>17.9301</v>
+        <v>17.8226</v>
       </c>
       <c r="F99" t="n">
-        <v>20.6033</v>
+        <v>20.623</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>23.1846</v>
+        <v>23.1622</v>
       </c>
       <c r="C100" t="n">
-        <v>24.7354</v>
+        <v>23.6962</v>
       </c>
       <c r="D100" t="n">
-        <v>28.5001</v>
+        <v>28.2683</v>
       </c>
       <c r="E100" t="n">
-        <v>18.0442</v>
+        <v>18.0105</v>
       </c>
       <c r="F100" t="n">
-        <v>20.7292</v>
+        <v>20.7411</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>23.2525</v>
+        <v>23.1484</v>
       </c>
       <c r="C101" t="n">
-        <v>24.7682</v>
+        <v>23.7398</v>
       </c>
       <c r="D101" t="n">
-        <v>29.1318</v>
+        <v>28.8807</v>
       </c>
       <c r="E101" t="n">
-        <v>18.24</v>
+        <v>18.2367</v>
       </c>
       <c r="F101" t="n">
-        <v>20.7426</v>
+        <v>20.8854</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>23.2495</v>
+        <v>23.1655</v>
       </c>
       <c r="C102" t="n">
-        <v>24.7937</v>
+        <v>23.7619</v>
       </c>
       <c r="D102" t="n">
-        <v>29.8719</v>
+        <v>29.6312</v>
       </c>
       <c r="E102" t="n">
-        <v>18.4606</v>
+        <v>18.3893</v>
       </c>
       <c r="F102" t="n">
-        <v>20.9396</v>
+        <v>21.0187</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>23.2335</v>
+        <v>23.2117</v>
       </c>
       <c r="C103" t="n">
-        <v>24.758</v>
+        <v>23.7739</v>
       </c>
       <c r="D103" t="n">
-        <v>30.5293</v>
+        <v>30.3847</v>
       </c>
       <c r="E103" t="n">
-        <v>18.6366</v>
+        <v>18.5829</v>
       </c>
       <c r="F103" t="n">
-        <v>21.1536</v>
+        <v>21.1441</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>23.2324</v>
+        <v>23.1648</v>
       </c>
       <c r="C104" t="n">
-        <v>24.9776</v>
+        <v>23.9247</v>
       </c>
       <c r="D104" t="n">
-        <v>31.4238</v>
+        <v>31.1696</v>
       </c>
       <c r="E104" t="n">
-        <v>18.8394</v>
+        <v>18.7218</v>
       </c>
       <c r="F104" t="n">
-        <v>21.3072</v>
+        <v>21.265</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>23.2517</v>
+        <v>23.1857</v>
       </c>
       <c r="C105" t="n">
-        <v>25.0788</v>
+        <v>24.0129</v>
       </c>
       <c r="D105" t="n">
-        <v>32.2123</v>
+        <v>31.8597</v>
       </c>
       <c r="E105" t="n">
-        <v>18.9631</v>
+        <v>18.9289</v>
       </c>
       <c r="F105" t="n">
-        <v>21.4563</v>
+        <v>21.5115</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>23.3791</v>
+        <v>23.2845</v>
       </c>
       <c r="C106" t="n">
-        <v>25.3001</v>
+        <v>24.1241</v>
       </c>
       <c r="D106" t="n">
-        <v>32.9819</v>
+        <v>32.6927</v>
       </c>
       <c r="E106" t="n">
-        <v>19.2529</v>
+        <v>19.2126</v>
       </c>
       <c r="F106" t="n">
-        <v>21.7224</v>
+        <v>21.8344</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>23.426</v>
+        <v>23.3132</v>
       </c>
       <c r="C107" t="n">
-        <v>25.555</v>
+        <v>24.3163</v>
       </c>
       <c r="D107" t="n">
-        <v>28.7564</v>
+        <v>28.5719</v>
       </c>
       <c r="E107" t="n">
-        <v>19.5906</v>
+        <v>19.5357</v>
       </c>
       <c r="F107" t="n">
-        <v>22.2556</v>
+        <v>22.2216</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.6443</v>
+        <v>23.4832</v>
       </c>
       <c r="C108" t="n">
-        <v>25.9414</v>
+        <v>27.7499</v>
       </c>
       <c r="D108" t="n">
-        <v>29.3593</v>
+        <v>29.1361</v>
       </c>
       <c r="E108" t="n">
-        <v>22.97</v>
+        <v>22.7861</v>
       </c>
       <c r="F108" t="n">
-        <v>25.4924</v>
+        <v>25.4917</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.5457</v>
+        <v>23.8626</v>
       </c>
       <c r="C109" t="n">
-        <v>26.6742</v>
+        <v>27.8001</v>
       </c>
       <c r="D109" t="n">
-        <v>29.7866</v>
+        <v>29.5017</v>
       </c>
       <c r="E109" t="n">
-        <v>23.0626</v>
+        <v>22.9001</v>
       </c>
       <c r="F109" t="n">
-        <v>25.645</v>
+        <v>25.6895</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>26.3946</v>
+        <v>26.213</v>
       </c>
       <c r="C110" t="n">
-        <v>30.4226</v>
+        <v>27.7884</v>
       </c>
       <c r="D110" t="n">
-        <v>30.2497</v>
+        <v>30.003</v>
       </c>
       <c r="E110" t="n">
-        <v>23.2175</v>
+        <v>23.1894</v>
       </c>
       <c r="F110" t="n">
-        <v>25.8241</v>
+        <v>25.8137</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>26.3595</v>
+        <v>26.1285</v>
       </c>
       <c r="C111" t="n">
-        <v>30.5155</v>
+        <v>27.8311</v>
       </c>
       <c r="D111" t="n">
-        <v>30.8281</v>
+        <v>30.6664</v>
       </c>
       <c r="E111" t="n">
-        <v>23.3864</v>
+        <v>23.3258</v>
       </c>
       <c r="F111" t="n">
-        <v>25.9106</v>
+        <v>25.874</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>26.3329</v>
+        <v>26.1715</v>
       </c>
       <c r="C112" t="n">
-        <v>30.6025</v>
+        <v>27.9159</v>
       </c>
       <c r="D112" t="n">
-        <v>31.4159</v>
+        <v>31.1965</v>
       </c>
       <c r="E112" t="n">
-        <v>23.5788</v>
+        <v>23.4852</v>
       </c>
       <c r="F112" t="n">
-        <v>26.1686</v>
+        <v>26.0591</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>26.3076</v>
+        <v>26.1653</v>
       </c>
       <c r="C113" t="n">
-        <v>30.574</v>
+        <v>27.9669</v>
       </c>
       <c r="D113" t="n">
-        <v>32.1624</v>
+        <v>31.7958</v>
       </c>
       <c r="E113" t="n">
-        <v>23.7493</v>
+        <v>23.6808</v>
       </c>
       <c r="F113" t="n">
-        <v>26.2198</v>
+        <v>26.2436</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>26.3912</v>
+        <v>26.2303</v>
       </c>
       <c r="C114" t="n">
-        <v>30.6549</v>
+        <v>28.0562</v>
       </c>
       <c r="D114" t="n">
-        <v>32.8138</v>
+        <v>32.4823</v>
       </c>
       <c r="E114" t="n">
-        <v>23.8353</v>
+        <v>23.7573</v>
       </c>
       <c r="F114" t="n">
-        <v>26.4941</v>
+        <v>26.3527</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>26.3899</v>
+        <v>26.2841</v>
       </c>
       <c r="C115" t="n">
-        <v>30.6364</v>
+        <v>28.0951</v>
       </c>
       <c r="D115" t="n">
-        <v>33.3464</v>
+        <v>33.1352</v>
       </c>
       <c r="E115" t="n">
-        <v>24.1096</v>
+        <v>23.938</v>
       </c>
       <c r="F115" t="n">
-        <v>26.5625</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>26.3129</v>
+        <v>26.2829</v>
       </c>
       <c r="C116" t="n">
-        <v>30.7741</v>
+        <v>28.1802</v>
       </c>
       <c r="D116" t="n">
-        <v>34.1433</v>
+        <v>33.8393</v>
       </c>
       <c r="E116" t="n">
-        <v>24.3161</v>
+        <v>24.1806</v>
       </c>
       <c r="F116" t="n">
-        <v>26.8483</v>
+        <v>26.7809</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>26.3772</v>
+        <v>26.2534</v>
       </c>
       <c r="C117" t="n">
-        <v>30.9333</v>
+        <v>28.3088</v>
       </c>
       <c r="D117" t="n">
-        <v>34.9322</v>
+        <v>34.6455</v>
       </c>
       <c r="E117" t="n">
-        <v>24.4689</v>
+        <v>24.332</v>
       </c>
       <c r="F117" t="n">
-        <v>27.1309</v>
+        <v>27.0454</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>26.3178</v>
+        <v>26.2516</v>
       </c>
       <c r="C118" t="n">
-        <v>30.9669</v>
+        <v>28.3606</v>
       </c>
       <c r="D118" t="n">
-        <v>35.7991</v>
+        <v>35.4433</v>
       </c>
       <c r="E118" t="n">
-        <v>24.6707</v>
+        <v>24.6221</v>
       </c>
       <c r="F118" t="n">
-        <v>27.405</v>
+        <v>27.2721</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>26.4693</v>
+        <v>26.3478</v>
       </c>
       <c r="C119" t="n">
-        <v>31.0908</v>
+        <v>28.5982</v>
       </c>
       <c r="D119" t="n">
-        <v>36.4421</v>
+        <v>36.2089</v>
       </c>
       <c r="E119" t="n">
-        <v>24.9715</v>
+        <v>24.8065</v>
       </c>
       <c r="F119" t="n">
-        <v>27.6808</v>
+        <v>27.7629</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>26.5515</v>
+        <v>26.4881</v>
       </c>
       <c r="C120" t="n">
-        <v>31.3961</v>
+        <v>28.7943</v>
       </c>
       <c r="D120" t="n">
-        <v>37.4546</v>
+        <v>37.0797</v>
       </c>
       <c r="E120" t="n">
-        <v>25.2599</v>
+        <v>25.2262</v>
       </c>
       <c r="F120" t="n">
-        <v>28.1029</v>
+        <v>28.1352</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>26.7045</v>
+        <v>26.5744</v>
       </c>
       <c r="C121" t="n">
-        <v>31.6169</v>
+        <v>29.0409</v>
       </c>
       <c r="D121" t="n">
-        <v>31.5395</v>
+        <v>31.2631</v>
       </c>
       <c r="E121" t="n">
-        <v>25.7006</v>
+        <v>25.4424</v>
       </c>
       <c r="F121" t="n">
-        <v>28.8409</v>
+        <v>28.8026</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.8953</v>
+        <v>26.8164</v>
       </c>
       <c r="C122" t="n">
-        <v>32.1947</v>
+        <v>30.9523</v>
       </c>
       <c r="D122" t="n">
-        <v>31.8508</v>
+        <v>31.7729</v>
       </c>
       <c r="E122" t="n">
-        <v>26.1184</v>
+        <v>26.0473</v>
       </c>
       <c r="F122" t="n">
-        <v>29.6986</v>
+        <v>29.5732</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>27.2005</v>
+        <v>27.0581</v>
       </c>
       <c r="C123" t="n">
-        <v>32.7741</v>
+        <v>31.1114</v>
       </c>
       <c r="D123" t="n">
-        <v>32.4598</v>
+        <v>32.0286</v>
       </c>
       <c r="E123" t="n">
-        <v>26.2577</v>
+        <v>26.0432</v>
       </c>
       <c r="F123" t="n">
-        <v>29.9653</v>
+        <v>29.9142</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>33.7939</v>
+        <v>33.5413</v>
       </c>
       <c r="C124" t="n">
-        <v>38.5798</v>
+        <v>30.9942</v>
       </c>
       <c r="D124" t="n">
-        <v>32.9482</v>
+        <v>32.7033</v>
       </c>
       <c r="E124" t="n">
-        <v>26.3371</v>
+        <v>26.216</v>
       </c>
       <c r="F124" t="n">
-        <v>30.1819</v>
+        <v>29.9138</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>33.5842</v>
+        <v>33.5702</v>
       </c>
       <c r="C125" t="n">
-        <v>38.6873</v>
+        <v>31.039</v>
       </c>
       <c r="D125" t="n">
-        <v>33.5269</v>
+        <v>33.1977</v>
       </c>
       <c r="E125" t="n">
-        <v>26.6401</v>
+        <v>26.3776</v>
       </c>
       <c r="F125" t="n">
-        <v>30.2946</v>
+        <v>30.0975</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>33.7552</v>
+        <v>33.5763</v>
       </c>
       <c r="C126" t="n">
-        <v>38.726</v>
+        <v>31.1924</v>
       </c>
       <c r="D126" t="n">
-        <v>34.0286</v>
+        <v>33.7775</v>
       </c>
       <c r="E126" t="n">
-        <v>26.582</v>
+        <v>26.5051</v>
       </c>
       <c r="F126" t="n">
-        <v>30.4571</v>
+        <v>30.2399</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>33.7242</v>
+        <v>33.492</v>
       </c>
       <c r="C127" t="n">
-        <v>38.918</v>
+        <v>31.3042</v>
       </c>
       <c r="D127" t="n">
-        <v>34.6143</v>
+        <v>34.4478</v>
       </c>
       <c r="E127" t="n">
-        <v>26.8563</v>
+        <v>26.6462</v>
       </c>
       <c r="F127" t="n">
-        <v>30.6619</v>
+        <v>30.5266</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.7475</v>
+        <v>33.5729</v>
       </c>
       <c r="C128" t="n">
-        <v>38.8845</v>
+        <v>31.3774</v>
       </c>
       <c r="D128" t="n">
-        <v>35.3303</v>
+        <v>35.076</v>
       </c>
       <c r="E128" t="n">
-        <v>27.1409</v>
+        <v>26.9278</v>
       </c>
       <c r="F128" t="n">
-        <v>30.8435</v>
+        <v>30.7473</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.7541</v>
+        <v>33.7585</v>
       </c>
       <c r="C129" t="n">
-        <v>38.9353</v>
+        <v>31.4981</v>
       </c>
       <c r="D129" t="n">
-        <v>36.0526</v>
+        <v>35.787</v>
       </c>
       <c r="E129" t="n">
-        <v>27.3137</v>
+        <v>27.0532</v>
       </c>
       <c r="F129" t="n">
-        <v>31.1023</v>
+        <v>30.9473</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.7642</v>
+        <v>33.6885</v>
       </c>
       <c r="C130" t="n">
-        <v>38.9172</v>
+        <v>31.6431</v>
       </c>
       <c r="D130" t="n">
-        <v>36.8609</v>
+        <v>36.5337</v>
       </c>
       <c r="E130" t="n">
-        <v>27.389</v>
+        <v>27.3007</v>
       </c>
       <c r="F130" t="n">
-        <v>31.3707</v>
+        <v>31.2765</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>33.775</v>
+        <v>33.6729</v>
       </c>
       <c r="C131" t="n">
-        <v>39.0183</v>
+        <v>31.8904</v>
       </c>
       <c r="D131" t="n">
-        <v>37.6747</v>
+        <v>37.2057</v>
       </c>
       <c r="E131" t="n">
-        <v>27.6648</v>
+        <v>27.508</v>
       </c>
       <c r="F131" t="n">
-        <v>31.6949</v>
+        <v>31.5935</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>33.846</v>
+        <v>33.5964</v>
       </c>
       <c r="C132" t="n">
-        <v>39.2259</v>
+        <v>32.0885</v>
       </c>
       <c r="D132" t="n">
-        <v>38.4184</v>
+        <v>38.0383</v>
       </c>
       <c r="E132" t="n">
-        <v>27.9166</v>
+        <v>27.894</v>
       </c>
       <c r="F132" t="n">
-        <v>31.9246</v>
+        <v>31.8439</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>33.822</v>
+        <v>33.6898</v>
       </c>
       <c r="C133" t="n">
-        <v>39.4946</v>
+        <v>32.3402</v>
       </c>
       <c r="D133" t="n">
-        <v>39.1283</v>
+        <v>38.7479</v>
       </c>
       <c r="E133" t="n">
-        <v>28.2112</v>
+        <v>28.2015</v>
       </c>
       <c r="F133" t="n">
-        <v>32.3916</v>
+        <v>32.3464</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>33.9028</v>
+        <v>33.7995</v>
       </c>
       <c r="C134" t="n">
-        <v>39.783</v>
+        <v>32.6432</v>
       </c>
       <c r="D134" t="n">
-        <v>39.911</v>
+        <v>39.5463</v>
       </c>
       <c r="E134" t="n">
-        <v>28.6995</v>
+        <v>28.6102</v>
       </c>
       <c r="F134" t="n">
-        <v>32.9488</v>
+        <v>32.824</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.8259</v>
+        <v>33.8399</v>
       </c>
       <c r="C135" t="n">
-        <v>40.0797</v>
+        <v>33.092</v>
       </c>
       <c r="D135" t="n">
-        <v>33.1807</v>
+        <v>32.9288</v>
       </c>
       <c r="E135" t="n">
-        <v>29.2153</v>
+        <v>29.0626</v>
       </c>
       <c r="F135" t="n">
-        <v>33.7906</v>
+        <v>33.6094</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.9305</v>
+        <v>33.8255</v>
       </c>
       <c r="C136" t="n">
-        <v>40.4353</v>
+        <v>34.1308</v>
       </c>
       <c r="D136" t="n">
-        <v>33.6874</v>
+        <v>33.2902</v>
       </c>
       <c r="E136" t="n">
-        <v>29.7835</v>
+        <v>29.7458</v>
       </c>
       <c r="F136" t="n">
-        <v>34.6775</v>
+        <v>34.6064</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>34.3095</v>
+        <v>34.0879</v>
       </c>
       <c r="C137" t="n">
-        <v>41.1345</v>
+        <v>34.0949</v>
       </c>
       <c r="D137" t="n">
-        <v>34.2605</v>
+        <v>33.9023</v>
       </c>
       <c r="E137" t="n">
-        <v>28.4714</v>
+        <v>28.1855</v>
       </c>
       <c r="F137" t="n">
-        <v>32.6125</v>
+        <v>32.5275</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>40.8295</v>
+        <v>40.6278</v>
       </c>
       <c r="C138" t="n">
-        <v>44.8217</v>
+        <v>34.2924</v>
       </c>
       <c r="D138" t="n">
-        <v>34.6645</v>
+        <v>34.264</v>
       </c>
       <c r="E138" t="n">
-        <v>28.4962</v>
+        <v>28.3137</v>
       </c>
       <c r="F138" t="n">
-        <v>32.872</v>
+        <v>32.718</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>40.6773</v>
+        <v>40.605</v>
       </c>
       <c r="C139" t="n">
-        <v>44.8303</v>
+        <v>34.3002</v>
       </c>
       <c r="D139" t="n">
-        <v>35.1433</v>
+        <v>34.7941</v>
       </c>
       <c r="E139" t="n">
-        <v>28.9743</v>
+        <v>28.5331</v>
       </c>
       <c r="F139" t="n">
-        <v>32.9459</v>
+        <v>32.8561</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>40.7602</v>
+        <v>40.6235</v>
       </c>
       <c r="C140" t="n">
-        <v>45.0274</v>
+        <v>34.3497</v>
       </c>
       <c r="D140" t="n">
-        <v>35.8032</v>
+        <v>35.4413</v>
       </c>
       <c r="E140" t="n">
-        <v>28.9306</v>
+        <v>28.5681</v>
       </c>
       <c r="F140" t="n">
-        <v>33.1562</v>
+        <v>33.0925</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>40.6423</v>
+        <v>40.693</v>
       </c>
       <c r="C141" t="n">
-        <v>45.0624</v>
+        <v>34.5774</v>
       </c>
       <c r="D141" t="n">
-        <v>36.3214</v>
+        <v>36.0948</v>
       </c>
       <c r="E141" t="n">
-        <v>28.9638</v>
+        <v>28.8415</v>
       </c>
       <c r="F141" t="n">
-        <v>33.31</v>
+        <v>33.2425</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>40.6184</v>
+        <v>40.5665</v>
       </c>
       <c r="C142" t="n">
-        <v>45.0484</v>
+        <v>34.6459</v>
       </c>
       <c r="D142" t="n">
-        <v>37.0907</v>
+        <v>36.6584</v>
       </c>
       <c r="E142" t="n">
-        <v>29.0046</v>
+        <v>29.292</v>
       </c>
       <c r="F142" t="n">
-        <v>33.5654</v>
+        <v>33.3599</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>40.9049</v>
+        <v>40.6431</v>
       </c>
       <c r="C143" t="n">
-        <v>45.1248</v>
+        <v>34.817</v>
       </c>
       <c r="D143" t="n">
-        <v>37.5872</v>
+        <v>37.4191</v>
       </c>
       <c r="E143" t="n">
-        <v>29.4222</v>
+        <v>29.1128</v>
       </c>
       <c r="F143" t="n">
-        <v>33.7944</v>
+        <v>33.6595</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.77317</v>
+        <v>2.77589</v>
       </c>
       <c r="C2" t="n">
-        <v>4.46411</v>
+        <v>4.48075</v>
       </c>
       <c r="D2" t="n">
-        <v>5.43261</v>
+        <v>5.47094</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2428</v>
+        <v>3.23776</v>
       </c>
       <c r="F2" t="n">
-        <v>3.49734</v>
+        <v>3.50726</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.78564</v>
+        <v>2.7972</v>
       </c>
       <c r="C3" t="n">
-        <v>4.48369</v>
+        <v>4.51132</v>
       </c>
       <c r="D3" t="n">
-        <v>5.81488</v>
+        <v>5.7812</v>
       </c>
       <c r="E3" t="n">
-        <v>3.25656</v>
+        <v>3.26027</v>
       </c>
       <c r="F3" t="n">
-        <v>3.54381</v>
+        <v>3.5286</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.80361</v>
+        <v>2.8109</v>
       </c>
       <c r="C4" t="n">
-        <v>4.50774</v>
+        <v>4.54144</v>
       </c>
       <c r="D4" t="n">
-        <v>6.16753</v>
+        <v>6.12099</v>
       </c>
       <c r="E4" t="n">
-        <v>3.27189</v>
+        <v>3.27788</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5596</v>
+        <v>3.56149</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.8332</v>
+        <v>2.85629</v>
       </c>
       <c r="C5" t="n">
-        <v>4.58133</v>
+        <v>4.58371</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49229</v>
+        <v>6.48273</v>
       </c>
       <c r="E5" t="n">
-        <v>3.34125</v>
+        <v>3.30669</v>
       </c>
       <c r="F5" t="n">
-        <v>3.62001</v>
+        <v>3.5802</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.88448</v>
+        <v>2.87233</v>
       </c>
       <c r="C6" t="n">
-        <v>4.61373</v>
+        <v>4.59692</v>
       </c>
       <c r="D6" t="n">
-        <v>6.83479</v>
+        <v>6.84888</v>
       </c>
       <c r="E6" t="n">
-        <v>3.34473</v>
+        <v>3.36699</v>
       </c>
       <c r="F6" t="n">
-        <v>3.62104</v>
+        <v>3.63527</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.90804</v>
+        <v>2.90708</v>
       </c>
       <c r="C7" t="n">
-        <v>4.6911</v>
+        <v>4.66999</v>
       </c>
       <c r="D7" t="n">
-        <v>5.21186</v>
+        <v>5.18768</v>
       </c>
       <c r="E7" t="n">
-        <v>3.42537</v>
+        <v>3.241</v>
       </c>
       <c r="F7" t="n">
-        <v>3.74061</v>
+        <v>3.51483</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.96019</v>
+        <v>2.94118</v>
       </c>
       <c r="C8" t="n">
-        <v>4.57205</v>
+        <v>4.52288</v>
       </c>
       <c r="D8" t="n">
-        <v>5.36288</v>
+        <v>5.37082</v>
       </c>
       <c r="E8" t="n">
-        <v>3.46096</v>
+        <v>3.27455</v>
       </c>
       <c r="F8" t="n">
-        <v>3.89833</v>
+        <v>3.57776</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>2.99413</v>
+        <v>3.00404</v>
       </c>
       <c r="C9" t="n">
-        <v>4.54977</v>
+        <v>4.54311</v>
       </c>
       <c r="D9" t="n">
-        <v>5.56589</v>
+        <v>5.57848</v>
       </c>
       <c r="E9" t="n">
-        <v>3.29522</v>
+        <v>3.27849</v>
       </c>
       <c r="F9" t="n">
-        <v>3.56963</v>
+        <v>3.60697</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.42062</v>
+        <v>3.41135</v>
       </c>
       <c r="C10" t="n">
-        <v>4.55329</v>
+        <v>4.54636</v>
       </c>
       <c r="D10" t="n">
-        <v>5.80704</v>
+        <v>5.81696</v>
       </c>
       <c r="E10" t="n">
-        <v>3.31451</v>
+        <v>3.33579</v>
       </c>
       <c r="F10" t="n">
-        <v>3.61352</v>
+        <v>3.64895</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.42352</v>
+        <v>3.43083</v>
       </c>
       <c r="C11" t="n">
-        <v>4.57474</v>
+        <v>4.5759</v>
       </c>
       <c r="D11" t="n">
-        <v>6.06986</v>
+        <v>6.06059</v>
       </c>
       <c r="E11" t="n">
-        <v>3.36107</v>
+        <v>3.33417</v>
       </c>
       <c r="F11" t="n">
-        <v>3.64705</v>
+        <v>3.66349</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.43131</v>
+        <v>3.42897</v>
       </c>
       <c r="C12" t="n">
-        <v>4.55224</v>
+        <v>4.54903</v>
       </c>
       <c r="D12" t="n">
-        <v>6.33168</v>
+        <v>6.32358</v>
       </c>
       <c r="E12" t="n">
-        <v>3.37943</v>
+        <v>3.36209</v>
       </c>
       <c r="F12" t="n">
-        <v>3.66541</v>
+        <v>3.68206</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.44094</v>
+        <v>3.45159</v>
       </c>
       <c r="C13" t="n">
-        <v>4.61928</v>
+        <v>4.60031</v>
       </c>
       <c r="D13" t="n">
-        <v>6.57262</v>
+        <v>6.6056</v>
       </c>
       <c r="E13" t="n">
-        <v>3.39078</v>
+        <v>3.38877</v>
       </c>
       <c r="F13" t="n">
-        <v>3.68418</v>
+        <v>3.71322</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.46657</v>
+        <v>3.4681</v>
       </c>
       <c r="C14" t="n">
-        <v>4.56986</v>
+        <v>4.59074</v>
       </c>
       <c r="D14" t="n">
-        <v>6.91251</v>
+        <v>6.91609</v>
       </c>
       <c r="E14" t="n">
-        <v>3.41561</v>
+        <v>3.43473</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7336</v>
+        <v>3.73065</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.4793</v>
+        <v>3.46633</v>
       </c>
       <c r="C15" t="n">
-        <v>4.63583</v>
+        <v>4.62159</v>
       </c>
       <c r="D15" t="n">
-        <v>7.17692</v>
+        <v>7.17458</v>
       </c>
       <c r="E15" t="n">
-        <v>3.46442</v>
+        <v>3.46049</v>
       </c>
       <c r="F15" t="n">
-        <v>3.75442</v>
+        <v>3.76066</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.476</v>
+        <v>3.4841</v>
       </c>
       <c r="C16" t="n">
-        <v>4.64015</v>
+        <v>4.63067</v>
       </c>
       <c r="D16" t="n">
-        <v>7.38737</v>
+        <v>7.39548</v>
       </c>
       <c r="E16" t="n">
-        <v>3.46852</v>
+        <v>3.48386</v>
       </c>
       <c r="F16" t="n">
-        <v>3.76796</v>
+        <v>3.77754</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.49067</v>
+        <v>3.503</v>
       </c>
       <c r="C17" t="n">
-        <v>4.66799</v>
+        <v>4.66484</v>
       </c>
       <c r="D17" t="n">
-        <v>7.70302</v>
+        <v>7.69862</v>
       </c>
       <c r="E17" t="n">
-        <v>3.49924</v>
+        <v>3.51592</v>
       </c>
       <c r="F17" t="n">
-        <v>3.80257</v>
+        <v>3.82152</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.53818</v>
+        <v>3.53775</v>
       </c>
       <c r="C18" t="n">
-        <v>4.72742</v>
+        <v>4.73612</v>
       </c>
       <c r="D18" t="n">
-        <v>7.97476</v>
+        <v>7.9854</v>
       </c>
       <c r="E18" t="n">
-        <v>3.53628</v>
+        <v>3.53957</v>
       </c>
       <c r="F18" t="n">
-        <v>3.85254</v>
+        <v>3.851</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.55532</v>
+        <v>3.56509</v>
       </c>
       <c r="C19" t="n">
-        <v>4.77164</v>
+        <v>4.78914</v>
       </c>
       <c r="D19" t="n">
-        <v>8.220319999999999</v>
+        <v>8.259</v>
       </c>
       <c r="E19" t="n">
-        <v>3.58521</v>
+        <v>3.58186</v>
       </c>
       <c r="F19" t="n">
-        <v>3.89429</v>
+        <v>3.90976</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.58301</v>
+        <v>3.59133</v>
       </c>
       <c r="C20" t="n">
-        <v>4.8328</v>
+        <v>4.82232</v>
       </c>
       <c r="D20" t="n">
-        <v>8.488530000000001</v>
+        <v>8.50765</v>
       </c>
       <c r="E20" t="n">
-        <v>3.66769</v>
+        <v>3.61511</v>
       </c>
       <c r="F20" t="n">
-        <v>3.98797</v>
+        <v>3.98871</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.60326</v>
+        <v>3.63306</v>
       </c>
       <c r="C21" t="n">
-        <v>4.92003</v>
+        <v>4.93658</v>
       </c>
       <c r="D21" t="n">
-        <v>6.32396</v>
+        <v>6.33297</v>
       </c>
       <c r="E21" t="n">
-        <v>3.78528</v>
+        <v>3.5657</v>
       </c>
       <c r="F21" t="n">
-        <v>4.12308</v>
+        <v>3.92195</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.67645</v>
+        <v>3.66911</v>
       </c>
       <c r="C22" t="n">
-        <v>4.73121</v>
+        <v>4.82836</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53127</v>
+        <v>6.53473</v>
       </c>
       <c r="E22" t="n">
-        <v>4.07486</v>
+        <v>3.54432</v>
       </c>
       <c r="F22" t="n">
-        <v>4.40767</v>
+        <v>3.95742</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.76615</v>
+        <v>3.75138</v>
       </c>
       <c r="C23" t="n">
-        <v>4.81232</v>
+        <v>4.81087</v>
       </c>
       <c r="D23" t="n">
-        <v>6.76091</v>
+        <v>6.74393</v>
       </c>
       <c r="E23" t="n">
-        <v>3.57691</v>
+        <v>3.60285</v>
       </c>
       <c r="F23" t="n">
-        <v>3.97671</v>
+        <v>3.96458</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.93579</v>
+        <v>3.93962</v>
       </c>
       <c r="C24" t="n">
-        <v>4.78801</v>
+        <v>4.82332</v>
       </c>
       <c r="D24" t="n">
-        <v>6.99868</v>
+        <v>7.00246</v>
       </c>
       <c r="E24" t="n">
-        <v>3.59763</v>
+        <v>3.59091</v>
       </c>
       <c r="F24" t="n">
-        <v>4.01273</v>
+        <v>4.01802</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.94544</v>
+        <v>3.9359</v>
       </c>
       <c r="C25" t="n">
-        <v>4.81231</v>
+        <v>4.86842</v>
       </c>
       <c r="D25" t="n">
-        <v>7.26491</v>
+        <v>7.2608</v>
       </c>
       <c r="E25" t="n">
-        <v>3.66269</v>
+        <v>3.60417</v>
       </c>
       <c r="F25" t="n">
-        <v>4.03586</v>
+        <v>4.02889</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.92856</v>
+        <v>3.93931</v>
       </c>
       <c r="C26" t="n">
-        <v>4.79388</v>
+        <v>4.8446</v>
       </c>
       <c r="D26" t="n">
-        <v>7.4973</v>
+        <v>7.50263</v>
       </c>
       <c r="E26" t="n">
-        <v>3.66169</v>
+        <v>3.6775</v>
       </c>
       <c r="F26" t="n">
-        <v>4.06888</v>
+        <v>4.06373</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.95237</v>
+        <v>3.95598</v>
       </c>
       <c r="C27" t="n">
-        <v>4.78961</v>
+        <v>4.81444</v>
       </c>
       <c r="D27" t="n">
-        <v>7.74064</v>
+        <v>7.77533</v>
       </c>
       <c r="E27" t="n">
-        <v>3.69924</v>
+        <v>3.66844</v>
       </c>
       <c r="F27" t="n">
-        <v>4.09649</v>
+        <v>4.10234</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.93362</v>
+        <v>3.95538</v>
       </c>
       <c r="C28" t="n">
-        <v>4.84054</v>
+        <v>4.85614</v>
       </c>
       <c r="D28" t="n">
-        <v>8.014570000000001</v>
+        <v>8.02783</v>
       </c>
       <c r="E28" t="n">
-        <v>3.72557</v>
+        <v>3.77273</v>
       </c>
       <c r="F28" t="n">
-        <v>4.1061</v>
+        <v>4.12055</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.96482</v>
+        <v>3.95805</v>
       </c>
       <c r="C29" t="n">
-        <v>4.82873</v>
+        <v>4.89304</v>
       </c>
       <c r="D29" t="n">
-        <v>8.302070000000001</v>
+        <v>8.298069999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>3.74471</v>
+        <v>3.73053</v>
       </c>
       <c r="F29" t="n">
-        <v>4.16269</v>
+        <v>4.16132</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.95396</v>
+        <v>3.97377</v>
       </c>
       <c r="C30" t="n">
-        <v>4.89605</v>
+        <v>4.91091</v>
       </c>
       <c r="D30" t="n">
-        <v>8.558310000000001</v>
+        <v>8.54326</v>
       </c>
       <c r="E30" t="n">
-        <v>3.83772</v>
+        <v>3.84547</v>
       </c>
       <c r="F30" t="n">
-        <v>4.20011</v>
+        <v>4.2067</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.98808</v>
+        <v>3.99655</v>
       </c>
       <c r="C31" t="n">
-        <v>4.93966</v>
+        <v>4.93758</v>
       </c>
       <c r="D31" t="n">
-        <v>8.8064</v>
+        <v>8.77214</v>
       </c>
       <c r="E31" t="n">
-        <v>3.85219</v>
+        <v>3.82652</v>
       </c>
       <c r="F31" t="n">
-        <v>4.23347</v>
+        <v>4.24891</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.01535</v>
+        <v>4.01201</v>
       </c>
       <c r="C32" t="n">
-        <v>5.00366</v>
+        <v>4.96634</v>
       </c>
       <c r="D32" t="n">
-        <v>9.01778</v>
+        <v>8.99377</v>
       </c>
       <c r="E32" t="n">
-        <v>3.88423</v>
+        <v>3.88212</v>
       </c>
       <c r="F32" t="n">
-        <v>4.26776</v>
+        <v>4.26451</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.04519</v>
+        <v>4.04412</v>
       </c>
       <c r="C33" t="n">
-        <v>5.03926</v>
+        <v>4.99318</v>
       </c>
       <c r="D33" t="n">
-        <v>9.263019999999999</v>
+        <v>9.263540000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>3.93927</v>
+        <v>3.91272</v>
       </c>
       <c r="F33" t="n">
-        <v>4.33705</v>
+        <v>4.36136</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.08725</v>
+        <v>4.05782</v>
       </c>
       <c r="C34" t="n">
-        <v>5.08795</v>
+        <v>5.09661</v>
       </c>
       <c r="D34" t="n">
-        <v>9.472479999999999</v>
+        <v>9.46231</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11397</v>
+        <v>4.0845</v>
       </c>
       <c r="F34" t="n">
-        <v>4.46981</v>
+        <v>4.46218</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.13164</v>
+        <v>4.11139</v>
       </c>
       <c r="C35" t="n">
-        <v>5.14056</v>
+        <v>5.15694</v>
       </c>
       <c r="D35" t="n">
-        <v>6.84225</v>
+        <v>6.85026</v>
       </c>
       <c r="E35" t="n">
-        <v>4.26099</v>
+        <v>3.81722</v>
       </c>
       <c r="F35" t="n">
-        <v>4.67349</v>
+        <v>4.24127</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.23128</v>
+        <v>4.19962</v>
       </c>
       <c r="C36" t="n">
-        <v>5.276</v>
+        <v>5.26003</v>
       </c>
       <c r="D36" t="n">
-        <v>7.03419</v>
+        <v>7.02676</v>
       </c>
       <c r="E36" t="n">
-        <v>4.65805</v>
+        <v>3.84068</v>
       </c>
       <c r="F36" t="n">
-        <v>5.0754</v>
+        <v>4.27271</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.43898</v>
+        <v>4.42779</v>
       </c>
       <c r="C37" t="n">
-        <v>5.01629</v>
+        <v>5.0459</v>
       </c>
       <c r="D37" t="n">
-        <v>7.19999</v>
+        <v>7.20789</v>
       </c>
       <c r="E37" t="n">
-        <v>3.87754</v>
+        <v>3.91617</v>
       </c>
       <c r="F37" t="n">
-        <v>4.31404</v>
+        <v>4.34121</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.21256</v>
+        <v>4.24333</v>
       </c>
       <c r="C38" t="n">
-        <v>5.01178</v>
+        <v>5.0503</v>
       </c>
       <c r="D38" t="n">
-        <v>7.43447</v>
+        <v>7.44156</v>
       </c>
       <c r="E38" t="n">
-        <v>3.89444</v>
+        <v>3.93604</v>
       </c>
       <c r="F38" t="n">
-        <v>4.31705</v>
+        <v>4.29553</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.22872</v>
+        <v>4.27088</v>
       </c>
       <c r="C39" t="n">
-        <v>5.04069</v>
+        <v>5.07921</v>
       </c>
       <c r="D39" t="n">
-        <v>7.6447</v>
+        <v>7.66113</v>
       </c>
       <c r="E39" t="n">
-        <v>3.93097</v>
+        <v>3.92734</v>
       </c>
       <c r="F39" t="n">
-        <v>4.32464</v>
+        <v>4.36703</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.21571</v>
+        <v>4.22096</v>
       </c>
       <c r="C40" t="n">
-        <v>5.03608</v>
+        <v>5.11583</v>
       </c>
       <c r="D40" t="n">
-        <v>7.88315</v>
+        <v>7.9063</v>
       </c>
       <c r="E40" t="n">
-        <v>3.97459</v>
+        <v>3.98835</v>
       </c>
       <c r="F40" t="n">
-        <v>4.35384</v>
+        <v>4.38961</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.28589</v>
+        <v>4.28849</v>
       </c>
       <c r="C41" t="n">
-        <v>5.04954</v>
+        <v>5.17176</v>
       </c>
       <c r="D41" t="n">
-        <v>8.153090000000001</v>
+        <v>8.17089</v>
       </c>
       <c r="E41" t="n">
-        <v>4.00517</v>
+        <v>3.98799</v>
       </c>
       <c r="F41" t="n">
-        <v>4.39098</v>
+        <v>4.42071</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.25319</v>
+        <v>4.28971</v>
       </c>
       <c r="C42" t="n">
-        <v>5.094</v>
+        <v>5.16377</v>
       </c>
       <c r="D42" t="n">
-        <v>8.38808</v>
+        <v>8.40246</v>
       </c>
       <c r="E42" t="n">
-        <v>4.03559</v>
+        <v>4.04955</v>
       </c>
       <c r="F42" t="n">
-        <v>4.41144</v>
+        <v>4.43387</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.27162</v>
+        <v>4.24434</v>
       </c>
       <c r="C43" t="n">
-        <v>5.17536</v>
+        <v>5.19783</v>
       </c>
       <c r="D43" t="n">
-        <v>8.666980000000001</v>
+        <v>8.66503</v>
       </c>
       <c r="E43" t="n">
-        <v>4.0886</v>
+        <v>4.08176</v>
       </c>
       <c r="F43" t="n">
-        <v>4.4814</v>
+        <v>4.4718</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.30493</v>
+        <v>4.30684</v>
       </c>
       <c r="C44" t="n">
-        <v>5.21388</v>
+        <v>5.23538</v>
       </c>
       <c r="D44" t="n">
-        <v>8.927479999999999</v>
+        <v>8.94032</v>
       </c>
       <c r="E44" t="n">
-        <v>4.12794</v>
+        <v>4.10118</v>
       </c>
       <c r="F44" t="n">
-        <v>4.48502</v>
+        <v>4.50935</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.30891</v>
+        <v>4.29494</v>
       </c>
       <c r="C45" t="n">
-        <v>5.20223</v>
+        <v>5.241</v>
       </c>
       <c r="D45" t="n">
-        <v>9.167859999999999</v>
+        <v>9.155060000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>4.18101</v>
+        <v>4.18256</v>
       </c>
       <c r="F45" t="n">
-        <v>4.55057</v>
+        <v>4.58721</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.3063</v>
+        <v>4.33896</v>
       </c>
       <c r="C46" t="n">
-        <v>5.23542</v>
+        <v>5.33158</v>
       </c>
       <c r="D46" t="n">
-        <v>9.393750000000001</v>
+        <v>9.407830000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>4.22927</v>
+        <v>4.23189</v>
       </c>
       <c r="F46" t="n">
-        <v>4.58474</v>
+        <v>4.62043</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.31102</v>
+        <v>4.35197</v>
       </c>
       <c r="C47" t="n">
-        <v>5.26793</v>
+        <v>5.36155</v>
       </c>
       <c r="D47" t="n">
-        <v>9.63293</v>
+        <v>9.623659999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>4.33101</v>
+        <v>4.30822</v>
       </c>
       <c r="F47" t="n">
-        <v>4.68551</v>
+        <v>4.73699</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.39604</v>
+        <v>4.37095</v>
       </c>
       <c r="C48" t="n">
-        <v>5.44879</v>
+        <v>5.40954</v>
       </c>
       <c r="D48" t="n">
-        <v>9.866020000000001</v>
+        <v>9.88715</v>
       </c>
       <c r="E48" t="n">
-        <v>4.49364</v>
+        <v>4.49323</v>
       </c>
       <c r="F48" t="n">
-        <v>4.89678</v>
+        <v>4.87697</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.47423</v>
+        <v>4.44024</v>
       </c>
       <c r="C49" t="n">
-        <v>5.47269</v>
+        <v>5.49011</v>
       </c>
       <c r="D49" t="n">
-        <v>10.1115</v>
+        <v>10.1154</v>
       </c>
       <c r="E49" t="n">
-        <v>4.73351</v>
+        <v>4.73939</v>
       </c>
       <c r="F49" t="n">
-        <v>5.1026</v>
+        <v>5.12512</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.52413</v>
+        <v>4.57945</v>
       </c>
       <c r="C50" t="n">
-        <v>5.635</v>
+        <v>5.66852</v>
       </c>
       <c r="D50" t="n">
-        <v>7.12593</v>
+        <v>7.19196</v>
       </c>
       <c r="E50" t="n">
-        <v>5.07022</v>
+        <v>4.14482</v>
       </c>
       <c r="F50" t="n">
-        <v>5.5223</v>
+        <v>4.51844</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.74661</v>
+        <v>4.73176</v>
       </c>
       <c r="C51" t="n">
-        <v>5.5</v>
+        <v>5.42859</v>
       </c>
       <c r="D51" t="n">
-        <v>7.3525</v>
+        <v>7.32276</v>
       </c>
       <c r="E51" t="n">
-        <v>4.21661</v>
+        <v>4.18773</v>
       </c>
       <c r="F51" t="n">
-        <v>4.50271</v>
+        <v>4.5454</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.1375</v>
+        <v>5.13956</v>
       </c>
       <c r="C52" t="n">
-        <v>5.37744</v>
+        <v>5.43567</v>
       </c>
       <c r="D52" t="n">
-        <v>7.53598</v>
+        <v>7.54838</v>
       </c>
       <c r="E52" t="n">
-        <v>4.24318</v>
+        <v>4.19745</v>
       </c>
       <c r="F52" t="n">
-        <v>4.52318</v>
+        <v>4.58951</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.73604</v>
+        <v>4.74078</v>
       </c>
       <c r="C53" t="n">
-        <v>5.43808</v>
+        <v>5.47035</v>
       </c>
       <c r="D53" t="n">
-        <v>7.76013</v>
+        <v>7.76985</v>
       </c>
       <c r="E53" t="n">
-        <v>4.26599</v>
+        <v>4.23245</v>
       </c>
       <c r="F53" t="n">
-        <v>4.56057</v>
+        <v>4.60776</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.75898</v>
+        <v>4.76859</v>
       </c>
       <c r="C54" t="n">
-        <v>5.46552</v>
+        <v>5.48413</v>
       </c>
       <c r="D54" t="n">
-        <v>8.006119999999999</v>
+        <v>7.98786</v>
       </c>
       <c r="E54" t="n">
-        <v>4.30863</v>
+        <v>4.26458</v>
       </c>
       <c r="F54" t="n">
-        <v>4.57842</v>
+        <v>4.59202</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.79694</v>
+        <v>4.7733</v>
       </c>
       <c r="C55" t="n">
-        <v>5.47634</v>
+        <v>5.54742</v>
       </c>
       <c r="D55" t="n">
-        <v>8.245279999999999</v>
+        <v>8.267939999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>4.34616</v>
+        <v>4.30646</v>
       </c>
       <c r="F55" t="n">
-        <v>4.62735</v>
+        <v>4.66975</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.79083</v>
+        <v>4.78359</v>
       </c>
       <c r="C56" t="n">
-        <v>5.53167</v>
+        <v>5.54089</v>
       </c>
       <c r="D56" t="n">
-        <v>8.49508</v>
+        <v>8.49799</v>
       </c>
       <c r="E56" t="n">
-        <v>4.3787</v>
+        <v>4.32476</v>
       </c>
       <c r="F56" t="n">
-        <v>4.67304</v>
+        <v>4.69202</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.79609</v>
+        <v>4.7848</v>
       </c>
       <c r="C57" t="n">
-        <v>5.51851</v>
+        <v>5.54086</v>
       </c>
       <c r="D57" t="n">
-        <v>8.759650000000001</v>
+        <v>8.78593</v>
       </c>
       <c r="E57" t="n">
-        <v>4.42236</v>
+        <v>4.39093</v>
       </c>
       <c r="F57" t="n">
-        <v>4.70616</v>
+        <v>4.68818</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.79478</v>
+        <v>4.79209</v>
       </c>
       <c r="C58" t="n">
-        <v>5.54186</v>
+        <v>5.59152</v>
       </c>
       <c r="D58" t="n">
-        <v>9.02112</v>
+        <v>9.019019999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>4.45302</v>
+        <v>4.43148</v>
       </c>
       <c r="F58" t="n">
-        <v>4.77011</v>
+        <v>4.80735</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.81561</v>
+        <v>4.82043</v>
       </c>
       <c r="C59" t="n">
-        <v>5.5974</v>
+        <v>5.64187</v>
       </c>
       <c r="D59" t="n">
-        <v>9.25812</v>
+        <v>9.272819999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>4.52436</v>
+        <v>4.46256</v>
       </c>
       <c r="F59" t="n">
-        <v>4.81619</v>
+        <v>4.84356</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.82074</v>
+        <v>4.81542</v>
       </c>
       <c r="C60" t="n">
-        <v>5.63022</v>
+        <v>5.67719</v>
       </c>
       <c r="D60" t="n">
-        <v>9.492179999999999</v>
+        <v>9.5343</v>
       </c>
       <c r="E60" t="n">
-        <v>4.58403</v>
+        <v>4.55734</v>
       </c>
       <c r="F60" t="n">
-        <v>4.88718</v>
+        <v>4.93827</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.8647</v>
+        <v>4.85335</v>
       </c>
       <c r="C61" t="n">
-        <v>5.70015</v>
+        <v>5.74946</v>
       </c>
       <c r="D61" t="n">
-        <v>9.764099999999999</v>
+        <v>9.796720000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>4.70997</v>
+        <v>4.67515</v>
       </c>
       <c r="F61" t="n">
-        <v>5.04634</v>
+        <v>5.03483</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.88579</v>
+        <v>4.91712</v>
       </c>
       <c r="C62" t="n">
-        <v>5.78966</v>
+        <v>5.78834</v>
       </c>
       <c r="D62" t="n">
-        <v>10.0014</v>
+        <v>10.0125</v>
       </c>
       <c r="E62" t="n">
-        <v>4.87374</v>
+        <v>4.8403</v>
       </c>
       <c r="F62" t="n">
-        <v>5.19723</v>
+        <v>5.19848</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.95897</v>
+        <v>4.95963</v>
       </c>
       <c r="C63" t="n">
-        <v>5.89205</v>
+        <v>5.85508</v>
       </c>
       <c r="D63" t="n">
-        <v>10.2822</v>
+        <v>10.2609</v>
       </c>
       <c r="E63" t="n">
-        <v>5.10195</v>
+        <v>5.05928</v>
       </c>
       <c r="F63" t="n">
-        <v>5.42183</v>
+        <v>5.42781</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.05303</v>
+        <v>5.08537</v>
       </c>
       <c r="C64" t="n">
-        <v>6.0225</v>
+        <v>6.02207</v>
       </c>
       <c r="D64" t="n">
-        <v>7.33586</v>
+        <v>7.35416</v>
       </c>
       <c r="E64" t="n">
-        <v>5.34382</v>
+        <v>4.4312</v>
       </c>
       <c r="F64" t="n">
-        <v>5.69963</v>
+        <v>4.69922</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.24465</v>
+        <v>5.22456</v>
       </c>
       <c r="C65" t="n">
-        <v>5.72006</v>
+        <v>5.73697</v>
       </c>
       <c r="D65" t="n">
-        <v>7.56633</v>
+        <v>7.60885</v>
       </c>
       <c r="E65" t="n">
-        <v>5.78589</v>
+        <v>4.46561</v>
       </c>
       <c r="F65" t="n">
-        <v>6.19606</v>
+        <v>4.74425</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.55476</v>
+        <v>5.54518</v>
       </c>
       <c r="C66" t="n">
-        <v>5.77679</v>
+        <v>5.76633</v>
       </c>
       <c r="D66" t="n">
-        <v>7.82064</v>
+        <v>7.85583</v>
       </c>
       <c r="E66" t="n">
-        <v>4.48706</v>
+        <v>4.50616</v>
       </c>
       <c r="F66" t="n">
-        <v>4.83102</v>
+        <v>4.76359</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.44426</v>
+        <v>5.38765</v>
       </c>
       <c r="C67" t="n">
-        <v>5.76183</v>
+        <v>5.80019</v>
       </c>
       <c r="D67" t="n">
-        <v>8.07211</v>
+        <v>8.113099999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>4.51664</v>
+        <v>4.5318</v>
       </c>
       <c r="F67" t="n">
-        <v>4.85443</v>
+        <v>4.84402</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.46606</v>
+        <v>5.37472</v>
       </c>
       <c r="C68" t="n">
-        <v>5.80028</v>
+        <v>5.7986</v>
       </c>
       <c r="D68" t="n">
-        <v>8.36769</v>
+        <v>8.45997</v>
       </c>
       <c r="E68" t="n">
-        <v>4.53958</v>
+        <v>4.54646</v>
       </c>
       <c r="F68" t="n">
-        <v>4.87802</v>
+        <v>4.94887</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.41172</v>
+        <v>5.38851</v>
       </c>
       <c r="C69" t="n">
-        <v>5.79744</v>
+        <v>5.78182</v>
       </c>
       <c r="D69" t="n">
-        <v>8.670120000000001</v>
+        <v>8.74363</v>
       </c>
       <c r="E69" t="n">
-        <v>4.56664</v>
+        <v>4.59768</v>
       </c>
       <c r="F69" t="n">
-        <v>5.21001</v>
+        <v>4.91935</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.4416</v>
+        <v>5.39472</v>
       </c>
       <c r="C70" t="n">
-        <v>5.82549</v>
+        <v>5.82788</v>
       </c>
       <c r="D70" t="n">
-        <v>8.960509999999999</v>
+        <v>8.9876</v>
       </c>
       <c r="E70" t="n">
-        <v>4.62274</v>
+        <v>4.63741</v>
       </c>
       <c r="F70" t="n">
-        <v>5.46995</v>
+        <v>5.18275</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.45247</v>
+        <v>5.39216</v>
       </c>
       <c r="C71" t="n">
-        <v>5.86327</v>
+        <v>5.83242</v>
       </c>
       <c r="D71" t="n">
-        <v>9.39343</v>
+        <v>9.28181</v>
       </c>
       <c r="E71" t="n">
-        <v>4.64578</v>
+        <v>4.67546</v>
       </c>
       <c r="F71" t="n">
-        <v>5.47242</v>
+        <v>5.33788</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.47247</v>
+        <v>5.40275</v>
       </c>
       <c r="C72" t="n">
-        <v>5.87039</v>
+        <v>5.87332</v>
       </c>
       <c r="D72" t="n">
-        <v>9.75816</v>
+        <v>9.645799999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>4.69465</v>
+        <v>4.73089</v>
       </c>
       <c r="F72" t="n">
-        <v>6.07832</v>
+        <v>5.80227</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.47303</v>
+        <v>5.40989</v>
       </c>
       <c r="C73" t="n">
-        <v>5.98748</v>
+        <v>5.8985</v>
       </c>
       <c r="D73" t="n">
-        <v>10.1615</v>
+        <v>10.4658</v>
       </c>
       <c r="E73" t="n">
-        <v>4.76117</v>
+        <v>4.79124</v>
       </c>
       <c r="F73" t="n">
-        <v>6.54273</v>
+        <v>6.4111</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.46141</v>
+        <v>5.45045</v>
       </c>
       <c r="C74" t="n">
-        <v>6.00812</v>
+        <v>5.99716</v>
       </c>
       <c r="D74" t="n">
-        <v>10.7497</v>
+        <v>10.5615</v>
       </c>
       <c r="E74" t="n">
-        <v>4.84193</v>
+        <v>4.87374</v>
       </c>
       <c r="F74" t="n">
-        <v>7.19232</v>
+        <v>7.20332</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.5358</v>
+        <v>5.48406</v>
       </c>
       <c r="C75" t="n">
-        <v>6.03387</v>
+        <v>6.03618</v>
       </c>
       <c r="D75" t="n">
-        <v>11.4493</v>
+        <v>11.1879</v>
       </c>
       <c r="E75" t="n">
-        <v>4.96514</v>
+        <v>4.94869</v>
       </c>
       <c r="F75" t="n">
-        <v>7.91379</v>
+        <v>7.85555</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.56347</v>
+        <v>5.499</v>
       </c>
       <c r="C76" t="n">
-        <v>6.10959</v>
+        <v>6.08531</v>
       </c>
       <c r="D76" t="n">
-        <v>12.1216</v>
+        <v>12.0887</v>
       </c>
       <c r="E76" t="n">
-        <v>5.08714</v>
+        <v>5.13156</v>
       </c>
       <c r="F76" t="n">
-        <v>8.56245</v>
+        <v>8.67384</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.61352</v>
+        <v>5.56247</v>
       </c>
       <c r="C77" t="n">
-        <v>6.157</v>
+        <v>6.17549</v>
       </c>
       <c r="D77" t="n">
-        <v>12.865</v>
+        <v>12.8832</v>
       </c>
       <c r="E77" t="n">
-        <v>5.29448</v>
+        <v>5.3269</v>
       </c>
       <c r="F77" t="n">
-        <v>9.222619999999999</v>
+        <v>9.243779999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.75826</v>
+        <v>5.67988</v>
       </c>
       <c r="C78" t="n">
-        <v>6.34097</v>
+        <v>6.38699</v>
       </c>
       <c r="D78" t="n">
-        <v>14.9221</v>
+        <v>14.821</v>
       </c>
       <c r="E78" t="n">
-        <v>5.57328</v>
+        <v>5.4933</v>
       </c>
       <c r="F78" t="n">
-        <v>9.81817</v>
+        <v>10.5594</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>5.88829</v>
+        <v>5.84497</v>
       </c>
       <c r="C79" t="n">
-        <v>17.6182</v>
+        <v>13.3792</v>
       </c>
       <c r="D79" t="n">
-        <v>15.721</v>
+        <v>15.6575</v>
       </c>
       <c r="E79" t="n">
-        <v>5.98344</v>
+        <v>5.66924</v>
       </c>
       <c r="F79" t="n">
-        <v>10.5438</v>
+        <v>10.7427</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.15068</v>
+        <v>6.10148</v>
       </c>
       <c r="C80" t="n">
-        <v>17.2813</v>
+        <v>13.4563</v>
       </c>
       <c r="D80" t="n">
-        <v>16.4635</v>
+        <v>16.3795</v>
       </c>
       <c r="E80" t="n">
-        <v>10.3848</v>
+        <v>5.82598</v>
       </c>
       <c r="F80" t="n">
-        <v>10.8029</v>
+        <v>10.7491</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>13.4109</v>
+        <v>14.4396</v>
       </c>
       <c r="C81" t="n">
-        <v>17.6997</v>
+        <v>13.9113</v>
       </c>
       <c r="D81" t="n">
-        <v>17.2119</v>
+        <v>17.2175</v>
       </c>
       <c r="E81" t="n">
-        <v>10.8586</v>
+        <v>6.20276</v>
       </c>
       <c r="F81" t="n">
-        <v>10.7802</v>
+        <v>10.9465</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.5734</v>
+        <v>13.8214</v>
       </c>
       <c r="C82" t="n">
-        <v>17.71</v>
+        <v>13.7342</v>
       </c>
       <c r="D82" t="n">
-        <v>17.8746</v>
+        <v>17.9512</v>
       </c>
       <c r="E82" t="n">
-        <v>10.6309</v>
+        <v>6.27162</v>
       </c>
       <c r="F82" t="n">
-        <v>11.0597</v>
+        <v>10.937</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.6974</v>
+        <v>13.6352</v>
       </c>
       <c r="C83" t="n">
-        <v>17.7773</v>
+        <v>13.7619</v>
       </c>
       <c r="D83" t="n">
-        <v>18.5549</v>
+        <v>18.6093</v>
       </c>
       <c r="E83" t="n">
-        <v>11.8324</v>
+        <v>6.28795</v>
       </c>
       <c r="F83" t="n">
-        <v>11.1505</v>
+        <v>11.0555</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.7221</v>
+        <v>13.8944</v>
       </c>
       <c r="C84" t="n">
-        <v>17.9003</v>
+        <v>13.6815</v>
       </c>
       <c r="D84" t="n">
-        <v>19.2972</v>
+        <v>19.3169</v>
       </c>
       <c r="E84" t="n">
-        <v>11.4263</v>
+        <v>6.48025</v>
       </c>
       <c r="F84" t="n">
-        <v>11.2144</v>
+        <v>11.0389</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.8503</v>
+        <v>13.9187</v>
       </c>
       <c r="C85" t="n">
-        <v>17.273</v>
+        <v>14.0681</v>
       </c>
       <c r="D85" t="n">
-        <v>19.954</v>
+        <v>20.0264</v>
       </c>
       <c r="E85" t="n">
-        <v>10.8707</v>
+        <v>6.61521</v>
       </c>
       <c r="F85" t="n">
-        <v>11.4785</v>
+        <v>11.2209</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>13.8494</v>
+        <v>14.0874</v>
       </c>
       <c r="C86" t="n">
-        <v>17.4805</v>
+        <v>14.1432</v>
       </c>
       <c r="D86" t="n">
-        <v>20.6055</v>
+        <v>20.6617</v>
       </c>
       <c r="E86" t="n">
-        <v>11.7211</v>
+        <v>6.89663</v>
       </c>
       <c r="F86" t="n">
-        <v>11.3091</v>
+        <v>11.323</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>13.9829</v>
+        <v>14.1301</v>
       </c>
       <c r="C87" t="n">
-        <v>17.3823</v>
+        <v>14.1127</v>
       </c>
       <c r="D87" t="n">
-        <v>21.2935</v>
+        <v>21.3045</v>
       </c>
       <c r="E87" t="n">
-        <v>12.0355</v>
+        <v>6.96124</v>
       </c>
       <c r="F87" t="n">
-        <v>11.3984</v>
+        <v>11.4378</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.0352</v>
+        <v>14.2812</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8131</v>
+        <v>13.9389</v>
       </c>
       <c r="D88" t="n">
-        <v>21.931</v>
+        <v>21.9135</v>
       </c>
       <c r="E88" t="n">
-        <v>11.6565</v>
+        <v>7.33992</v>
       </c>
       <c r="F88" t="n">
-        <v>11.529</v>
+        <v>11.5334</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>13.9968</v>
+        <v>14.1847</v>
       </c>
       <c r="C89" t="n">
-        <v>17.398</v>
+        <v>14.1551</v>
       </c>
       <c r="D89" t="n">
-        <v>22.6042</v>
+        <v>22.5541</v>
       </c>
       <c r="E89" t="n">
-        <v>12.0448</v>
+        <v>7.31961</v>
       </c>
       <c r="F89" t="n">
-        <v>11.7269</v>
+        <v>11.7424</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>13.9888</v>
+        <v>14.3297</v>
       </c>
       <c r="C90" t="n">
-        <v>17.777</v>
+        <v>14.1376</v>
       </c>
       <c r="D90" t="n">
-        <v>23.2509</v>
+        <v>23.3217</v>
       </c>
       <c r="E90" t="n">
-        <v>12.5201</v>
+        <v>7.56489</v>
       </c>
       <c r="F90" t="n">
-        <v>12.0219</v>
+        <v>11.9369</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.2249</v>
+        <v>14.3545</v>
       </c>
       <c r="C91" t="n">
-        <v>17.8031</v>
+        <v>14.3102</v>
       </c>
       <c r="D91" t="n">
-        <v>23.9691</v>
+        <v>24.1228</v>
       </c>
       <c r="E91" t="n">
-        <v>12.8115</v>
+        <v>7.71245</v>
       </c>
       <c r="F91" t="n">
-        <v>12.1113</v>
+        <v>12.2356</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.2744</v>
+        <v>14.5067</v>
       </c>
       <c r="C92" t="n">
-        <v>17.7929</v>
+        <v>14.1645</v>
       </c>
       <c r="D92" t="n">
-        <v>23.9214</v>
+        <v>24.1217</v>
       </c>
       <c r="E92" t="n">
-        <v>11.7576</v>
+        <v>14.8038</v>
       </c>
       <c r="F92" t="n">
-        <v>12.8537</v>
+        <v>17.5784</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.4664</v>
+        <v>14.5909</v>
       </c>
       <c r="C93" t="n">
-        <v>18.2759</v>
+        <v>14.3372</v>
       </c>
       <c r="D93" t="n">
-        <v>24.4577</v>
+        <v>24.6109</v>
       </c>
       <c r="E93" t="n">
-        <v>11.4731</v>
+        <v>14.9627</v>
       </c>
       <c r="F93" t="n">
-        <v>13.5772</v>
+        <v>17.5833</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.5086</v>
+        <v>14.7079</v>
       </c>
       <c r="C94" t="n">
-        <v>22.9399</v>
+        <v>23.0653</v>
       </c>
       <c r="D94" t="n">
-        <v>25.0965</v>
+        <v>25.0747</v>
       </c>
       <c r="E94" t="n">
-        <v>15.1142</v>
+        <v>15.0844</v>
       </c>
       <c r="F94" t="n">
-        <v>17.8658</v>
+        <v>17.6301</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.7349</v>
+        <v>20.8778</v>
       </c>
       <c r="C95" t="n">
-        <v>22.8348</v>
+        <v>22.9438</v>
       </c>
       <c r="D95" t="n">
-        <v>25.699</v>
+        <v>25.5498</v>
       </c>
       <c r="E95" t="n">
-        <v>15.2853</v>
+        <v>15.1439</v>
       </c>
       <c r="F95" t="n">
-        <v>18.4321</v>
+        <v>17.6845</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.7541</v>
+        <v>20.881</v>
       </c>
       <c r="C96" t="n">
-        <v>22.8297</v>
+        <v>23.0077</v>
       </c>
       <c r="D96" t="n">
-        <v>26.1589</v>
+        <v>26.0636</v>
       </c>
       <c r="E96" t="n">
-        <v>15.4696</v>
+        <v>15.3747</v>
       </c>
       <c r="F96" t="n">
-        <v>17.8761</v>
+        <v>17.8103</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.7451</v>
+        <v>20.9262</v>
       </c>
       <c r="C97" t="n">
-        <v>22.8557</v>
+        <v>23.0921</v>
       </c>
       <c r="D97" t="n">
-        <v>26.6815</v>
+        <v>26.6084</v>
       </c>
       <c r="E97" t="n">
-        <v>15.5388</v>
+        <v>15.4966</v>
       </c>
       <c r="F97" t="n">
-        <v>17.966</v>
+        <v>17.9022</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.8634</v>
+        <v>20.9839</v>
       </c>
       <c r="C98" t="n">
-        <v>22.869</v>
+        <v>23.1038</v>
       </c>
       <c r="D98" t="n">
-        <v>27.1598</v>
+        <v>27.1983</v>
       </c>
       <c r="E98" t="n">
-        <v>15.6328</v>
+        <v>15.6639</v>
       </c>
       <c r="F98" t="n">
-        <v>18.3132</v>
+        <v>18.0204</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>20.7655</v>
+        <v>20.9586</v>
       </c>
       <c r="C99" t="n">
-        <v>22.9405</v>
+        <v>23.1166</v>
       </c>
       <c r="D99" t="n">
-        <v>27.9081</v>
+        <v>27.8828</v>
       </c>
       <c r="E99" t="n">
-        <v>15.7555</v>
+        <v>15.8156</v>
       </c>
       <c r="F99" t="n">
-        <v>18.2183</v>
+        <v>18.0628</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>20.8681</v>
+        <v>20.9984</v>
       </c>
       <c r="C100" t="n">
-        <v>23.0179</v>
+        <v>23.1467</v>
       </c>
       <c r="D100" t="n">
-        <v>28.5724</v>
+        <v>28.579</v>
       </c>
       <c r="E100" t="n">
-        <v>16.0404</v>
+        <v>15.9514</v>
       </c>
       <c r="F100" t="n">
-        <v>18.2788</v>
+        <v>18.1908</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9096</v>
+        <v>20.9846</v>
       </c>
       <c r="C101" t="n">
-        <v>23.0651</v>
+        <v>23.1894</v>
       </c>
       <c r="D101" t="n">
-        <v>29.2034</v>
+        <v>29.1542</v>
       </c>
       <c r="E101" t="n">
-        <v>16.1574</v>
+        <v>16.0636</v>
       </c>
       <c r="F101" t="n">
-        <v>18.9016</v>
+        <v>18.319</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.8136</v>
+        <v>21.0423</v>
       </c>
       <c r="C102" t="n">
-        <v>23.0788</v>
+        <v>23.2759</v>
       </c>
       <c r="D102" t="n">
-        <v>29.9938</v>
+        <v>29.9634</v>
       </c>
       <c r="E102" t="n">
-        <v>16.2116</v>
+        <v>16.237</v>
       </c>
       <c r="F102" t="n">
-        <v>18.8403</v>
+        <v>18.4783</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>20.8826</v>
+        <v>21.0371</v>
       </c>
       <c r="C103" t="n">
-        <v>23.1624</v>
+        <v>23.2628</v>
       </c>
       <c r="D103" t="n">
-        <v>30.5429</v>
+        <v>30.7185</v>
       </c>
       <c r="E103" t="n">
-        <v>16.3623</v>
+        <v>16.4253</v>
       </c>
       <c r="F103" t="n">
-        <v>18.9122</v>
+        <v>18.6254</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>20.9589</v>
+        <v>21.0499</v>
       </c>
       <c r="C104" t="n">
-        <v>23.2427</v>
+        <v>23.2724</v>
       </c>
       <c r="D104" t="n">
-        <v>31.398</v>
+        <v>31.4027</v>
       </c>
       <c r="E104" t="n">
-        <v>16.6686</v>
+        <v>16.6132</v>
       </c>
       <c r="F104" t="n">
-        <v>19.0571</v>
+        <v>18.8156</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>20.9947</v>
+        <v>21.0457</v>
       </c>
       <c r="C105" t="n">
-        <v>23.2891</v>
+        <v>23.3367</v>
       </c>
       <c r="D105" t="n">
-        <v>32.1959</v>
+        <v>32.1815</v>
       </c>
       <c r="E105" t="n">
-        <v>16.9559</v>
+        <v>16.8259</v>
       </c>
       <c r="F105" t="n">
-        <v>19.0733</v>
+        <v>19.0679</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.0431</v>
+        <v>21.186</v>
       </c>
       <c r="C106" t="n">
-        <v>23.4214</v>
+        <v>23.5783</v>
       </c>
       <c r="D106" t="n">
-        <v>32.965</v>
+        <v>33.075</v>
       </c>
       <c r="E106" t="n">
-        <v>17.1428</v>
+        <v>17.0596</v>
       </c>
       <c r="F106" t="n">
-        <v>20.3595</v>
+        <v>19.4095</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.1456</v>
+        <v>21.2805</v>
       </c>
       <c r="C107" t="n">
-        <v>23.4778</v>
+        <v>23.596</v>
       </c>
       <c r="D107" t="n">
-        <v>28.6491</v>
+        <v>28.8538</v>
       </c>
       <c r="E107" t="n">
-        <v>17.5165</v>
+        <v>19.8508</v>
       </c>
       <c r="F107" t="n">
-        <v>19.9835</v>
+        <v>22.3826</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.2889</v>
+        <v>21.3957</v>
       </c>
       <c r="C108" t="n">
-        <v>27.0319</v>
+        <v>27.104</v>
       </c>
       <c r="D108" t="n">
-        <v>29.1393</v>
+        <v>29.2396</v>
       </c>
       <c r="E108" t="n">
-        <v>19.7589</v>
+        <v>19.9756</v>
       </c>
       <c r="F108" t="n">
-        <v>22.4152</v>
+        <v>22.3518</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.6072</v>
+        <v>21.7416</v>
       </c>
       <c r="C109" t="n">
-        <v>26.9316</v>
+        <v>27.2001</v>
       </c>
       <c r="D109" t="n">
-        <v>29.705</v>
+        <v>29.865</v>
       </c>
       <c r="E109" t="n">
-        <v>19.9483</v>
+        <v>20.1072</v>
       </c>
       <c r="F109" t="n">
-        <v>22.3855</v>
+        <v>22.5201</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.2689</v>
+        <v>23.3758</v>
       </c>
       <c r="C110" t="n">
-        <v>27.0572</v>
+        <v>27.1697</v>
       </c>
       <c r="D110" t="n">
-        <v>30.2308</v>
+        <v>30.2389</v>
       </c>
       <c r="E110" t="n">
-        <v>20.0872</v>
+        <v>20.2891</v>
       </c>
       <c r="F110" t="n">
-        <v>22.5265</v>
+        <v>22.7328</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.3836</v>
+        <v>23.5116</v>
       </c>
       <c r="C111" t="n">
-        <v>27.1023</v>
+        <v>27.2266</v>
       </c>
       <c r="D111" t="n">
-        <v>30.6975</v>
+        <v>30.942</v>
       </c>
       <c r="E111" t="n">
-        <v>20.2719</v>
+        <v>20.4619</v>
       </c>
       <c r="F111" t="n">
-        <v>22.6756</v>
+        <v>22.7377</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.3844</v>
+        <v>23.4381</v>
       </c>
       <c r="C112" t="n">
-        <v>27.0177</v>
+        <v>27.273</v>
       </c>
       <c r="D112" t="n">
-        <v>31.2914</v>
+        <v>31.4142</v>
       </c>
       <c r="E112" t="n">
-        <v>20.4705</v>
+        <v>20.5629</v>
       </c>
       <c r="F112" t="n">
-        <v>22.7488</v>
+        <v>22.8673</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.487</v>
+        <v>23.4728</v>
       </c>
       <c r="C113" t="n">
-        <v>27.2241</v>
+        <v>27.2169</v>
       </c>
       <c r="D113" t="n">
-        <v>32.0219</v>
+        <v>32.1145</v>
       </c>
       <c r="E113" t="n">
-        <v>20.6202</v>
+        <v>20.7768</v>
       </c>
       <c r="F113" t="n">
-        <v>23.096</v>
+        <v>23.1294</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.407</v>
+        <v>23.3904</v>
       </c>
       <c r="C114" t="n">
-        <v>27.2121</v>
+        <v>27.2531</v>
       </c>
       <c r="D114" t="n">
-        <v>32.5797</v>
+        <v>32.632</v>
       </c>
       <c r="E114" t="n">
-        <v>20.7919</v>
+        <v>20.8628</v>
       </c>
       <c r="F114" t="n">
-        <v>23.1291</v>
+        <v>23.2116</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.568</v>
+        <v>23.4062</v>
       </c>
       <c r="C115" t="n">
-        <v>27.2277</v>
+        <v>27.4829</v>
       </c>
       <c r="D115" t="n">
-        <v>33.415</v>
+        <v>33.4697</v>
       </c>
       <c r="E115" t="n">
-        <v>20.969</v>
+        <v>21.0171</v>
       </c>
       <c r="F115" t="n">
-        <v>23.262</v>
+        <v>23.4111</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.4713</v>
+        <v>23.5389</v>
       </c>
       <c r="C116" t="n">
-        <v>27.3426</v>
+        <v>27.4383</v>
       </c>
       <c r="D116" t="n">
-        <v>33.9754</v>
+        <v>34.0349</v>
       </c>
       <c r="E116" t="n">
-        <v>21.0998</v>
+        <v>21.1842</v>
       </c>
       <c r="F116" t="n">
-        <v>23.4635</v>
+        <v>23.7342</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.5402</v>
+        <v>23.5703</v>
       </c>
       <c r="C117" t="n">
-        <v>27.362</v>
+        <v>27.6767</v>
       </c>
       <c r="D117" t="n">
-        <v>34.8185</v>
+        <v>34.8836</v>
       </c>
       <c r="E117" t="n">
-        <v>21.3367</v>
+        <v>21.5063</v>
       </c>
       <c r="F117" t="n">
-        <v>23.7886</v>
+        <v>23.8819</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.5034</v>
+        <v>23.6432</v>
       </c>
       <c r="C118" t="n">
-        <v>27.5949</v>
+        <v>27.7255</v>
       </c>
       <c r="D118" t="n">
-        <v>35.6521</v>
+        <v>35.6572</v>
       </c>
       <c r="E118" t="n">
-        <v>21.5846</v>
+        <v>21.7419</v>
       </c>
       <c r="F118" t="n">
-        <v>23.9863</v>
+        <v>24.1615</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.5599</v>
+        <v>23.6125</v>
       </c>
       <c r="C119" t="n">
-        <v>27.5994</v>
+        <v>27.8801</v>
       </c>
       <c r="D119" t="n">
-        <v>36.3061</v>
+        <v>36.5873</v>
       </c>
       <c r="E119" t="n">
-        <v>21.7439</v>
+        <v>22.0096</v>
       </c>
       <c r="F119" t="n">
-        <v>24.437</v>
+        <v>24.5633</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.5733</v>
+        <v>23.7888</v>
       </c>
       <c r="C120" t="n">
-        <v>27.8245</v>
+        <v>28.0859</v>
       </c>
       <c r="D120" t="n">
-        <v>37.2918</v>
+        <v>37.3888</v>
       </c>
       <c r="E120" t="n">
-        <v>22.1226</v>
+        <v>22.2239</v>
       </c>
       <c r="F120" t="n">
-        <v>24.899</v>
+        <v>25.0599</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.785</v>
+        <v>23.899</v>
       </c>
       <c r="C121" t="n">
-        <v>28.0753</v>
+        <v>28.1754</v>
       </c>
       <c r="D121" t="n">
-        <v>31.265</v>
+        <v>31.5602</v>
       </c>
       <c r="E121" t="n">
-        <v>22.5391</v>
+        <v>22.6886</v>
       </c>
       <c r="F121" t="n">
-        <v>25.5634</v>
+        <v>26.0937</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>23.9132</v>
+        <v>24.1039</v>
       </c>
       <c r="C122" t="n">
-        <v>29.4233</v>
+        <v>29.8279</v>
       </c>
       <c r="D122" t="n">
-        <v>31.8506</v>
+        <v>31.9551</v>
       </c>
       <c r="E122" t="n">
-        <v>23.0921</v>
+        <v>22.8675</v>
       </c>
       <c r="F122" t="n">
-        <v>26.4115</v>
+        <v>26.309</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.387</v>
+        <v>24.4296</v>
       </c>
       <c r="C123" t="n">
-        <v>29.5182</v>
+        <v>30.01</v>
       </c>
       <c r="D123" t="n">
-        <v>32.2898</v>
+        <v>32.5763</v>
       </c>
       <c r="E123" t="n">
-        <v>22.8478</v>
+        <v>23.0888</v>
       </c>
       <c r="F123" t="n">
-        <v>26.1967</v>
+        <v>26.3611</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>30.9856</v>
+        <v>29.7153</v>
       </c>
       <c r="C124" t="n">
-        <v>29.645</v>
+        <v>29.8831</v>
       </c>
       <c r="D124" t="n">
-        <v>32.8558</v>
+        <v>32.9671</v>
       </c>
       <c r="E124" t="n">
-        <v>22.9091</v>
+        <v>23.2735</v>
       </c>
       <c r="F124" t="n">
-        <v>26.2701</v>
+        <v>26.6356</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>30.7195</v>
+        <v>29.8195</v>
       </c>
       <c r="C125" t="n">
-        <v>29.6088</v>
+        <v>30.0213</v>
       </c>
       <c r="D125" t="n">
-        <v>33.4027</v>
+        <v>33.7077</v>
       </c>
       <c r="E125" t="n">
-        <v>23.11</v>
+        <v>23.3231</v>
       </c>
       <c r="F125" t="n">
-        <v>26.422</v>
+        <v>26.7142</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>31.4875</v>
+        <v>29.8419</v>
       </c>
       <c r="C126" t="n">
-        <v>29.7065</v>
+        <v>30.1273</v>
       </c>
       <c r="D126" t="n">
-        <v>33.8668</v>
+        <v>34.1782</v>
       </c>
       <c r="E126" t="n">
-        <v>23.3427</v>
+        <v>23.5829</v>
       </c>
       <c r="F126" t="n">
-        <v>26.544</v>
+        <v>26.9382</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>31.0531</v>
+        <v>29.7891</v>
       </c>
       <c r="C127" t="n">
-        <v>29.8581</v>
+        <v>30.2645</v>
       </c>
       <c r="D127" t="n">
-        <v>34.5049</v>
+        <v>34.8688</v>
       </c>
       <c r="E127" t="n">
-        <v>23.4346</v>
+        <v>23.7769</v>
       </c>
       <c r="F127" t="n">
-        <v>26.8423</v>
+        <v>27.0329</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.5364</v>
+        <v>29.7368</v>
       </c>
       <c r="C128" t="n">
-        <v>29.8335</v>
+        <v>30.3497</v>
       </c>
       <c r="D128" t="n">
-        <v>35.281</v>
+        <v>35.5199</v>
       </c>
       <c r="E128" t="n">
-        <v>23.6659</v>
+        <v>23.8506</v>
       </c>
       <c r="F128" t="n">
-        <v>27.0882</v>
+        <v>27.1376</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>31.0819</v>
+        <v>29.7393</v>
       </c>
       <c r="C129" t="n">
-        <v>29.9161</v>
+        <v>30.6602</v>
       </c>
       <c r="D129" t="n">
-        <v>35.9661</v>
+        <v>36.1111</v>
       </c>
       <c r="E129" t="n">
-        <v>23.8476</v>
+        <v>24.0661</v>
       </c>
       <c r="F129" t="n">
-        <v>27.1569</v>
+        <v>27.4486</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>30.8942</v>
+        <v>29.7682</v>
       </c>
       <c r="C130" t="n">
-        <v>30.2629</v>
+        <v>30.5673</v>
       </c>
       <c r="D130" t="n">
-        <v>36.6607</v>
+        <v>36.9593</v>
       </c>
       <c r="E130" t="n">
-        <v>24.1075</v>
+        <v>24.2707</v>
       </c>
       <c r="F130" t="n">
-        <v>27.3834</v>
+        <v>27.8158</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.8213</v>
+        <v>29.8978</v>
       </c>
       <c r="C131" t="n">
-        <v>30.3981</v>
+        <v>30.8269</v>
       </c>
       <c r="D131" t="n">
-        <v>37.3912</v>
+        <v>37.5351</v>
       </c>
       <c r="E131" t="n">
-        <v>24.2704</v>
+        <v>24.4714</v>
       </c>
       <c r="F131" t="n">
-        <v>27.734</v>
+        <v>28.0028</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>31.2883</v>
+        <v>29.9017</v>
       </c>
       <c r="C132" t="n">
-        <v>30.5603</v>
+        <v>30.9848</v>
       </c>
       <c r="D132" t="n">
-        <v>38.3022</v>
+        <v>38.426</v>
       </c>
       <c r="E132" t="n">
-        <v>24.5898</v>
+        <v>24.7002</v>
       </c>
       <c r="F132" t="n">
-        <v>28.1027</v>
+        <v>28.387</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>30.1672</v>
+        <v>29.8698</v>
       </c>
       <c r="C133" t="n">
-        <v>30.7943</v>
+        <v>31.1216</v>
       </c>
       <c r="D133" t="n">
-        <v>39.0755</v>
+        <v>39.3048</v>
       </c>
       <c r="E133" t="n">
-        <v>24.9147</v>
+        <v>25.0504</v>
       </c>
       <c r="F133" t="n">
-        <v>28.5984</v>
+        <v>28.8241</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>31.1046</v>
+        <v>29.9543</v>
       </c>
       <c r="C134" t="n">
-        <v>31.0496</v>
+        <v>31.5101</v>
       </c>
       <c r="D134" t="n">
-        <v>39.729</v>
+        <v>40.0118</v>
       </c>
       <c r="E134" t="n">
-        <v>25.3577</v>
+        <v>25.4909</v>
       </c>
       <c r="F134" t="n">
-        <v>29.1537</v>
+        <v>29.2899</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>31.5212</v>
+        <v>30.0937</v>
       </c>
       <c r="C135" t="n">
-        <v>31.4184</v>
+        <v>31.7471</v>
       </c>
       <c r="D135" t="n">
-        <v>33.1039</v>
+        <v>33.2145</v>
       </c>
       <c r="E135" t="n">
-        <v>25.7295</v>
+        <v>25.5362</v>
       </c>
       <c r="F135" t="n">
-        <v>29.8837</v>
+        <v>28.5333</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.2273</v>
+        <v>30.1585</v>
       </c>
       <c r="C136" t="n">
-        <v>31.2545</v>
+        <v>31.9553</v>
       </c>
       <c r="D136" t="n">
-        <v>33.589</v>
+        <v>33.7917</v>
       </c>
       <c r="E136" t="n">
-        <v>26.5211</v>
+        <v>25.3439</v>
       </c>
       <c r="F136" t="n">
-        <v>30.891</v>
+        <v>28.8858</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.2773</v>
+        <v>30.4773</v>
       </c>
       <c r="C137" t="n">
-        <v>31.4697</v>
+        <v>31.8303</v>
       </c>
       <c r="D137" t="n">
-        <v>34.0335</v>
+        <v>34.2308</v>
       </c>
       <c r="E137" t="n">
-        <v>25.1518</v>
+        <v>25.6936</v>
       </c>
       <c r="F137" t="n">
-        <v>28.5329</v>
+        <v>29.0439</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>34.8871</v>
+        <v>35.3425</v>
       </c>
       <c r="C138" t="n">
-        <v>31.3625</v>
+        <v>31.8697</v>
       </c>
       <c r="D138" t="n">
-        <v>34.4691</v>
+        <v>34.9212</v>
       </c>
       <c r="E138" t="n">
-        <v>25.3438</v>
+        <v>25.8401</v>
       </c>
       <c r="F138" t="n">
-        <v>28.4677</v>
+        <v>29.0873</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.1301</v>
+        <v>35.2515</v>
       </c>
       <c r="C139" t="n">
-        <v>31.4937</v>
+        <v>31.9356</v>
       </c>
       <c r="D139" t="n">
-        <v>35.0562</v>
+        <v>35.4314</v>
       </c>
       <c r="E139" t="n">
-        <v>25.4778</v>
+        <v>26.0718</v>
       </c>
       <c r="F139" t="n">
-        <v>28.6904</v>
+        <v>29.3997</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>34.9564</v>
+        <v>35.2916</v>
       </c>
       <c r="C140" t="n">
-        <v>31.5637</v>
+        <v>32.2154</v>
       </c>
       <c r="D140" t="n">
-        <v>35.5317</v>
+        <v>35.979</v>
       </c>
       <c r="E140" t="n">
-        <v>25.6392</v>
+        <v>26.4176</v>
       </c>
       <c r="F140" t="n">
-        <v>28.8913</v>
+        <v>29.4155</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.0175</v>
+        <v>35.3774</v>
       </c>
       <c r="C141" t="n">
-        <v>31.6359</v>
+        <v>32.18</v>
       </c>
       <c r="D141" t="n">
-        <v>36.2705</v>
+        <v>36.6169</v>
       </c>
       <c r="E141" t="n">
-        <v>25.679</v>
+        <v>26.412</v>
       </c>
       <c r="F141" t="n">
-        <v>29.1023</v>
+        <v>29.624</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>34.9017</v>
+        <v>35.4676</v>
       </c>
       <c r="C142" t="n">
-        <v>31.9268</v>
+        <v>32.4726</v>
       </c>
       <c r="D142" t="n">
-        <v>36.7639</v>
+        <v>37.2453</v>
       </c>
       <c r="E142" t="n">
-        <v>26.0198</v>
+        <v>26.3683</v>
       </c>
       <c r="F142" t="n">
-        <v>29.2899</v>
+        <v>29.8731</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>34.9476</v>
+        <v>35.3116</v>
       </c>
       <c r="C143" t="n">
-        <v>32.0745</v>
+        <v>32.612</v>
       </c>
       <c r="D143" t="n">
-        <v>37.5252</v>
+        <v>37.8696</v>
       </c>
       <c r="E143" t="n">
-        <v>26.1053</v>
+        <v>26.7283</v>
       </c>
       <c r="F143" t="n">
-        <v>29.4784</v>
+        <v>29.8382</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.77589</v>
+        <v>2.79628</v>
       </c>
       <c r="C2" t="n">
-        <v>4.48075</v>
+        <v>4.48201</v>
       </c>
       <c r="D2" t="n">
-        <v>5.47094</v>
+        <v>5.38938</v>
       </c>
       <c r="E2" t="n">
-        <v>3.23776</v>
+        <v>3.89993</v>
       </c>
       <c r="F2" t="n">
-        <v>3.50726</v>
+        <v>3.93303</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.7972</v>
+        <v>2.79316</v>
       </c>
       <c r="C3" t="n">
-        <v>4.51132</v>
+        <v>4.5052</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7812</v>
+        <v>5.62191</v>
       </c>
       <c r="E3" t="n">
-        <v>3.26027</v>
+        <v>3.91872</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5286</v>
+        <v>3.92377</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.8109</v>
+        <v>2.81903</v>
       </c>
       <c r="C4" t="n">
-        <v>4.54144</v>
+        <v>4.53462</v>
       </c>
       <c r="D4" t="n">
-        <v>6.12099</v>
+        <v>6.06935</v>
       </c>
       <c r="E4" t="n">
-        <v>3.27788</v>
+        <v>3.96303</v>
       </c>
       <c r="F4" t="n">
-        <v>3.56149</v>
+        <v>4.01356</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.85629</v>
+        <v>2.84315</v>
       </c>
       <c r="C5" t="n">
-        <v>4.58371</v>
+        <v>4.57105</v>
       </c>
       <c r="D5" t="n">
-        <v>6.48273</v>
+        <v>6.41982</v>
       </c>
       <c r="E5" t="n">
-        <v>3.30669</v>
+        <v>4.01403</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5802</v>
+        <v>4.01266</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.87233</v>
+        <v>2.89094</v>
       </c>
       <c r="C6" t="n">
-        <v>4.59692</v>
+        <v>4.632</v>
       </c>
       <c r="D6" t="n">
-        <v>6.84888</v>
+        <v>6.72705</v>
       </c>
       <c r="E6" t="n">
-        <v>3.36699</v>
+        <v>4.06327</v>
       </c>
       <c r="F6" t="n">
-        <v>3.63527</v>
+        <v>4.08701</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.90708</v>
+        <v>2.92253</v>
       </c>
       <c r="C7" t="n">
-        <v>4.66999</v>
+        <v>4.68063</v>
       </c>
       <c r="D7" t="n">
-        <v>5.18768</v>
+        <v>5.05087</v>
       </c>
       <c r="E7" t="n">
-        <v>3.241</v>
+        <v>3.81042</v>
       </c>
       <c r="F7" t="n">
-        <v>3.51483</v>
+        <v>3.97481</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.94118</v>
+        <v>2.95763</v>
       </c>
       <c r="C8" t="n">
-        <v>4.52288</v>
+        <v>4.55342</v>
       </c>
       <c r="D8" t="n">
-        <v>5.37082</v>
+        <v>5.21702</v>
       </c>
       <c r="E8" t="n">
-        <v>3.27455</v>
+        <v>3.83185</v>
       </c>
       <c r="F8" t="n">
-        <v>3.57776</v>
+        <v>3.98448</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.00404</v>
+        <v>2.97767</v>
       </c>
       <c r="C9" t="n">
-        <v>4.54311</v>
+        <v>4.55121</v>
       </c>
       <c r="D9" t="n">
-        <v>5.57848</v>
+        <v>5.41875</v>
       </c>
       <c r="E9" t="n">
-        <v>3.27849</v>
+        <v>3.87512</v>
       </c>
       <c r="F9" t="n">
-        <v>3.60697</v>
+        <v>4.0025</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.41135</v>
+        <v>3.42033</v>
       </c>
       <c r="C10" t="n">
-        <v>4.54636</v>
+        <v>4.54976</v>
       </c>
       <c r="D10" t="n">
-        <v>5.81696</v>
+        <v>5.68566</v>
       </c>
       <c r="E10" t="n">
-        <v>3.33579</v>
+        <v>3.89224</v>
       </c>
       <c r="F10" t="n">
-        <v>3.64895</v>
+        <v>4.02665</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.43083</v>
+        <v>3.43806</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5759</v>
+        <v>4.55395</v>
       </c>
       <c r="D11" t="n">
-        <v>6.06059</v>
+        <v>5.93488</v>
       </c>
       <c r="E11" t="n">
-        <v>3.33417</v>
+        <v>3.94369</v>
       </c>
       <c r="F11" t="n">
-        <v>3.66349</v>
+        <v>4.08172</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.42897</v>
+        <v>3.45115</v>
       </c>
       <c r="C12" t="n">
-        <v>4.54903</v>
+        <v>4.58273</v>
       </c>
       <c r="D12" t="n">
-        <v>6.32358</v>
+        <v>6.20103</v>
       </c>
       <c r="E12" t="n">
-        <v>3.36209</v>
+        <v>3.96394</v>
       </c>
       <c r="F12" t="n">
-        <v>3.68206</v>
+        <v>4.09819</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.45159</v>
+        <v>3.46375</v>
       </c>
       <c r="C13" t="n">
-        <v>4.60031</v>
+        <v>4.59138</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6056</v>
+        <v>6.46969</v>
       </c>
       <c r="E13" t="n">
-        <v>3.38877</v>
+        <v>4.00087</v>
       </c>
       <c r="F13" t="n">
-        <v>3.71322</v>
+        <v>4.14069</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4681</v>
+        <v>3.48694</v>
       </c>
       <c r="C14" t="n">
-        <v>4.59074</v>
+        <v>4.60241</v>
       </c>
       <c r="D14" t="n">
-        <v>6.91609</v>
+        <v>6.78532</v>
       </c>
       <c r="E14" t="n">
-        <v>3.43473</v>
+        <v>4.02013</v>
       </c>
       <c r="F14" t="n">
-        <v>3.73065</v>
+        <v>4.16647</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.46633</v>
+        <v>3.50369</v>
       </c>
       <c r="C15" t="n">
-        <v>4.62159</v>
+        <v>4.61228</v>
       </c>
       <c r="D15" t="n">
-        <v>7.17458</v>
+        <v>7.00443</v>
       </c>
       <c r="E15" t="n">
-        <v>3.46049</v>
+        <v>4.06367</v>
       </c>
       <c r="F15" t="n">
-        <v>3.76066</v>
+        <v>4.20334</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.4841</v>
+        <v>3.49911</v>
       </c>
       <c r="C16" t="n">
-        <v>4.63067</v>
+        <v>4.63827</v>
       </c>
       <c r="D16" t="n">
-        <v>7.39548</v>
+        <v>7.27809</v>
       </c>
       <c r="E16" t="n">
-        <v>3.48386</v>
+        <v>4.11181</v>
       </c>
       <c r="F16" t="n">
-        <v>3.77754</v>
+        <v>4.2459</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.503</v>
+        <v>3.54246</v>
       </c>
       <c r="C17" t="n">
-        <v>4.66484</v>
+        <v>4.67448</v>
       </c>
       <c r="D17" t="n">
-        <v>7.69862</v>
+        <v>7.57883</v>
       </c>
       <c r="E17" t="n">
-        <v>3.51592</v>
+        <v>4.16523</v>
       </c>
       <c r="F17" t="n">
-        <v>3.82152</v>
+        <v>4.27435</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.53775</v>
+        <v>3.56469</v>
       </c>
       <c r="C18" t="n">
-        <v>4.73612</v>
+        <v>4.73081</v>
       </c>
       <c r="D18" t="n">
-        <v>7.9854</v>
+        <v>7.86113</v>
       </c>
       <c r="E18" t="n">
-        <v>3.53957</v>
+        <v>4.18638</v>
       </c>
       <c r="F18" t="n">
-        <v>3.851</v>
+        <v>4.32378</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.56509</v>
+        <v>3.56948</v>
       </c>
       <c r="C19" t="n">
-        <v>4.78914</v>
+        <v>4.77065</v>
       </c>
       <c r="D19" t="n">
-        <v>8.259</v>
+        <v>8.14307</v>
       </c>
       <c r="E19" t="n">
-        <v>3.58186</v>
+        <v>4.28049</v>
       </c>
       <c r="F19" t="n">
-        <v>3.90976</v>
+        <v>4.36814</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.59133</v>
+        <v>3.59127</v>
       </c>
       <c r="C20" t="n">
-        <v>4.82232</v>
+        <v>4.82818</v>
       </c>
       <c r="D20" t="n">
-        <v>8.50765</v>
+        <v>8.366680000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>3.61511</v>
+        <v>4.36733</v>
       </c>
       <c r="F20" t="n">
-        <v>3.98871</v>
+        <v>4.45338</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.63306</v>
+        <v>3.6421</v>
       </c>
       <c r="C21" t="n">
-        <v>4.93658</v>
+        <v>4.89989</v>
       </c>
       <c r="D21" t="n">
-        <v>6.33297</v>
+        <v>6.24618</v>
       </c>
       <c r="E21" t="n">
-        <v>3.5657</v>
+        <v>4.29408</v>
       </c>
       <c r="F21" t="n">
-        <v>3.92195</v>
+        <v>4.36456</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.66911</v>
+        <v>3.68896</v>
       </c>
       <c r="C22" t="n">
-        <v>4.82836</v>
+        <v>4.73158</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53473</v>
+        <v>6.44878</v>
       </c>
       <c r="E22" t="n">
-        <v>3.54432</v>
+        <v>4.30476</v>
       </c>
       <c r="F22" t="n">
-        <v>3.95742</v>
+        <v>4.38933</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.75138</v>
+        <v>3.76171</v>
       </c>
       <c r="C23" t="n">
-        <v>4.81087</v>
+        <v>4.74429</v>
       </c>
       <c r="D23" t="n">
-        <v>6.74393</v>
+        <v>6.65924</v>
       </c>
       <c r="E23" t="n">
-        <v>3.60285</v>
+        <v>4.35502</v>
       </c>
       <c r="F23" t="n">
-        <v>3.96458</v>
+        <v>4.41494</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.93962</v>
+        <v>3.93364</v>
       </c>
       <c r="C24" t="n">
-        <v>4.82332</v>
+        <v>4.75965</v>
       </c>
       <c r="D24" t="n">
-        <v>7.00246</v>
+        <v>6.92592</v>
       </c>
       <c r="E24" t="n">
-        <v>3.59091</v>
+        <v>4.38852</v>
       </c>
       <c r="F24" t="n">
-        <v>4.01802</v>
+        <v>4.43848</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.9359</v>
+        <v>3.95509</v>
       </c>
       <c r="C25" t="n">
-        <v>4.86842</v>
+        <v>4.78142</v>
       </c>
       <c r="D25" t="n">
-        <v>7.2608</v>
+        <v>7.16069</v>
       </c>
       <c r="E25" t="n">
-        <v>3.60417</v>
+        <v>4.42586</v>
       </c>
       <c r="F25" t="n">
-        <v>4.02889</v>
+        <v>4.47436</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.93931</v>
+        <v>3.94261</v>
       </c>
       <c r="C26" t="n">
-        <v>4.8446</v>
+        <v>4.79097</v>
       </c>
       <c r="D26" t="n">
-        <v>7.50263</v>
+        <v>7.39326</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6775</v>
+        <v>4.4613</v>
       </c>
       <c r="F26" t="n">
-        <v>4.06373</v>
+        <v>4.50144</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.95598</v>
+        <v>3.9589</v>
       </c>
       <c r="C27" t="n">
-        <v>4.81444</v>
+        <v>4.81632</v>
       </c>
       <c r="D27" t="n">
-        <v>7.77533</v>
+        <v>7.66413</v>
       </c>
       <c r="E27" t="n">
-        <v>3.66844</v>
+        <v>4.47883</v>
       </c>
       <c r="F27" t="n">
-        <v>4.10234</v>
+        <v>4.54672</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.95538</v>
+        <v>3.96447</v>
       </c>
       <c r="C28" t="n">
-        <v>4.85614</v>
+        <v>4.80759</v>
       </c>
       <c r="D28" t="n">
-        <v>8.02783</v>
+        <v>7.89033</v>
       </c>
       <c r="E28" t="n">
-        <v>3.77273</v>
+        <v>4.57167</v>
       </c>
       <c r="F28" t="n">
-        <v>4.12055</v>
+        <v>4.56299</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.95805</v>
+        <v>3.95219</v>
       </c>
       <c r="C29" t="n">
-        <v>4.89304</v>
+        <v>4.85785</v>
       </c>
       <c r="D29" t="n">
-        <v>8.298069999999999</v>
+        <v>8.16057</v>
       </c>
       <c r="E29" t="n">
-        <v>3.73053</v>
+        <v>4.59535</v>
       </c>
       <c r="F29" t="n">
-        <v>4.16132</v>
+        <v>4.60706</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.97377</v>
+        <v>3.959</v>
       </c>
       <c r="C30" t="n">
-        <v>4.91091</v>
+        <v>4.86982</v>
       </c>
       <c r="D30" t="n">
-        <v>8.54326</v>
+        <v>8.432550000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>3.84547</v>
+        <v>4.64826</v>
       </c>
       <c r="F30" t="n">
-        <v>4.2067</v>
+        <v>4.64751</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.99655</v>
+        <v>3.97878</v>
       </c>
       <c r="C31" t="n">
-        <v>4.93758</v>
+        <v>4.92993</v>
       </c>
       <c r="D31" t="n">
-        <v>8.77214</v>
+        <v>8.614599999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>3.82652</v>
+        <v>4.69909</v>
       </c>
       <c r="F31" t="n">
-        <v>4.24891</v>
+        <v>4.67751</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.01201</v>
+        <v>4.00822</v>
       </c>
       <c r="C32" t="n">
-        <v>4.96634</v>
+        <v>4.96568</v>
       </c>
       <c r="D32" t="n">
-        <v>8.99377</v>
+        <v>8.912789999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>3.88212</v>
+        <v>4.74342</v>
       </c>
       <c r="F32" t="n">
-        <v>4.26451</v>
+        <v>4.74069</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.04412</v>
+        <v>4.03094</v>
       </c>
       <c r="C33" t="n">
-        <v>4.99318</v>
+        <v>5.00076</v>
       </c>
       <c r="D33" t="n">
-        <v>9.263540000000001</v>
+        <v>9.154920000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>3.91272</v>
+        <v>4.86771</v>
       </c>
       <c r="F33" t="n">
-        <v>4.36136</v>
+        <v>4.81692</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.05782</v>
+        <v>4.0628</v>
       </c>
       <c r="C34" t="n">
-        <v>5.09661</v>
+        <v>5.07783</v>
       </c>
       <c r="D34" t="n">
-        <v>9.46231</v>
+        <v>9.38979</v>
       </c>
       <c r="E34" t="n">
-        <v>4.0845</v>
+        <v>4.96314</v>
       </c>
       <c r="F34" t="n">
-        <v>4.46218</v>
+        <v>4.95773</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.11139</v>
+        <v>4.10915</v>
       </c>
       <c r="C35" t="n">
-        <v>5.15694</v>
+        <v>5.17525</v>
       </c>
       <c r="D35" t="n">
-        <v>6.85026</v>
+        <v>6.76122</v>
       </c>
       <c r="E35" t="n">
-        <v>3.81722</v>
+        <v>4.90389</v>
       </c>
       <c r="F35" t="n">
-        <v>4.24127</v>
+        <v>4.71076</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.19962</v>
+        <v>4.20278</v>
       </c>
       <c r="C36" t="n">
-        <v>5.26003</v>
+        <v>5.2675</v>
       </c>
       <c r="D36" t="n">
-        <v>7.02676</v>
+        <v>6.89592</v>
       </c>
       <c r="E36" t="n">
-        <v>3.84068</v>
+        <v>4.96382</v>
       </c>
       <c r="F36" t="n">
-        <v>4.27271</v>
+        <v>4.72673</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.42779</v>
+        <v>4.44806</v>
       </c>
       <c r="C37" t="n">
-        <v>5.0459</v>
+        <v>5.04403</v>
       </c>
       <c r="D37" t="n">
-        <v>7.20789</v>
+        <v>7.07918</v>
       </c>
       <c r="E37" t="n">
-        <v>3.91617</v>
+        <v>5.01551</v>
       </c>
       <c r="F37" t="n">
-        <v>4.34121</v>
+        <v>4.75392</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.24333</v>
+        <v>4.26205</v>
       </c>
       <c r="C38" t="n">
-        <v>5.0503</v>
+        <v>5.02339</v>
       </c>
       <c r="D38" t="n">
-        <v>7.44156</v>
+        <v>7.30399</v>
       </c>
       <c r="E38" t="n">
-        <v>3.93604</v>
+        <v>5.0154</v>
       </c>
       <c r="F38" t="n">
-        <v>4.29553</v>
+        <v>4.75969</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.27088</v>
+        <v>4.25783</v>
       </c>
       <c r="C39" t="n">
-        <v>5.07921</v>
+        <v>5.02677</v>
       </c>
       <c r="D39" t="n">
-        <v>7.66113</v>
+        <v>7.48766</v>
       </c>
       <c r="E39" t="n">
-        <v>3.92734</v>
+        <v>5.05686</v>
       </c>
       <c r="F39" t="n">
-        <v>4.36703</v>
+        <v>4.79124</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.22096</v>
+        <v>4.2802</v>
       </c>
       <c r="C40" t="n">
-        <v>5.11583</v>
+        <v>5.07911</v>
       </c>
       <c r="D40" t="n">
-        <v>7.9063</v>
+        <v>7.75277</v>
       </c>
       <c r="E40" t="n">
-        <v>3.98835</v>
+        <v>5.0875</v>
       </c>
       <c r="F40" t="n">
-        <v>4.38961</v>
+        <v>4.82095</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.28849</v>
+        <v>4.29054</v>
       </c>
       <c r="C41" t="n">
-        <v>5.17176</v>
+        <v>5.0873</v>
       </c>
       <c r="D41" t="n">
-        <v>8.17089</v>
+        <v>7.97105</v>
       </c>
       <c r="E41" t="n">
-        <v>3.98799</v>
+        <v>5.1183</v>
       </c>
       <c r="F41" t="n">
-        <v>4.42071</v>
+        <v>4.85581</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.28971</v>
+        <v>4.26749</v>
       </c>
       <c r="C42" t="n">
-        <v>5.16377</v>
+        <v>5.1068</v>
       </c>
       <c r="D42" t="n">
-        <v>8.40246</v>
+        <v>8.2196</v>
       </c>
       <c r="E42" t="n">
-        <v>4.04955</v>
+        <v>5.16986</v>
       </c>
       <c r="F42" t="n">
-        <v>4.43387</v>
+        <v>4.89918</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.24434</v>
+        <v>4.25201</v>
       </c>
       <c r="C43" t="n">
-        <v>5.19783</v>
+        <v>5.15248</v>
       </c>
       <c r="D43" t="n">
-        <v>8.66503</v>
+        <v>8.4847</v>
       </c>
       <c r="E43" t="n">
-        <v>4.08176</v>
+        <v>5.23179</v>
       </c>
       <c r="F43" t="n">
-        <v>4.4718</v>
+        <v>4.90711</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.30684</v>
+        <v>4.30067</v>
       </c>
       <c r="C44" t="n">
-        <v>5.23538</v>
+        <v>5.16283</v>
       </c>
       <c r="D44" t="n">
-        <v>8.94032</v>
+        <v>8.73089</v>
       </c>
       <c r="E44" t="n">
-        <v>4.10118</v>
+        <v>5.23762</v>
       </c>
       <c r="F44" t="n">
-        <v>4.50935</v>
+        <v>4.97611</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.29494</v>
+        <v>4.32986</v>
       </c>
       <c r="C45" t="n">
-        <v>5.241</v>
+        <v>5.22712</v>
       </c>
       <c r="D45" t="n">
-        <v>9.155060000000001</v>
+        <v>9.011900000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>4.18256</v>
+        <v>5.33103</v>
       </c>
       <c r="F45" t="n">
-        <v>4.58721</v>
+        <v>5.04987</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.33896</v>
+        <v>4.33432</v>
       </c>
       <c r="C46" t="n">
-        <v>5.33158</v>
+        <v>5.24862</v>
       </c>
       <c r="D46" t="n">
-        <v>9.407830000000001</v>
+        <v>9.26125</v>
       </c>
       <c r="E46" t="n">
-        <v>4.23189</v>
+        <v>5.41533</v>
       </c>
       <c r="F46" t="n">
-        <v>4.62043</v>
+        <v>5.10821</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.35197</v>
+        <v>4.35284</v>
       </c>
       <c r="C47" t="n">
-        <v>5.36155</v>
+        <v>5.29543</v>
       </c>
       <c r="D47" t="n">
-        <v>9.623659999999999</v>
+        <v>9.46912</v>
       </c>
       <c r="E47" t="n">
-        <v>4.30822</v>
+        <v>5.53564</v>
       </c>
       <c r="F47" t="n">
-        <v>4.73699</v>
+        <v>5.23654</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.37095</v>
+        <v>4.40526</v>
       </c>
       <c r="C48" t="n">
-        <v>5.40954</v>
+        <v>5.36314</v>
       </c>
       <c r="D48" t="n">
-        <v>9.88715</v>
+        <v>9.733359999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>4.49323</v>
+        <v>5.66301</v>
       </c>
       <c r="F48" t="n">
-        <v>4.87697</v>
+        <v>5.43598</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.44024</v>
+        <v>4.45756</v>
       </c>
       <c r="C49" t="n">
-        <v>5.49011</v>
+        <v>5.44409</v>
       </c>
       <c r="D49" t="n">
-        <v>10.1154</v>
+        <v>9.95219</v>
       </c>
       <c r="E49" t="n">
-        <v>4.73939</v>
+        <v>5.87467</v>
       </c>
       <c r="F49" t="n">
-        <v>5.12512</v>
+        <v>5.73151</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.57945</v>
+        <v>4.56666</v>
       </c>
       <c r="C50" t="n">
-        <v>5.66852</v>
+        <v>5.55498</v>
       </c>
       <c r="D50" t="n">
-        <v>7.19196</v>
+        <v>7.02373</v>
       </c>
       <c r="E50" t="n">
-        <v>4.14482</v>
+        <v>5.30589</v>
       </c>
       <c r="F50" t="n">
-        <v>4.51844</v>
+        <v>4.95811</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.73176</v>
+        <v>4.73121</v>
       </c>
       <c r="C51" t="n">
-        <v>5.42859</v>
+        <v>5.41464</v>
       </c>
       <c r="D51" t="n">
-        <v>7.32276</v>
+        <v>7.19314</v>
       </c>
       <c r="E51" t="n">
-        <v>4.18773</v>
+        <v>5.34528</v>
       </c>
       <c r="F51" t="n">
-        <v>4.5454</v>
+        <v>5.00405</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.13956</v>
+        <v>5.11468</v>
       </c>
       <c r="C52" t="n">
-        <v>5.43567</v>
+        <v>5.43821</v>
       </c>
       <c r="D52" t="n">
-        <v>7.54838</v>
+        <v>7.40035</v>
       </c>
       <c r="E52" t="n">
-        <v>4.19745</v>
+        <v>5.37443</v>
       </c>
       <c r="F52" t="n">
-        <v>4.58951</v>
+        <v>5.02547</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.74078</v>
+        <v>4.78484</v>
       </c>
       <c r="C53" t="n">
-        <v>5.47035</v>
+        <v>5.4737</v>
       </c>
       <c r="D53" t="n">
-        <v>7.76985</v>
+        <v>7.62302</v>
       </c>
       <c r="E53" t="n">
-        <v>4.23245</v>
+        <v>5.40082</v>
       </c>
       <c r="F53" t="n">
-        <v>4.60776</v>
+        <v>5.05976</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.76859</v>
+        <v>4.80413</v>
       </c>
       <c r="C54" t="n">
-        <v>5.48413</v>
+        <v>5.47335</v>
       </c>
       <c r="D54" t="n">
-        <v>7.98786</v>
+        <v>7.8491</v>
       </c>
       <c r="E54" t="n">
-        <v>4.26458</v>
+        <v>5.46565</v>
       </c>
       <c r="F54" t="n">
-        <v>4.59202</v>
+        <v>5.08201</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.7733</v>
+        <v>4.80447</v>
       </c>
       <c r="C55" t="n">
-        <v>5.54742</v>
+        <v>5.5074</v>
       </c>
       <c r="D55" t="n">
-        <v>8.267939999999999</v>
+        <v>8.084390000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>4.30646</v>
+        <v>5.50358</v>
       </c>
       <c r="F55" t="n">
-        <v>4.66975</v>
+        <v>5.12539</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.78359</v>
+        <v>4.78947</v>
       </c>
       <c r="C56" t="n">
-        <v>5.54089</v>
+        <v>5.50288</v>
       </c>
       <c r="D56" t="n">
-        <v>8.49799</v>
+        <v>8.325570000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>4.32476</v>
+        <v>5.55495</v>
       </c>
       <c r="F56" t="n">
-        <v>4.69202</v>
+        <v>5.1386</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.7848</v>
+        <v>4.81367</v>
       </c>
       <c r="C57" t="n">
-        <v>5.54086</v>
+        <v>5.54021</v>
       </c>
       <c r="D57" t="n">
-        <v>8.78593</v>
+        <v>8.579470000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>4.39093</v>
+        <v>5.58615</v>
       </c>
       <c r="F57" t="n">
-        <v>4.68818</v>
+        <v>5.22629</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.79209</v>
+        <v>4.81437</v>
       </c>
       <c r="C58" t="n">
-        <v>5.59152</v>
+        <v>5.54262</v>
       </c>
       <c r="D58" t="n">
-        <v>9.019019999999999</v>
+        <v>8.84333</v>
       </c>
       <c r="E58" t="n">
-        <v>4.43148</v>
+        <v>5.66923</v>
       </c>
       <c r="F58" t="n">
-        <v>4.80735</v>
+        <v>5.27057</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.82043</v>
+        <v>4.81817</v>
       </c>
       <c r="C59" t="n">
-        <v>5.64187</v>
+        <v>5.57382</v>
       </c>
       <c r="D59" t="n">
-        <v>9.272819999999999</v>
+        <v>9.10449</v>
       </c>
       <c r="E59" t="n">
-        <v>4.46256</v>
+        <v>5.71561</v>
       </c>
       <c r="F59" t="n">
-        <v>4.84356</v>
+        <v>5.3482</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.81542</v>
+        <v>4.84232</v>
       </c>
       <c r="C60" t="n">
-        <v>5.67719</v>
+        <v>5.61594</v>
       </c>
       <c r="D60" t="n">
-        <v>9.5343</v>
+        <v>9.3314</v>
       </c>
       <c r="E60" t="n">
-        <v>4.55734</v>
+        <v>5.79258</v>
       </c>
       <c r="F60" t="n">
-        <v>4.93827</v>
+        <v>5.4498</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.85335</v>
+        <v>4.89883</v>
       </c>
       <c r="C61" t="n">
-        <v>5.74946</v>
+        <v>5.68467</v>
       </c>
       <c r="D61" t="n">
-        <v>9.796720000000001</v>
+        <v>9.617000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>4.67515</v>
+        <v>5.91556</v>
       </c>
       <c r="F61" t="n">
-        <v>5.03483</v>
+        <v>5.57191</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.91712</v>
+        <v>4.91552</v>
       </c>
       <c r="C62" t="n">
-        <v>5.78834</v>
+        <v>5.78148</v>
       </c>
       <c r="D62" t="n">
-        <v>10.0125</v>
+        <v>9.846310000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>4.8403</v>
+        <v>6.08457</v>
       </c>
       <c r="F62" t="n">
-        <v>5.19848</v>
+        <v>5.78057</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.95963</v>
+        <v>4.97298</v>
       </c>
       <c r="C63" t="n">
-        <v>5.85508</v>
+        <v>5.87491</v>
       </c>
       <c r="D63" t="n">
-        <v>10.2609</v>
+        <v>10.0959</v>
       </c>
       <c r="E63" t="n">
-        <v>5.05928</v>
+        <v>6.31373</v>
       </c>
       <c r="F63" t="n">
-        <v>5.42781</v>
+        <v>6.056</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.08537</v>
+        <v>5.08535</v>
       </c>
       <c r="C64" t="n">
-        <v>6.02207</v>
+        <v>6.02072</v>
       </c>
       <c r="D64" t="n">
-        <v>7.35416</v>
+        <v>7.32434</v>
       </c>
       <c r="E64" t="n">
-        <v>4.4312</v>
+        <v>5.547</v>
       </c>
       <c r="F64" t="n">
-        <v>4.69922</v>
+        <v>5.19049</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.22456</v>
+        <v>5.28456</v>
       </c>
       <c r="C65" t="n">
-        <v>5.73697</v>
+        <v>5.72652</v>
       </c>
       <c r="D65" t="n">
-        <v>7.60885</v>
+        <v>7.5362</v>
       </c>
       <c r="E65" t="n">
-        <v>4.46561</v>
+        <v>5.58537</v>
       </c>
       <c r="F65" t="n">
-        <v>4.74425</v>
+        <v>5.22416</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.54518</v>
+        <v>5.59819</v>
       </c>
       <c r="C66" t="n">
-        <v>5.76633</v>
+        <v>5.74078</v>
       </c>
       <c r="D66" t="n">
-        <v>7.85583</v>
+        <v>7.80618</v>
       </c>
       <c r="E66" t="n">
-        <v>4.50616</v>
+        <v>5.60776</v>
       </c>
       <c r="F66" t="n">
-        <v>4.76359</v>
+        <v>5.2577</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.38765</v>
+        <v>5.56111</v>
       </c>
       <c r="C67" t="n">
-        <v>5.80019</v>
+        <v>5.75509</v>
       </c>
       <c r="D67" t="n">
-        <v>8.113099999999999</v>
+        <v>8.056900000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>4.5318</v>
+        <v>5.63817</v>
       </c>
       <c r="F67" t="n">
-        <v>4.84402</v>
+        <v>5.31078</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.37472</v>
+        <v>5.56891</v>
       </c>
       <c r="C68" t="n">
-        <v>5.7986</v>
+        <v>5.77577</v>
       </c>
       <c r="D68" t="n">
-        <v>8.45997</v>
+        <v>8.35514</v>
       </c>
       <c r="E68" t="n">
-        <v>4.54646</v>
+        <v>5.67263</v>
       </c>
       <c r="F68" t="n">
-        <v>4.94887</v>
+        <v>5.36354</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.38851</v>
+        <v>5.59813</v>
       </c>
       <c r="C69" t="n">
-        <v>5.78182</v>
+        <v>5.82727</v>
       </c>
       <c r="D69" t="n">
-        <v>8.74363</v>
+        <v>8.64888</v>
       </c>
       <c r="E69" t="n">
-        <v>4.59768</v>
+        <v>5.69864</v>
       </c>
       <c r="F69" t="n">
-        <v>4.91935</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.39472</v>
+        <v>5.58983</v>
       </c>
       <c r="C70" t="n">
-        <v>5.82788</v>
+        <v>5.85431</v>
       </c>
       <c r="D70" t="n">
-        <v>8.9876</v>
+        <v>8.924720000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>4.63741</v>
+        <v>5.73945</v>
       </c>
       <c r="F70" t="n">
-        <v>5.18275</v>
+        <v>5.51995</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.39216</v>
+        <v>5.59083</v>
       </c>
       <c r="C71" t="n">
-        <v>5.83242</v>
+        <v>5.84194</v>
       </c>
       <c r="D71" t="n">
-        <v>9.28181</v>
+        <v>9.230700000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>4.67546</v>
+        <v>5.79809</v>
       </c>
       <c r="F71" t="n">
-        <v>5.33788</v>
+        <v>5.8919</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.40275</v>
+        <v>5.601</v>
       </c>
       <c r="C72" t="n">
-        <v>5.87332</v>
+        <v>5.88457</v>
       </c>
       <c r="D72" t="n">
-        <v>9.645799999999999</v>
+        <v>9.56996</v>
       </c>
       <c r="E72" t="n">
-        <v>4.73089</v>
+        <v>5.86497</v>
       </c>
       <c r="F72" t="n">
-        <v>5.80227</v>
+        <v>6.67848</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.40989</v>
+        <v>5.6574</v>
       </c>
       <c r="C73" t="n">
-        <v>5.8985</v>
+        <v>5.91628</v>
       </c>
       <c r="D73" t="n">
-        <v>10.4658</v>
+        <v>10.1582</v>
       </c>
       <c r="E73" t="n">
-        <v>4.79124</v>
+        <v>5.9318</v>
       </c>
       <c r="F73" t="n">
-        <v>6.4111</v>
+        <v>7.03558</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.45045</v>
+        <v>5.61534</v>
       </c>
       <c r="C74" t="n">
-        <v>5.99716</v>
+        <v>5.91748</v>
       </c>
       <c r="D74" t="n">
-        <v>10.5615</v>
+        <v>10.4737</v>
       </c>
       <c r="E74" t="n">
-        <v>4.87374</v>
+        <v>6.02585</v>
       </c>
       <c r="F74" t="n">
-        <v>7.20332</v>
+        <v>7.8532</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.48406</v>
+        <v>5.65092</v>
       </c>
       <c r="C75" t="n">
-        <v>6.03618</v>
+        <v>5.99691</v>
       </c>
       <c r="D75" t="n">
-        <v>11.1879</v>
+        <v>11.4297</v>
       </c>
       <c r="E75" t="n">
-        <v>4.94869</v>
+        <v>6.13429</v>
       </c>
       <c r="F75" t="n">
-        <v>7.85555</v>
+        <v>8.671189999999999</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.499</v>
+        <v>5.67342</v>
       </c>
       <c r="C76" t="n">
-        <v>6.08531</v>
+        <v>6.07655</v>
       </c>
       <c r="D76" t="n">
-        <v>12.0887</v>
+        <v>11.8788</v>
       </c>
       <c r="E76" t="n">
-        <v>5.13156</v>
+        <v>6.30839</v>
       </c>
       <c r="F76" t="n">
-        <v>8.67384</v>
+        <v>9.454639999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.56247</v>
+        <v>5.75082</v>
       </c>
       <c r="C77" t="n">
-        <v>6.17549</v>
+        <v>6.16393</v>
       </c>
       <c r="D77" t="n">
-        <v>12.8832</v>
+        <v>12.8373</v>
       </c>
       <c r="E77" t="n">
-        <v>5.3269</v>
+        <v>6.50211</v>
       </c>
       <c r="F77" t="n">
-        <v>9.243779999999999</v>
+        <v>10.2226</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.67988</v>
+        <v>5.82752</v>
       </c>
       <c r="C78" t="n">
-        <v>6.38699</v>
+        <v>6.30837</v>
       </c>
       <c r="D78" t="n">
-        <v>14.821</v>
+        <v>14.9708</v>
       </c>
       <c r="E78" t="n">
-        <v>5.4933</v>
+        <v>8.81264</v>
       </c>
       <c r="F78" t="n">
-        <v>10.5594</v>
+        <v>11.5227</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>5.84497</v>
+        <v>5.99142</v>
       </c>
       <c r="C79" t="n">
-        <v>13.3792</v>
+        <v>13.2451</v>
       </c>
       <c r="D79" t="n">
-        <v>15.6575</v>
+        <v>15.6417</v>
       </c>
       <c r="E79" t="n">
-        <v>5.66924</v>
+        <v>8.75367</v>
       </c>
       <c r="F79" t="n">
-        <v>10.7427</v>
+        <v>11.7595</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.10148</v>
+        <v>6.16509</v>
       </c>
       <c r="C80" t="n">
-        <v>13.4563</v>
+        <v>13.4781</v>
       </c>
       <c r="D80" t="n">
-        <v>16.3795</v>
+        <v>16.3514</v>
       </c>
       <c r="E80" t="n">
-        <v>5.82598</v>
+        <v>8.77055</v>
       </c>
       <c r="F80" t="n">
-        <v>10.7491</v>
+        <v>11.7136</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>14.4396</v>
+        <v>13.6387</v>
       </c>
       <c r="C81" t="n">
-        <v>13.9113</v>
+        <v>13.7165</v>
       </c>
       <c r="D81" t="n">
-        <v>17.2175</v>
+        <v>17.008</v>
       </c>
       <c r="E81" t="n">
-        <v>6.20276</v>
+        <v>8.62832</v>
       </c>
       <c r="F81" t="n">
-        <v>10.9465</v>
+        <v>11.9179</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.8214</v>
+        <v>13.7291</v>
       </c>
       <c r="C82" t="n">
-        <v>13.7342</v>
+        <v>13.6594</v>
       </c>
       <c r="D82" t="n">
-        <v>17.9512</v>
+        <v>17.7779</v>
       </c>
       <c r="E82" t="n">
-        <v>6.27162</v>
+        <v>8.87804</v>
       </c>
       <c r="F82" t="n">
-        <v>10.937</v>
+        <v>11.9732</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.6352</v>
+        <v>13.78</v>
       </c>
       <c r="C83" t="n">
-        <v>13.7619</v>
+        <v>14.0143</v>
       </c>
       <c r="D83" t="n">
-        <v>18.6093</v>
+        <v>18.53</v>
       </c>
       <c r="E83" t="n">
-        <v>6.28795</v>
+        <v>8.93698</v>
       </c>
       <c r="F83" t="n">
-        <v>11.0555</v>
+        <v>12.0955</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.8944</v>
+        <v>13.8216</v>
       </c>
       <c r="C84" t="n">
-        <v>13.6815</v>
+        <v>13.897</v>
       </c>
       <c r="D84" t="n">
-        <v>19.3169</v>
+        <v>19.1772</v>
       </c>
       <c r="E84" t="n">
-        <v>6.48025</v>
+        <v>9.275080000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>11.0389</v>
+        <v>12.1614</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.9187</v>
+        <v>13.9887</v>
       </c>
       <c r="C85" t="n">
-        <v>14.0681</v>
+        <v>13.9165</v>
       </c>
       <c r="D85" t="n">
-        <v>20.0264</v>
+        <v>19.8749</v>
       </c>
       <c r="E85" t="n">
-        <v>6.61521</v>
+        <v>8.985810000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>11.2209</v>
+        <v>12.2109</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>14.0874</v>
+        <v>14.0313</v>
       </c>
       <c r="C86" t="n">
-        <v>14.1432</v>
+        <v>14.1823</v>
       </c>
       <c r="D86" t="n">
-        <v>20.6617</v>
+        <v>20.548</v>
       </c>
       <c r="E86" t="n">
-        <v>6.89663</v>
+        <v>9.28129</v>
       </c>
       <c r="F86" t="n">
-        <v>11.323</v>
+        <v>12.3415</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.1301</v>
+        <v>14.155</v>
       </c>
       <c r="C87" t="n">
-        <v>14.1127</v>
+        <v>14.1645</v>
       </c>
       <c r="D87" t="n">
-        <v>21.3045</v>
+        <v>21.2062</v>
       </c>
       <c r="E87" t="n">
-        <v>6.96124</v>
+        <v>9.24127</v>
       </c>
       <c r="F87" t="n">
-        <v>11.4378</v>
+        <v>12.5156</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.2812</v>
+        <v>14.1911</v>
       </c>
       <c r="C88" t="n">
-        <v>13.9389</v>
+        <v>14.1068</v>
       </c>
       <c r="D88" t="n">
-        <v>21.9135</v>
+        <v>21.86</v>
       </c>
       <c r="E88" t="n">
-        <v>7.33992</v>
+        <v>9.083920000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>11.5334</v>
+        <v>12.6014</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.1847</v>
+        <v>14.3142</v>
       </c>
       <c r="C89" t="n">
-        <v>14.1551</v>
+        <v>14.2644</v>
       </c>
       <c r="D89" t="n">
-        <v>22.5541</v>
+        <v>22.5144</v>
       </c>
       <c r="E89" t="n">
-        <v>7.31961</v>
+        <v>9.47955</v>
       </c>
       <c r="F89" t="n">
-        <v>11.7424</v>
+        <v>12.7442</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.3297</v>
+        <v>14.2799</v>
       </c>
       <c r="C90" t="n">
-        <v>14.1376</v>
+        <v>14.2235</v>
       </c>
       <c r="D90" t="n">
-        <v>23.3217</v>
+        <v>23.2168</v>
       </c>
       <c r="E90" t="n">
-        <v>7.56489</v>
+        <v>9.47409</v>
       </c>
       <c r="F90" t="n">
-        <v>11.9369</v>
+        <v>13.0101</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3545</v>
+        <v>14.375</v>
       </c>
       <c r="C91" t="n">
-        <v>14.3102</v>
+        <v>14.3647</v>
       </c>
       <c r="D91" t="n">
-        <v>24.1228</v>
+        <v>23.9121</v>
       </c>
       <c r="E91" t="n">
-        <v>7.71245</v>
+        <v>9.701549999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>12.2356</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.5067</v>
+        <v>14.4832</v>
       </c>
       <c r="C92" t="n">
-        <v>14.1645</v>
+        <v>14.3953</v>
       </c>
       <c r="D92" t="n">
-        <v>24.1217</v>
+        <v>24.0284</v>
       </c>
       <c r="E92" t="n">
-        <v>14.8038</v>
+        <v>21.2458</v>
       </c>
       <c r="F92" t="n">
-        <v>17.5784</v>
+        <v>19.8292</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5909</v>
+        <v>14.5252</v>
       </c>
       <c r="C93" t="n">
-        <v>14.3372</v>
+        <v>14.3672</v>
       </c>
       <c r="D93" t="n">
-        <v>24.6109</v>
+        <v>24.4187</v>
       </c>
       <c r="E93" t="n">
-        <v>14.9627</v>
+        <v>21.4121</v>
       </c>
       <c r="F93" t="n">
-        <v>17.5833</v>
+        <v>19.9556</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.7079</v>
+        <v>14.723</v>
       </c>
       <c r="C94" t="n">
-        <v>23.0653</v>
+        <v>22.944</v>
       </c>
       <c r="D94" t="n">
-        <v>25.0747</v>
+        <v>24.9992</v>
       </c>
       <c r="E94" t="n">
-        <v>15.0844</v>
+        <v>21.3955</v>
       </c>
       <c r="F94" t="n">
-        <v>17.6301</v>
+        <v>20.1531</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.8778</v>
+        <v>20.9163</v>
       </c>
       <c r="C95" t="n">
-        <v>22.9438</v>
+        <v>23.0474</v>
       </c>
       <c r="D95" t="n">
-        <v>25.5498</v>
+        <v>25.439</v>
       </c>
       <c r="E95" t="n">
-        <v>15.1439</v>
+        <v>21.5806</v>
       </c>
       <c r="F95" t="n">
-        <v>17.6845</v>
+        <v>20.0989</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.881</v>
+        <v>20.8538</v>
       </c>
       <c r="C96" t="n">
-        <v>23.0077</v>
+        <v>23.1033</v>
       </c>
       <c r="D96" t="n">
-        <v>26.0636</v>
+        <v>25.992</v>
       </c>
       <c r="E96" t="n">
-        <v>15.3747</v>
+        <v>21.658</v>
       </c>
       <c r="F96" t="n">
-        <v>17.8103</v>
+        <v>20.1926</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.9262</v>
+        <v>20.912</v>
       </c>
       <c r="C97" t="n">
-        <v>23.0921</v>
+        <v>23.1449</v>
       </c>
       <c r="D97" t="n">
-        <v>26.6084</v>
+        <v>26.5787</v>
       </c>
       <c r="E97" t="n">
-        <v>15.4966</v>
+        <v>21.7735</v>
       </c>
       <c r="F97" t="n">
-        <v>17.9022</v>
+        <v>20.2284</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.9839</v>
+        <v>20.9562</v>
       </c>
       <c r="C98" t="n">
-        <v>23.1038</v>
+        <v>23.0838</v>
       </c>
       <c r="D98" t="n">
-        <v>27.1983</v>
+        <v>27.0914</v>
       </c>
       <c r="E98" t="n">
-        <v>15.6639</v>
+        <v>21.8496</v>
       </c>
       <c r="F98" t="n">
-        <v>18.0204</v>
+        <v>20.459</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>20.9586</v>
+        <v>21.02</v>
       </c>
       <c r="C99" t="n">
-        <v>23.1166</v>
+        <v>23.1926</v>
       </c>
       <c r="D99" t="n">
-        <v>27.8828</v>
+        <v>27.6577</v>
       </c>
       <c r="E99" t="n">
-        <v>15.8156</v>
+        <v>22.0847</v>
       </c>
       <c r="F99" t="n">
-        <v>18.0628</v>
+        <v>20.4766</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>20.9984</v>
+        <v>20.9761</v>
       </c>
       <c r="C100" t="n">
-        <v>23.1467</v>
+        <v>23.1331</v>
       </c>
       <c r="D100" t="n">
-        <v>28.579</v>
+        <v>28.3458</v>
       </c>
       <c r="E100" t="n">
-        <v>15.9514</v>
+        <v>22.1673</v>
       </c>
       <c r="F100" t="n">
-        <v>18.1908</v>
+        <v>20.5069</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9846</v>
+        <v>20.9933</v>
       </c>
       <c r="C101" t="n">
-        <v>23.1894</v>
+        <v>23.1941</v>
       </c>
       <c r="D101" t="n">
-        <v>29.1542</v>
+        <v>29.0628</v>
       </c>
       <c r="E101" t="n">
-        <v>16.0636</v>
+        <v>22.2758</v>
       </c>
       <c r="F101" t="n">
-        <v>18.319</v>
+        <v>20.6862</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.0423</v>
+        <v>21.0239</v>
       </c>
       <c r="C102" t="n">
-        <v>23.2759</v>
+        <v>23.2199</v>
       </c>
       <c r="D102" t="n">
-        <v>29.9634</v>
+        <v>29.6576</v>
       </c>
       <c r="E102" t="n">
-        <v>16.237</v>
+        <v>22.4211</v>
       </c>
       <c r="F102" t="n">
-        <v>18.4783</v>
+        <v>20.8383</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.0371</v>
+        <v>21.0838</v>
       </c>
       <c r="C103" t="n">
-        <v>23.2628</v>
+        <v>23.3415</v>
       </c>
       <c r="D103" t="n">
-        <v>30.7185</v>
+        <v>30.3977</v>
       </c>
       <c r="E103" t="n">
-        <v>16.4253</v>
+        <v>22.6637</v>
       </c>
       <c r="F103" t="n">
-        <v>18.6254</v>
+        <v>21.0429</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.0499</v>
+        <v>21.1399</v>
       </c>
       <c r="C104" t="n">
-        <v>23.2724</v>
+        <v>23.4109</v>
       </c>
       <c r="D104" t="n">
-        <v>31.4027</v>
+        <v>31.1771</v>
       </c>
       <c r="E104" t="n">
-        <v>16.6132</v>
+        <v>22.8676</v>
       </c>
       <c r="F104" t="n">
-        <v>18.8156</v>
+        <v>21.1946</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.0457</v>
+        <v>21.0853</v>
       </c>
       <c r="C105" t="n">
-        <v>23.3367</v>
+        <v>23.3843</v>
       </c>
       <c r="D105" t="n">
-        <v>32.1815</v>
+        <v>32.0336</v>
       </c>
       <c r="E105" t="n">
-        <v>16.8259</v>
+        <v>23.0832</v>
       </c>
       <c r="F105" t="n">
-        <v>19.0679</v>
+        <v>21.3764</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.186</v>
+        <v>21.183</v>
       </c>
       <c r="C106" t="n">
-        <v>23.5783</v>
+        <v>23.5829</v>
       </c>
       <c r="D106" t="n">
-        <v>33.075</v>
+        <v>32.8382</v>
       </c>
       <c r="E106" t="n">
-        <v>17.0596</v>
+        <v>23.4019</v>
       </c>
       <c r="F106" t="n">
-        <v>19.4095</v>
+        <v>21.7114</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.2805</v>
+        <v>21.3186</v>
       </c>
       <c r="C107" t="n">
-        <v>23.596</v>
+        <v>23.7042</v>
       </c>
       <c r="D107" t="n">
-        <v>28.8538</v>
+        <v>28.7974</v>
       </c>
       <c r="E107" t="n">
-        <v>19.8508</v>
+        <v>26.5352</v>
       </c>
       <c r="F107" t="n">
-        <v>22.3826</v>
+        <v>25.7303</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.3957</v>
+        <v>21.4779</v>
       </c>
       <c r="C108" t="n">
-        <v>27.104</v>
+        <v>27.151</v>
       </c>
       <c r="D108" t="n">
-        <v>29.2396</v>
+        <v>29.1922</v>
       </c>
       <c r="E108" t="n">
-        <v>19.9756</v>
+        <v>26.6731</v>
       </c>
       <c r="F108" t="n">
-        <v>22.3518</v>
+        <v>25.9029</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.7416</v>
+        <v>21.82</v>
       </c>
       <c r="C109" t="n">
-        <v>27.2001</v>
+        <v>27.2745</v>
       </c>
       <c r="D109" t="n">
-        <v>29.865</v>
+        <v>29.7309</v>
       </c>
       <c r="E109" t="n">
-        <v>20.1072</v>
+        <v>26.8545</v>
       </c>
       <c r="F109" t="n">
-        <v>22.5201</v>
+        <v>25.9613</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.3758</v>
+        <v>23.4699</v>
       </c>
       <c r="C110" t="n">
-        <v>27.1697</v>
+        <v>27.2655</v>
       </c>
       <c r="D110" t="n">
-        <v>30.2389</v>
+        <v>30.1757</v>
       </c>
       <c r="E110" t="n">
-        <v>20.2891</v>
+        <v>26.9383</v>
       </c>
       <c r="F110" t="n">
-        <v>22.7328</v>
+        <v>26.2009</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.5116</v>
+        <v>23.4861</v>
       </c>
       <c r="C111" t="n">
-        <v>27.2266</v>
+        <v>27.3144</v>
       </c>
       <c r="D111" t="n">
-        <v>30.942</v>
+        <v>30.687</v>
       </c>
       <c r="E111" t="n">
-        <v>20.4619</v>
+        <v>27.1641</v>
       </c>
       <c r="F111" t="n">
-        <v>22.7377</v>
+        <v>26.3048</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.4381</v>
+        <v>23.5373</v>
       </c>
       <c r="C112" t="n">
-        <v>27.273</v>
+        <v>27.2916</v>
       </c>
       <c r="D112" t="n">
-        <v>31.4142</v>
+        <v>31.4246</v>
       </c>
       <c r="E112" t="n">
-        <v>20.5629</v>
+        <v>27.2904</v>
       </c>
       <c r="F112" t="n">
-        <v>22.8673</v>
+        <v>26.3881</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.4728</v>
+        <v>23.4852</v>
       </c>
       <c r="C113" t="n">
-        <v>27.2169</v>
+        <v>27.3404</v>
       </c>
       <c r="D113" t="n">
-        <v>32.1145</v>
+        <v>31.9648</v>
       </c>
       <c r="E113" t="n">
-        <v>20.7768</v>
+        <v>27.4596</v>
       </c>
       <c r="F113" t="n">
-        <v>23.1294</v>
+        <v>26.6021</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.3904</v>
+        <v>23.5872</v>
       </c>
       <c r="C114" t="n">
-        <v>27.2531</v>
+        <v>27.4675</v>
       </c>
       <c r="D114" t="n">
-        <v>32.632</v>
+        <v>32.6907</v>
       </c>
       <c r="E114" t="n">
-        <v>20.8628</v>
+        <v>27.6058</v>
       </c>
       <c r="F114" t="n">
-        <v>23.2116</v>
+        <v>26.7692</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.4062</v>
+        <v>23.6375</v>
       </c>
       <c r="C115" t="n">
-        <v>27.4829</v>
+        <v>27.4837</v>
       </c>
       <c r="D115" t="n">
-        <v>33.4697</v>
+        <v>33.3957</v>
       </c>
       <c r="E115" t="n">
-        <v>21.0171</v>
+        <v>27.7011</v>
       </c>
       <c r="F115" t="n">
-        <v>23.4111</v>
+        <v>26.876</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.5389</v>
+        <v>23.6884</v>
       </c>
       <c r="C116" t="n">
-        <v>27.4383</v>
+        <v>27.6665</v>
       </c>
       <c r="D116" t="n">
-        <v>34.0349</v>
+        <v>34.0178</v>
       </c>
       <c r="E116" t="n">
-        <v>21.1842</v>
+        <v>27.974</v>
       </c>
       <c r="F116" t="n">
-        <v>23.7342</v>
+        <v>27.2173</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.5703</v>
+        <v>23.6843</v>
       </c>
       <c r="C117" t="n">
-        <v>27.6767</v>
+        <v>27.594</v>
       </c>
       <c r="D117" t="n">
-        <v>34.8836</v>
+        <v>34.9095</v>
       </c>
       <c r="E117" t="n">
-        <v>21.5063</v>
+        <v>28.1358</v>
       </c>
       <c r="F117" t="n">
-        <v>23.8819</v>
+        <v>27.3471</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.6432</v>
+        <v>23.7211</v>
       </c>
       <c r="C118" t="n">
-        <v>27.7255</v>
+        <v>27.7753</v>
       </c>
       <c r="D118" t="n">
-        <v>35.6572</v>
+        <v>35.4699</v>
       </c>
       <c r="E118" t="n">
-        <v>21.7419</v>
+        <v>28.364</v>
       </c>
       <c r="F118" t="n">
-        <v>24.1615</v>
+        <v>27.7448</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.6125</v>
+        <v>23.7745</v>
       </c>
       <c r="C119" t="n">
-        <v>27.8801</v>
+        <v>27.8136</v>
       </c>
       <c r="D119" t="n">
-        <v>36.5873</v>
+        <v>36.283</v>
       </c>
       <c r="E119" t="n">
-        <v>22.0096</v>
+        <v>28.6588</v>
       </c>
       <c r="F119" t="n">
-        <v>24.5633</v>
+        <v>27.9692</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.7888</v>
+        <v>23.8211</v>
       </c>
       <c r="C120" t="n">
-        <v>28.0859</v>
+        <v>28.059</v>
       </c>
       <c r="D120" t="n">
-        <v>37.3888</v>
+        <v>37.285</v>
       </c>
       <c r="E120" t="n">
-        <v>22.2239</v>
+        <v>29.2096</v>
       </c>
       <c r="F120" t="n">
-        <v>25.0599</v>
+        <v>28.6732</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.899</v>
+        <v>23.9702</v>
       </c>
       <c r="C121" t="n">
-        <v>28.1754</v>
+        <v>28.2249</v>
       </c>
       <c r="D121" t="n">
-        <v>31.5602</v>
+        <v>31.4786</v>
       </c>
       <c r="E121" t="n">
-        <v>22.6886</v>
+        <v>29.3453</v>
       </c>
       <c r="F121" t="n">
-        <v>26.0937</v>
+        <v>29.8504</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>24.1039</v>
+        <v>24.1509</v>
       </c>
       <c r="C122" t="n">
-        <v>29.8279</v>
+        <v>29.829</v>
       </c>
       <c r="D122" t="n">
-        <v>31.9551</v>
+        <v>31.8715</v>
       </c>
       <c r="E122" t="n">
-        <v>22.8675</v>
+        <v>29.4706</v>
       </c>
       <c r="F122" t="n">
-        <v>26.309</v>
+        <v>30.0815</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.4296</v>
+        <v>24.4422</v>
       </c>
       <c r="C123" t="n">
-        <v>30.01</v>
+        <v>29.861</v>
       </c>
       <c r="D123" t="n">
-        <v>32.5763</v>
+        <v>32.4391</v>
       </c>
       <c r="E123" t="n">
-        <v>23.0888</v>
+        <v>29.5609</v>
       </c>
       <c r="F123" t="n">
-        <v>26.3611</v>
+        <v>30.1729</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>29.7153</v>
+        <v>29.8361</v>
       </c>
       <c r="C124" t="n">
-        <v>29.8831</v>
+        <v>29.954</v>
       </c>
       <c r="D124" t="n">
-        <v>32.9671</v>
+        <v>32.8657</v>
       </c>
       <c r="E124" t="n">
-        <v>23.2735</v>
+        <v>29.7341</v>
       </c>
       <c r="F124" t="n">
-        <v>26.6356</v>
+        <v>30.4913</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>29.8195</v>
+        <v>29.833</v>
       </c>
       <c r="C125" t="n">
-        <v>30.0213</v>
+        <v>29.8364</v>
       </c>
       <c r="D125" t="n">
-        <v>33.7077</v>
+        <v>33.4487</v>
       </c>
       <c r="E125" t="n">
-        <v>23.3231</v>
+        <v>29.8601</v>
       </c>
       <c r="F125" t="n">
-        <v>26.7142</v>
+        <v>30.385</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>29.8419</v>
+        <v>29.9229</v>
       </c>
       <c r="C126" t="n">
-        <v>30.1273</v>
+        <v>30.0132</v>
       </c>
       <c r="D126" t="n">
-        <v>34.1782</v>
+        <v>33.9863</v>
       </c>
       <c r="E126" t="n">
-        <v>23.5829</v>
+        <v>30.287</v>
       </c>
       <c r="F126" t="n">
-        <v>26.9382</v>
+        <v>30.7021</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>29.7891</v>
+        <v>29.7746</v>
       </c>
       <c r="C127" t="n">
-        <v>30.2645</v>
+        <v>30.1694</v>
       </c>
       <c r="D127" t="n">
-        <v>34.8688</v>
+        <v>34.5806</v>
       </c>
       <c r="E127" t="n">
-        <v>23.7769</v>
+        <v>30.1314</v>
       </c>
       <c r="F127" t="n">
-        <v>27.0329</v>
+        <v>30.8662</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.7368</v>
+        <v>29.8125</v>
       </c>
       <c r="C128" t="n">
-        <v>30.3497</v>
+        <v>30.1354</v>
       </c>
       <c r="D128" t="n">
-        <v>35.5199</v>
+        <v>35.3014</v>
       </c>
       <c r="E128" t="n">
-        <v>23.8506</v>
+        <v>30.281</v>
       </c>
       <c r="F128" t="n">
-        <v>27.1376</v>
+        <v>31.0545</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>29.7393</v>
+        <v>29.8116</v>
       </c>
       <c r="C129" t="n">
-        <v>30.6602</v>
+        <v>30.4383</v>
       </c>
       <c r="D129" t="n">
-        <v>36.1111</v>
+        <v>36.0438</v>
       </c>
       <c r="E129" t="n">
-        <v>24.0661</v>
+        <v>30.5406</v>
       </c>
       <c r="F129" t="n">
-        <v>27.4486</v>
+        <v>31.2804</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>29.7682</v>
+        <v>29.8131</v>
       </c>
       <c r="C130" t="n">
-        <v>30.5673</v>
+        <v>30.5261</v>
       </c>
       <c r="D130" t="n">
-        <v>36.9593</v>
+        <v>36.6006</v>
       </c>
       <c r="E130" t="n">
-        <v>24.2707</v>
+        <v>30.7092</v>
       </c>
       <c r="F130" t="n">
-        <v>27.8158</v>
+        <v>31.6274</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.8978</v>
+        <v>29.8395</v>
       </c>
       <c r="C131" t="n">
-        <v>30.8269</v>
+        <v>30.6073</v>
       </c>
       <c r="D131" t="n">
-        <v>37.5351</v>
+        <v>37.4343</v>
       </c>
       <c r="E131" t="n">
-        <v>24.4714</v>
+        <v>30.9594</v>
       </c>
       <c r="F131" t="n">
-        <v>28.0028</v>
+        <v>31.8941</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.9017</v>
+        <v>29.9452</v>
       </c>
       <c r="C132" t="n">
-        <v>30.9848</v>
+        <v>30.8768</v>
       </c>
       <c r="D132" t="n">
-        <v>38.426</v>
+        <v>38.1728</v>
       </c>
       <c r="E132" t="n">
-        <v>24.7002</v>
+        <v>31.3662</v>
       </c>
       <c r="F132" t="n">
-        <v>28.387</v>
+        <v>32.0929</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>29.8698</v>
+        <v>29.9789</v>
       </c>
       <c r="C133" t="n">
-        <v>31.1216</v>
+        <v>31.0605</v>
       </c>
       <c r="D133" t="n">
-        <v>39.3048</v>
+        <v>39.1076</v>
       </c>
       <c r="E133" t="n">
-        <v>25.0504</v>
+        <v>31.6284</v>
       </c>
       <c r="F133" t="n">
-        <v>28.8241</v>
+        <v>32.5257</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>29.9543</v>
+        <v>30.021</v>
       </c>
       <c r="C134" t="n">
-        <v>31.5101</v>
+        <v>31.3069</v>
       </c>
       <c r="D134" t="n">
-        <v>40.0118</v>
+        <v>39.9813</v>
       </c>
       <c r="E134" t="n">
-        <v>25.4909</v>
+        <v>32.1141</v>
       </c>
       <c r="F134" t="n">
-        <v>29.2899</v>
+        <v>33.4349</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>30.0937</v>
+        <v>30.0003</v>
       </c>
       <c r="C135" t="n">
-        <v>31.7471</v>
+        <v>31.6</v>
       </c>
       <c r="D135" t="n">
-        <v>33.2145</v>
+        <v>33.333</v>
       </c>
       <c r="E135" t="n">
-        <v>25.5362</v>
+        <v>31.6972</v>
       </c>
       <c r="F135" t="n">
-        <v>28.5333</v>
+        <v>32.5662</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.1585</v>
+        <v>30.1927</v>
       </c>
       <c r="C136" t="n">
-        <v>31.9553</v>
+        <v>31.5224</v>
       </c>
       <c r="D136" t="n">
-        <v>33.7917</v>
+        <v>33.6627</v>
       </c>
       <c r="E136" t="n">
-        <v>25.3439</v>
+        <v>32.6108</v>
       </c>
       <c r="F136" t="n">
-        <v>28.8858</v>
+        <v>32.7805</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.4773</v>
+        <v>30.464</v>
       </c>
       <c r="C137" t="n">
-        <v>31.8303</v>
+        <v>31.7171</v>
       </c>
       <c r="D137" t="n">
-        <v>34.2308</v>
+        <v>33.984</v>
       </c>
       <c r="E137" t="n">
-        <v>25.6936</v>
+        <v>32.3443</v>
       </c>
       <c r="F137" t="n">
-        <v>29.0439</v>
+        <v>32.5951</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>35.3425</v>
+        <v>35.2074</v>
       </c>
       <c r="C138" t="n">
-        <v>31.8697</v>
+        <v>31.6697</v>
       </c>
       <c r="D138" t="n">
-        <v>34.9212</v>
+        <v>34.6308</v>
       </c>
       <c r="E138" t="n">
-        <v>25.8401</v>
+        <v>32.8597</v>
       </c>
       <c r="F138" t="n">
-        <v>29.0873</v>
+        <v>32.866</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.2515</v>
+        <v>35.2579</v>
       </c>
       <c r="C139" t="n">
-        <v>31.9356</v>
+        <v>31.6435</v>
       </c>
       <c r="D139" t="n">
-        <v>35.4314</v>
+        <v>35.1535</v>
       </c>
       <c r="E139" t="n">
-        <v>26.0718</v>
+        <v>32.4787</v>
       </c>
       <c r="F139" t="n">
-        <v>29.3997</v>
+        <v>32.8985</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>35.2916</v>
+        <v>35.2519</v>
       </c>
       <c r="C140" t="n">
-        <v>32.2154</v>
+        <v>32.2366</v>
       </c>
       <c r="D140" t="n">
-        <v>35.979</v>
+        <v>35.7204</v>
       </c>
       <c r="E140" t="n">
-        <v>26.4176</v>
+        <v>32.6527</v>
       </c>
       <c r="F140" t="n">
-        <v>29.4155</v>
+        <v>33.2528</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.3774</v>
+        <v>35.229</v>
       </c>
       <c r="C141" t="n">
-        <v>32.18</v>
+        <v>32.1337</v>
       </c>
       <c r="D141" t="n">
-        <v>36.6169</v>
+        <v>36.2314</v>
       </c>
       <c r="E141" t="n">
-        <v>26.412</v>
+        <v>32.9681</v>
       </c>
       <c r="F141" t="n">
-        <v>29.624</v>
+        <v>33.4606</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>35.4676</v>
+        <v>35.3934</v>
       </c>
       <c r="C142" t="n">
-        <v>32.4726</v>
+        <v>32.2602</v>
       </c>
       <c r="D142" t="n">
-        <v>37.2453</v>
+        <v>36.9735</v>
       </c>
       <c r="E142" t="n">
-        <v>26.3683</v>
+        <v>32.916</v>
       </c>
       <c r="F142" t="n">
-        <v>29.8731</v>
+        <v>33.7207</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>35.3116</v>
+        <v>35.1228</v>
       </c>
       <c r="C143" t="n">
-        <v>32.612</v>
+        <v>32.3329</v>
       </c>
       <c r="D143" t="n">
-        <v>37.8696</v>
+        <v>37.6111</v>
       </c>
       <c r="E143" t="n">
-        <v>26.7283</v>
+        <v>33.4008</v>
       </c>
       <c r="F143" t="n">
-        <v>29.8382</v>
+        <v>33.8165</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.79628</v>
+        <v>2.77701</v>
       </c>
       <c r="C2" t="n">
-        <v>4.48201</v>
+        <v>4.47683</v>
       </c>
       <c r="D2" t="n">
-        <v>5.38938</v>
+        <v>5.43047</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89993</v>
+        <v>3.28677</v>
       </c>
       <c r="F2" t="n">
-        <v>3.93303</v>
+        <v>3.64678</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.79316</v>
+        <v>2.78839</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5052</v>
+        <v>4.49035</v>
       </c>
       <c r="D3" t="n">
-        <v>5.62191</v>
+        <v>5.68804</v>
       </c>
       <c r="E3" t="n">
-        <v>3.91872</v>
+        <v>3.29727</v>
       </c>
       <c r="F3" t="n">
-        <v>3.92377</v>
+        <v>3.66616</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.81903</v>
+        <v>2.82196</v>
       </c>
       <c r="C4" t="n">
-        <v>4.53462</v>
+        <v>4.50833</v>
       </c>
       <c r="D4" t="n">
-        <v>6.06935</v>
+        <v>6.14074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.96303</v>
+        <v>3.32607</v>
       </c>
       <c r="F4" t="n">
-        <v>4.01356</v>
+        <v>3.67717</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.84315</v>
+        <v>2.85718</v>
       </c>
       <c r="C5" t="n">
-        <v>4.57105</v>
+        <v>4.5478</v>
       </c>
       <c r="D5" t="n">
-        <v>6.41982</v>
+        <v>6.35681</v>
       </c>
       <c r="E5" t="n">
-        <v>4.01403</v>
+        <v>3.34039</v>
       </c>
       <c r="F5" t="n">
-        <v>4.01266</v>
+        <v>3.69037</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.89094</v>
+        <v>2.85582</v>
       </c>
       <c r="C6" t="n">
-        <v>4.632</v>
+        <v>4.59029</v>
       </c>
       <c r="D6" t="n">
-        <v>6.72705</v>
+        <v>6.77867</v>
       </c>
       <c r="E6" t="n">
-        <v>4.06327</v>
+        <v>3.38421</v>
       </c>
       <c r="F6" t="n">
-        <v>4.08701</v>
+        <v>3.74891</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.92253</v>
+        <v>2.89672</v>
       </c>
       <c r="C7" t="n">
-        <v>4.68063</v>
+        <v>4.66774</v>
       </c>
       <c r="D7" t="n">
-        <v>5.05087</v>
+        <v>5.10464</v>
       </c>
       <c r="E7" t="n">
-        <v>3.81042</v>
+        <v>3.28933</v>
       </c>
       <c r="F7" t="n">
-        <v>3.97481</v>
+        <v>3.66606</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.95763</v>
+        <v>2.9228</v>
       </c>
       <c r="C8" t="n">
-        <v>4.55342</v>
+        <v>4.5348</v>
       </c>
       <c r="D8" t="n">
-        <v>5.21702</v>
+        <v>5.23619</v>
       </c>
       <c r="E8" t="n">
-        <v>3.83185</v>
+        <v>3.30997</v>
       </c>
       <c r="F8" t="n">
-        <v>3.98448</v>
+        <v>3.68343</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>2.97767</v>
+        <v>2.98609</v>
       </c>
       <c r="C9" t="n">
-        <v>4.55121</v>
+        <v>4.55692</v>
       </c>
       <c r="D9" t="n">
-        <v>5.41875</v>
+        <v>5.47796</v>
       </c>
       <c r="E9" t="n">
-        <v>3.87512</v>
+        <v>3.3517</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0025</v>
+        <v>3.72337</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.42033</v>
+        <v>3.39837</v>
       </c>
       <c r="C10" t="n">
-        <v>4.54976</v>
+        <v>4.55387</v>
       </c>
       <c r="D10" t="n">
-        <v>5.68566</v>
+        <v>5.70895</v>
       </c>
       <c r="E10" t="n">
-        <v>3.89224</v>
+        <v>3.36211</v>
       </c>
       <c r="F10" t="n">
-        <v>4.02665</v>
+        <v>3.74346</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.43806</v>
+        <v>3.41091</v>
       </c>
       <c r="C11" t="n">
-        <v>4.55395</v>
+        <v>4.5688</v>
       </c>
       <c r="D11" t="n">
-        <v>5.93488</v>
+        <v>5.92685</v>
       </c>
       <c r="E11" t="n">
-        <v>3.94369</v>
+        <v>3.38685</v>
       </c>
       <c r="F11" t="n">
-        <v>4.08172</v>
+        <v>3.76127</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.45115</v>
+        <v>3.42046</v>
       </c>
       <c r="C12" t="n">
-        <v>4.58273</v>
+        <v>4.57755</v>
       </c>
       <c r="D12" t="n">
-        <v>6.20103</v>
+        <v>6.2339</v>
       </c>
       <c r="E12" t="n">
-        <v>3.96394</v>
+        <v>3.43885</v>
       </c>
       <c r="F12" t="n">
-        <v>4.09819</v>
+        <v>3.80432</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.46375</v>
+        <v>3.44707</v>
       </c>
       <c r="C13" t="n">
-        <v>4.59138</v>
+        <v>4.57759</v>
       </c>
       <c r="D13" t="n">
-        <v>6.46969</v>
+        <v>6.44153</v>
       </c>
       <c r="E13" t="n">
-        <v>4.00087</v>
+        <v>3.43839</v>
       </c>
       <c r="F13" t="n">
-        <v>4.14069</v>
+        <v>3.82487</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.48694</v>
+        <v>3.47098</v>
       </c>
       <c r="C14" t="n">
-        <v>4.60241</v>
+        <v>4.60316</v>
       </c>
       <c r="D14" t="n">
-        <v>6.78532</v>
+        <v>6.73975</v>
       </c>
       <c r="E14" t="n">
-        <v>4.02013</v>
+        <v>3.48175</v>
       </c>
       <c r="F14" t="n">
-        <v>4.16647</v>
+        <v>3.83857</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.50369</v>
+        <v>3.46939</v>
       </c>
       <c r="C15" t="n">
-        <v>4.61228</v>
+        <v>4.62341</v>
       </c>
       <c r="D15" t="n">
-        <v>7.00443</v>
+        <v>7.01173</v>
       </c>
       <c r="E15" t="n">
-        <v>4.06367</v>
+        <v>3.50653</v>
       </c>
       <c r="F15" t="n">
-        <v>4.20334</v>
+        <v>3.8486</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.49911</v>
+        <v>3.49325</v>
       </c>
       <c r="C16" t="n">
-        <v>4.63827</v>
+        <v>4.63184</v>
       </c>
       <c r="D16" t="n">
-        <v>7.27809</v>
+        <v>7.28409</v>
       </c>
       <c r="E16" t="n">
-        <v>4.11181</v>
+        <v>3.50338</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2459</v>
+        <v>3.90563</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.54246</v>
+        <v>3.51009</v>
       </c>
       <c r="C17" t="n">
-        <v>4.67448</v>
+        <v>4.66072</v>
       </c>
       <c r="D17" t="n">
-        <v>7.57883</v>
+        <v>7.5478</v>
       </c>
       <c r="E17" t="n">
-        <v>4.16523</v>
+        <v>3.57371</v>
       </c>
       <c r="F17" t="n">
-        <v>4.27435</v>
+        <v>3.94676</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.56469</v>
+        <v>3.53852</v>
       </c>
       <c r="C18" t="n">
-        <v>4.73081</v>
+        <v>4.70355</v>
       </c>
       <c r="D18" t="n">
-        <v>7.86113</v>
+        <v>7.82181</v>
       </c>
       <c r="E18" t="n">
-        <v>4.18638</v>
+        <v>3.5864</v>
       </c>
       <c r="F18" t="n">
-        <v>4.32378</v>
+        <v>3.97456</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.56948</v>
+        <v>3.57001</v>
       </c>
       <c r="C19" t="n">
-        <v>4.77065</v>
+        <v>4.75069</v>
       </c>
       <c r="D19" t="n">
-        <v>8.14307</v>
+        <v>8.096080000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>4.28049</v>
+        <v>3.6196</v>
       </c>
       <c r="F19" t="n">
-        <v>4.36814</v>
+        <v>4.01542</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.59127</v>
+        <v>3.5978</v>
       </c>
       <c r="C20" t="n">
-        <v>4.82818</v>
+        <v>4.80382</v>
       </c>
       <c r="D20" t="n">
-        <v>8.366680000000001</v>
+        <v>8.36401</v>
       </c>
       <c r="E20" t="n">
-        <v>4.36733</v>
+        <v>3.66723</v>
       </c>
       <c r="F20" t="n">
-        <v>4.45338</v>
+        <v>4.0777</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.6421</v>
+        <v>3.63503</v>
       </c>
       <c r="C21" t="n">
-        <v>4.89989</v>
+        <v>4.87234</v>
       </c>
       <c r="D21" t="n">
-        <v>6.24618</v>
+        <v>6.26181</v>
       </c>
       <c r="E21" t="n">
-        <v>4.29408</v>
+        <v>3.60177</v>
       </c>
       <c r="F21" t="n">
-        <v>4.36456</v>
+        <v>4.06049</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.68896</v>
+        <v>3.68428</v>
       </c>
       <c r="C22" t="n">
-        <v>4.73158</v>
+        <v>4.76474</v>
       </c>
       <c r="D22" t="n">
-        <v>6.44878</v>
+        <v>6.43088</v>
       </c>
       <c r="E22" t="n">
-        <v>4.30476</v>
+        <v>3.60843</v>
       </c>
       <c r="F22" t="n">
-        <v>4.38933</v>
+        <v>4.08234</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.76171</v>
+        <v>3.74757</v>
       </c>
       <c r="C23" t="n">
-        <v>4.74429</v>
+        <v>4.73225</v>
       </c>
       <c r="D23" t="n">
-        <v>6.65924</v>
+        <v>6.64952</v>
       </c>
       <c r="E23" t="n">
-        <v>4.35502</v>
+        <v>3.65408</v>
       </c>
       <c r="F23" t="n">
-        <v>4.41494</v>
+        <v>4.09804</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.93364</v>
+        <v>3.91833</v>
       </c>
       <c r="C24" t="n">
-        <v>4.75965</v>
+        <v>4.79963</v>
       </c>
       <c r="D24" t="n">
-        <v>6.92592</v>
+        <v>6.90753</v>
       </c>
       <c r="E24" t="n">
-        <v>4.38852</v>
+        <v>3.71013</v>
       </c>
       <c r="F24" t="n">
-        <v>4.43848</v>
+        <v>4.12759</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.95509</v>
+        <v>3.92191</v>
       </c>
       <c r="C25" t="n">
-        <v>4.78142</v>
+        <v>4.81392</v>
       </c>
       <c r="D25" t="n">
-        <v>7.16069</v>
+        <v>7.1337</v>
       </c>
       <c r="E25" t="n">
-        <v>4.42586</v>
+        <v>3.70274</v>
       </c>
       <c r="F25" t="n">
-        <v>4.47436</v>
+        <v>4.1489</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.94261</v>
+        <v>3.9275</v>
       </c>
       <c r="C26" t="n">
-        <v>4.79097</v>
+        <v>4.81364</v>
       </c>
       <c r="D26" t="n">
-        <v>7.39326</v>
+        <v>7.34533</v>
       </c>
       <c r="E26" t="n">
-        <v>4.4613</v>
+        <v>3.78568</v>
       </c>
       <c r="F26" t="n">
-        <v>4.50144</v>
+        <v>4.18991</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.9589</v>
+        <v>3.93718</v>
       </c>
       <c r="C27" t="n">
-        <v>4.81632</v>
+        <v>4.8132</v>
       </c>
       <c r="D27" t="n">
-        <v>7.66413</v>
+        <v>7.651</v>
       </c>
       <c r="E27" t="n">
-        <v>4.47883</v>
+        <v>3.80416</v>
       </c>
       <c r="F27" t="n">
-        <v>4.54672</v>
+        <v>4.20423</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.96447</v>
+        <v>3.95232</v>
       </c>
       <c r="C28" t="n">
-        <v>4.80759</v>
+        <v>4.82228</v>
       </c>
       <c r="D28" t="n">
-        <v>7.89033</v>
+        <v>7.87643</v>
       </c>
       <c r="E28" t="n">
-        <v>4.57167</v>
+        <v>3.81927</v>
       </c>
       <c r="F28" t="n">
-        <v>4.56299</v>
+        <v>4.24817</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.95219</v>
+        <v>3.94197</v>
       </c>
       <c r="C29" t="n">
-        <v>4.85785</v>
+        <v>4.82535</v>
       </c>
       <c r="D29" t="n">
-        <v>8.16057</v>
+        <v>8.105829999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>4.59535</v>
+        <v>3.84955</v>
       </c>
       <c r="F29" t="n">
-        <v>4.60706</v>
+        <v>4.26482</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.959</v>
+        <v>3.96165</v>
       </c>
       <c r="C30" t="n">
-        <v>4.86982</v>
+        <v>4.8959</v>
       </c>
       <c r="D30" t="n">
-        <v>8.432550000000001</v>
+        <v>8.386749999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>4.64826</v>
+        <v>3.90207</v>
       </c>
       <c r="F30" t="n">
-        <v>4.64751</v>
+        <v>4.29885</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.97878</v>
+        <v>3.97707</v>
       </c>
       <c r="C31" t="n">
-        <v>4.92993</v>
+        <v>4.95308</v>
       </c>
       <c r="D31" t="n">
-        <v>8.614599999999999</v>
+        <v>8.62384</v>
       </c>
       <c r="E31" t="n">
-        <v>4.69909</v>
+        <v>3.89719</v>
       </c>
       <c r="F31" t="n">
-        <v>4.67751</v>
+        <v>4.35156</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.00822</v>
+        <v>3.99697</v>
       </c>
       <c r="C32" t="n">
-        <v>4.96568</v>
+        <v>4.91169</v>
       </c>
       <c r="D32" t="n">
-        <v>8.912789999999999</v>
+        <v>8.847239999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>4.74342</v>
+        <v>3.92425</v>
       </c>
       <c r="F32" t="n">
-        <v>4.74069</v>
+        <v>4.39495</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.03094</v>
+        <v>4.03664</v>
       </c>
       <c r="C33" t="n">
-        <v>5.00076</v>
+        <v>4.98697</v>
       </c>
       <c r="D33" t="n">
-        <v>9.154920000000001</v>
+        <v>9.131880000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>4.86771</v>
+        <v>4.06605</v>
       </c>
       <c r="F33" t="n">
-        <v>4.81692</v>
+        <v>4.45359</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.0628</v>
+        <v>4.08122</v>
       </c>
       <c r="C34" t="n">
-        <v>5.07783</v>
+        <v>5.04435</v>
       </c>
       <c r="D34" t="n">
-        <v>9.38979</v>
+        <v>9.3573</v>
       </c>
       <c r="E34" t="n">
-        <v>4.96314</v>
+        <v>4.08435</v>
       </c>
       <c r="F34" t="n">
-        <v>4.95773</v>
+        <v>4.56406</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.10915</v>
+        <v>4.10339</v>
       </c>
       <c r="C35" t="n">
-        <v>5.17525</v>
+        <v>5.18297</v>
       </c>
       <c r="D35" t="n">
-        <v>6.76122</v>
+        <v>6.72726</v>
       </c>
       <c r="E35" t="n">
-        <v>4.90389</v>
+        <v>3.94231</v>
       </c>
       <c r="F35" t="n">
-        <v>4.71076</v>
+        <v>4.34076</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.20278</v>
+        <v>4.21562</v>
       </c>
       <c r="C36" t="n">
-        <v>5.2675</v>
+        <v>5.26819</v>
       </c>
       <c r="D36" t="n">
-        <v>6.89592</v>
+        <v>6.88844</v>
       </c>
       <c r="E36" t="n">
-        <v>4.96382</v>
+        <v>3.98094</v>
       </c>
       <c r="F36" t="n">
-        <v>4.72673</v>
+        <v>4.42477</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.44806</v>
+        <v>4.42105</v>
       </c>
       <c r="C37" t="n">
-        <v>5.04403</v>
+        <v>5.05757</v>
       </c>
       <c r="D37" t="n">
-        <v>7.07918</v>
+        <v>7.07118</v>
       </c>
       <c r="E37" t="n">
-        <v>5.01551</v>
+        <v>3.99447</v>
       </c>
       <c r="F37" t="n">
-        <v>4.75392</v>
+        <v>4.42342</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.26205</v>
+        <v>4.23178</v>
       </c>
       <c r="C38" t="n">
-        <v>5.02339</v>
+        <v>5.08553</v>
       </c>
       <c r="D38" t="n">
-        <v>7.30399</v>
+        <v>7.25645</v>
       </c>
       <c r="E38" t="n">
-        <v>5.0154</v>
+        <v>4.02948</v>
       </c>
       <c r="F38" t="n">
-        <v>4.75969</v>
+        <v>4.46376</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.25783</v>
+        <v>4.26442</v>
       </c>
       <c r="C39" t="n">
-        <v>5.02677</v>
+        <v>5.06722</v>
       </c>
       <c r="D39" t="n">
-        <v>7.48766</v>
+        <v>7.49598</v>
       </c>
       <c r="E39" t="n">
-        <v>5.05686</v>
+        <v>4.03617</v>
       </c>
       <c r="F39" t="n">
-        <v>4.79124</v>
+        <v>4.48748</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.2802</v>
+        <v>4.25833</v>
       </c>
       <c r="C40" t="n">
-        <v>5.07911</v>
+        <v>5.09091</v>
       </c>
       <c r="D40" t="n">
-        <v>7.75277</v>
+        <v>7.75529</v>
       </c>
       <c r="E40" t="n">
-        <v>5.0875</v>
+        <v>4.09251</v>
       </c>
       <c r="F40" t="n">
-        <v>4.82095</v>
+        <v>4.53963</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.29054</v>
+        <v>4.28787</v>
       </c>
       <c r="C41" t="n">
-        <v>5.0873</v>
+        <v>5.10969</v>
       </c>
       <c r="D41" t="n">
-        <v>7.97105</v>
+        <v>7.93503</v>
       </c>
       <c r="E41" t="n">
-        <v>5.1183</v>
+        <v>4.11759</v>
       </c>
       <c r="F41" t="n">
-        <v>4.85581</v>
+        <v>4.53699</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.26749</v>
+        <v>4.30297</v>
       </c>
       <c r="C42" t="n">
-        <v>5.1068</v>
+        <v>5.12232</v>
       </c>
       <c r="D42" t="n">
-        <v>8.2196</v>
+        <v>8.187939999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>5.16986</v>
+        <v>4.16073</v>
       </c>
       <c r="F42" t="n">
-        <v>4.89918</v>
+        <v>4.54654</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.25201</v>
+        <v>4.28411</v>
       </c>
       <c r="C43" t="n">
-        <v>5.15248</v>
+        <v>5.15987</v>
       </c>
       <c r="D43" t="n">
-        <v>8.4847</v>
+        <v>8.47255</v>
       </c>
       <c r="E43" t="n">
-        <v>5.23179</v>
+        <v>4.1994</v>
       </c>
       <c r="F43" t="n">
-        <v>4.90711</v>
+        <v>4.56836</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.30067</v>
+        <v>4.27583</v>
       </c>
       <c r="C44" t="n">
-        <v>5.16283</v>
+        <v>5.18857</v>
       </c>
       <c r="D44" t="n">
-        <v>8.73089</v>
+        <v>8.76252</v>
       </c>
       <c r="E44" t="n">
-        <v>5.23762</v>
+        <v>4.24346</v>
       </c>
       <c r="F44" t="n">
-        <v>4.97611</v>
+        <v>4.64584</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.32986</v>
+        <v>4.29273</v>
       </c>
       <c r="C45" t="n">
-        <v>5.22712</v>
+        <v>5.2217</v>
       </c>
       <c r="D45" t="n">
-        <v>9.011900000000001</v>
+        <v>9.010350000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>5.33103</v>
+        <v>4.28985</v>
       </c>
       <c r="F45" t="n">
-        <v>5.04987</v>
+        <v>4.69251</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.33432</v>
+        <v>4.34125</v>
       </c>
       <c r="C46" t="n">
-        <v>5.24862</v>
+        <v>5.25078</v>
       </c>
       <c r="D46" t="n">
-        <v>9.26125</v>
+        <v>9.245509999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>5.41533</v>
+        <v>4.35451</v>
       </c>
       <c r="F46" t="n">
-        <v>5.10821</v>
+        <v>4.72162</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.35284</v>
+        <v>4.36854</v>
       </c>
       <c r="C47" t="n">
-        <v>5.29543</v>
+        <v>5.31051</v>
       </c>
       <c r="D47" t="n">
-        <v>9.46912</v>
+        <v>9.46561</v>
       </c>
       <c r="E47" t="n">
-        <v>5.53564</v>
+        <v>4.45062</v>
       </c>
       <c r="F47" t="n">
-        <v>5.23654</v>
+        <v>4.85823</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.40526</v>
+        <v>4.40941</v>
       </c>
       <c r="C48" t="n">
-        <v>5.36314</v>
+        <v>5.3526</v>
       </c>
       <c r="D48" t="n">
-        <v>9.733359999999999</v>
+        <v>9.75062</v>
       </c>
       <c r="E48" t="n">
-        <v>5.66301</v>
+        <v>4.59685</v>
       </c>
       <c r="F48" t="n">
-        <v>5.43598</v>
+        <v>5.01883</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.45756</v>
+        <v>4.43324</v>
       </c>
       <c r="C49" t="n">
-        <v>5.44409</v>
+        <v>5.48731</v>
       </c>
       <c r="D49" t="n">
-        <v>9.95219</v>
+        <v>9.927860000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>5.87467</v>
+        <v>4.84229</v>
       </c>
       <c r="F49" t="n">
-        <v>5.73151</v>
+        <v>5.2723</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.56666</v>
+        <v>4.5312</v>
       </c>
       <c r="C50" t="n">
-        <v>5.55498</v>
+        <v>5.58586</v>
       </c>
       <c r="D50" t="n">
-        <v>7.02373</v>
+        <v>7.03613</v>
       </c>
       <c r="E50" t="n">
-        <v>5.30589</v>
+        <v>4.32619</v>
       </c>
       <c r="F50" t="n">
-        <v>4.95811</v>
+        <v>4.63667</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.73121</v>
+        <v>4.77493</v>
       </c>
       <c r="C51" t="n">
-        <v>5.41464</v>
+        <v>5.47518</v>
       </c>
       <c r="D51" t="n">
-        <v>7.19314</v>
+        <v>7.17196</v>
       </c>
       <c r="E51" t="n">
-        <v>5.34528</v>
+        <v>4.34314</v>
       </c>
       <c r="F51" t="n">
-        <v>5.00405</v>
+        <v>4.66716</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.11468</v>
+        <v>5.1633</v>
       </c>
       <c r="C52" t="n">
-        <v>5.43821</v>
+        <v>5.41737</v>
       </c>
       <c r="D52" t="n">
-        <v>7.40035</v>
+        <v>7.38042</v>
       </c>
       <c r="E52" t="n">
-        <v>5.37443</v>
+        <v>4.36299</v>
       </c>
       <c r="F52" t="n">
-        <v>5.02547</v>
+        <v>4.68308</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.78484</v>
+        <v>4.73061</v>
       </c>
       <c r="C53" t="n">
-        <v>5.4737</v>
+        <v>5.43315</v>
       </c>
       <c r="D53" t="n">
-        <v>7.62302</v>
+        <v>7.58992</v>
       </c>
       <c r="E53" t="n">
-        <v>5.40082</v>
+        <v>4.40468</v>
       </c>
       <c r="F53" t="n">
-        <v>5.05976</v>
+        <v>4.7328</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.80413</v>
+        <v>4.73752</v>
       </c>
       <c r="C54" t="n">
-        <v>5.47335</v>
+        <v>5.48869</v>
       </c>
       <c r="D54" t="n">
-        <v>7.8491</v>
+        <v>7.85586</v>
       </c>
       <c r="E54" t="n">
-        <v>5.46565</v>
+        <v>4.39502</v>
       </c>
       <c r="F54" t="n">
-        <v>5.08201</v>
+        <v>4.73299</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.80447</v>
+        <v>4.76356</v>
       </c>
       <c r="C55" t="n">
-        <v>5.5074</v>
+        <v>5.50177</v>
       </c>
       <c r="D55" t="n">
-        <v>8.084390000000001</v>
+        <v>8.060449999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>5.50358</v>
+        <v>4.47279</v>
       </c>
       <c r="F55" t="n">
-        <v>5.12539</v>
+        <v>4.80852</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.78947</v>
+        <v>4.76678</v>
       </c>
       <c r="C56" t="n">
-        <v>5.50288</v>
+        <v>5.51169</v>
       </c>
       <c r="D56" t="n">
-        <v>8.325570000000001</v>
+        <v>8.33944</v>
       </c>
       <c r="E56" t="n">
-        <v>5.55495</v>
+        <v>4.48875</v>
       </c>
       <c r="F56" t="n">
-        <v>5.1386</v>
+        <v>4.82737</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.81367</v>
+        <v>4.80935</v>
       </c>
       <c r="C57" t="n">
-        <v>5.54021</v>
+        <v>5.50144</v>
       </c>
       <c r="D57" t="n">
-        <v>8.579470000000001</v>
+        <v>8.597490000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>5.58615</v>
+        <v>4.53961</v>
       </c>
       <c r="F57" t="n">
-        <v>5.22629</v>
+        <v>4.87707</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.81437</v>
+        <v>4.79993</v>
       </c>
       <c r="C58" t="n">
-        <v>5.54262</v>
+        <v>5.57821</v>
       </c>
       <c r="D58" t="n">
-        <v>8.84333</v>
+        <v>8.807980000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>5.66923</v>
+        <v>4.58329</v>
       </c>
       <c r="F58" t="n">
-        <v>5.27057</v>
+        <v>4.89868</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.81817</v>
+        <v>4.82959</v>
       </c>
       <c r="C59" t="n">
-        <v>5.57382</v>
+        <v>5.60092</v>
       </c>
       <c r="D59" t="n">
-        <v>9.10449</v>
+        <v>9.08779</v>
       </c>
       <c r="E59" t="n">
-        <v>5.71561</v>
+        <v>4.62734</v>
       </c>
       <c r="F59" t="n">
-        <v>5.3482</v>
+        <v>4.95914</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.84232</v>
+        <v>4.81813</v>
       </c>
       <c r="C60" t="n">
-        <v>5.61594</v>
+        <v>5.64912</v>
       </c>
       <c r="D60" t="n">
-        <v>9.3314</v>
+        <v>9.35031</v>
       </c>
       <c r="E60" t="n">
-        <v>5.79258</v>
+        <v>4.70701</v>
       </c>
       <c r="F60" t="n">
-        <v>5.4498</v>
+        <v>5.06229</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.89883</v>
+        <v>4.83931</v>
       </c>
       <c r="C61" t="n">
-        <v>5.68467</v>
+        <v>5.75781</v>
       </c>
       <c r="D61" t="n">
-        <v>9.617000000000001</v>
+        <v>9.624459999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>5.91556</v>
+        <v>4.83398</v>
       </c>
       <c r="F61" t="n">
-        <v>5.57191</v>
+        <v>5.14722</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.91552</v>
+        <v>4.88233</v>
       </c>
       <c r="C62" t="n">
-        <v>5.78148</v>
+        <v>5.75592</v>
       </c>
       <c r="D62" t="n">
-        <v>9.846310000000001</v>
+        <v>9.815849999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>6.08457</v>
+        <v>4.98918</v>
       </c>
       <c r="F62" t="n">
-        <v>5.78057</v>
+        <v>5.34991</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.97298</v>
+        <v>4.98866</v>
       </c>
       <c r="C63" t="n">
-        <v>5.87491</v>
+        <v>5.86834</v>
       </c>
       <c r="D63" t="n">
-        <v>10.0959</v>
+        <v>10.07</v>
       </c>
       <c r="E63" t="n">
-        <v>6.31373</v>
+        <v>5.20166</v>
       </c>
       <c r="F63" t="n">
-        <v>6.056</v>
+        <v>5.56979</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.08535</v>
+        <v>5.0705</v>
       </c>
       <c r="C64" t="n">
-        <v>6.02072</v>
+        <v>5.99459</v>
       </c>
       <c r="D64" t="n">
-        <v>7.32434</v>
+        <v>7.29642</v>
       </c>
       <c r="E64" t="n">
-        <v>5.547</v>
+        <v>4.56505</v>
       </c>
       <c r="F64" t="n">
-        <v>5.19049</v>
+        <v>4.89452</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.28456</v>
+        <v>5.25154</v>
       </c>
       <c r="C65" t="n">
-        <v>5.72652</v>
+        <v>5.73106</v>
       </c>
       <c r="D65" t="n">
-        <v>7.5362</v>
+        <v>7.4893</v>
       </c>
       <c r="E65" t="n">
-        <v>5.58537</v>
+        <v>4.59064</v>
       </c>
       <c r="F65" t="n">
-        <v>5.22416</v>
+        <v>4.91671</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.59819</v>
+        <v>5.57561</v>
       </c>
       <c r="C66" t="n">
-        <v>5.74078</v>
+        <v>5.73249</v>
       </c>
       <c r="D66" t="n">
-        <v>7.80618</v>
+        <v>7.76596</v>
       </c>
       <c r="E66" t="n">
-        <v>5.60776</v>
+        <v>4.6195</v>
       </c>
       <c r="F66" t="n">
-        <v>5.2577</v>
+        <v>4.95665</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.56111</v>
+        <v>5.55375</v>
       </c>
       <c r="C67" t="n">
-        <v>5.75509</v>
+        <v>5.76285</v>
       </c>
       <c r="D67" t="n">
-        <v>8.056900000000001</v>
+        <v>8.021850000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>5.63817</v>
+        <v>4.66785</v>
       </c>
       <c r="F67" t="n">
-        <v>5.31078</v>
+        <v>4.96175</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.56891</v>
+        <v>5.56632</v>
       </c>
       <c r="C68" t="n">
-        <v>5.77577</v>
+        <v>5.79003</v>
       </c>
       <c r="D68" t="n">
-        <v>8.35514</v>
+        <v>8.32568</v>
       </c>
       <c r="E68" t="n">
-        <v>5.67263</v>
+        <v>4.69919</v>
       </c>
       <c r="F68" t="n">
-        <v>5.36354</v>
+        <v>5.05854</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.59813</v>
+        <v>5.55047</v>
       </c>
       <c r="C69" t="n">
-        <v>5.82727</v>
+        <v>5.7998</v>
       </c>
       <c r="D69" t="n">
-        <v>8.64888</v>
+        <v>8.581670000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>5.69864</v>
+        <v>4.7173</v>
       </c>
       <c r="F69" t="n">
-        <v>5.5296</v>
+        <v>5.22609</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.58983</v>
+        <v>5.55975</v>
       </c>
       <c r="C70" t="n">
-        <v>5.85431</v>
+        <v>5.81025</v>
       </c>
       <c r="D70" t="n">
-        <v>8.924720000000001</v>
+        <v>8.89024</v>
       </c>
       <c r="E70" t="n">
-        <v>5.73945</v>
+        <v>4.73485</v>
       </c>
       <c r="F70" t="n">
-        <v>5.51995</v>
+        <v>5.17986</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.59083</v>
+        <v>5.52712</v>
       </c>
       <c r="C71" t="n">
-        <v>5.84194</v>
+        <v>5.8352</v>
       </c>
       <c r="D71" t="n">
-        <v>9.230700000000001</v>
+        <v>9.18768</v>
       </c>
       <c r="E71" t="n">
-        <v>5.79809</v>
+        <v>4.78676</v>
       </c>
       <c r="F71" t="n">
-        <v>5.8919</v>
+        <v>5.54108</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.601</v>
+        <v>5.55788</v>
       </c>
       <c r="C72" t="n">
-        <v>5.88457</v>
+        <v>5.87112</v>
       </c>
       <c r="D72" t="n">
-        <v>9.56996</v>
+        <v>9.657360000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>5.86497</v>
+        <v>4.83339</v>
       </c>
       <c r="F72" t="n">
-        <v>6.67848</v>
+        <v>5.92379</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.6574</v>
+        <v>5.57201</v>
       </c>
       <c r="C73" t="n">
-        <v>5.91628</v>
+        <v>5.89279</v>
       </c>
       <c r="D73" t="n">
-        <v>10.1582</v>
+        <v>10.0223</v>
       </c>
       <c r="E73" t="n">
-        <v>5.9318</v>
+        <v>4.89178</v>
       </c>
       <c r="F73" t="n">
-        <v>7.03558</v>
+        <v>6.58122</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.61534</v>
+        <v>5.57678</v>
       </c>
       <c r="C74" t="n">
-        <v>5.91748</v>
+        <v>5.94052</v>
       </c>
       <c r="D74" t="n">
-        <v>10.4737</v>
+        <v>10.4674</v>
       </c>
       <c r="E74" t="n">
-        <v>6.02585</v>
+        <v>4.96986</v>
       </c>
       <c r="F74" t="n">
-        <v>7.8532</v>
+        <v>7.28242</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.65092</v>
+        <v>5.61497</v>
       </c>
       <c r="C75" t="n">
-        <v>5.99691</v>
+        <v>5.99281</v>
       </c>
       <c r="D75" t="n">
-        <v>11.4297</v>
+        <v>11.3789</v>
       </c>
       <c r="E75" t="n">
-        <v>6.13429</v>
+        <v>5.11167</v>
       </c>
       <c r="F75" t="n">
-        <v>8.671189999999999</v>
+        <v>8.07761</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.67342</v>
+        <v>5.72301</v>
       </c>
       <c r="C76" t="n">
-        <v>6.07655</v>
+        <v>6.06337</v>
       </c>
       <c r="D76" t="n">
-        <v>11.8788</v>
+        <v>12.0084</v>
       </c>
       <c r="E76" t="n">
-        <v>6.30839</v>
+        <v>5.22201</v>
       </c>
       <c r="F76" t="n">
-        <v>9.454639999999999</v>
+        <v>8.92306</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.75082</v>
+        <v>5.73082</v>
       </c>
       <c r="C77" t="n">
-        <v>6.16393</v>
+        <v>6.1453</v>
       </c>
       <c r="D77" t="n">
-        <v>12.8373</v>
+        <v>12.7913</v>
       </c>
       <c r="E77" t="n">
-        <v>6.50211</v>
+        <v>5.42418</v>
       </c>
       <c r="F77" t="n">
-        <v>10.2226</v>
+        <v>9.42559</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.82752</v>
+        <v>5.79142</v>
       </c>
       <c r="C78" t="n">
-        <v>6.30837</v>
+        <v>6.30244</v>
       </c>
       <c r="D78" t="n">
-        <v>14.9708</v>
+        <v>14.9112</v>
       </c>
       <c r="E78" t="n">
-        <v>8.81264</v>
+        <v>5.645</v>
       </c>
       <c r="F78" t="n">
-        <v>11.5227</v>
+        <v>10.887</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>5.99142</v>
+        <v>5.95443</v>
       </c>
       <c r="C79" t="n">
-        <v>13.2451</v>
+        <v>13.4834</v>
       </c>
       <c r="D79" t="n">
-        <v>15.6417</v>
+        <v>15.6926</v>
       </c>
       <c r="E79" t="n">
-        <v>8.75367</v>
+        <v>5.91246</v>
       </c>
       <c r="F79" t="n">
-        <v>11.7595</v>
+        <v>10.922</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.16509</v>
+        <v>6.19522</v>
       </c>
       <c r="C80" t="n">
-        <v>13.4781</v>
+        <v>13.53</v>
       </c>
       <c r="D80" t="n">
-        <v>16.3514</v>
+        <v>16.3326</v>
       </c>
       <c r="E80" t="n">
-        <v>8.77055</v>
+        <v>6.05798</v>
       </c>
       <c r="F80" t="n">
-        <v>11.7136</v>
+        <v>10.9763</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>13.6387</v>
+        <v>13.6363</v>
       </c>
       <c r="C81" t="n">
-        <v>13.7165</v>
+        <v>13.8605</v>
       </c>
       <c r="D81" t="n">
-        <v>17.008</v>
+        <v>17.0535</v>
       </c>
       <c r="E81" t="n">
-        <v>8.62832</v>
+        <v>6.12282</v>
       </c>
       <c r="F81" t="n">
-        <v>11.9179</v>
+        <v>11.0931</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.7291</v>
+        <v>13.868</v>
       </c>
       <c r="C82" t="n">
-        <v>13.6594</v>
+        <v>13.8442</v>
       </c>
       <c r="D82" t="n">
-        <v>17.7779</v>
+        <v>17.775</v>
       </c>
       <c r="E82" t="n">
-        <v>8.87804</v>
+        <v>6.32867</v>
       </c>
       <c r="F82" t="n">
-        <v>11.9732</v>
+        <v>11.1763</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.78</v>
+        <v>13.8311</v>
       </c>
       <c r="C83" t="n">
-        <v>14.0143</v>
+        <v>14.0131</v>
       </c>
       <c r="D83" t="n">
-        <v>18.53</v>
+        <v>18.5345</v>
       </c>
       <c r="E83" t="n">
-        <v>8.93698</v>
+        <v>6.63047</v>
       </c>
       <c r="F83" t="n">
-        <v>12.0955</v>
+        <v>11.2269</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.8216</v>
+        <v>13.9421</v>
       </c>
       <c r="C84" t="n">
-        <v>13.897</v>
+        <v>13.8665</v>
       </c>
       <c r="D84" t="n">
-        <v>19.1772</v>
+        <v>19.2301</v>
       </c>
       <c r="E84" t="n">
-        <v>9.275080000000001</v>
+        <v>6.66348</v>
       </c>
       <c r="F84" t="n">
-        <v>12.1614</v>
+        <v>11.368</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.9887</v>
+        <v>13.8621</v>
       </c>
       <c r="C85" t="n">
-        <v>13.9165</v>
+        <v>14.2064</v>
       </c>
       <c r="D85" t="n">
-        <v>19.8749</v>
+        <v>19.8847</v>
       </c>
       <c r="E85" t="n">
-        <v>8.985810000000001</v>
+        <v>6.92911</v>
       </c>
       <c r="F85" t="n">
-        <v>12.2109</v>
+        <v>11.4713</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>14.0313</v>
+        <v>13.9959</v>
       </c>
       <c r="C86" t="n">
-        <v>14.1823</v>
+        <v>14.2205</v>
       </c>
       <c r="D86" t="n">
-        <v>20.548</v>
+        <v>20.4827</v>
       </c>
       <c r="E86" t="n">
-        <v>9.28129</v>
+        <v>6.92932</v>
       </c>
       <c r="F86" t="n">
-        <v>12.3415</v>
+        <v>11.5121</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.155</v>
+        <v>14.0546</v>
       </c>
       <c r="C87" t="n">
-        <v>14.1645</v>
+        <v>14.1878</v>
       </c>
       <c r="D87" t="n">
-        <v>21.2062</v>
+        <v>21.2048</v>
       </c>
       <c r="E87" t="n">
-        <v>9.24127</v>
+        <v>7.02639</v>
       </c>
       <c r="F87" t="n">
-        <v>12.5156</v>
+        <v>11.6408</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.1911</v>
+        <v>14.1978</v>
       </c>
       <c r="C88" t="n">
-        <v>14.1068</v>
+        <v>14.2176</v>
       </c>
       <c r="D88" t="n">
-        <v>21.86</v>
+        <v>21.7641</v>
       </c>
       <c r="E88" t="n">
-        <v>9.083920000000001</v>
+        <v>7.35115</v>
       </c>
       <c r="F88" t="n">
-        <v>12.6014</v>
+        <v>11.708</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.3142</v>
+        <v>14.2789</v>
       </c>
       <c r="C89" t="n">
-        <v>14.2644</v>
+        <v>14.2804</v>
       </c>
       <c r="D89" t="n">
-        <v>22.5144</v>
+        <v>22.486</v>
       </c>
       <c r="E89" t="n">
-        <v>9.47955</v>
+        <v>7.63055</v>
       </c>
       <c r="F89" t="n">
-        <v>12.7442</v>
+        <v>11.884</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.2799</v>
+        <v>14.1899</v>
       </c>
       <c r="C90" t="n">
-        <v>14.2235</v>
+        <v>14.3318</v>
       </c>
       <c r="D90" t="n">
-        <v>23.2168</v>
+        <v>23.2026</v>
       </c>
       <c r="E90" t="n">
-        <v>9.47409</v>
+        <v>7.85657</v>
       </c>
       <c r="F90" t="n">
-        <v>13.0101</v>
+        <v>12.1025</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.375</v>
+        <v>14.4348</v>
       </c>
       <c r="C91" t="n">
-        <v>14.3647</v>
+        <v>14.3671</v>
       </c>
       <c r="D91" t="n">
-        <v>23.9121</v>
+        <v>23.921</v>
       </c>
       <c r="E91" t="n">
-        <v>9.701549999999999</v>
+        <v>7.89118</v>
       </c>
       <c r="F91" t="n">
-        <v>13.34</v>
+        <v>12.3842</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.4832</v>
+        <v>14.4927</v>
       </c>
       <c r="C92" t="n">
-        <v>14.3953</v>
+        <v>14.3014</v>
       </c>
       <c r="D92" t="n">
-        <v>24.0284</v>
+        <v>23.9784</v>
       </c>
       <c r="E92" t="n">
-        <v>21.2458</v>
+        <v>14.9889</v>
       </c>
       <c r="F92" t="n">
-        <v>19.8292</v>
+        <v>17.8378</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5252</v>
+        <v>14.5659</v>
       </c>
       <c r="C93" t="n">
-        <v>14.3672</v>
+        <v>14.5201</v>
       </c>
       <c r="D93" t="n">
-        <v>24.4187</v>
+        <v>24.4281</v>
       </c>
       <c r="E93" t="n">
-        <v>21.4121</v>
+        <v>15.1086</v>
       </c>
       <c r="F93" t="n">
-        <v>19.9556</v>
+        <v>17.8988</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.723</v>
+        <v>14.7204</v>
       </c>
       <c r="C94" t="n">
-        <v>22.944</v>
+        <v>22.9702</v>
       </c>
       <c r="D94" t="n">
-        <v>24.9992</v>
+        <v>24.9084</v>
       </c>
       <c r="E94" t="n">
-        <v>21.3955</v>
+        <v>15.2423</v>
       </c>
       <c r="F94" t="n">
-        <v>20.1531</v>
+        <v>17.986</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.9163</v>
+        <v>20.9206</v>
       </c>
       <c r="C95" t="n">
-        <v>23.0474</v>
+        <v>23.1269</v>
       </c>
       <c r="D95" t="n">
-        <v>25.439</v>
+        <v>25.5284</v>
       </c>
       <c r="E95" t="n">
-        <v>21.5806</v>
+        <v>15.4741</v>
       </c>
       <c r="F95" t="n">
-        <v>20.0989</v>
+        <v>18.063</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.8538</v>
+        <v>20.828</v>
       </c>
       <c r="C96" t="n">
-        <v>23.1033</v>
+        <v>23.1303</v>
       </c>
       <c r="D96" t="n">
-        <v>25.992</v>
+        <v>25.9983</v>
       </c>
       <c r="E96" t="n">
-        <v>21.658</v>
+        <v>15.6062</v>
       </c>
       <c r="F96" t="n">
-        <v>20.1926</v>
+        <v>18.0864</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.912</v>
+        <v>20.9133</v>
       </c>
       <c r="C97" t="n">
-        <v>23.1449</v>
+        <v>23.1641</v>
       </c>
       <c r="D97" t="n">
-        <v>26.5787</v>
+        <v>26.5378</v>
       </c>
       <c r="E97" t="n">
-        <v>21.7735</v>
+        <v>15.7227</v>
       </c>
       <c r="F97" t="n">
-        <v>20.2284</v>
+        <v>18.1572</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.9562</v>
+        <v>20.9991</v>
       </c>
       <c r="C98" t="n">
-        <v>23.0838</v>
+        <v>23.1816</v>
       </c>
       <c r="D98" t="n">
-        <v>27.0914</v>
+        <v>27.0445</v>
       </c>
       <c r="E98" t="n">
-        <v>21.8496</v>
+        <v>15.9099</v>
       </c>
       <c r="F98" t="n">
-        <v>20.459</v>
+        <v>18.2806</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.02</v>
+        <v>20.9974</v>
       </c>
       <c r="C99" t="n">
-        <v>23.1926</v>
+        <v>23.141</v>
       </c>
       <c r="D99" t="n">
-        <v>27.6577</v>
+        <v>27.6381</v>
       </c>
       <c r="E99" t="n">
-        <v>22.0847</v>
+        <v>16.0689</v>
       </c>
       <c r="F99" t="n">
-        <v>20.4766</v>
+        <v>18.3766</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>20.9761</v>
+        <v>21.0088</v>
       </c>
       <c r="C100" t="n">
-        <v>23.1331</v>
+        <v>23.1585</v>
       </c>
       <c r="D100" t="n">
-        <v>28.3458</v>
+        <v>28.3462</v>
       </c>
       <c r="E100" t="n">
-        <v>22.1673</v>
+        <v>16.2335</v>
       </c>
       <c r="F100" t="n">
-        <v>20.5069</v>
+        <v>18.4972</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9933</v>
+        <v>21.0184</v>
       </c>
       <c r="C101" t="n">
-        <v>23.1941</v>
+        <v>23.2762</v>
       </c>
       <c r="D101" t="n">
-        <v>29.0628</v>
+        <v>29.0981</v>
       </c>
       <c r="E101" t="n">
-        <v>22.2758</v>
+        <v>16.452</v>
       </c>
       <c r="F101" t="n">
-        <v>20.6862</v>
+        <v>18.5479</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.0239</v>
+        <v>21.0222</v>
       </c>
       <c r="C102" t="n">
-        <v>23.2199</v>
+        <v>23.3382</v>
       </c>
       <c r="D102" t="n">
-        <v>29.6576</v>
+        <v>29.742</v>
       </c>
       <c r="E102" t="n">
-        <v>22.4211</v>
+        <v>16.5809</v>
       </c>
       <c r="F102" t="n">
-        <v>20.8383</v>
+        <v>18.8068</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.0838</v>
+        <v>21.0997</v>
       </c>
       <c r="C103" t="n">
-        <v>23.3415</v>
+        <v>23.3543</v>
       </c>
       <c r="D103" t="n">
-        <v>30.3977</v>
+        <v>30.4801</v>
       </c>
       <c r="E103" t="n">
-        <v>22.6637</v>
+        <v>16.7967</v>
       </c>
       <c r="F103" t="n">
-        <v>21.0429</v>
+        <v>18.933</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.1399</v>
+        <v>21.0442</v>
       </c>
       <c r="C104" t="n">
-        <v>23.4109</v>
+        <v>23.4357</v>
       </c>
       <c r="D104" t="n">
-        <v>31.1771</v>
+        <v>31.2357</v>
       </c>
       <c r="E104" t="n">
-        <v>22.8676</v>
+        <v>17.0432</v>
       </c>
       <c r="F104" t="n">
-        <v>21.1946</v>
+        <v>19.1196</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.0853</v>
+        <v>21.1033</v>
       </c>
       <c r="C105" t="n">
-        <v>23.3843</v>
+        <v>23.5073</v>
       </c>
       <c r="D105" t="n">
-        <v>32.0336</v>
+        <v>32.0261</v>
       </c>
       <c r="E105" t="n">
-        <v>23.0832</v>
+        <v>17.2627</v>
       </c>
       <c r="F105" t="n">
-        <v>21.3764</v>
+        <v>19.3957</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.183</v>
+        <v>21.1643</v>
       </c>
       <c r="C106" t="n">
-        <v>23.5829</v>
+        <v>23.6088</v>
       </c>
       <c r="D106" t="n">
-        <v>32.8382</v>
+        <v>32.8805</v>
       </c>
       <c r="E106" t="n">
-        <v>23.4019</v>
+        <v>17.4756</v>
       </c>
       <c r="F106" t="n">
-        <v>21.7114</v>
+        <v>19.5931</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.3186</v>
+        <v>21.2934</v>
       </c>
       <c r="C107" t="n">
-        <v>23.7042</v>
+        <v>23.7589</v>
       </c>
       <c r="D107" t="n">
-        <v>28.7974</v>
+        <v>28.7782</v>
       </c>
       <c r="E107" t="n">
-        <v>26.5352</v>
+        <v>20.3333</v>
       </c>
       <c r="F107" t="n">
-        <v>25.7303</v>
+        <v>23.0206</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.4779</v>
+        <v>21.4944</v>
       </c>
       <c r="C108" t="n">
-        <v>27.151</v>
+        <v>27.1878</v>
       </c>
       <c r="D108" t="n">
-        <v>29.1922</v>
+        <v>29.1991</v>
       </c>
       <c r="E108" t="n">
-        <v>26.6731</v>
+        <v>20.4942</v>
       </c>
       <c r="F108" t="n">
-        <v>25.9029</v>
+        <v>23.1015</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.82</v>
+        <v>21.8204</v>
       </c>
       <c r="C109" t="n">
-        <v>27.2745</v>
+        <v>27.2631</v>
       </c>
       <c r="D109" t="n">
-        <v>29.7309</v>
+        <v>29.6943</v>
       </c>
       <c r="E109" t="n">
-        <v>26.8545</v>
+        <v>20.7282</v>
       </c>
       <c r="F109" t="n">
-        <v>25.9613</v>
+        <v>23.1917</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.4699</v>
+        <v>23.555</v>
       </c>
       <c r="C110" t="n">
-        <v>27.2655</v>
+        <v>27.3135</v>
       </c>
       <c r="D110" t="n">
-        <v>30.1757</v>
+        <v>30.2324</v>
       </c>
       <c r="E110" t="n">
-        <v>26.9383</v>
+        <v>20.8416</v>
       </c>
       <c r="F110" t="n">
-        <v>26.2009</v>
+        <v>23.3487</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.4861</v>
+        <v>23.5407</v>
       </c>
       <c r="C111" t="n">
-        <v>27.3144</v>
+        <v>27.3758</v>
       </c>
       <c r="D111" t="n">
-        <v>30.687</v>
+        <v>30.7136</v>
       </c>
       <c r="E111" t="n">
-        <v>27.1641</v>
+        <v>20.9883</v>
       </c>
       <c r="F111" t="n">
-        <v>26.3048</v>
+        <v>23.5708</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.5373</v>
+        <v>23.5528</v>
       </c>
       <c r="C112" t="n">
-        <v>27.2916</v>
+        <v>27.3615</v>
       </c>
       <c r="D112" t="n">
-        <v>31.4246</v>
+        <v>31.3912</v>
       </c>
       <c r="E112" t="n">
-        <v>27.2904</v>
+        <v>21.1752</v>
       </c>
       <c r="F112" t="n">
-        <v>26.3881</v>
+        <v>23.5883</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.4852</v>
+        <v>23.5811</v>
       </c>
       <c r="C113" t="n">
-        <v>27.3404</v>
+        <v>27.4631</v>
       </c>
       <c r="D113" t="n">
-        <v>31.9648</v>
+        <v>31.9979</v>
       </c>
       <c r="E113" t="n">
-        <v>27.4596</v>
+        <v>21.3011</v>
       </c>
       <c r="F113" t="n">
-        <v>26.6021</v>
+        <v>23.8047</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.5872</v>
+        <v>23.6042</v>
       </c>
       <c r="C114" t="n">
-        <v>27.4675</v>
+        <v>27.436</v>
       </c>
       <c r="D114" t="n">
-        <v>32.6907</v>
+        <v>32.5582</v>
       </c>
       <c r="E114" t="n">
-        <v>27.6058</v>
+        <v>21.4538</v>
       </c>
       <c r="F114" t="n">
-        <v>26.7692</v>
+        <v>23.9293</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.6375</v>
+        <v>23.5076</v>
       </c>
       <c r="C115" t="n">
-        <v>27.4837</v>
+        <v>27.5203</v>
       </c>
       <c r="D115" t="n">
-        <v>33.3957</v>
+        <v>33.2484</v>
       </c>
       <c r="E115" t="n">
-        <v>27.7011</v>
+        <v>21.6908</v>
       </c>
       <c r="F115" t="n">
-        <v>26.876</v>
+        <v>24.202</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.6884</v>
+        <v>23.6203</v>
       </c>
       <c r="C116" t="n">
-        <v>27.6665</v>
+        <v>27.6338</v>
       </c>
       <c r="D116" t="n">
-        <v>34.0178</v>
+        <v>33.9777</v>
       </c>
       <c r="E116" t="n">
-        <v>27.974</v>
+        <v>21.8643</v>
       </c>
       <c r="F116" t="n">
-        <v>27.2173</v>
+        <v>24.3849</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.6843</v>
+        <v>23.6141</v>
       </c>
       <c r="C117" t="n">
-        <v>27.594</v>
+        <v>27.6826</v>
       </c>
       <c r="D117" t="n">
-        <v>34.9095</v>
+        <v>34.7554</v>
       </c>
       <c r="E117" t="n">
-        <v>28.1358</v>
+        <v>22.1236</v>
       </c>
       <c r="F117" t="n">
-        <v>27.3471</v>
+        <v>24.6359</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.7211</v>
+        <v>23.5334</v>
       </c>
       <c r="C118" t="n">
-        <v>27.7753</v>
+        <v>27.7671</v>
       </c>
       <c r="D118" t="n">
-        <v>35.4699</v>
+        <v>35.5805</v>
       </c>
       <c r="E118" t="n">
-        <v>28.364</v>
+        <v>22.3342</v>
       </c>
       <c r="F118" t="n">
-        <v>27.7448</v>
+        <v>25.004</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.7745</v>
+        <v>23.7011</v>
       </c>
       <c r="C119" t="n">
-        <v>27.8136</v>
+        <v>27.9519</v>
       </c>
       <c r="D119" t="n">
-        <v>36.283</v>
+        <v>36.3222</v>
       </c>
       <c r="E119" t="n">
-        <v>28.6588</v>
+        <v>22.6255</v>
       </c>
       <c r="F119" t="n">
-        <v>27.9692</v>
+        <v>25.424</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.8211</v>
+        <v>23.7044</v>
       </c>
       <c r="C120" t="n">
-        <v>28.059</v>
+        <v>28.0112</v>
       </c>
       <c r="D120" t="n">
-        <v>37.285</v>
+        <v>37.3197</v>
       </c>
       <c r="E120" t="n">
-        <v>29.2096</v>
+        <v>22.9071</v>
       </c>
       <c r="F120" t="n">
-        <v>28.6732</v>
+        <v>25.7509</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.9702</v>
+        <v>23.8656</v>
       </c>
       <c r="C121" t="n">
-        <v>28.2249</v>
+        <v>28.2243</v>
       </c>
       <c r="D121" t="n">
-        <v>31.4786</v>
+        <v>31.3233</v>
       </c>
       <c r="E121" t="n">
-        <v>29.3453</v>
+        <v>23.3915</v>
       </c>
       <c r="F121" t="n">
-        <v>29.8504</v>
+        <v>26.8733</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>24.1509</v>
+        <v>24.1043</v>
       </c>
       <c r="C122" t="n">
-        <v>29.829</v>
+        <v>29.6108</v>
       </c>
       <c r="D122" t="n">
-        <v>31.8715</v>
+        <v>31.7811</v>
       </c>
       <c r="E122" t="n">
-        <v>29.4706</v>
+        <v>23.5605</v>
       </c>
       <c r="F122" t="n">
-        <v>30.0815</v>
+        <v>26.9716</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.4422</v>
+        <v>24.3904</v>
       </c>
       <c r="C123" t="n">
-        <v>29.861</v>
+        <v>29.715</v>
       </c>
       <c r="D123" t="n">
-        <v>32.4391</v>
+        <v>32.3025</v>
       </c>
       <c r="E123" t="n">
-        <v>29.5609</v>
+        <v>23.7275</v>
       </c>
       <c r="F123" t="n">
-        <v>30.1729</v>
+        <v>27.1154</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>29.8361</v>
+        <v>29.8777</v>
       </c>
       <c r="C124" t="n">
-        <v>29.954</v>
+        <v>29.9967</v>
       </c>
       <c r="D124" t="n">
-        <v>32.8657</v>
+        <v>32.9503</v>
       </c>
       <c r="E124" t="n">
-        <v>29.7341</v>
+        <v>23.9718</v>
       </c>
       <c r="F124" t="n">
-        <v>30.4913</v>
+        <v>27.3319</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>29.833</v>
+        <v>29.8456</v>
       </c>
       <c r="C125" t="n">
-        <v>29.8364</v>
+        <v>29.9223</v>
       </c>
       <c r="D125" t="n">
-        <v>33.4487</v>
+        <v>33.4649</v>
       </c>
       <c r="E125" t="n">
-        <v>29.8601</v>
+        <v>24.0358</v>
       </c>
       <c r="F125" t="n">
-        <v>30.385</v>
+        <v>27.3521</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>29.9229</v>
+        <v>29.8394</v>
       </c>
       <c r="C126" t="n">
-        <v>30.0132</v>
+        <v>30.0656</v>
       </c>
       <c r="D126" t="n">
-        <v>33.9863</v>
+        <v>34.0515</v>
       </c>
       <c r="E126" t="n">
-        <v>30.287</v>
+        <v>24.1935</v>
       </c>
       <c r="F126" t="n">
-        <v>30.7021</v>
+        <v>27.4835</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>29.7746</v>
+        <v>29.7881</v>
       </c>
       <c r="C127" t="n">
-        <v>30.1694</v>
+        <v>30.097</v>
       </c>
       <c r="D127" t="n">
-        <v>34.5806</v>
+        <v>34.6691</v>
       </c>
       <c r="E127" t="n">
-        <v>30.1314</v>
+        <v>24.2888</v>
       </c>
       <c r="F127" t="n">
-        <v>30.8662</v>
+        <v>27.7456</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.8125</v>
+        <v>29.896</v>
       </c>
       <c r="C128" t="n">
-        <v>30.1354</v>
+        <v>30.1465</v>
       </c>
       <c r="D128" t="n">
-        <v>35.3014</v>
+        <v>35.2135</v>
       </c>
       <c r="E128" t="n">
-        <v>30.281</v>
+        <v>24.6011</v>
       </c>
       <c r="F128" t="n">
-        <v>31.0545</v>
+        <v>27.9863</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>29.8116</v>
+        <v>29.809</v>
       </c>
       <c r="C129" t="n">
-        <v>30.4383</v>
+        <v>30.2908</v>
       </c>
       <c r="D129" t="n">
-        <v>36.0438</v>
+        <v>35.8524</v>
       </c>
       <c r="E129" t="n">
-        <v>30.5406</v>
+        <v>24.7644</v>
       </c>
       <c r="F129" t="n">
-        <v>31.2804</v>
+        <v>28.0596</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>29.8131</v>
+        <v>29.8965</v>
       </c>
       <c r="C130" t="n">
-        <v>30.5261</v>
+        <v>30.5682</v>
       </c>
       <c r="D130" t="n">
-        <v>36.6006</v>
+        <v>36.6835</v>
       </c>
       <c r="E130" t="n">
-        <v>30.7092</v>
+        <v>24.9971</v>
       </c>
       <c r="F130" t="n">
-        <v>31.6274</v>
+        <v>28.273</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.8395</v>
+        <v>29.8677</v>
       </c>
       <c r="C131" t="n">
-        <v>30.6073</v>
+        <v>30.6322</v>
       </c>
       <c r="D131" t="n">
-        <v>37.4343</v>
+        <v>37.3784</v>
       </c>
       <c r="E131" t="n">
-        <v>30.9594</v>
+        <v>25.2964</v>
       </c>
       <c r="F131" t="n">
-        <v>31.8941</v>
+        <v>28.609</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.9452</v>
+        <v>29.8304</v>
       </c>
       <c r="C132" t="n">
-        <v>30.8768</v>
+        <v>30.7451</v>
       </c>
       <c r="D132" t="n">
-        <v>38.1728</v>
+        <v>38.1384</v>
       </c>
       <c r="E132" t="n">
-        <v>31.3662</v>
+        <v>25.4987</v>
       </c>
       <c r="F132" t="n">
-        <v>32.0929</v>
+        <v>29.0287</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>29.9789</v>
+        <v>29.9218</v>
       </c>
       <c r="C133" t="n">
-        <v>31.0605</v>
+        <v>31.0773</v>
       </c>
       <c r="D133" t="n">
-        <v>39.1076</v>
+        <v>39.0666</v>
       </c>
       <c r="E133" t="n">
-        <v>31.6284</v>
+        <v>25.7193</v>
       </c>
       <c r="F133" t="n">
-        <v>32.5257</v>
+        <v>29.5675</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>30.021</v>
+        <v>29.9406</v>
       </c>
       <c r="C134" t="n">
-        <v>31.3069</v>
+        <v>31.4048</v>
       </c>
       <c r="D134" t="n">
-        <v>39.9813</v>
+        <v>39.8096</v>
       </c>
       <c r="E134" t="n">
-        <v>32.1141</v>
+        <v>26.1035</v>
       </c>
       <c r="F134" t="n">
-        <v>33.4349</v>
+        <v>30.0929</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>30.0003</v>
+        <v>30.0802</v>
       </c>
       <c r="C135" t="n">
-        <v>31.6</v>
+        <v>31.7517</v>
       </c>
       <c r="D135" t="n">
-        <v>33.333</v>
+        <v>33.1138</v>
       </c>
       <c r="E135" t="n">
-        <v>31.6972</v>
+        <v>26.1894</v>
       </c>
       <c r="F135" t="n">
-        <v>32.5662</v>
+        <v>29.4856</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.1927</v>
+        <v>30.2503</v>
       </c>
       <c r="C136" t="n">
-        <v>31.5224</v>
+        <v>31.6828</v>
       </c>
       <c r="D136" t="n">
-        <v>33.6627</v>
+        <v>33.6116</v>
       </c>
       <c r="E136" t="n">
-        <v>32.6108</v>
+        <v>26.1766</v>
       </c>
       <c r="F136" t="n">
-        <v>32.7805</v>
+        <v>29.5521</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.464</v>
+        <v>30.4287</v>
       </c>
       <c r="C137" t="n">
-        <v>31.7171</v>
+        <v>31.7935</v>
       </c>
       <c r="D137" t="n">
-        <v>33.984</v>
+        <v>34.0162</v>
       </c>
       <c r="E137" t="n">
-        <v>32.3443</v>
+        <v>26.7253</v>
       </c>
       <c r="F137" t="n">
-        <v>32.5951</v>
+        <v>29.6601</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>35.2074</v>
+        <v>35.0556</v>
       </c>
       <c r="C138" t="n">
-        <v>31.6697</v>
+        <v>31.6735</v>
       </c>
       <c r="D138" t="n">
-        <v>34.6308</v>
+        <v>34.5788</v>
       </c>
       <c r="E138" t="n">
-        <v>32.8597</v>
+        <v>26.6891</v>
       </c>
       <c r="F138" t="n">
-        <v>32.866</v>
+        <v>29.583</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.2579</v>
+        <v>35.2057</v>
       </c>
       <c r="C139" t="n">
-        <v>31.6435</v>
+        <v>31.8617</v>
       </c>
       <c r="D139" t="n">
-        <v>35.1535</v>
+        <v>35.1881</v>
       </c>
       <c r="E139" t="n">
-        <v>32.4787</v>
+        <v>26.7369</v>
       </c>
       <c r="F139" t="n">
-        <v>32.8985</v>
+        <v>29.7766</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>35.2519</v>
+        <v>35.2919</v>
       </c>
       <c r="C140" t="n">
-        <v>32.2366</v>
+        <v>32.0111</v>
       </c>
       <c r="D140" t="n">
-        <v>35.7204</v>
+        <v>35.7643</v>
       </c>
       <c r="E140" t="n">
-        <v>32.6527</v>
+        <v>26.9491</v>
       </c>
       <c r="F140" t="n">
-        <v>33.2528</v>
+        <v>29.9725</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.229</v>
+        <v>35.0705</v>
       </c>
       <c r="C141" t="n">
-        <v>32.1337</v>
+        <v>32.0027</v>
       </c>
       <c r="D141" t="n">
-        <v>36.2314</v>
+        <v>36.2102</v>
       </c>
       <c r="E141" t="n">
-        <v>32.9681</v>
+        <v>27.2384</v>
       </c>
       <c r="F141" t="n">
-        <v>33.4606</v>
+        <v>30.391</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>35.3934</v>
+        <v>35.3319</v>
       </c>
       <c r="C142" t="n">
-        <v>32.2602</v>
+        <v>32.244</v>
       </c>
       <c r="D142" t="n">
-        <v>36.9735</v>
+        <v>36.8885</v>
       </c>
       <c r="E142" t="n">
-        <v>32.916</v>
+        <v>27.3141</v>
       </c>
       <c r="F142" t="n">
-        <v>33.7207</v>
+        <v>30.4727</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>35.1228</v>
+        <v>35.1524</v>
       </c>
       <c r="C143" t="n">
-        <v>32.3329</v>
+        <v>32.3218</v>
       </c>
       <c r="D143" t="n">
-        <v>37.6111</v>
+        <v>37.6496</v>
       </c>
       <c r="E143" t="n">
-        <v>33.4008</v>
+        <v>27.5136</v>
       </c>
       <c r="F143" t="n">
-        <v>33.8165</v>
+        <v>30.7703</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.77701</v>
+        <v>2.78262</v>
       </c>
       <c r="C2" t="n">
-        <v>4.47683</v>
+        <v>4.48099</v>
       </c>
       <c r="D2" t="n">
-        <v>5.43047</v>
+        <v>5.44236</v>
       </c>
       <c r="E2" t="n">
-        <v>3.28677</v>
+        <v>3.2846</v>
       </c>
       <c r="F2" t="n">
-        <v>3.64678</v>
+        <v>3.64552</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.78839</v>
+        <v>2.8089</v>
       </c>
       <c r="C3" t="n">
-        <v>4.49035</v>
+        <v>4.50676</v>
       </c>
       <c r="D3" t="n">
-        <v>5.68804</v>
+        <v>5.64114</v>
       </c>
       <c r="E3" t="n">
-        <v>3.29727</v>
+        <v>3.28093</v>
       </c>
       <c r="F3" t="n">
-        <v>3.66616</v>
+        <v>3.64769</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.82196</v>
+        <v>2.83277</v>
       </c>
       <c r="C4" t="n">
-        <v>4.50833</v>
+        <v>4.53658</v>
       </c>
       <c r="D4" t="n">
-        <v>6.14074</v>
+        <v>6.11339</v>
       </c>
       <c r="E4" t="n">
-        <v>3.32607</v>
+        <v>3.3047</v>
       </c>
       <c r="F4" t="n">
-        <v>3.67717</v>
+        <v>3.67188</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.85718</v>
+        <v>2.85579</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5478</v>
+        <v>4.55391</v>
       </c>
       <c r="D5" t="n">
-        <v>6.35681</v>
+        <v>6.37789</v>
       </c>
       <c r="E5" t="n">
-        <v>3.34039</v>
+        <v>3.35008</v>
       </c>
       <c r="F5" t="n">
-        <v>3.69037</v>
+        <v>3.69503</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.85582</v>
+        <v>2.88507</v>
       </c>
       <c r="C6" t="n">
-        <v>4.59029</v>
+        <v>4.62273</v>
       </c>
       <c r="D6" t="n">
-        <v>6.77867</v>
+        <v>6.74651</v>
       </c>
       <c r="E6" t="n">
-        <v>3.38421</v>
+        <v>3.37017</v>
       </c>
       <c r="F6" t="n">
-        <v>3.74891</v>
+        <v>3.76553</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.89672</v>
+        <v>2.91301</v>
       </c>
       <c r="C7" t="n">
-        <v>4.66774</v>
+        <v>4.66653</v>
       </c>
       <c r="D7" t="n">
-        <v>5.10464</v>
+        <v>5.07833</v>
       </c>
       <c r="E7" t="n">
-        <v>3.28933</v>
+        <v>3.29518</v>
       </c>
       <c r="F7" t="n">
-        <v>3.66606</v>
+        <v>3.67352</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.9228</v>
+        <v>2.98209</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5348</v>
+        <v>4.53996</v>
       </c>
       <c r="D8" t="n">
-        <v>5.23619</v>
+        <v>5.21807</v>
       </c>
       <c r="E8" t="n">
-        <v>3.30997</v>
+        <v>3.32444</v>
       </c>
       <c r="F8" t="n">
-        <v>3.68343</v>
+        <v>3.69463</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>2.98609</v>
+        <v>2.98822</v>
       </c>
       <c r="C9" t="n">
-        <v>4.55692</v>
+        <v>4.52413</v>
       </c>
       <c r="D9" t="n">
-        <v>5.47796</v>
+        <v>5.43239</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3517</v>
+        <v>3.33339</v>
       </c>
       <c r="F9" t="n">
-        <v>3.72337</v>
+        <v>3.73098</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.39837</v>
+        <v>3.414</v>
       </c>
       <c r="C10" t="n">
-        <v>4.55387</v>
+        <v>4.5587</v>
       </c>
       <c r="D10" t="n">
-        <v>5.70895</v>
+        <v>5.69395</v>
       </c>
       <c r="E10" t="n">
-        <v>3.36211</v>
+        <v>3.37331</v>
       </c>
       <c r="F10" t="n">
-        <v>3.74346</v>
+        <v>3.75679</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.41091</v>
+        <v>3.42066</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5688</v>
+        <v>4.55199</v>
       </c>
       <c r="D11" t="n">
-        <v>5.92685</v>
+        <v>5.9275</v>
       </c>
       <c r="E11" t="n">
-        <v>3.38685</v>
+        <v>3.39681</v>
       </c>
       <c r="F11" t="n">
-        <v>3.76127</v>
+        <v>3.78722</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.42046</v>
+        <v>3.42828</v>
       </c>
       <c r="C12" t="n">
-        <v>4.57755</v>
+        <v>4.53628</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2339</v>
+        <v>6.20841</v>
       </c>
       <c r="E12" t="n">
-        <v>3.43885</v>
+        <v>3.40574</v>
       </c>
       <c r="F12" t="n">
-        <v>3.80432</v>
+        <v>3.80928</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.44707</v>
+        <v>3.43899</v>
       </c>
       <c r="C13" t="n">
-        <v>4.57759</v>
+        <v>4.56325</v>
       </c>
       <c r="D13" t="n">
-        <v>6.44153</v>
+        <v>6.46514</v>
       </c>
       <c r="E13" t="n">
-        <v>3.43839</v>
+        <v>3.45144</v>
       </c>
       <c r="F13" t="n">
-        <v>3.82487</v>
+        <v>3.84123</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.47098</v>
+        <v>3.46162</v>
       </c>
       <c r="C14" t="n">
-        <v>4.60316</v>
+        <v>4.56089</v>
       </c>
       <c r="D14" t="n">
-        <v>6.73975</v>
+        <v>6.76134</v>
       </c>
       <c r="E14" t="n">
-        <v>3.48175</v>
+        <v>3.45604</v>
       </c>
       <c r="F14" t="n">
-        <v>3.83857</v>
+        <v>3.85531</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.46939</v>
+        <v>3.47116</v>
       </c>
       <c r="C15" t="n">
-        <v>4.62341</v>
+        <v>4.5831</v>
       </c>
       <c r="D15" t="n">
-        <v>7.01173</v>
+        <v>6.99496</v>
       </c>
       <c r="E15" t="n">
-        <v>3.50653</v>
+        <v>3.4799</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8486</v>
+        <v>3.86974</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.49325</v>
+        <v>3.48463</v>
       </c>
       <c r="C16" t="n">
-        <v>4.63184</v>
+        <v>4.60761</v>
       </c>
       <c r="D16" t="n">
-        <v>7.28409</v>
+        <v>7.3052</v>
       </c>
       <c r="E16" t="n">
-        <v>3.50338</v>
+        <v>3.53329</v>
       </c>
       <c r="F16" t="n">
-        <v>3.90563</v>
+        <v>3.92458</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.51009</v>
+        <v>3.50677</v>
       </c>
       <c r="C17" t="n">
-        <v>4.66072</v>
+        <v>4.65641</v>
       </c>
       <c r="D17" t="n">
-        <v>7.5478</v>
+        <v>7.55144</v>
       </c>
       <c r="E17" t="n">
-        <v>3.57371</v>
+        <v>3.56033</v>
       </c>
       <c r="F17" t="n">
-        <v>3.94676</v>
+        <v>3.93596</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.53852</v>
+        <v>3.53807</v>
       </c>
       <c r="C18" t="n">
-        <v>4.70355</v>
+        <v>4.68529</v>
       </c>
       <c r="D18" t="n">
-        <v>7.82181</v>
+        <v>7.81272</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5864</v>
+        <v>3.6014</v>
       </c>
       <c r="F18" t="n">
-        <v>3.97456</v>
+        <v>3.96598</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.57001</v>
+        <v>3.55124</v>
       </c>
       <c r="C19" t="n">
-        <v>4.75069</v>
+        <v>4.75619</v>
       </c>
       <c r="D19" t="n">
-        <v>8.096080000000001</v>
+        <v>8.1211</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6196</v>
+        <v>3.63898</v>
       </c>
       <c r="F19" t="n">
-        <v>4.01542</v>
+        <v>4.00309</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.5978</v>
+        <v>3.57954</v>
       </c>
       <c r="C20" t="n">
-        <v>4.80382</v>
+        <v>4.80578</v>
       </c>
       <c r="D20" t="n">
-        <v>8.36401</v>
+        <v>8.346069999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>3.66723</v>
+        <v>3.69301</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0777</v>
+        <v>4.09304</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.63503</v>
+        <v>3.61211</v>
       </c>
       <c r="C21" t="n">
-        <v>4.87234</v>
+        <v>4.85311</v>
       </c>
       <c r="D21" t="n">
-        <v>6.26181</v>
+        <v>6.24691</v>
       </c>
       <c r="E21" t="n">
-        <v>3.60177</v>
+        <v>3.64118</v>
       </c>
       <c r="F21" t="n">
-        <v>4.06049</v>
+        <v>4.04907</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.68428</v>
+        <v>3.67934</v>
       </c>
       <c r="C22" t="n">
-        <v>4.76474</v>
+        <v>4.74038</v>
       </c>
       <c r="D22" t="n">
-        <v>6.43088</v>
+        <v>6.44765</v>
       </c>
       <c r="E22" t="n">
-        <v>3.60843</v>
+        <v>3.58663</v>
       </c>
       <c r="F22" t="n">
-        <v>4.08234</v>
+        <v>4.06378</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.74757</v>
+        <v>3.74157</v>
       </c>
       <c r="C23" t="n">
-        <v>4.73225</v>
+        <v>4.7531</v>
       </c>
       <c r="D23" t="n">
-        <v>6.64952</v>
+        <v>6.66263</v>
       </c>
       <c r="E23" t="n">
-        <v>3.65408</v>
+        <v>3.6212</v>
       </c>
       <c r="F23" t="n">
-        <v>4.09804</v>
+        <v>4.07513</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.91833</v>
+        <v>3.92523</v>
       </c>
       <c r="C24" t="n">
-        <v>4.79963</v>
+        <v>4.77259</v>
       </c>
       <c r="D24" t="n">
-        <v>6.90753</v>
+        <v>6.91544</v>
       </c>
       <c r="E24" t="n">
-        <v>3.71013</v>
+        <v>3.63408</v>
       </c>
       <c r="F24" t="n">
-        <v>4.12759</v>
+        <v>4.11605</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.92191</v>
+        <v>3.94325</v>
       </c>
       <c r="C25" t="n">
-        <v>4.81392</v>
+        <v>4.83994</v>
       </c>
       <c r="D25" t="n">
-        <v>7.1337</v>
+        <v>7.16488</v>
       </c>
       <c r="E25" t="n">
-        <v>3.70274</v>
+        <v>3.71655</v>
       </c>
       <c r="F25" t="n">
-        <v>4.1489</v>
+        <v>4.14188</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.9275</v>
+        <v>3.9411</v>
       </c>
       <c r="C26" t="n">
-        <v>4.81364</v>
+        <v>4.83997</v>
       </c>
       <c r="D26" t="n">
-        <v>7.34533</v>
+        <v>7.34851</v>
       </c>
       <c r="E26" t="n">
-        <v>3.78568</v>
+        <v>3.70965</v>
       </c>
       <c r="F26" t="n">
-        <v>4.18991</v>
+        <v>4.17189</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.93718</v>
+        <v>3.93408</v>
       </c>
       <c r="C27" t="n">
-        <v>4.8132</v>
+        <v>4.81458</v>
       </c>
       <c r="D27" t="n">
-        <v>7.651</v>
+        <v>7.63087</v>
       </c>
       <c r="E27" t="n">
-        <v>3.80416</v>
+        <v>3.79924</v>
       </c>
       <c r="F27" t="n">
-        <v>4.20423</v>
+        <v>4.20828</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.95232</v>
+        <v>3.94069</v>
       </c>
       <c r="C28" t="n">
-        <v>4.82228</v>
+        <v>4.82567</v>
       </c>
       <c r="D28" t="n">
-        <v>7.87643</v>
+        <v>7.87429</v>
       </c>
       <c r="E28" t="n">
-        <v>3.81927</v>
+        <v>3.8074</v>
       </c>
       <c r="F28" t="n">
-        <v>4.24817</v>
+        <v>4.24555</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.94197</v>
+        <v>3.95486</v>
       </c>
       <c r="C29" t="n">
-        <v>4.82535</v>
+        <v>4.83244</v>
       </c>
       <c r="D29" t="n">
-        <v>8.105829999999999</v>
+        <v>8.09455</v>
       </c>
       <c r="E29" t="n">
-        <v>3.84955</v>
+        <v>3.84804</v>
       </c>
       <c r="F29" t="n">
-        <v>4.26482</v>
+        <v>4.27314</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.96165</v>
+        <v>3.98072</v>
       </c>
       <c r="C30" t="n">
-        <v>4.8959</v>
+        <v>4.87722</v>
       </c>
       <c r="D30" t="n">
-        <v>8.386749999999999</v>
+        <v>8.345840000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>3.90207</v>
+        <v>3.8402</v>
       </c>
       <c r="F30" t="n">
-        <v>4.29885</v>
+        <v>4.31475</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.97707</v>
+        <v>3.98947</v>
       </c>
       <c r="C31" t="n">
-        <v>4.95308</v>
+        <v>4.94023</v>
       </c>
       <c r="D31" t="n">
-        <v>8.62384</v>
+        <v>8.616619999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>3.89719</v>
+        <v>3.96741</v>
       </c>
       <c r="F31" t="n">
-        <v>4.35156</v>
+        <v>4.34578</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.99697</v>
+        <v>4.01516</v>
       </c>
       <c r="C32" t="n">
-        <v>4.91169</v>
+        <v>4.95068</v>
       </c>
       <c r="D32" t="n">
-        <v>8.847239999999999</v>
+        <v>8.874140000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>3.92425</v>
+        <v>3.92607</v>
       </c>
       <c r="F32" t="n">
-        <v>4.39495</v>
+        <v>4.40219</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.03664</v>
+        <v>4.05356</v>
       </c>
       <c r="C33" t="n">
-        <v>4.98697</v>
+        <v>4.97063</v>
       </c>
       <c r="D33" t="n">
-        <v>9.131880000000001</v>
+        <v>9.116630000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>4.06605</v>
+        <v>4.03797</v>
       </c>
       <c r="F33" t="n">
-        <v>4.45359</v>
+        <v>4.44759</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.08122</v>
+        <v>4.08731</v>
       </c>
       <c r="C34" t="n">
-        <v>5.04435</v>
+        <v>5.06313</v>
       </c>
       <c r="D34" t="n">
-        <v>9.3573</v>
+        <v>9.356780000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>4.08435</v>
+        <v>4.17229</v>
       </c>
       <c r="F34" t="n">
-        <v>4.56406</v>
+        <v>4.58206</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.10339</v>
+        <v>4.12672</v>
       </c>
       <c r="C35" t="n">
-        <v>5.18297</v>
+        <v>5.19911</v>
       </c>
       <c r="D35" t="n">
-        <v>6.72726</v>
+        <v>6.71739</v>
       </c>
       <c r="E35" t="n">
-        <v>3.94231</v>
+        <v>3.93909</v>
       </c>
       <c r="F35" t="n">
-        <v>4.34076</v>
+        <v>4.39292</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.21562</v>
+        <v>4.20593</v>
       </c>
       <c r="C36" t="n">
-        <v>5.26819</v>
+        <v>5.23521</v>
       </c>
       <c r="D36" t="n">
-        <v>6.88844</v>
+        <v>6.88667</v>
       </c>
       <c r="E36" t="n">
-        <v>3.98094</v>
+        <v>3.96352</v>
       </c>
       <c r="F36" t="n">
-        <v>4.42477</v>
+        <v>4.39746</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.42105</v>
+        <v>4.42548</v>
       </c>
       <c r="C37" t="n">
-        <v>5.05757</v>
+        <v>5.02008</v>
       </c>
       <c r="D37" t="n">
-        <v>7.07118</v>
+        <v>7.05813</v>
       </c>
       <c r="E37" t="n">
-        <v>3.99447</v>
+        <v>4.01615</v>
       </c>
       <c r="F37" t="n">
-        <v>4.42342</v>
+        <v>4.44934</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.23178</v>
+        <v>4.1784</v>
       </c>
       <c r="C38" t="n">
-        <v>5.08553</v>
+        <v>5.06402</v>
       </c>
       <c r="D38" t="n">
-        <v>7.25645</v>
+        <v>7.26121</v>
       </c>
       <c r="E38" t="n">
-        <v>4.02948</v>
+        <v>4.03519</v>
       </c>
       <c r="F38" t="n">
-        <v>4.46376</v>
+        <v>4.4996</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.26442</v>
+        <v>4.22669</v>
       </c>
       <c r="C39" t="n">
-        <v>5.06722</v>
+        <v>5.05394</v>
       </c>
       <c r="D39" t="n">
-        <v>7.49598</v>
+        <v>7.46894</v>
       </c>
       <c r="E39" t="n">
-        <v>4.03617</v>
+        <v>4.0023</v>
       </c>
       <c r="F39" t="n">
-        <v>4.48748</v>
+        <v>4.45485</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.25833</v>
+        <v>4.20192</v>
       </c>
       <c r="C40" t="n">
-        <v>5.09091</v>
+        <v>5.09747</v>
       </c>
       <c r="D40" t="n">
-        <v>7.75529</v>
+        <v>7.75179</v>
       </c>
       <c r="E40" t="n">
-        <v>4.09251</v>
+        <v>4.08031</v>
       </c>
       <c r="F40" t="n">
-        <v>4.53963</v>
+        <v>4.48634</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.28787</v>
+        <v>4.19828</v>
       </c>
       <c r="C41" t="n">
-        <v>5.10969</v>
+        <v>5.11691</v>
       </c>
       <c r="D41" t="n">
-        <v>7.93503</v>
+        <v>7.95824</v>
       </c>
       <c r="E41" t="n">
-        <v>4.11759</v>
+        <v>4.12689</v>
       </c>
       <c r="F41" t="n">
-        <v>4.53699</v>
+        <v>4.46013</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.30297</v>
+        <v>4.18995</v>
       </c>
       <c r="C42" t="n">
-        <v>5.12232</v>
+        <v>5.15041</v>
       </c>
       <c r="D42" t="n">
-        <v>8.187939999999999</v>
+        <v>8.227309999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>4.16073</v>
+        <v>4.15372</v>
       </c>
       <c r="F42" t="n">
-        <v>4.54654</v>
+        <v>4.54133</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.28411</v>
+        <v>4.19577</v>
       </c>
       <c r="C43" t="n">
-        <v>5.15987</v>
+        <v>5.15992</v>
       </c>
       <c r="D43" t="n">
-        <v>8.47255</v>
+        <v>8.468260000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>4.1994</v>
+        <v>4.18901</v>
       </c>
       <c r="F43" t="n">
-        <v>4.56836</v>
+        <v>4.60404</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.27583</v>
+        <v>4.2358</v>
       </c>
       <c r="C44" t="n">
-        <v>5.18857</v>
+        <v>5.15622</v>
       </c>
       <c r="D44" t="n">
-        <v>8.76252</v>
+        <v>8.702579999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>4.24346</v>
+        <v>4.23003</v>
       </c>
       <c r="F44" t="n">
-        <v>4.64584</v>
+        <v>4.63624</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.29273</v>
+        <v>4.19822</v>
       </c>
       <c r="C45" t="n">
-        <v>5.2217</v>
+        <v>5.20758</v>
       </c>
       <c r="D45" t="n">
-        <v>9.010350000000001</v>
+        <v>8.9703</v>
       </c>
       <c r="E45" t="n">
-        <v>4.28985</v>
+        <v>4.27691</v>
       </c>
       <c r="F45" t="n">
-        <v>4.69251</v>
+        <v>4.73477</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.34125</v>
+        <v>4.2962</v>
       </c>
       <c r="C46" t="n">
-        <v>5.25078</v>
+        <v>5.26324</v>
       </c>
       <c r="D46" t="n">
-        <v>9.245509999999999</v>
+        <v>9.25342</v>
       </c>
       <c r="E46" t="n">
-        <v>4.35451</v>
+        <v>4.34075</v>
       </c>
       <c r="F46" t="n">
-        <v>4.72162</v>
+        <v>4.76198</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.36854</v>
+        <v>4.27331</v>
       </c>
       <c r="C47" t="n">
-        <v>5.31051</v>
+        <v>5.32715</v>
       </c>
       <c r="D47" t="n">
-        <v>9.46561</v>
+        <v>9.422029999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>4.45062</v>
+        <v>4.42686</v>
       </c>
       <c r="F47" t="n">
-        <v>4.85823</v>
+        <v>4.84208</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.40941</v>
+        <v>4.3533</v>
       </c>
       <c r="C48" t="n">
-        <v>5.3526</v>
+        <v>5.38649</v>
       </c>
       <c r="D48" t="n">
-        <v>9.75062</v>
+        <v>9.69918</v>
       </c>
       <c r="E48" t="n">
-        <v>4.59685</v>
+        <v>4.58895</v>
       </c>
       <c r="F48" t="n">
-        <v>5.01883</v>
+        <v>5.03434</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.43324</v>
+        <v>4.41293</v>
       </c>
       <c r="C49" t="n">
-        <v>5.48731</v>
+        <v>5.45466</v>
       </c>
       <c r="D49" t="n">
-        <v>9.927860000000001</v>
+        <v>9.91835</v>
       </c>
       <c r="E49" t="n">
-        <v>4.84229</v>
+        <v>4.8454</v>
       </c>
       <c r="F49" t="n">
-        <v>5.2723</v>
+        <v>5.28317</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.5312</v>
+        <v>4.50306</v>
       </c>
       <c r="C50" t="n">
-        <v>5.58586</v>
+        <v>5.58974</v>
       </c>
       <c r="D50" t="n">
-        <v>7.03613</v>
+        <v>7.00343</v>
       </c>
       <c r="E50" t="n">
-        <v>4.32619</v>
+        <v>4.30424</v>
       </c>
       <c r="F50" t="n">
-        <v>4.63667</v>
+        <v>4.64614</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.77493</v>
+        <v>4.76142</v>
       </c>
       <c r="C51" t="n">
-        <v>5.47518</v>
+        <v>5.43744</v>
       </c>
       <c r="D51" t="n">
-        <v>7.17196</v>
+        <v>7.16743</v>
       </c>
       <c r="E51" t="n">
-        <v>4.34314</v>
+        <v>4.34261</v>
       </c>
       <c r="F51" t="n">
-        <v>4.66716</v>
+        <v>4.68609</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.1633</v>
+        <v>5.11385</v>
       </c>
       <c r="C52" t="n">
-        <v>5.41737</v>
+        <v>5.48404</v>
       </c>
       <c r="D52" t="n">
-        <v>7.38042</v>
+        <v>7.36239</v>
       </c>
       <c r="E52" t="n">
-        <v>4.36299</v>
+        <v>4.36509</v>
       </c>
       <c r="F52" t="n">
-        <v>4.68308</v>
+        <v>4.68977</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.73061</v>
+        <v>4.76011</v>
       </c>
       <c r="C53" t="n">
-        <v>5.43315</v>
+        <v>5.52428</v>
       </c>
       <c r="D53" t="n">
-        <v>7.58992</v>
+        <v>7.58171</v>
       </c>
       <c r="E53" t="n">
-        <v>4.40468</v>
+        <v>4.37051</v>
       </c>
       <c r="F53" t="n">
-        <v>4.7328</v>
+        <v>4.73597</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.73752</v>
+        <v>4.76836</v>
       </c>
       <c r="C54" t="n">
-        <v>5.48869</v>
+        <v>5.48755</v>
       </c>
       <c r="D54" t="n">
-        <v>7.85586</v>
+        <v>7.79357</v>
       </c>
       <c r="E54" t="n">
-        <v>4.39502</v>
+        <v>4.42483</v>
       </c>
       <c r="F54" t="n">
-        <v>4.73299</v>
+        <v>4.77932</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.76356</v>
+        <v>4.77398</v>
       </c>
       <c r="C55" t="n">
-        <v>5.50177</v>
+        <v>5.5267</v>
       </c>
       <c r="D55" t="n">
-        <v>8.060449999999999</v>
+        <v>8.06331</v>
       </c>
       <c r="E55" t="n">
-        <v>4.47279</v>
+        <v>4.46207</v>
       </c>
       <c r="F55" t="n">
-        <v>4.80852</v>
+        <v>4.81648</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.76678</v>
+        <v>4.77681</v>
       </c>
       <c r="C56" t="n">
-        <v>5.51169</v>
+        <v>5.5143</v>
       </c>
       <c r="D56" t="n">
-        <v>8.33944</v>
+        <v>8.282389999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>4.48875</v>
+        <v>4.46519</v>
       </c>
       <c r="F56" t="n">
-        <v>4.82737</v>
+        <v>4.81604</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.80935</v>
+        <v>4.76523</v>
       </c>
       <c r="C57" t="n">
-        <v>5.50144</v>
+        <v>5.53302</v>
       </c>
       <c r="D57" t="n">
-        <v>8.597490000000001</v>
+        <v>8.58344</v>
       </c>
       <c r="E57" t="n">
-        <v>4.53961</v>
+        <v>4.54613</v>
       </c>
       <c r="F57" t="n">
-        <v>4.87707</v>
+        <v>4.89165</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.79993</v>
+        <v>4.78864</v>
       </c>
       <c r="C58" t="n">
-        <v>5.57821</v>
+        <v>5.5971</v>
       </c>
       <c r="D58" t="n">
-        <v>8.807980000000001</v>
+        <v>8.805339999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>4.58329</v>
+        <v>4.53783</v>
       </c>
       <c r="F58" t="n">
-        <v>4.89868</v>
+        <v>4.92723</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.82959</v>
+        <v>4.82278</v>
       </c>
       <c r="C59" t="n">
-        <v>5.60092</v>
+        <v>5.59957</v>
       </c>
       <c r="D59" t="n">
-        <v>9.08779</v>
+        <v>9.067909999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>4.62734</v>
+        <v>4.63409</v>
       </c>
       <c r="F59" t="n">
-        <v>4.95914</v>
+        <v>4.99513</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.81813</v>
+        <v>4.83803</v>
       </c>
       <c r="C60" t="n">
-        <v>5.64912</v>
+        <v>5.62254</v>
       </c>
       <c r="D60" t="n">
-        <v>9.35031</v>
+        <v>9.303979999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>4.70701</v>
+        <v>4.70252</v>
       </c>
       <c r="F60" t="n">
-        <v>5.06229</v>
+        <v>5.05295</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.83931</v>
+        <v>4.87448</v>
       </c>
       <c r="C61" t="n">
-        <v>5.75781</v>
+        <v>5.67811</v>
       </c>
       <c r="D61" t="n">
-        <v>9.624459999999999</v>
+        <v>9.57887</v>
       </c>
       <c r="E61" t="n">
-        <v>4.83398</v>
+        <v>4.80215</v>
       </c>
       <c r="F61" t="n">
-        <v>5.14722</v>
+        <v>5.19465</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.88233</v>
+        <v>4.90721</v>
       </c>
       <c r="C62" t="n">
-        <v>5.75592</v>
+        <v>5.74677</v>
       </c>
       <c r="D62" t="n">
-        <v>9.815849999999999</v>
+        <v>9.81209</v>
       </c>
       <c r="E62" t="n">
-        <v>4.98918</v>
+        <v>4.99349</v>
       </c>
       <c r="F62" t="n">
-        <v>5.34991</v>
+        <v>5.38167</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.98866</v>
+        <v>4.93976</v>
       </c>
       <c r="C63" t="n">
-        <v>5.86834</v>
+        <v>5.89494</v>
       </c>
       <c r="D63" t="n">
-        <v>10.07</v>
+        <v>10.1302</v>
       </c>
       <c r="E63" t="n">
-        <v>5.20166</v>
+        <v>5.18282</v>
       </c>
       <c r="F63" t="n">
-        <v>5.56979</v>
+        <v>5.57744</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.0705</v>
+        <v>5.07927</v>
       </c>
       <c r="C64" t="n">
-        <v>5.99459</v>
+        <v>5.98853</v>
       </c>
       <c r="D64" t="n">
-        <v>7.29642</v>
+        <v>7.22311</v>
       </c>
       <c r="E64" t="n">
-        <v>4.56505</v>
+        <v>4.5974</v>
       </c>
       <c r="F64" t="n">
-        <v>4.89452</v>
+        <v>4.86741</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.25154</v>
+        <v>5.22715</v>
       </c>
       <c r="C65" t="n">
-        <v>5.73106</v>
+        <v>5.76294</v>
       </c>
       <c r="D65" t="n">
-        <v>7.4893</v>
+        <v>7.42362</v>
       </c>
       <c r="E65" t="n">
-        <v>4.59064</v>
+        <v>4.61974</v>
       </c>
       <c r="F65" t="n">
-        <v>4.91671</v>
+        <v>4.92383</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.57561</v>
+        <v>5.52738</v>
       </c>
       <c r="C66" t="n">
-        <v>5.73249</v>
+        <v>5.78722</v>
       </c>
       <c r="D66" t="n">
-        <v>7.76596</v>
+        <v>7.6955</v>
       </c>
       <c r="E66" t="n">
-        <v>4.6195</v>
+        <v>4.64826</v>
       </c>
       <c r="F66" t="n">
-        <v>4.95665</v>
+        <v>4.94298</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.55375</v>
+        <v>5.53023</v>
       </c>
       <c r="C67" t="n">
-        <v>5.76285</v>
+        <v>5.74874</v>
       </c>
       <c r="D67" t="n">
-        <v>8.021850000000001</v>
+        <v>7.95533</v>
       </c>
       <c r="E67" t="n">
-        <v>4.66785</v>
+        <v>4.64557</v>
       </c>
       <c r="F67" t="n">
-        <v>4.96175</v>
+        <v>4.95322</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.56632</v>
+        <v>5.49232</v>
       </c>
       <c r="C68" t="n">
-        <v>5.79003</v>
+        <v>5.78742</v>
       </c>
       <c r="D68" t="n">
-        <v>8.32568</v>
+        <v>8.21397</v>
       </c>
       <c r="E68" t="n">
-        <v>4.69919</v>
+        <v>4.66805</v>
       </c>
       <c r="F68" t="n">
-        <v>5.05854</v>
+        <v>5.03867</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.55047</v>
+        <v>5.54229</v>
       </c>
       <c r="C69" t="n">
-        <v>5.7998</v>
+        <v>5.76029</v>
       </c>
       <c r="D69" t="n">
-        <v>8.581670000000001</v>
+        <v>8.51957</v>
       </c>
       <c r="E69" t="n">
-        <v>4.7173</v>
+        <v>4.72185</v>
       </c>
       <c r="F69" t="n">
-        <v>5.22609</v>
+        <v>5.09585</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.55975</v>
+        <v>5.54125</v>
       </c>
       <c r="C70" t="n">
-        <v>5.81025</v>
+        <v>5.81233</v>
       </c>
       <c r="D70" t="n">
-        <v>8.89024</v>
+        <v>8.81912</v>
       </c>
       <c r="E70" t="n">
-        <v>4.73485</v>
+        <v>4.74926</v>
       </c>
       <c r="F70" t="n">
-        <v>5.17986</v>
+        <v>5.27302</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.52712</v>
+        <v>5.55415</v>
       </c>
       <c r="C71" t="n">
-        <v>5.8352</v>
+        <v>5.83173</v>
       </c>
       <c r="D71" t="n">
-        <v>9.18768</v>
+        <v>9.16086</v>
       </c>
       <c r="E71" t="n">
-        <v>4.78676</v>
+        <v>4.79578</v>
       </c>
       <c r="F71" t="n">
-        <v>5.54108</v>
+        <v>5.62885</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.55788</v>
+        <v>5.51892</v>
       </c>
       <c r="C72" t="n">
-        <v>5.87112</v>
+        <v>5.84008</v>
       </c>
       <c r="D72" t="n">
-        <v>9.657360000000001</v>
+        <v>9.523400000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>4.83339</v>
+        <v>4.8477</v>
       </c>
       <c r="F72" t="n">
-        <v>5.92379</v>
+        <v>5.99111</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.57201</v>
+        <v>5.57242</v>
       </c>
       <c r="C73" t="n">
-        <v>5.89279</v>
+        <v>5.90322</v>
       </c>
       <c r="D73" t="n">
-        <v>10.0223</v>
+        <v>10.0434</v>
       </c>
       <c r="E73" t="n">
-        <v>4.89178</v>
+        <v>4.91056</v>
       </c>
       <c r="F73" t="n">
-        <v>6.58122</v>
+        <v>6.47871</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.57678</v>
+        <v>5.61516</v>
       </c>
       <c r="C74" t="n">
-        <v>5.94052</v>
+        <v>5.9442</v>
       </c>
       <c r="D74" t="n">
-        <v>10.4674</v>
+        <v>10.3211</v>
       </c>
       <c r="E74" t="n">
-        <v>4.96986</v>
+        <v>4.97372</v>
       </c>
       <c r="F74" t="n">
-        <v>7.28242</v>
+        <v>7.24326</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.61497</v>
+        <v>5.62344</v>
       </c>
       <c r="C75" t="n">
-        <v>5.99281</v>
+        <v>6.02058</v>
       </c>
       <c r="D75" t="n">
-        <v>11.3789</v>
+        <v>11.2298</v>
       </c>
       <c r="E75" t="n">
-        <v>5.11167</v>
+        <v>5.09232</v>
       </c>
       <c r="F75" t="n">
-        <v>8.07761</v>
+        <v>8.165710000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.72301</v>
+        <v>5.6972</v>
       </c>
       <c r="C76" t="n">
-        <v>6.06337</v>
+        <v>6.03811</v>
       </c>
       <c r="D76" t="n">
-        <v>12.0084</v>
+        <v>11.8319</v>
       </c>
       <c r="E76" t="n">
-        <v>5.22201</v>
+        <v>5.23504</v>
       </c>
       <c r="F76" t="n">
-        <v>8.92306</v>
+        <v>8.909129999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.73082</v>
+        <v>5.72108</v>
       </c>
       <c r="C77" t="n">
-        <v>6.1453</v>
+        <v>6.15744</v>
       </c>
       <c r="D77" t="n">
-        <v>12.7913</v>
+        <v>12.8675</v>
       </c>
       <c r="E77" t="n">
-        <v>5.42418</v>
+        <v>5.44769</v>
       </c>
       <c r="F77" t="n">
-        <v>9.42559</v>
+        <v>9.420959999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.79142</v>
+        <v>5.82921</v>
       </c>
       <c r="C78" t="n">
-        <v>6.30244</v>
+        <v>6.28409</v>
       </c>
       <c r="D78" t="n">
-        <v>14.9112</v>
+        <v>14.9375</v>
       </c>
       <c r="E78" t="n">
-        <v>5.645</v>
+        <v>5.68437</v>
       </c>
       <c r="F78" t="n">
-        <v>10.887</v>
+        <v>10.7621</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>5.95443</v>
+        <v>5.99255</v>
       </c>
       <c r="C79" t="n">
-        <v>13.4834</v>
+        <v>13.5173</v>
       </c>
       <c r="D79" t="n">
-        <v>15.6926</v>
+        <v>15.6744</v>
       </c>
       <c r="E79" t="n">
-        <v>5.91246</v>
+        <v>5.94126</v>
       </c>
       <c r="F79" t="n">
-        <v>10.922</v>
+        <v>10.9811</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.19522</v>
+        <v>6.23646</v>
       </c>
       <c r="C80" t="n">
-        <v>13.53</v>
+        <v>13.6685</v>
       </c>
       <c r="D80" t="n">
-        <v>16.3326</v>
+        <v>16.4343</v>
       </c>
       <c r="E80" t="n">
-        <v>6.05798</v>
+        <v>6.02543</v>
       </c>
       <c r="F80" t="n">
-        <v>10.9763</v>
+        <v>11.0253</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>13.6363</v>
+        <v>13.4608</v>
       </c>
       <c r="C81" t="n">
-        <v>13.8605</v>
+        <v>13.5002</v>
       </c>
       <c r="D81" t="n">
-        <v>17.0535</v>
+        <v>17.0807</v>
       </c>
       <c r="E81" t="n">
-        <v>6.12282</v>
+        <v>6.10677</v>
       </c>
       <c r="F81" t="n">
-        <v>11.0931</v>
+        <v>11.0782</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.868</v>
+        <v>13.6422</v>
       </c>
       <c r="C82" t="n">
-        <v>13.8442</v>
+        <v>13.6555</v>
       </c>
       <c r="D82" t="n">
-        <v>17.775</v>
+        <v>17.8014</v>
       </c>
       <c r="E82" t="n">
-        <v>6.32867</v>
+        <v>6.40182</v>
       </c>
       <c r="F82" t="n">
-        <v>11.1763</v>
+        <v>11.1876</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.8311</v>
+        <v>13.7219</v>
       </c>
       <c r="C83" t="n">
-        <v>14.0131</v>
+        <v>13.7999</v>
       </c>
       <c r="D83" t="n">
-        <v>18.5345</v>
+        <v>18.4762</v>
       </c>
       <c r="E83" t="n">
-        <v>6.63047</v>
+        <v>6.46345</v>
       </c>
       <c r="F83" t="n">
-        <v>11.2269</v>
+        <v>11.1585</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.9421</v>
+        <v>13.8468</v>
       </c>
       <c r="C84" t="n">
-        <v>13.8665</v>
+        <v>13.9412</v>
       </c>
       <c r="D84" t="n">
-        <v>19.2301</v>
+        <v>19.1305</v>
       </c>
       <c r="E84" t="n">
-        <v>6.66348</v>
+        <v>6.74544</v>
       </c>
       <c r="F84" t="n">
-        <v>11.368</v>
+        <v>11.3538</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.8621</v>
+        <v>13.9573</v>
       </c>
       <c r="C85" t="n">
-        <v>14.2064</v>
+        <v>14.0415</v>
       </c>
       <c r="D85" t="n">
-        <v>19.8847</v>
+        <v>19.805</v>
       </c>
       <c r="E85" t="n">
-        <v>6.92911</v>
+        <v>6.91905</v>
       </c>
       <c r="F85" t="n">
-        <v>11.4713</v>
+        <v>11.4182</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>13.9959</v>
+        <v>14.1128</v>
       </c>
       <c r="C86" t="n">
-        <v>14.2205</v>
+        <v>14.1012</v>
       </c>
       <c r="D86" t="n">
-        <v>20.4827</v>
+        <v>20.5123</v>
       </c>
       <c r="E86" t="n">
-        <v>6.92932</v>
+        <v>6.94568</v>
       </c>
       <c r="F86" t="n">
-        <v>11.5121</v>
+        <v>11.5022</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.0546</v>
+        <v>13.9557</v>
       </c>
       <c r="C87" t="n">
-        <v>14.1878</v>
+        <v>14.2017</v>
       </c>
       <c r="D87" t="n">
-        <v>21.2048</v>
+        <v>21.1897</v>
       </c>
       <c r="E87" t="n">
-        <v>7.02639</v>
+        <v>7.18506</v>
       </c>
       <c r="F87" t="n">
-        <v>11.6408</v>
+        <v>11.5667</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.1978</v>
+        <v>14.118</v>
       </c>
       <c r="C88" t="n">
-        <v>14.2176</v>
+        <v>14.2506</v>
       </c>
       <c r="D88" t="n">
-        <v>21.7641</v>
+        <v>21.8381</v>
       </c>
       <c r="E88" t="n">
-        <v>7.35115</v>
+        <v>7.42201</v>
       </c>
       <c r="F88" t="n">
-        <v>11.708</v>
+        <v>11.7004</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.2789</v>
+        <v>14.284</v>
       </c>
       <c r="C89" t="n">
-        <v>14.2804</v>
+        <v>14.1884</v>
       </c>
       <c r="D89" t="n">
-        <v>22.486</v>
+        <v>22.4381</v>
       </c>
       <c r="E89" t="n">
-        <v>7.63055</v>
+        <v>7.54219</v>
       </c>
       <c r="F89" t="n">
-        <v>11.884</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.1899</v>
+        <v>14.221</v>
       </c>
       <c r="C90" t="n">
-        <v>14.3318</v>
+        <v>14.2</v>
       </c>
       <c r="D90" t="n">
-        <v>23.2026</v>
+        <v>23.0767</v>
       </c>
       <c r="E90" t="n">
-        <v>7.85657</v>
+        <v>7.76895</v>
       </c>
       <c r="F90" t="n">
-        <v>12.1025</v>
+        <v>12.1038</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.4348</v>
+        <v>14.4018</v>
       </c>
       <c r="C91" t="n">
-        <v>14.3671</v>
+        <v>14.3576</v>
       </c>
       <c r="D91" t="n">
-        <v>23.921</v>
+        <v>23.9406</v>
       </c>
       <c r="E91" t="n">
-        <v>7.89118</v>
+        <v>8.039759999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>12.3842</v>
+        <v>12.4245</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.4927</v>
+        <v>14.4001</v>
       </c>
       <c r="C92" t="n">
-        <v>14.3014</v>
+        <v>14.2672</v>
       </c>
       <c r="D92" t="n">
-        <v>23.9784</v>
+        <v>23.9816</v>
       </c>
       <c r="E92" t="n">
-        <v>14.9889</v>
+        <v>14.9478</v>
       </c>
       <c r="F92" t="n">
-        <v>17.8378</v>
+        <v>17.7344</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5659</v>
+        <v>14.5754</v>
       </c>
       <c r="C93" t="n">
-        <v>14.5201</v>
+        <v>14.4115</v>
       </c>
       <c r="D93" t="n">
-        <v>24.4281</v>
+        <v>24.3838</v>
       </c>
       <c r="E93" t="n">
-        <v>15.1086</v>
+        <v>15.0872</v>
       </c>
       <c r="F93" t="n">
-        <v>17.8988</v>
+        <v>17.9251</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.7204</v>
+        <v>14.6966</v>
       </c>
       <c r="C94" t="n">
-        <v>22.9702</v>
+        <v>22.9716</v>
       </c>
       <c r="D94" t="n">
-        <v>24.9084</v>
+        <v>24.969</v>
       </c>
       <c r="E94" t="n">
-        <v>15.2423</v>
+        <v>15.2981</v>
       </c>
       <c r="F94" t="n">
-        <v>17.986</v>
+        <v>17.9397</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.9206</v>
+        <v>20.8822</v>
       </c>
       <c r="C95" t="n">
-        <v>23.1269</v>
+        <v>22.983</v>
       </c>
       <c r="D95" t="n">
-        <v>25.5284</v>
+        <v>25.3789</v>
       </c>
       <c r="E95" t="n">
-        <v>15.4741</v>
+        <v>15.3894</v>
       </c>
       <c r="F95" t="n">
-        <v>18.063</v>
+        <v>18.0499</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.828</v>
+        <v>20.8158</v>
       </c>
       <c r="C96" t="n">
-        <v>23.1303</v>
+        <v>23.0999</v>
       </c>
       <c r="D96" t="n">
-        <v>25.9983</v>
+        <v>26.0186</v>
       </c>
       <c r="E96" t="n">
-        <v>15.6062</v>
+        <v>15.583</v>
       </c>
       <c r="F96" t="n">
-        <v>18.0864</v>
+        <v>18.1227</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.9133</v>
+        <v>20.8585</v>
       </c>
       <c r="C97" t="n">
-        <v>23.1641</v>
+        <v>22.9937</v>
       </c>
       <c r="D97" t="n">
-        <v>26.5378</v>
+        <v>26.4545</v>
       </c>
       <c r="E97" t="n">
-        <v>15.7227</v>
+        <v>15.7336</v>
       </c>
       <c r="F97" t="n">
-        <v>18.1572</v>
+        <v>18.1054</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.9991</v>
+        <v>20.883</v>
       </c>
       <c r="C98" t="n">
-        <v>23.1816</v>
+        <v>23.0632</v>
       </c>
       <c r="D98" t="n">
-        <v>27.0445</v>
+        <v>27.1477</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9099</v>
+        <v>15.9054</v>
       </c>
       <c r="F98" t="n">
-        <v>18.2806</v>
+        <v>18.2449</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>20.9974</v>
+        <v>20.7615</v>
       </c>
       <c r="C99" t="n">
-        <v>23.141</v>
+        <v>23.144</v>
       </c>
       <c r="D99" t="n">
-        <v>27.6381</v>
+        <v>27.6461</v>
       </c>
       <c r="E99" t="n">
-        <v>16.0689</v>
+        <v>16.1092</v>
       </c>
       <c r="F99" t="n">
-        <v>18.3766</v>
+        <v>18.3587</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.0088</v>
+        <v>20.9155</v>
       </c>
       <c r="C100" t="n">
-        <v>23.1585</v>
+        <v>23.0745</v>
       </c>
       <c r="D100" t="n">
-        <v>28.3462</v>
+        <v>28.3243</v>
       </c>
       <c r="E100" t="n">
-        <v>16.2335</v>
+        <v>16.2302</v>
       </c>
       <c r="F100" t="n">
-        <v>18.4972</v>
+        <v>18.4035</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>21.0184</v>
+        <v>20.9842</v>
       </c>
       <c r="C101" t="n">
-        <v>23.2762</v>
+        <v>23.2198</v>
       </c>
       <c r="D101" t="n">
-        <v>29.0981</v>
+        <v>29.0328</v>
       </c>
       <c r="E101" t="n">
-        <v>16.452</v>
+        <v>16.4205</v>
       </c>
       <c r="F101" t="n">
-        <v>18.5479</v>
+        <v>18.5138</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.0222</v>
+        <v>20.9513</v>
       </c>
       <c r="C102" t="n">
-        <v>23.3382</v>
+        <v>23.25</v>
       </c>
       <c r="D102" t="n">
-        <v>29.742</v>
+        <v>29.6763</v>
       </c>
       <c r="E102" t="n">
-        <v>16.5809</v>
+        <v>16.6266</v>
       </c>
       <c r="F102" t="n">
-        <v>18.8068</v>
+        <v>18.7799</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.0997</v>
+        <v>21.0314</v>
       </c>
       <c r="C103" t="n">
-        <v>23.3543</v>
+        <v>23.3084</v>
       </c>
       <c r="D103" t="n">
-        <v>30.4801</v>
+        <v>30.5005</v>
       </c>
       <c r="E103" t="n">
-        <v>16.7967</v>
+        <v>16.8276</v>
       </c>
       <c r="F103" t="n">
-        <v>18.933</v>
+        <v>18.9496</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.0442</v>
+        <v>20.9714</v>
       </c>
       <c r="C104" t="n">
-        <v>23.4357</v>
+        <v>23.2628</v>
       </c>
       <c r="D104" t="n">
-        <v>31.2357</v>
+        <v>31.2177</v>
       </c>
       <c r="E104" t="n">
-        <v>17.0432</v>
+        <v>17.0027</v>
       </c>
       <c r="F104" t="n">
-        <v>19.1196</v>
+        <v>19.1266</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.1033</v>
+        <v>21.0246</v>
       </c>
       <c r="C105" t="n">
-        <v>23.5073</v>
+        <v>23.4641</v>
       </c>
       <c r="D105" t="n">
-        <v>32.0261</v>
+        <v>32.0661</v>
       </c>
       <c r="E105" t="n">
-        <v>17.2627</v>
+        <v>17.2131</v>
       </c>
       <c r="F105" t="n">
-        <v>19.3957</v>
+        <v>19.2993</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.1643</v>
+        <v>21.1697</v>
       </c>
       <c r="C106" t="n">
-        <v>23.6088</v>
+        <v>23.5662</v>
       </c>
       <c r="D106" t="n">
-        <v>32.8805</v>
+        <v>32.7982</v>
       </c>
       <c r="E106" t="n">
-        <v>17.4756</v>
+        <v>17.4703</v>
       </c>
       <c r="F106" t="n">
-        <v>19.5931</v>
+        <v>19.6505</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.2934</v>
+        <v>21.27</v>
       </c>
       <c r="C107" t="n">
-        <v>23.7589</v>
+        <v>23.6975</v>
       </c>
       <c r="D107" t="n">
-        <v>28.7782</v>
+        <v>28.7655</v>
       </c>
       <c r="E107" t="n">
-        <v>20.3333</v>
+        <v>20.4053</v>
       </c>
       <c r="F107" t="n">
-        <v>23.0206</v>
+        <v>22.9931</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.4944</v>
+        <v>21.4268</v>
       </c>
       <c r="C108" t="n">
-        <v>27.1878</v>
+        <v>27.27</v>
       </c>
       <c r="D108" t="n">
-        <v>29.1991</v>
+        <v>29.2312</v>
       </c>
       <c r="E108" t="n">
-        <v>20.4942</v>
+        <v>20.61</v>
       </c>
       <c r="F108" t="n">
-        <v>23.1015</v>
+        <v>23.0691</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.8204</v>
+        <v>21.6889</v>
       </c>
       <c r="C109" t="n">
-        <v>27.2631</v>
+        <v>27.2447</v>
       </c>
       <c r="D109" t="n">
-        <v>29.6943</v>
+        <v>29.7687</v>
       </c>
       <c r="E109" t="n">
-        <v>20.7282</v>
+        <v>20.5878</v>
       </c>
       <c r="F109" t="n">
-        <v>23.1917</v>
+        <v>23.0878</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.555</v>
+        <v>23.5401</v>
       </c>
       <c r="C110" t="n">
-        <v>27.3135</v>
+        <v>27.2825</v>
       </c>
       <c r="D110" t="n">
-        <v>30.2324</v>
+        <v>30.1196</v>
       </c>
       <c r="E110" t="n">
-        <v>20.8416</v>
+        <v>20.766</v>
       </c>
       <c r="F110" t="n">
-        <v>23.3487</v>
+        <v>23.3908</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.5407</v>
+        <v>23.5367</v>
       </c>
       <c r="C111" t="n">
-        <v>27.3758</v>
+        <v>27.3874</v>
       </c>
       <c r="D111" t="n">
-        <v>30.7136</v>
+        <v>30.7785</v>
       </c>
       <c r="E111" t="n">
-        <v>20.9883</v>
+        <v>20.9796</v>
       </c>
       <c r="F111" t="n">
-        <v>23.5708</v>
+        <v>23.446</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.5528</v>
+        <v>23.6026</v>
       </c>
       <c r="C112" t="n">
-        <v>27.3615</v>
+        <v>27.4434</v>
       </c>
       <c r="D112" t="n">
-        <v>31.3912</v>
+        <v>31.2508</v>
       </c>
       <c r="E112" t="n">
-        <v>21.1752</v>
+        <v>21.1843</v>
       </c>
       <c r="F112" t="n">
-        <v>23.5883</v>
+        <v>23.6556</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.5811</v>
+        <v>23.5568</v>
       </c>
       <c r="C113" t="n">
-        <v>27.4631</v>
+        <v>27.3971</v>
       </c>
       <c r="D113" t="n">
-        <v>31.9979</v>
+        <v>31.9942</v>
       </c>
       <c r="E113" t="n">
-        <v>21.3011</v>
+        <v>21.4315</v>
       </c>
       <c r="F113" t="n">
-        <v>23.8047</v>
+        <v>23.7571</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.6042</v>
+        <v>23.5956</v>
       </c>
       <c r="C114" t="n">
-        <v>27.436</v>
+        <v>27.3882</v>
       </c>
       <c r="D114" t="n">
-        <v>32.5582</v>
+        <v>32.5713</v>
       </c>
       <c r="E114" t="n">
-        <v>21.4538</v>
+        <v>21.4968</v>
       </c>
       <c r="F114" t="n">
-        <v>23.9293</v>
+        <v>23.8951</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.5076</v>
+        <v>23.5289</v>
       </c>
       <c r="C115" t="n">
-        <v>27.5203</v>
+        <v>27.4996</v>
       </c>
       <c r="D115" t="n">
-        <v>33.2484</v>
+        <v>33.1804</v>
       </c>
       <c r="E115" t="n">
-        <v>21.6908</v>
+        <v>21.6236</v>
       </c>
       <c r="F115" t="n">
-        <v>24.202</v>
+        <v>24.1313</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.6203</v>
+        <v>23.5085</v>
       </c>
       <c r="C116" t="n">
-        <v>27.6338</v>
+        <v>27.4579</v>
       </c>
       <c r="D116" t="n">
-        <v>33.9777</v>
+        <v>33.9325</v>
       </c>
       <c r="E116" t="n">
-        <v>21.8643</v>
+        <v>21.8215</v>
       </c>
       <c r="F116" t="n">
-        <v>24.3849</v>
+        <v>24.3445</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.6141</v>
+        <v>23.6102</v>
       </c>
       <c r="C117" t="n">
-        <v>27.6826</v>
+        <v>27.6695</v>
       </c>
       <c r="D117" t="n">
-        <v>34.7554</v>
+        <v>34.8089</v>
       </c>
       <c r="E117" t="n">
-        <v>22.1236</v>
+        <v>22.1179</v>
       </c>
       <c r="F117" t="n">
-        <v>24.6359</v>
+        <v>24.671</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.5334</v>
+        <v>23.7494</v>
       </c>
       <c r="C118" t="n">
-        <v>27.7671</v>
+        <v>27.7709</v>
       </c>
       <c r="D118" t="n">
-        <v>35.5805</v>
+        <v>35.5454</v>
       </c>
       <c r="E118" t="n">
-        <v>22.3342</v>
+        <v>22.3411</v>
       </c>
       <c r="F118" t="n">
-        <v>25.004</v>
+        <v>24.9829</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.7011</v>
+        <v>23.7889</v>
       </c>
       <c r="C119" t="n">
-        <v>27.9519</v>
+        <v>27.9008</v>
       </c>
       <c r="D119" t="n">
-        <v>36.3222</v>
+        <v>36.4407</v>
       </c>
       <c r="E119" t="n">
-        <v>22.6255</v>
+        <v>22.5677</v>
       </c>
       <c r="F119" t="n">
-        <v>25.424</v>
+        <v>25.324</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.7044</v>
+        <v>23.8391</v>
       </c>
       <c r="C120" t="n">
-        <v>28.0112</v>
+        <v>28.0768</v>
       </c>
       <c r="D120" t="n">
-        <v>37.3197</v>
+        <v>37.0768</v>
       </c>
       <c r="E120" t="n">
-        <v>22.9071</v>
+        <v>22.9435</v>
       </c>
       <c r="F120" t="n">
-        <v>25.7509</v>
+        <v>25.9174</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.8656</v>
+        <v>23.9468</v>
       </c>
       <c r="C121" t="n">
-        <v>28.2243</v>
+        <v>28.3743</v>
       </c>
       <c r="D121" t="n">
-        <v>31.3233</v>
+        <v>31.4868</v>
       </c>
       <c r="E121" t="n">
-        <v>23.3915</v>
+        <v>23.6487</v>
       </c>
       <c r="F121" t="n">
-        <v>26.8733</v>
+        <v>26.8097</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>24.1043</v>
+        <v>24.0823</v>
       </c>
       <c r="C122" t="n">
-        <v>29.6108</v>
+        <v>29.6572</v>
       </c>
       <c r="D122" t="n">
-        <v>31.7811</v>
+        <v>31.7727</v>
       </c>
       <c r="E122" t="n">
-        <v>23.5605</v>
+        <v>23.6439</v>
       </c>
       <c r="F122" t="n">
-        <v>26.9716</v>
+        <v>26.9347</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.3904</v>
+        <v>24.3971</v>
       </c>
       <c r="C123" t="n">
-        <v>29.715</v>
+        <v>29.7686</v>
       </c>
       <c r="D123" t="n">
-        <v>32.3025</v>
+        <v>32.2913</v>
       </c>
       <c r="E123" t="n">
-        <v>23.7275</v>
+        <v>23.7404</v>
       </c>
       <c r="F123" t="n">
-        <v>27.1154</v>
+        <v>27.1495</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>29.8777</v>
+        <v>29.8368</v>
       </c>
       <c r="C124" t="n">
-        <v>29.9967</v>
+        <v>29.7268</v>
       </c>
       <c r="D124" t="n">
-        <v>32.9503</v>
+        <v>32.7323</v>
       </c>
       <c r="E124" t="n">
-        <v>23.9718</v>
+        <v>23.8275</v>
       </c>
       <c r="F124" t="n">
-        <v>27.3319</v>
+        <v>27.1119</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>29.8456</v>
+        <v>29.8848</v>
       </c>
       <c r="C125" t="n">
-        <v>29.9223</v>
+        <v>29.947</v>
       </c>
       <c r="D125" t="n">
-        <v>33.4649</v>
+        <v>33.3309</v>
       </c>
       <c r="E125" t="n">
-        <v>24.0358</v>
+        <v>24.0681</v>
       </c>
       <c r="F125" t="n">
-        <v>27.3521</v>
+        <v>27.2627</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>29.8394</v>
+        <v>29.8593</v>
       </c>
       <c r="C126" t="n">
-        <v>30.0656</v>
+        <v>30.0778</v>
       </c>
       <c r="D126" t="n">
-        <v>34.0515</v>
+        <v>34.0403</v>
       </c>
       <c r="E126" t="n">
-        <v>24.1935</v>
+        <v>24.2011</v>
       </c>
       <c r="F126" t="n">
-        <v>27.4835</v>
+        <v>27.4627</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>29.7881</v>
+        <v>29.7272</v>
       </c>
       <c r="C127" t="n">
-        <v>30.097</v>
+        <v>30.0119</v>
       </c>
       <c r="D127" t="n">
-        <v>34.6691</v>
+        <v>34.6932</v>
       </c>
       <c r="E127" t="n">
-        <v>24.2888</v>
+        <v>24.4301</v>
       </c>
       <c r="F127" t="n">
-        <v>27.7456</v>
+        <v>27.6673</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.896</v>
+        <v>29.777</v>
       </c>
       <c r="C128" t="n">
-        <v>30.1465</v>
+        <v>30.423</v>
       </c>
       <c r="D128" t="n">
-        <v>35.2135</v>
+        <v>35.251</v>
       </c>
       <c r="E128" t="n">
-        <v>24.6011</v>
+        <v>24.5516</v>
       </c>
       <c r="F128" t="n">
-        <v>27.9863</v>
+        <v>27.8427</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>29.809</v>
+        <v>29.8669</v>
       </c>
       <c r="C129" t="n">
-        <v>30.2908</v>
+        <v>30.3546</v>
       </c>
       <c r="D129" t="n">
-        <v>35.8524</v>
+        <v>35.9747</v>
       </c>
       <c r="E129" t="n">
-        <v>24.7644</v>
+        <v>24.6677</v>
       </c>
       <c r="F129" t="n">
-        <v>28.0596</v>
+        <v>28.2547</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>29.8965</v>
+        <v>29.8097</v>
       </c>
       <c r="C130" t="n">
-        <v>30.5682</v>
+        <v>30.4756</v>
       </c>
       <c r="D130" t="n">
-        <v>36.6835</v>
+        <v>36.5453</v>
       </c>
       <c r="E130" t="n">
-        <v>24.9971</v>
+        <v>24.9776</v>
       </c>
       <c r="F130" t="n">
-        <v>28.273</v>
+        <v>28.3535</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.8677</v>
+        <v>29.8118</v>
       </c>
       <c r="C131" t="n">
-        <v>30.6322</v>
+        <v>30.5959</v>
       </c>
       <c r="D131" t="n">
-        <v>37.3784</v>
+        <v>37.4672</v>
       </c>
       <c r="E131" t="n">
-        <v>25.2964</v>
+        <v>25.1235</v>
       </c>
       <c r="F131" t="n">
-        <v>28.609</v>
+        <v>28.6692</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.8304</v>
+        <v>29.8991</v>
       </c>
       <c r="C132" t="n">
-        <v>30.7451</v>
+        <v>30.8665</v>
       </c>
       <c r="D132" t="n">
-        <v>38.1384</v>
+        <v>38.0954</v>
       </c>
       <c r="E132" t="n">
-        <v>25.4987</v>
+        <v>25.5649</v>
       </c>
       <c r="F132" t="n">
-        <v>29.0287</v>
+        <v>29.0344</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>29.9218</v>
+        <v>29.8229</v>
       </c>
       <c r="C133" t="n">
-        <v>31.0773</v>
+        <v>30.9372</v>
       </c>
       <c r="D133" t="n">
-        <v>39.0666</v>
+        <v>38.8895</v>
       </c>
       <c r="E133" t="n">
-        <v>25.7193</v>
+        <v>25.7473</v>
       </c>
       <c r="F133" t="n">
-        <v>29.5675</v>
+        <v>29.4415</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>29.9406</v>
+        <v>29.9696</v>
       </c>
       <c r="C134" t="n">
-        <v>31.4048</v>
+        <v>31.2014</v>
       </c>
       <c r="D134" t="n">
-        <v>39.8096</v>
+        <v>39.8055</v>
       </c>
       <c r="E134" t="n">
-        <v>26.1035</v>
+        <v>26.2364</v>
       </c>
       <c r="F134" t="n">
-        <v>30.0929</v>
+        <v>30.0476</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>30.0802</v>
+        <v>29.9162</v>
       </c>
       <c r="C135" t="n">
-        <v>31.7517</v>
+        <v>31.7552</v>
       </c>
       <c r="D135" t="n">
-        <v>33.1138</v>
+        <v>33.2217</v>
       </c>
       <c r="E135" t="n">
-        <v>26.1894</v>
+        <v>26.0297</v>
       </c>
       <c r="F135" t="n">
-        <v>29.4856</v>
+        <v>29.2993</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.2503</v>
+        <v>30.1398</v>
       </c>
       <c r="C136" t="n">
-        <v>31.6828</v>
+        <v>31.6524</v>
       </c>
       <c r="D136" t="n">
-        <v>33.6116</v>
+        <v>33.6848</v>
       </c>
       <c r="E136" t="n">
-        <v>26.1766</v>
+        <v>26.3175</v>
       </c>
       <c r="F136" t="n">
-        <v>29.5521</v>
+        <v>29.602</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.4287</v>
+        <v>30.3849</v>
       </c>
       <c r="C137" t="n">
-        <v>31.7935</v>
+        <v>31.6592</v>
       </c>
       <c r="D137" t="n">
-        <v>34.0162</v>
+        <v>34.1958</v>
       </c>
       <c r="E137" t="n">
-        <v>26.7253</v>
+        <v>26.5787</v>
       </c>
       <c r="F137" t="n">
-        <v>29.6601</v>
+        <v>29.7386</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>35.0556</v>
+        <v>35.1921</v>
       </c>
       <c r="C138" t="n">
-        <v>31.6735</v>
+        <v>31.8814</v>
       </c>
       <c r="D138" t="n">
-        <v>34.5788</v>
+        <v>34.5317</v>
       </c>
       <c r="E138" t="n">
-        <v>26.6891</v>
+        <v>26.6598</v>
       </c>
       <c r="F138" t="n">
-        <v>29.583</v>
+        <v>29.8888</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.2057</v>
+        <v>35.1316</v>
       </c>
       <c r="C139" t="n">
-        <v>31.8617</v>
+        <v>31.9512</v>
       </c>
       <c r="D139" t="n">
-        <v>35.1881</v>
+        <v>35.1219</v>
       </c>
       <c r="E139" t="n">
-        <v>26.7369</v>
+        <v>26.7891</v>
       </c>
       <c r="F139" t="n">
-        <v>29.7766</v>
+        <v>29.9101</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>35.2919</v>
+        <v>35.1517</v>
       </c>
       <c r="C140" t="n">
-        <v>32.0111</v>
+        <v>31.9783</v>
       </c>
       <c r="D140" t="n">
-        <v>35.7643</v>
+        <v>35.6807</v>
       </c>
       <c r="E140" t="n">
-        <v>26.9491</v>
+        <v>26.9637</v>
       </c>
       <c r="F140" t="n">
-        <v>29.9725</v>
+        <v>30.1935</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.0705</v>
+        <v>35.2478</v>
       </c>
       <c r="C141" t="n">
-        <v>32.0027</v>
+        <v>32.0236</v>
       </c>
       <c r="D141" t="n">
-        <v>36.2102</v>
+        <v>36.278</v>
       </c>
       <c r="E141" t="n">
-        <v>27.2384</v>
+        <v>26.8801</v>
       </c>
       <c r="F141" t="n">
-        <v>30.391</v>
+        <v>30.3138</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>35.3319</v>
+        <v>35.235</v>
       </c>
       <c r="C142" t="n">
-        <v>32.244</v>
+        <v>32.3271</v>
       </c>
       <c r="D142" t="n">
-        <v>36.8885</v>
+        <v>36.8457</v>
       </c>
       <c r="E142" t="n">
-        <v>27.3141</v>
+        <v>27.3265</v>
       </c>
       <c r="F142" t="n">
-        <v>30.4727</v>
+        <v>30.5755</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>35.1524</v>
+        <v>35.247</v>
       </c>
       <c r="C143" t="n">
-        <v>32.3218</v>
+        <v>32.4427</v>
       </c>
       <c r="D143" t="n">
-        <v>37.6496</v>
+        <v>37.6136</v>
       </c>
       <c r="E143" t="n">
-        <v>27.5136</v>
+        <v>27.4242</v>
       </c>
       <c r="F143" t="n">
-        <v>30.7703</v>
+        <v>30.7814</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.78262</v>
+        <v>2.78684</v>
       </c>
       <c r="C2" t="n">
-        <v>4.48099</v>
+        <v>4.5409</v>
       </c>
       <c r="D2" t="n">
-        <v>5.44236</v>
+        <v>5.42457</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2846</v>
+        <v>3.88736</v>
       </c>
       <c r="F2" t="n">
-        <v>3.64552</v>
+        <v>4.00944</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.8089</v>
+        <v>2.78524</v>
       </c>
       <c r="C3" t="n">
-        <v>4.50676</v>
+        <v>4.55906</v>
       </c>
       <c r="D3" t="n">
-        <v>5.64114</v>
+        <v>5.7362</v>
       </c>
       <c r="E3" t="n">
-        <v>3.28093</v>
+        <v>3.89453</v>
       </c>
       <c r="F3" t="n">
-        <v>3.64769</v>
+        <v>4.01049</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.83277</v>
+        <v>2.81309</v>
       </c>
       <c r="C4" t="n">
-        <v>4.53658</v>
+        <v>4.59621</v>
       </c>
       <c r="D4" t="n">
-        <v>6.11339</v>
+        <v>6.17019</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3047</v>
+        <v>3.91311</v>
       </c>
       <c r="F4" t="n">
-        <v>3.67188</v>
+        <v>4.04558</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.85579</v>
+        <v>2.83056</v>
       </c>
       <c r="C5" t="n">
-        <v>4.55391</v>
+        <v>4.64149</v>
       </c>
       <c r="D5" t="n">
-        <v>6.37789</v>
+        <v>6.49925</v>
       </c>
       <c r="E5" t="n">
-        <v>3.35008</v>
+        <v>3.93975</v>
       </c>
       <c r="F5" t="n">
-        <v>3.69503</v>
+        <v>4.08654</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.88507</v>
+        <v>2.85869</v>
       </c>
       <c r="C6" t="n">
-        <v>4.62273</v>
+        <v>4.71375</v>
       </c>
       <c r="D6" t="n">
-        <v>6.74651</v>
+        <v>6.9429</v>
       </c>
       <c r="E6" t="n">
-        <v>3.37017</v>
+        <v>3.96152</v>
       </c>
       <c r="F6" t="n">
-        <v>3.76553</v>
+        <v>4.16083</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.91301</v>
+        <v>2.88229</v>
       </c>
       <c r="C7" t="n">
-        <v>4.66653</v>
+        <v>4.76535</v>
       </c>
       <c r="D7" t="n">
-        <v>5.07833</v>
+        <v>5.14033</v>
       </c>
       <c r="E7" t="n">
-        <v>3.29518</v>
+        <v>3.86374</v>
       </c>
       <c r="F7" t="n">
-        <v>3.67352</v>
+        <v>4.04947</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.98209</v>
+        <v>2.90896</v>
       </c>
       <c r="C8" t="n">
-        <v>4.53996</v>
+        <v>4.84528</v>
       </c>
       <c r="D8" t="n">
-        <v>5.21807</v>
+        <v>5.31581</v>
       </c>
       <c r="E8" t="n">
-        <v>3.32444</v>
+        <v>3.8901</v>
       </c>
       <c r="F8" t="n">
-        <v>3.69463</v>
+        <v>4.07833</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>2.98822</v>
+        <v>2.9733</v>
       </c>
       <c r="C9" t="n">
-        <v>4.52413</v>
+        <v>4.83918</v>
       </c>
       <c r="D9" t="n">
-        <v>5.43239</v>
+        <v>5.53076</v>
       </c>
       <c r="E9" t="n">
-        <v>3.33339</v>
+        <v>3.91051</v>
       </c>
       <c r="F9" t="n">
-        <v>3.73098</v>
+        <v>4.10921</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.414</v>
+        <v>3.40813</v>
       </c>
       <c r="C10" t="n">
-        <v>4.5587</v>
+        <v>4.86257</v>
       </c>
       <c r="D10" t="n">
-        <v>5.69395</v>
+        <v>5.79279</v>
       </c>
       <c r="E10" t="n">
-        <v>3.37331</v>
+        <v>3.93613</v>
       </c>
       <c r="F10" t="n">
-        <v>3.75679</v>
+        <v>4.15084</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.42066</v>
+        <v>3.42317</v>
       </c>
       <c r="C11" t="n">
-        <v>4.55199</v>
+        <v>4.84206</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9275</v>
+        <v>6.01959</v>
       </c>
       <c r="E11" t="n">
-        <v>3.39681</v>
+        <v>3.9278</v>
       </c>
       <c r="F11" t="n">
-        <v>3.78722</v>
+        <v>4.15128</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.42828</v>
+        <v>3.43705</v>
       </c>
       <c r="C12" t="n">
-        <v>4.53628</v>
+        <v>4.90423</v>
       </c>
       <c r="D12" t="n">
-        <v>6.20841</v>
+        <v>6.30423</v>
       </c>
       <c r="E12" t="n">
-        <v>3.40574</v>
+        <v>3.96455</v>
       </c>
       <c r="F12" t="n">
-        <v>3.80928</v>
+        <v>4.19024</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.43899</v>
+        <v>3.45571</v>
       </c>
       <c r="C13" t="n">
-        <v>4.56325</v>
+        <v>4.92098</v>
       </c>
       <c r="D13" t="n">
-        <v>6.46514</v>
+        <v>6.63004</v>
       </c>
       <c r="E13" t="n">
-        <v>3.45144</v>
+        <v>3.99154</v>
       </c>
       <c r="F13" t="n">
-        <v>3.84123</v>
+        <v>4.19279</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.46162</v>
+        <v>3.4466</v>
       </c>
       <c r="C14" t="n">
-        <v>4.56089</v>
+        <v>4.88038</v>
       </c>
       <c r="D14" t="n">
-        <v>6.76134</v>
+        <v>6.90913</v>
       </c>
       <c r="E14" t="n">
-        <v>3.45604</v>
+        <v>4.00843</v>
       </c>
       <c r="F14" t="n">
-        <v>3.85531</v>
+        <v>4.2327</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.47116</v>
+        <v>3.46629</v>
       </c>
       <c r="C15" t="n">
-        <v>4.5831</v>
+        <v>4.96189</v>
       </c>
       <c r="D15" t="n">
-        <v>6.99496</v>
+        <v>7.18141</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4799</v>
+        <v>4.03184</v>
       </c>
       <c r="F15" t="n">
-        <v>3.86974</v>
+        <v>4.24432</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.48463</v>
+        <v>3.46969</v>
       </c>
       <c r="C16" t="n">
-        <v>4.60761</v>
+        <v>4.97441</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3052</v>
+        <v>7.44195</v>
       </c>
       <c r="E16" t="n">
-        <v>3.53329</v>
+        <v>4.07945</v>
       </c>
       <c r="F16" t="n">
-        <v>3.92458</v>
+        <v>4.28883</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.50677</v>
+        <v>3.51003</v>
       </c>
       <c r="C17" t="n">
-        <v>4.65641</v>
+        <v>5.00076</v>
       </c>
       <c r="D17" t="n">
-        <v>7.55144</v>
+        <v>7.70302</v>
       </c>
       <c r="E17" t="n">
-        <v>3.56033</v>
+        <v>4.09745</v>
       </c>
       <c r="F17" t="n">
-        <v>3.93596</v>
+        <v>4.30581</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.53807</v>
+        <v>3.52649</v>
       </c>
       <c r="C18" t="n">
-        <v>4.68529</v>
+        <v>5.04659</v>
       </c>
       <c r="D18" t="n">
-        <v>7.81272</v>
+        <v>7.98568</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6014</v>
+        <v>4.13723</v>
       </c>
       <c r="F18" t="n">
-        <v>3.96598</v>
+        <v>4.35351</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.55124</v>
+        <v>3.56161</v>
       </c>
       <c r="C19" t="n">
-        <v>4.75619</v>
+        <v>5.06043</v>
       </c>
       <c r="D19" t="n">
-        <v>8.1211</v>
+        <v>8.28417</v>
       </c>
       <c r="E19" t="n">
-        <v>3.63898</v>
+        <v>4.17481</v>
       </c>
       <c r="F19" t="n">
-        <v>4.00309</v>
+        <v>4.39498</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.57954</v>
+        <v>3.59424</v>
       </c>
       <c r="C20" t="n">
-        <v>4.80578</v>
+        <v>5.13711</v>
       </c>
       <c r="D20" t="n">
-        <v>8.346069999999999</v>
+        <v>8.49849</v>
       </c>
       <c r="E20" t="n">
-        <v>3.69301</v>
+        <v>4.24137</v>
       </c>
       <c r="F20" t="n">
-        <v>4.09304</v>
+        <v>4.48596</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.61211</v>
+        <v>3.62055</v>
       </c>
       <c r="C21" t="n">
-        <v>4.85311</v>
+        <v>5.20606</v>
       </c>
       <c r="D21" t="n">
-        <v>6.24691</v>
+        <v>6.28477</v>
       </c>
       <c r="E21" t="n">
-        <v>3.64118</v>
+        <v>4.13554</v>
       </c>
       <c r="F21" t="n">
-        <v>4.04907</v>
+        <v>4.5068</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.67934</v>
+        <v>3.67162</v>
       </c>
       <c r="C22" t="n">
-        <v>4.74038</v>
+        <v>5.22019</v>
       </c>
       <c r="D22" t="n">
-        <v>6.44765</v>
+        <v>6.53181</v>
       </c>
       <c r="E22" t="n">
-        <v>3.58663</v>
+        <v>4.19036</v>
       </c>
       <c r="F22" t="n">
-        <v>4.06378</v>
+        <v>4.5417</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.74157</v>
+        <v>3.72625</v>
       </c>
       <c r="C23" t="n">
-        <v>4.7531</v>
+        <v>5.26461</v>
       </c>
       <c r="D23" t="n">
-        <v>6.66263</v>
+        <v>6.73189</v>
       </c>
       <c r="E23" t="n">
-        <v>3.6212</v>
+        <v>4.17088</v>
       </c>
       <c r="F23" t="n">
-        <v>4.07513</v>
+        <v>4.54387</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.92523</v>
+        <v>3.91438</v>
       </c>
       <c r="C24" t="n">
-        <v>4.77259</v>
+        <v>5.2256</v>
       </c>
       <c r="D24" t="n">
-        <v>6.91544</v>
+        <v>7.02569</v>
       </c>
       <c r="E24" t="n">
-        <v>3.63408</v>
+        <v>4.20188</v>
       </c>
       <c r="F24" t="n">
-        <v>4.11605</v>
+        <v>4.57395</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.94325</v>
+        <v>3.93787</v>
       </c>
       <c r="C25" t="n">
-        <v>4.83994</v>
+        <v>5.33655</v>
       </c>
       <c r="D25" t="n">
-        <v>7.16488</v>
+        <v>7.26107</v>
       </c>
       <c r="E25" t="n">
-        <v>3.71655</v>
+        <v>4.24844</v>
       </c>
       <c r="F25" t="n">
-        <v>4.14188</v>
+        <v>4.60225</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.9411</v>
+        <v>3.92704</v>
       </c>
       <c r="C26" t="n">
-        <v>4.83997</v>
+        <v>5.22624</v>
       </c>
       <c r="D26" t="n">
-        <v>7.34851</v>
+        <v>7.48242</v>
       </c>
       <c r="E26" t="n">
-        <v>3.70965</v>
+        <v>4.26125</v>
       </c>
       <c r="F26" t="n">
-        <v>4.17189</v>
+        <v>4.63442</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.93408</v>
+        <v>3.94555</v>
       </c>
       <c r="C27" t="n">
-        <v>4.81458</v>
+        <v>5.26405</v>
       </c>
       <c r="D27" t="n">
-        <v>7.63087</v>
+        <v>7.75742</v>
       </c>
       <c r="E27" t="n">
-        <v>3.79924</v>
+        <v>4.27942</v>
       </c>
       <c r="F27" t="n">
-        <v>4.20828</v>
+        <v>4.65824</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.94069</v>
+        <v>3.93537</v>
       </c>
       <c r="C28" t="n">
-        <v>4.82567</v>
+        <v>5.33618</v>
       </c>
       <c r="D28" t="n">
-        <v>7.87429</v>
+        <v>8.00337</v>
       </c>
       <c r="E28" t="n">
-        <v>3.8074</v>
+        <v>4.35499</v>
       </c>
       <c r="F28" t="n">
-        <v>4.24555</v>
+        <v>4.68304</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.95486</v>
+        <v>3.96495</v>
       </c>
       <c r="C29" t="n">
-        <v>4.83244</v>
+        <v>5.32442</v>
       </c>
       <c r="D29" t="n">
-        <v>8.09455</v>
+        <v>8.2667</v>
       </c>
       <c r="E29" t="n">
-        <v>3.84804</v>
+        <v>4.38851</v>
       </c>
       <c r="F29" t="n">
-        <v>4.27314</v>
+        <v>4.69565</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.98072</v>
+        <v>3.96886</v>
       </c>
       <c r="C30" t="n">
-        <v>4.87722</v>
+        <v>5.40935</v>
       </c>
       <c r="D30" t="n">
-        <v>8.345840000000001</v>
+        <v>8.54987</v>
       </c>
       <c r="E30" t="n">
-        <v>3.8402</v>
+        <v>4.35598</v>
       </c>
       <c r="F30" t="n">
-        <v>4.31475</v>
+        <v>4.73712</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.98947</v>
+        <v>4.00135</v>
       </c>
       <c r="C31" t="n">
-        <v>4.94023</v>
+        <v>5.35808</v>
       </c>
       <c r="D31" t="n">
-        <v>8.616619999999999</v>
+        <v>8.76878</v>
       </c>
       <c r="E31" t="n">
-        <v>3.96741</v>
+        <v>4.40079</v>
       </c>
       <c r="F31" t="n">
-        <v>4.34578</v>
+        <v>4.78346</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.01516</v>
+        <v>3.99849</v>
       </c>
       <c r="C32" t="n">
-        <v>4.95068</v>
+        <v>5.40429</v>
       </c>
       <c r="D32" t="n">
-        <v>8.874140000000001</v>
+        <v>9.004160000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>3.92607</v>
+        <v>4.43087</v>
       </c>
       <c r="F32" t="n">
-        <v>4.40219</v>
+        <v>4.82469</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.05356</v>
+        <v>4.05683</v>
       </c>
       <c r="C33" t="n">
-        <v>4.97063</v>
+        <v>5.52158</v>
       </c>
       <c r="D33" t="n">
-        <v>9.116630000000001</v>
+        <v>9.247350000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>4.03797</v>
+        <v>4.56743</v>
       </c>
       <c r="F33" t="n">
-        <v>4.44759</v>
+        <v>4.90198</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.08731</v>
+        <v>4.0811</v>
       </c>
       <c r="C34" t="n">
-        <v>5.06313</v>
+        <v>5.58255</v>
       </c>
       <c r="D34" t="n">
-        <v>9.356780000000001</v>
+        <v>9.489269999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>4.17229</v>
+        <v>4.60126</v>
       </c>
       <c r="F34" t="n">
-        <v>4.58206</v>
+        <v>4.99071</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.12672</v>
+        <v>4.13285</v>
       </c>
       <c r="C35" t="n">
-        <v>5.19911</v>
+        <v>5.64236</v>
       </c>
       <c r="D35" t="n">
-        <v>6.71739</v>
+        <v>6.84559</v>
       </c>
       <c r="E35" t="n">
-        <v>3.93909</v>
+        <v>4.43326</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39292</v>
+        <v>4.83733</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.20593</v>
+        <v>4.22436</v>
       </c>
       <c r="C36" t="n">
-        <v>5.23521</v>
+        <v>5.7983</v>
       </c>
       <c r="D36" t="n">
-        <v>6.88667</v>
+        <v>7.01444</v>
       </c>
       <c r="E36" t="n">
-        <v>3.96352</v>
+        <v>4.40977</v>
       </c>
       <c r="F36" t="n">
-        <v>4.39746</v>
+        <v>4.88006</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.42548</v>
+        <v>4.41766</v>
       </c>
       <c r="C37" t="n">
-        <v>5.02008</v>
+        <v>5.57476</v>
       </c>
       <c r="D37" t="n">
-        <v>7.05813</v>
+        <v>7.20785</v>
       </c>
       <c r="E37" t="n">
-        <v>4.01615</v>
+        <v>4.49022</v>
       </c>
       <c r="F37" t="n">
-        <v>4.44934</v>
+        <v>4.89485</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.1784</v>
+        <v>4.20417</v>
       </c>
       <c r="C38" t="n">
-        <v>5.06402</v>
+        <v>5.5449</v>
       </c>
       <c r="D38" t="n">
-        <v>7.26121</v>
+        <v>7.4164</v>
       </c>
       <c r="E38" t="n">
-        <v>4.03519</v>
+        <v>4.5171</v>
       </c>
       <c r="F38" t="n">
-        <v>4.4996</v>
+        <v>4.89887</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.22669</v>
+        <v>4.1774</v>
       </c>
       <c r="C39" t="n">
-        <v>5.05394</v>
+        <v>5.5559</v>
       </c>
       <c r="D39" t="n">
-        <v>7.46894</v>
+        <v>7.64624</v>
       </c>
       <c r="E39" t="n">
-        <v>4.0023</v>
+        <v>4.54055</v>
       </c>
       <c r="F39" t="n">
-        <v>4.45485</v>
+        <v>4.89589</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.20192</v>
+        <v>4.24553</v>
       </c>
       <c r="C40" t="n">
-        <v>5.09747</v>
+        <v>5.61905</v>
       </c>
       <c r="D40" t="n">
-        <v>7.75179</v>
+        <v>7.89368</v>
       </c>
       <c r="E40" t="n">
-        <v>4.08031</v>
+        <v>4.59921</v>
       </c>
       <c r="F40" t="n">
-        <v>4.48634</v>
+        <v>4.9954</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.19828</v>
+        <v>4.19327</v>
       </c>
       <c r="C41" t="n">
-        <v>5.11691</v>
+        <v>5.63422</v>
       </c>
       <c r="D41" t="n">
-        <v>7.95824</v>
+        <v>8.143599999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>4.12689</v>
+        <v>4.61189</v>
       </c>
       <c r="F41" t="n">
-        <v>4.46013</v>
+        <v>5.00281</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.18995</v>
+        <v>4.28032</v>
       </c>
       <c r="C42" t="n">
-        <v>5.15041</v>
+        <v>5.62503</v>
       </c>
       <c r="D42" t="n">
-        <v>8.227309999999999</v>
+        <v>8.371040000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>4.15372</v>
+        <v>4.66568</v>
       </c>
       <c r="F42" t="n">
-        <v>4.54133</v>
+        <v>5.03659</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.19577</v>
+        <v>4.23979</v>
       </c>
       <c r="C43" t="n">
-        <v>5.15992</v>
+        <v>5.66979</v>
       </c>
       <c r="D43" t="n">
-        <v>8.468260000000001</v>
+        <v>8.653230000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>4.18901</v>
+        <v>4.70085</v>
       </c>
       <c r="F43" t="n">
-        <v>4.60404</v>
+        <v>5.04972</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.2358</v>
+        <v>4.21991</v>
       </c>
       <c r="C44" t="n">
-        <v>5.15622</v>
+        <v>5.68045</v>
       </c>
       <c r="D44" t="n">
-        <v>8.702579999999999</v>
+        <v>8.9069</v>
       </c>
       <c r="E44" t="n">
-        <v>4.23003</v>
+        <v>4.71356</v>
       </c>
       <c r="F44" t="n">
-        <v>4.63624</v>
+        <v>5.10924</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.19822</v>
+        <v>4.27109</v>
       </c>
       <c r="C45" t="n">
-        <v>5.20758</v>
+        <v>5.69605</v>
       </c>
       <c r="D45" t="n">
-        <v>8.9703</v>
+        <v>9.15779</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27691</v>
+        <v>4.79263</v>
       </c>
       <c r="F45" t="n">
-        <v>4.73477</v>
+        <v>5.15802</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.2962</v>
+        <v>4.29285</v>
       </c>
       <c r="C46" t="n">
-        <v>5.26324</v>
+        <v>5.75058</v>
       </c>
       <c r="D46" t="n">
-        <v>9.25342</v>
+        <v>9.36913</v>
       </c>
       <c r="E46" t="n">
-        <v>4.34075</v>
+        <v>4.8427</v>
       </c>
       <c r="F46" t="n">
-        <v>4.76198</v>
+        <v>5.21322</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.27331</v>
+        <v>4.32511</v>
       </c>
       <c r="C47" t="n">
-        <v>5.32715</v>
+        <v>5.83803</v>
       </c>
       <c r="D47" t="n">
-        <v>9.422029999999999</v>
+        <v>9.62233</v>
       </c>
       <c r="E47" t="n">
-        <v>4.42686</v>
+        <v>4.9379</v>
       </c>
       <c r="F47" t="n">
-        <v>4.84208</v>
+        <v>5.34204</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.3533</v>
+        <v>4.37632</v>
       </c>
       <c r="C48" t="n">
-        <v>5.38649</v>
+        <v>5.8416</v>
       </c>
       <c r="D48" t="n">
-        <v>9.69918</v>
+        <v>9.882709999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>4.58895</v>
+        <v>5.08012</v>
       </c>
       <c r="F48" t="n">
-        <v>5.03434</v>
+        <v>5.44474</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.41293</v>
+        <v>4.4032</v>
       </c>
       <c r="C49" t="n">
-        <v>5.45466</v>
+        <v>6.00206</v>
       </c>
       <c r="D49" t="n">
-        <v>9.91835</v>
+        <v>10.1162</v>
       </c>
       <c r="E49" t="n">
-        <v>4.8454</v>
+        <v>5.33</v>
       </c>
       <c r="F49" t="n">
-        <v>5.28317</v>
+        <v>5.73348</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.50306</v>
+        <v>4.5478</v>
       </c>
       <c r="C50" t="n">
-        <v>5.58974</v>
+        <v>6.11137</v>
       </c>
       <c r="D50" t="n">
-        <v>7.00343</v>
+        <v>7.14368</v>
       </c>
       <c r="E50" t="n">
-        <v>4.30424</v>
+        <v>4.80564</v>
       </c>
       <c r="F50" t="n">
-        <v>4.64614</v>
+        <v>5.14543</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.76142</v>
+        <v>4.74327</v>
       </c>
       <c r="C51" t="n">
-        <v>5.43744</v>
+        <v>5.94262</v>
       </c>
       <c r="D51" t="n">
-        <v>7.16743</v>
+        <v>7.32539</v>
       </c>
       <c r="E51" t="n">
-        <v>4.34261</v>
+        <v>4.83276</v>
       </c>
       <c r="F51" t="n">
-        <v>4.68609</v>
+        <v>5.16889</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.11385</v>
+        <v>5.08754</v>
       </c>
       <c r="C52" t="n">
-        <v>5.48404</v>
+        <v>5.99561</v>
       </c>
       <c r="D52" t="n">
-        <v>7.36239</v>
+        <v>7.504</v>
       </c>
       <c r="E52" t="n">
-        <v>4.36509</v>
+        <v>4.84938</v>
       </c>
       <c r="F52" t="n">
-        <v>4.68977</v>
+        <v>5.16571</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.76011</v>
+        <v>4.76938</v>
       </c>
       <c r="C53" t="n">
-        <v>5.52428</v>
+        <v>5.98844</v>
       </c>
       <c r="D53" t="n">
-        <v>7.58171</v>
+        <v>7.77121</v>
       </c>
       <c r="E53" t="n">
-        <v>4.37051</v>
+        <v>4.87676</v>
       </c>
       <c r="F53" t="n">
-        <v>4.73597</v>
+        <v>5.1657</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.76836</v>
+        <v>4.76662</v>
       </c>
       <c r="C54" t="n">
-        <v>5.48755</v>
+        <v>5.97762</v>
       </c>
       <c r="D54" t="n">
-        <v>7.79357</v>
+        <v>8.00389</v>
       </c>
       <c r="E54" t="n">
-        <v>4.42483</v>
+        <v>4.93212</v>
       </c>
       <c r="F54" t="n">
-        <v>4.77932</v>
+        <v>5.22857</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.77398</v>
+        <v>4.74368</v>
       </c>
       <c r="C55" t="n">
-        <v>5.5267</v>
+        <v>6.03157</v>
       </c>
       <c r="D55" t="n">
-        <v>8.06331</v>
+        <v>8.239369999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>4.46207</v>
+        <v>4.93493</v>
       </c>
       <c r="F55" t="n">
-        <v>4.81648</v>
+        <v>5.29365</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.77681</v>
+        <v>4.7941</v>
       </c>
       <c r="C56" t="n">
-        <v>5.5143</v>
+        <v>6.06145</v>
       </c>
       <c r="D56" t="n">
-        <v>8.282389999999999</v>
+        <v>8.48611</v>
       </c>
       <c r="E56" t="n">
-        <v>4.46519</v>
+        <v>4.98817</v>
       </c>
       <c r="F56" t="n">
-        <v>4.81604</v>
+        <v>5.32506</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.76523</v>
+        <v>4.80819</v>
       </c>
       <c r="C57" t="n">
-        <v>5.53302</v>
+        <v>6.08068</v>
       </c>
       <c r="D57" t="n">
-        <v>8.58344</v>
+        <v>8.768079999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>4.54613</v>
+        <v>5.05443</v>
       </c>
       <c r="F57" t="n">
-        <v>4.89165</v>
+        <v>5.36824</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.78864</v>
+        <v>4.77944</v>
       </c>
       <c r="C58" t="n">
-        <v>5.5971</v>
+        <v>6.11868</v>
       </c>
       <c r="D58" t="n">
-        <v>8.805339999999999</v>
+        <v>9.045199999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>4.53783</v>
+        <v>5.05923</v>
       </c>
       <c r="F58" t="n">
-        <v>4.92723</v>
+        <v>5.39494</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.82278</v>
+        <v>4.81816</v>
       </c>
       <c r="C59" t="n">
-        <v>5.59957</v>
+        <v>6.12808</v>
       </c>
       <c r="D59" t="n">
-        <v>9.067909999999999</v>
+        <v>9.242419999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>4.63409</v>
+        <v>5.14413</v>
       </c>
       <c r="F59" t="n">
-        <v>4.99513</v>
+        <v>5.47658</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.83803</v>
+        <v>4.84292</v>
       </c>
       <c r="C60" t="n">
-        <v>5.62254</v>
+        <v>6.1471</v>
       </c>
       <c r="D60" t="n">
-        <v>9.303979999999999</v>
+        <v>9.487450000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>4.70252</v>
+        <v>5.22879</v>
       </c>
       <c r="F60" t="n">
-        <v>5.05295</v>
+        <v>5.58914</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.87448</v>
+        <v>4.83284</v>
       </c>
       <c r="C61" t="n">
-        <v>5.67811</v>
+        <v>6.25833</v>
       </c>
       <c r="D61" t="n">
-        <v>9.57887</v>
+        <v>9.783379999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>4.80215</v>
+        <v>5.36052</v>
       </c>
       <c r="F61" t="n">
-        <v>5.19465</v>
+        <v>5.70852</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.90721</v>
+        <v>4.92625</v>
       </c>
       <c r="C62" t="n">
-        <v>5.74677</v>
+        <v>6.31707</v>
       </c>
       <c r="D62" t="n">
-        <v>9.81209</v>
+        <v>10.0162</v>
       </c>
       <c r="E62" t="n">
-        <v>4.99349</v>
+        <v>5.50943</v>
       </c>
       <c r="F62" t="n">
-        <v>5.38167</v>
+        <v>5.89134</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.93976</v>
+        <v>4.95339</v>
       </c>
       <c r="C63" t="n">
-        <v>5.89494</v>
+        <v>6.41525</v>
       </c>
       <c r="D63" t="n">
-        <v>10.1302</v>
+        <v>10.2587</v>
       </c>
       <c r="E63" t="n">
-        <v>5.18282</v>
+        <v>5.74494</v>
       </c>
       <c r="F63" t="n">
-        <v>5.57744</v>
+        <v>6.09161</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.07927</v>
+        <v>5.05091</v>
       </c>
       <c r="C64" t="n">
-        <v>5.98853</v>
+        <v>6.56677</v>
       </c>
       <c r="D64" t="n">
-        <v>7.22311</v>
+        <v>7.37446</v>
       </c>
       <c r="E64" t="n">
-        <v>4.5974</v>
+        <v>5.11412</v>
       </c>
       <c r="F64" t="n">
-        <v>4.86741</v>
+        <v>5.34094</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.22715</v>
+        <v>5.27946</v>
       </c>
       <c r="C65" t="n">
-        <v>5.76294</v>
+        <v>6.2914</v>
       </c>
       <c r="D65" t="n">
-        <v>7.42362</v>
+        <v>7.60869</v>
       </c>
       <c r="E65" t="n">
-        <v>4.61974</v>
+        <v>5.13946</v>
       </c>
       <c r="F65" t="n">
-        <v>4.92383</v>
+        <v>5.37675</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.52738</v>
+        <v>5.5984</v>
       </c>
       <c r="C66" t="n">
-        <v>5.78722</v>
+        <v>6.33606</v>
       </c>
       <c r="D66" t="n">
-        <v>7.6955</v>
+        <v>7.85155</v>
       </c>
       <c r="E66" t="n">
-        <v>4.64826</v>
+        <v>5.16681</v>
       </c>
       <c r="F66" t="n">
-        <v>4.94298</v>
+        <v>5.40176</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.53023</v>
+        <v>5.52099</v>
       </c>
       <c r="C67" t="n">
-        <v>5.74874</v>
+        <v>6.32449</v>
       </c>
       <c r="D67" t="n">
-        <v>7.95533</v>
+        <v>8.124980000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>4.64557</v>
+        <v>5.16532</v>
       </c>
       <c r="F67" t="n">
-        <v>4.95322</v>
+        <v>5.40732</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.49232</v>
+        <v>5.59872</v>
       </c>
       <c r="C68" t="n">
-        <v>5.78742</v>
+        <v>6.3858</v>
       </c>
       <c r="D68" t="n">
-        <v>8.21397</v>
+        <v>8.447089999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>4.66805</v>
+        <v>5.2128</v>
       </c>
       <c r="F68" t="n">
-        <v>5.03867</v>
+        <v>5.59304</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.54229</v>
+        <v>5.56679</v>
       </c>
       <c r="C69" t="n">
-        <v>5.76029</v>
+        <v>6.35879</v>
       </c>
       <c r="D69" t="n">
-        <v>8.51957</v>
+        <v>8.75836</v>
       </c>
       <c r="E69" t="n">
-        <v>4.72185</v>
+        <v>5.24209</v>
       </c>
       <c r="F69" t="n">
-        <v>5.09585</v>
+        <v>5.61902</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.54125</v>
+        <v>5.64783</v>
       </c>
       <c r="C70" t="n">
-        <v>5.81233</v>
+        <v>6.39462</v>
       </c>
       <c r="D70" t="n">
-        <v>8.81912</v>
+        <v>9.050280000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>4.74926</v>
+        <v>5.26831</v>
       </c>
       <c r="F70" t="n">
-        <v>5.27302</v>
+        <v>5.77442</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.55415</v>
+        <v>5.55404</v>
       </c>
       <c r="C71" t="n">
-        <v>5.83173</v>
+        <v>6.40677</v>
       </c>
       <c r="D71" t="n">
-        <v>9.16086</v>
+        <v>9.371980000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>4.79578</v>
+        <v>5.30995</v>
       </c>
       <c r="F71" t="n">
-        <v>5.62885</v>
+        <v>6.28842</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.51892</v>
+        <v>5.56922</v>
       </c>
       <c r="C72" t="n">
-        <v>5.84008</v>
+        <v>6.43838</v>
       </c>
       <c r="D72" t="n">
-        <v>9.523400000000001</v>
+        <v>9.65649</v>
       </c>
       <c r="E72" t="n">
-        <v>4.8477</v>
+        <v>5.35354</v>
       </c>
       <c r="F72" t="n">
-        <v>5.99111</v>
+        <v>6.44913</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.57242</v>
+        <v>5.66683</v>
       </c>
       <c r="C73" t="n">
-        <v>5.90322</v>
+        <v>6.48381</v>
       </c>
       <c r="D73" t="n">
-        <v>10.0434</v>
+        <v>10.2565</v>
       </c>
       <c r="E73" t="n">
-        <v>4.91056</v>
+        <v>5.44083</v>
       </c>
       <c r="F73" t="n">
-        <v>6.47871</v>
+        <v>7.36467</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.61516</v>
+        <v>5.66649</v>
       </c>
       <c r="C74" t="n">
-        <v>5.9442</v>
+        <v>6.51271</v>
       </c>
       <c r="D74" t="n">
-        <v>10.3211</v>
+        <v>10.8058</v>
       </c>
       <c r="E74" t="n">
-        <v>4.97372</v>
+        <v>5.51269</v>
       </c>
       <c r="F74" t="n">
-        <v>7.24326</v>
+        <v>8.008839999999999</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.62344</v>
+        <v>5.65999</v>
       </c>
       <c r="C75" t="n">
-        <v>6.02058</v>
+        <v>6.55917</v>
       </c>
       <c r="D75" t="n">
-        <v>11.2298</v>
+        <v>11.4116</v>
       </c>
       <c r="E75" t="n">
-        <v>5.09232</v>
+        <v>5.61547</v>
       </c>
       <c r="F75" t="n">
-        <v>8.165710000000001</v>
+        <v>8.89817</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.6972</v>
+        <v>5.68302</v>
       </c>
       <c r="C76" t="n">
-        <v>6.03811</v>
+        <v>6.63321</v>
       </c>
       <c r="D76" t="n">
-        <v>11.8319</v>
+        <v>12.0946</v>
       </c>
       <c r="E76" t="n">
-        <v>5.23504</v>
+        <v>5.77202</v>
       </c>
       <c r="F76" t="n">
-        <v>8.909129999999999</v>
+        <v>9.55917</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.72108</v>
+        <v>5.78347</v>
       </c>
       <c r="C77" t="n">
-        <v>6.15744</v>
+        <v>6.74035</v>
       </c>
       <c r="D77" t="n">
-        <v>12.8675</v>
+        <v>13.2006</v>
       </c>
       <c r="E77" t="n">
-        <v>5.44769</v>
+        <v>5.98177</v>
       </c>
       <c r="F77" t="n">
-        <v>9.420959999999999</v>
+        <v>10.2634</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.82921</v>
+        <v>5.88944</v>
       </c>
       <c r="C78" t="n">
-        <v>6.28409</v>
+        <v>6.88434</v>
       </c>
       <c r="D78" t="n">
-        <v>14.9375</v>
+        <v>15.0916</v>
       </c>
       <c r="E78" t="n">
-        <v>5.68437</v>
+        <v>6.40215</v>
       </c>
       <c r="F78" t="n">
-        <v>10.7621</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>5.99255</v>
+        <v>6.03409</v>
       </c>
       <c r="C79" t="n">
-        <v>13.5173</v>
+        <v>13.8842</v>
       </c>
       <c r="D79" t="n">
-        <v>15.6744</v>
+        <v>15.7975</v>
       </c>
       <c r="E79" t="n">
-        <v>5.94126</v>
+        <v>6.56624</v>
       </c>
       <c r="F79" t="n">
-        <v>10.9811</v>
+        <v>11.884</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.23646</v>
+        <v>6.27199</v>
       </c>
       <c r="C80" t="n">
-        <v>13.6685</v>
+        <v>14.0655</v>
       </c>
       <c r="D80" t="n">
-        <v>16.4343</v>
+        <v>16.5331</v>
       </c>
       <c r="E80" t="n">
-        <v>6.02543</v>
+        <v>6.55735</v>
       </c>
       <c r="F80" t="n">
-        <v>11.0253</v>
+        <v>11.9451</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>13.4608</v>
+        <v>13.6596</v>
       </c>
       <c r="C81" t="n">
-        <v>13.5002</v>
+        <v>14.128</v>
       </c>
       <c r="D81" t="n">
-        <v>17.0807</v>
+        <v>17.2646</v>
       </c>
       <c r="E81" t="n">
-        <v>6.10677</v>
+        <v>6.82306</v>
       </c>
       <c r="F81" t="n">
-        <v>11.0782</v>
+        <v>11.9125</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.6422</v>
+        <v>13.6514</v>
       </c>
       <c r="C82" t="n">
-        <v>13.6555</v>
+        <v>14.2417</v>
       </c>
       <c r="D82" t="n">
-        <v>17.8014</v>
+        <v>17.9128</v>
       </c>
       <c r="E82" t="n">
-        <v>6.40182</v>
+        <v>6.88466</v>
       </c>
       <c r="F82" t="n">
-        <v>11.1876</v>
+        <v>12.1348</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.7219</v>
+        <v>13.8818</v>
       </c>
       <c r="C83" t="n">
-        <v>13.7999</v>
+        <v>14.4407</v>
       </c>
       <c r="D83" t="n">
-        <v>18.4762</v>
+        <v>18.6659</v>
       </c>
       <c r="E83" t="n">
-        <v>6.46345</v>
+        <v>7.16849</v>
       </c>
       <c r="F83" t="n">
-        <v>11.1585</v>
+        <v>12.1904</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.8468</v>
+        <v>13.9472</v>
       </c>
       <c r="C84" t="n">
-        <v>13.9412</v>
+        <v>14.317</v>
       </c>
       <c r="D84" t="n">
-        <v>19.1305</v>
+        <v>19.2976</v>
       </c>
       <c r="E84" t="n">
-        <v>6.74544</v>
+        <v>7.2822</v>
       </c>
       <c r="F84" t="n">
-        <v>11.3538</v>
+        <v>12.314</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.9573</v>
+        <v>14.0605</v>
       </c>
       <c r="C85" t="n">
-        <v>14.0415</v>
+        <v>14.581</v>
       </c>
       <c r="D85" t="n">
-        <v>19.805</v>
+        <v>20.0046</v>
       </c>
       <c r="E85" t="n">
-        <v>6.91905</v>
+        <v>7.50027</v>
       </c>
       <c r="F85" t="n">
-        <v>11.4182</v>
+        <v>12.3396</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>14.1128</v>
+        <v>14.1248</v>
       </c>
       <c r="C86" t="n">
-        <v>14.1012</v>
+        <v>14.5038</v>
       </c>
       <c r="D86" t="n">
-        <v>20.5123</v>
+        <v>20.6627</v>
       </c>
       <c r="E86" t="n">
-        <v>6.94568</v>
+        <v>7.57652</v>
       </c>
       <c r="F86" t="n">
-        <v>11.5022</v>
+        <v>12.4681</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>13.9557</v>
+        <v>14.0488</v>
       </c>
       <c r="C87" t="n">
-        <v>14.2017</v>
+        <v>14.5822</v>
       </c>
       <c r="D87" t="n">
-        <v>21.1897</v>
+        <v>21.3247</v>
       </c>
       <c r="E87" t="n">
-        <v>7.18506</v>
+        <v>7.79324</v>
       </c>
       <c r="F87" t="n">
-        <v>11.5667</v>
+        <v>12.6692</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.118</v>
+        <v>14.1991</v>
       </c>
       <c r="C88" t="n">
-        <v>14.2506</v>
+        <v>14.6284</v>
       </c>
       <c r="D88" t="n">
-        <v>21.8381</v>
+        <v>22.0005</v>
       </c>
       <c r="E88" t="n">
-        <v>7.42201</v>
+        <v>7.95282</v>
       </c>
       <c r="F88" t="n">
-        <v>11.7004</v>
+        <v>12.6359</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.284</v>
+        <v>14.2217</v>
       </c>
       <c r="C89" t="n">
-        <v>14.1884</v>
+        <v>14.6104</v>
       </c>
       <c r="D89" t="n">
-        <v>22.4381</v>
+        <v>22.6709</v>
       </c>
       <c r="E89" t="n">
-        <v>7.54219</v>
+        <v>8.27988</v>
       </c>
       <c r="F89" t="n">
-        <v>11.9</v>
+        <v>12.9377</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.221</v>
+        <v>14.1883</v>
       </c>
       <c r="C90" t="n">
-        <v>14.2</v>
+        <v>14.7245</v>
       </c>
       <c r="D90" t="n">
-        <v>23.0767</v>
+        <v>23.3849</v>
       </c>
       <c r="E90" t="n">
-        <v>7.76895</v>
+        <v>8.46233</v>
       </c>
       <c r="F90" t="n">
-        <v>12.1038</v>
+        <v>13.1305</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.4018</v>
+        <v>14.3897</v>
       </c>
       <c r="C91" t="n">
-        <v>14.3576</v>
+        <v>14.7094</v>
       </c>
       <c r="D91" t="n">
-        <v>23.9406</v>
+        <v>24.1096</v>
       </c>
       <c r="E91" t="n">
-        <v>8.039759999999999</v>
+        <v>8.37809</v>
       </c>
       <c r="F91" t="n">
-        <v>12.4245</v>
+        <v>13.4082</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.4001</v>
+        <v>14.4342</v>
       </c>
       <c r="C92" t="n">
-        <v>14.2672</v>
+        <v>14.7847</v>
       </c>
       <c r="D92" t="n">
-        <v>23.9816</v>
+        <v>24.0064</v>
       </c>
       <c r="E92" t="n">
-        <v>14.9478</v>
+        <v>16.7159</v>
       </c>
       <c r="F92" t="n">
-        <v>17.7344</v>
+        <v>20.0151</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5754</v>
+        <v>14.6278</v>
       </c>
       <c r="C93" t="n">
-        <v>14.4115</v>
+        <v>14.8895</v>
       </c>
       <c r="D93" t="n">
-        <v>24.3838</v>
+        <v>24.4806</v>
       </c>
       <c r="E93" t="n">
-        <v>15.0872</v>
+        <v>16.8264</v>
       </c>
       <c r="F93" t="n">
-        <v>17.9251</v>
+        <v>20.0357</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.6966</v>
+        <v>14.7427</v>
       </c>
       <c r="C94" t="n">
-        <v>22.9716</v>
+        <v>23.5813</v>
       </c>
       <c r="D94" t="n">
-        <v>24.969</v>
+        <v>25.0758</v>
       </c>
       <c r="E94" t="n">
-        <v>15.2981</v>
+        <v>17.0497</v>
       </c>
       <c r="F94" t="n">
-        <v>17.9397</v>
+        <v>20.2206</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.8822</v>
+        <v>20.8041</v>
       </c>
       <c r="C95" t="n">
-        <v>22.983</v>
+        <v>23.5834</v>
       </c>
       <c r="D95" t="n">
-        <v>25.3789</v>
+        <v>25.646</v>
       </c>
       <c r="E95" t="n">
-        <v>15.3894</v>
+        <v>17.2328</v>
       </c>
       <c r="F95" t="n">
-        <v>18.0499</v>
+        <v>20.3332</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.8158</v>
+        <v>20.8851</v>
       </c>
       <c r="C96" t="n">
-        <v>23.0999</v>
+        <v>23.6335</v>
       </c>
       <c r="D96" t="n">
-        <v>26.0186</v>
+        <v>26.1023</v>
       </c>
       <c r="E96" t="n">
-        <v>15.583</v>
+        <v>17.3832</v>
       </c>
       <c r="F96" t="n">
-        <v>18.1227</v>
+        <v>20.3059</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.8585</v>
+        <v>20.931</v>
       </c>
       <c r="C97" t="n">
-        <v>22.9937</v>
+        <v>23.702</v>
       </c>
       <c r="D97" t="n">
-        <v>26.4545</v>
+        <v>26.637</v>
       </c>
       <c r="E97" t="n">
-        <v>15.7336</v>
+        <v>17.5479</v>
       </c>
       <c r="F97" t="n">
-        <v>18.1054</v>
+        <v>20.4584</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.883</v>
+        <v>20.9802</v>
       </c>
       <c r="C98" t="n">
-        <v>23.0632</v>
+        <v>23.7165</v>
       </c>
       <c r="D98" t="n">
-        <v>27.1477</v>
+        <v>27.2112</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9054</v>
+        <v>17.7182</v>
       </c>
       <c r="F98" t="n">
-        <v>18.2449</v>
+        <v>20.5767</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>20.7615</v>
+        <v>20.9591</v>
       </c>
       <c r="C99" t="n">
-        <v>23.144</v>
+        <v>23.7237</v>
       </c>
       <c r="D99" t="n">
-        <v>27.6461</v>
+        <v>27.8116</v>
       </c>
       <c r="E99" t="n">
-        <v>16.1092</v>
+        <v>17.8219</v>
       </c>
       <c r="F99" t="n">
-        <v>18.3587</v>
+        <v>20.6715</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>20.9155</v>
+        <v>20.9307</v>
       </c>
       <c r="C100" t="n">
-        <v>23.0745</v>
+        <v>23.679</v>
       </c>
       <c r="D100" t="n">
-        <v>28.3243</v>
+        <v>28.3994</v>
       </c>
       <c r="E100" t="n">
-        <v>16.2302</v>
+        <v>17.9866</v>
       </c>
       <c r="F100" t="n">
-        <v>18.4035</v>
+        <v>20.7421</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9842</v>
+        <v>20.8792</v>
       </c>
       <c r="C101" t="n">
-        <v>23.2198</v>
+        <v>23.8239</v>
       </c>
       <c r="D101" t="n">
-        <v>29.0328</v>
+        <v>29.219</v>
       </c>
       <c r="E101" t="n">
-        <v>16.4205</v>
+        <v>18.2627</v>
       </c>
       <c r="F101" t="n">
-        <v>18.5138</v>
+        <v>20.8673</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.9513</v>
+        <v>20.9967</v>
       </c>
       <c r="C102" t="n">
-        <v>23.25</v>
+        <v>23.8188</v>
       </c>
       <c r="D102" t="n">
-        <v>29.6763</v>
+        <v>29.887</v>
       </c>
       <c r="E102" t="n">
-        <v>16.6266</v>
+        <v>18.4009</v>
       </c>
       <c r="F102" t="n">
-        <v>18.7799</v>
+        <v>20.9254</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.0314</v>
+        <v>21.0691</v>
       </c>
       <c r="C103" t="n">
-        <v>23.3084</v>
+        <v>24.0348</v>
       </c>
       <c r="D103" t="n">
-        <v>30.5005</v>
+        <v>30.6492</v>
       </c>
       <c r="E103" t="n">
-        <v>16.8276</v>
+        <v>18.5941</v>
       </c>
       <c r="F103" t="n">
-        <v>18.9496</v>
+        <v>21.121</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>20.9714</v>
+        <v>21.0687</v>
       </c>
       <c r="C104" t="n">
-        <v>23.2628</v>
+        <v>23.997</v>
       </c>
       <c r="D104" t="n">
-        <v>31.2177</v>
+        <v>31.3173</v>
       </c>
       <c r="E104" t="n">
-        <v>17.0027</v>
+        <v>18.6904</v>
       </c>
       <c r="F104" t="n">
-        <v>19.1266</v>
+        <v>21.3369</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.0246</v>
+        <v>21.0929</v>
       </c>
       <c r="C105" t="n">
-        <v>23.4641</v>
+        <v>24.0406</v>
       </c>
       <c r="D105" t="n">
-        <v>32.0661</v>
+        <v>32.1426</v>
       </c>
       <c r="E105" t="n">
-        <v>17.2131</v>
+        <v>18.9795</v>
       </c>
       <c r="F105" t="n">
-        <v>19.2993</v>
+        <v>21.4792</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.1697</v>
+        <v>21.1117</v>
       </c>
       <c r="C106" t="n">
-        <v>23.5662</v>
+        <v>24.2898</v>
       </c>
       <c r="D106" t="n">
-        <v>32.7982</v>
+        <v>33.0657</v>
       </c>
       <c r="E106" t="n">
-        <v>17.4703</v>
+        <v>19.2012</v>
       </c>
       <c r="F106" t="n">
-        <v>19.6505</v>
+        <v>21.8125</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.27</v>
+        <v>21.2269</v>
       </c>
       <c r="C107" t="n">
-        <v>23.6975</v>
+        <v>24.4302</v>
       </c>
       <c r="D107" t="n">
-        <v>28.7655</v>
+        <v>28.7937</v>
       </c>
       <c r="E107" t="n">
-        <v>20.4053</v>
+        <v>22.6748</v>
       </c>
       <c r="F107" t="n">
-        <v>22.9931</v>
+        <v>25.5118</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.4268</v>
+        <v>21.4341</v>
       </c>
       <c r="C108" t="n">
-        <v>27.27</v>
+        <v>27.9571</v>
       </c>
       <c r="D108" t="n">
-        <v>29.2312</v>
+        <v>29.2327</v>
       </c>
       <c r="E108" t="n">
-        <v>20.61</v>
+        <v>22.8394</v>
       </c>
       <c r="F108" t="n">
-        <v>23.0691</v>
+        <v>25.6426</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.6889</v>
+        <v>21.8092</v>
       </c>
       <c r="C109" t="n">
-        <v>27.2447</v>
+        <v>27.9611</v>
       </c>
       <c r="D109" t="n">
-        <v>29.7687</v>
+        <v>29.8525</v>
       </c>
       <c r="E109" t="n">
-        <v>20.5878</v>
+        <v>23.0373</v>
       </c>
       <c r="F109" t="n">
-        <v>23.0878</v>
+        <v>25.773</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5401</v>
+        <v>23.6078</v>
       </c>
       <c r="C110" t="n">
-        <v>27.2825</v>
+        <v>27.9646</v>
       </c>
       <c r="D110" t="n">
-        <v>30.1196</v>
+        <v>30.2988</v>
       </c>
       <c r="E110" t="n">
-        <v>20.766</v>
+        <v>23.2238</v>
       </c>
       <c r="F110" t="n">
-        <v>23.3908</v>
+        <v>25.8229</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.5367</v>
+        <v>23.5484</v>
       </c>
       <c r="C111" t="n">
-        <v>27.3874</v>
+        <v>27.9992</v>
       </c>
       <c r="D111" t="n">
-        <v>30.7785</v>
+        <v>30.8236</v>
       </c>
       <c r="E111" t="n">
-        <v>20.9796</v>
+        <v>23.333</v>
       </c>
       <c r="F111" t="n">
-        <v>23.446</v>
+        <v>25.962</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.6026</v>
+        <v>23.5886</v>
       </c>
       <c r="C112" t="n">
-        <v>27.4434</v>
+        <v>28.101</v>
       </c>
       <c r="D112" t="n">
-        <v>31.2508</v>
+        <v>31.4848</v>
       </c>
       <c r="E112" t="n">
-        <v>21.1843</v>
+        <v>23.5096</v>
       </c>
       <c r="F112" t="n">
-        <v>23.6556</v>
+        <v>26.0415</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.5568</v>
+        <v>23.5079</v>
       </c>
       <c r="C113" t="n">
-        <v>27.3971</v>
+        <v>28.1023</v>
       </c>
       <c r="D113" t="n">
-        <v>31.9942</v>
+        <v>32.0425</v>
       </c>
       <c r="E113" t="n">
-        <v>21.4315</v>
+        <v>23.7162</v>
       </c>
       <c r="F113" t="n">
-        <v>23.7571</v>
+        <v>26.2848</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.5956</v>
+        <v>23.6608</v>
       </c>
       <c r="C114" t="n">
-        <v>27.3882</v>
+        <v>28.1757</v>
       </c>
       <c r="D114" t="n">
-        <v>32.5713</v>
+        <v>32.7029</v>
       </c>
       <c r="E114" t="n">
-        <v>21.4968</v>
+        <v>23.848</v>
       </c>
       <c r="F114" t="n">
-        <v>23.8951</v>
+        <v>26.4457</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.5289</v>
+        <v>23.5408</v>
       </c>
       <c r="C115" t="n">
-        <v>27.4996</v>
+        <v>28.1869</v>
       </c>
       <c r="D115" t="n">
-        <v>33.1804</v>
+        <v>33.505</v>
       </c>
       <c r="E115" t="n">
-        <v>21.6236</v>
+        <v>24.1686</v>
       </c>
       <c r="F115" t="n">
-        <v>24.1313</v>
+        <v>26.6014</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.5085</v>
+        <v>23.6419</v>
       </c>
       <c r="C116" t="n">
-        <v>27.4579</v>
+        <v>28.3794</v>
       </c>
       <c r="D116" t="n">
-        <v>33.9325</v>
+        <v>34.0844</v>
       </c>
       <c r="E116" t="n">
-        <v>21.8215</v>
+        <v>24.209</v>
       </c>
       <c r="F116" t="n">
-        <v>24.3445</v>
+        <v>26.9231</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.6102</v>
+        <v>23.5449</v>
       </c>
       <c r="C117" t="n">
-        <v>27.6695</v>
+        <v>28.4269</v>
       </c>
       <c r="D117" t="n">
-        <v>34.8089</v>
+        <v>34.9653</v>
       </c>
       <c r="E117" t="n">
-        <v>22.1179</v>
+        <v>24.3815</v>
       </c>
       <c r="F117" t="n">
-        <v>24.671</v>
+        <v>27.0286</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.7494</v>
+        <v>23.5938</v>
       </c>
       <c r="C118" t="n">
-        <v>27.7709</v>
+        <v>28.5904</v>
       </c>
       <c r="D118" t="n">
-        <v>35.5454</v>
+        <v>35.7095</v>
       </c>
       <c r="E118" t="n">
-        <v>22.3411</v>
+        <v>24.5968</v>
       </c>
       <c r="F118" t="n">
-        <v>24.9829</v>
+        <v>27.3911</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.7889</v>
+        <v>23.6953</v>
       </c>
       <c r="C119" t="n">
-        <v>27.9008</v>
+        <v>28.7508</v>
       </c>
       <c r="D119" t="n">
-        <v>36.4407</v>
+        <v>36.5141</v>
       </c>
       <c r="E119" t="n">
-        <v>22.5677</v>
+        <v>24.9574</v>
       </c>
       <c r="F119" t="n">
-        <v>25.324</v>
+        <v>27.663</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.8391</v>
+        <v>23.7039</v>
       </c>
       <c r="C120" t="n">
-        <v>28.0768</v>
+        <v>28.9205</v>
       </c>
       <c r="D120" t="n">
-        <v>37.0768</v>
+        <v>37.4513</v>
       </c>
       <c r="E120" t="n">
-        <v>22.9435</v>
+        <v>25.1611</v>
       </c>
       <c r="F120" t="n">
-        <v>25.9174</v>
+        <v>28.2581</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.9468</v>
+        <v>23.8795</v>
       </c>
       <c r="C121" t="n">
-        <v>28.3743</v>
+        <v>29.0549</v>
       </c>
       <c r="D121" t="n">
-        <v>31.4868</v>
+        <v>31.3979</v>
       </c>
       <c r="E121" t="n">
-        <v>23.6487</v>
+        <v>25.8814</v>
       </c>
       <c r="F121" t="n">
-        <v>26.8097</v>
+        <v>29.7061</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>24.0823</v>
+        <v>24.0289</v>
       </c>
       <c r="C122" t="n">
-        <v>29.6572</v>
+        <v>31.0216</v>
       </c>
       <c r="D122" t="n">
-        <v>31.7727</v>
+        <v>31.9428</v>
       </c>
       <c r="E122" t="n">
-        <v>23.6439</v>
+        <v>25.9811</v>
       </c>
       <c r="F122" t="n">
-        <v>26.9347</v>
+        <v>29.9717</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.3971</v>
+        <v>24.4527</v>
       </c>
       <c r="C123" t="n">
-        <v>29.7686</v>
+        <v>31.167</v>
       </c>
       <c r="D123" t="n">
-        <v>32.2913</v>
+        <v>32.5175</v>
       </c>
       <c r="E123" t="n">
-        <v>23.7404</v>
+        <v>26.3106</v>
       </c>
       <c r="F123" t="n">
-        <v>27.1495</v>
+        <v>29.9558</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>29.8368</v>
+        <v>29.8801</v>
       </c>
       <c r="C124" t="n">
-        <v>29.7268</v>
+        <v>31.2304</v>
       </c>
       <c r="D124" t="n">
-        <v>32.7323</v>
+        <v>32.8849</v>
       </c>
       <c r="E124" t="n">
-        <v>23.8275</v>
+        <v>26.3441</v>
       </c>
       <c r="F124" t="n">
-        <v>27.1119</v>
+        <v>30.1898</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>29.8848</v>
+        <v>29.7213</v>
       </c>
       <c r="C125" t="n">
-        <v>29.947</v>
+        <v>31.2368</v>
       </c>
       <c r="D125" t="n">
-        <v>33.3309</v>
+        <v>33.5798</v>
       </c>
       <c r="E125" t="n">
-        <v>24.0681</v>
+        <v>26.4139</v>
       </c>
       <c r="F125" t="n">
-        <v>27.2627</v>
+        <v>30.2592</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>29.8593</v>
+        <v>29.8165</v>
       </c>
       <c r="C126" t="n">
-        <v>30.0778</v>
+        <v>31.3812</v>
       </c>
       <c r="D126" t="n">
-        <v>34.0403</v>
+        <v>34.0748</v>
       </c>
       <c r="E126" t="n">
-        <v>24.2011</v>
+        <v>26.7319</v>
       </c>
       <c r="F126" t="n">
-        <v>27.4627</v>
+        <v>30.4872</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>29.7272</v>
+        <v>29.7723</v>
       </c>
       <c r="C127" t="n">
-        <v>30.0119</v>
+        <v>31.4756</v>
       </c>
       <c r="D127" t="n">
-        <v>34.6932</v>
+        <v>34.7512</v>
       </c>
       <c r="E127" t="n">
-        <v>24.4301</v>
+        <v>26.8412</v>
       </c>
       <c r="F127" t="n">
-        <v>27.6673</v>
+        <v>30.7049</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.777</v>
+        <v>29.7511</v>
       </c>
       <c r="C128" t="n">
-        <v>30.423</v>
+        <v>31.6618</v>
       </c>
       <c r="D128" t="n">
-        <v>35.251</v>
+        <v>35.3149</v>
       </c>
       <c r="E128" t="n">
-        <v>24.5516</v>
+        <v>26.9521</v>
       </c>
       <c r="F128" t="n">
-        <v>27.8427</v>
+        <v>30.9076</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>29.8669</v>
+        <v>29.7008</v>
       </c>
       <c r="C129" t="n">
-        <v>30.3546</v>
+        <v>31.6611</v>
       </c>
       <c r="D129" t="n">
-        <v>35.9747</v>
+        <v>35.9971</v>
       </c>
       <c r="E129" t="n">
-        <v>24.6677</v>
+        <v>27.1703</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2547</v>
+        <v>31.0804</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>29.8097</v>
+        <v>29.8024</v>
       </c>
       <c r="C130" t="n">
-        <v>30.4756</v>
+        <v>31.8418</v>
       </c>
       <c r="D130" t="n">
-        <v>36.5453</v>
+        <v>36.6811</v>
       </c>
       <c r="E130" t="n">
-        <v>24.9776</v>
+        <v>27.3666</v>
       </c>
       <c r="F130" t="n">
-        <v>28.3535</v>
+        <v>31.3934</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.8118</v>
+        <v>29.7075</v>
       </c>
       <c r="C131" t="n">
-        <v>30.5959</v>
+        <v>32.0279</v>
       </c>
       <c r="D131" t="n">
-        <v>37.4672</v>
+        <v>37.5609</v>
       </c>
       <c r="E131" t="n">
-        <v>25.1235</v>
+        <v>27.6806</v>
       </c>
       <c r="F131" t="n">
-        <v>28.6692</v>
+        <v>31.6385</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.8991</v>
+        <v>29.8625</v>
       </c>
       <c r="C132" t="n">
-        <v>30.8665</v>
+        <v>32.1385</v>
       </c>
       <c r="D132" t="n">
-        <v>38.0954</v>
+        <v>38.1944</v>
       </c>
       <c r="E132" t="n">
-        <v>25.5649</v>
+        <v>27.9293</v>
       </c>
       <c r="F132" t="n">
-        <v>29.0344</v>
+        <v>32.0141</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>29.8229</v>
+        <v>29.8937</v>
       </c>
       <c r="C133" t="n">
-        <v>30.9372</v>
+        <v>32.4106</v>
       </c>
       <c r="D133" t="n">
-        <v>38.8895</v>
+        <v>39.1734</v>
       </c>
       <c r="E133" t="n">
-        <v>25.7473</v>
+        <v>28.2431</v>
       </c>
       <c r="F133" t="n">
-        <v>29.4415</v>
+        <v>32.4472</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>29.9696</v>
+        <v>29.9283</v>
       </c>
       <c r="C134" t="n">
-        <v>31.2014</v>
+        <v>32.6252</v>
       </c>
       <c r="D134" t="n">
-        <v>39.8055</v>
+        <v>39.9302</v>
       </c>
       <c r="E134" t="n">
-        <v>26.2364</v>
+        <v>28.5039</v>
       </c>
       <c r="F134" t="n">
-        <v>30.0476</v>
+        <v>32.8753</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>29.9162</v>
+        <v>30.1125</v>
       </c>
       <c r="C135" t="n">
-        <v>31.7552</v>
+        <v>32.9787</v>
       </c>
       <c r="D135" t="n">
-        <v>33.2217</v>
+        <v>33.343</v>
       </c>
       <c r="E135" t="n">
-        <v>26.0297</v>
+        <v>27.749</v>
       </c>
       <c r="F135" t="n">
-        <v>29.2993</v>
+        <v>32.129</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.1398</v>
+        <v>30.2263</v>
       </c>
       <c r="C136" t="n">
-        <v>31.6524</v>
+        <v>34.2779</v>
       </c>
       <c r="D136" t="n">
-        <v>33.6848</v>
+        <v>33.657</v>
       </c>
       <c r="E136" t="n">
-        <v>26.3175</v>
+        <v>27.8152</v>
       </c>
       <c r="F136" t="n">
-        <v>29.602</v>
+        <v>32.2906</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.3849</v>
+        <v>30.4353</v>
       </c>
       <c r="C137" t="n">
-        <v>31.6592</v>
+        <v>34.3686</v>
       </c>
       <c r="D137" t="n">
-        <v>34.1958</v>
+        <v>34.1468</v>
       </c>
       <c r="E137" t="n">
-        <v>26.5787</v>
+        <v>28.0002</v>
       </c>
       <c r="F137" t="n">
-        <v>29.7386</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>35.1921</v>
+        <v>34.9929</v>
       </c>
       <c r="C138" t="n">
-        <v>31.8814</v>
+        <v>34.3267</v>
       </c>
       <c r="D138" t="n">
-        <v>34.5317</v>
+        <v>34.5873</v>
       </c>
       <c r="E138" t="n">
-        <v>26.6598</v>
+        <v>28.0951</v>
       </c>
       <c r="F138" t="n">
-        <v>29.8888</v>
+        <v>32.7806</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.1316</v>
+        <v>35.1613</v>
       </c>
       <c r="C139" t="n">
-        <v>31.9512</v>
+        <v>34.5015</v>
       </c>
       <c r="D139" t="n">
-        <v>35.1219</v>
+        <v>35.2163</v>
       </c>
       <c r="E139" t="n">
-        <v>26.7891</v>
+        <v>28.283</v>
       </c>
       <c r="F139" t="n">
-        <v>29.9101</v>
+        <v>33.037</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>35.1517</v>
+        <v>35.0463</v>
       </c>
       <c r="C140" t="n">
-        <v>31.9783</v>
+        <v>34.6422</v>
       </c>
       <c r="D140" t="n">
-        <v>35.6807</v>
+        <v>35.76</v>
       </c>
       <c r="E140" t="n">
-        <v>26.9637</v>
+        <v>28.5536</v>
       </c>
       <c r="F140" t="n">
-        <v>30.1935</v>
+        <v>32.8959</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.2478</v>
+        <v>35.15</v>
       </c>
       <c r="C141" t="n">
-        <v>32.0236</v>
+        <v>34.6201</v>
       </c>
       <c r="D141" t="n">
-        <v>36.278</v>
+        <v>36.2902</v>
       </c>
       <c r="E141" t="n">
-        <v>26.8801</v>
+        <v>28.6867</v>
       </c>
       <c r="F141" t="n">
-        <v>30.3138</v>
+        <v>33.2585</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>35.235</v>
+        <v>35.1196</v>
       </c>
       <c r="C142" t="n">
-        <v>32.3271</v>
+        <v>34.9538</v>
       </c>
       <c r="D142" t="n">
-        <v>36.8457</v>
+        <v>37.0234</v>
       </c>
       <c r="E142" t="n">
-        <v>27.3265</v>
+        <v>28.9124</v>
       </c>
       <c r="F142" t="n">
-        <v>30.5755</v>
+        <v>33.4706</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>35.247</v>
+        <v>35.2082</v>
       </c>
       <c r="C143" t="n">
-        <v>32.4427</v>
+        <v>34.9257</v>
       </c>
       <c r="D143" t="n">
-        <v>37.6136</v>
+        <v>37.7622</v>
       </c>
       <c r="E143" t="n">
-        <v>27.4242</v>
+        <v>29.0461</v>
       </c>
       <c r="F143" t="n">
-        <v>30.7814</v>
+        <v>33.7373</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Scattered successful looukp.xlsx
+++ b/vs-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.78684</v>
+        <v>3.25728</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5409</v>
+        <v>4.49876</v>
       </c>
       <c r="D2" t="n">
-        <v>5.42457</v>
+        <v>5.80836</v>
       </c>
       <c r="E2" t="n">
-        <v>3.88736</v>
+        <v>3.47638</v>
       </c>
       <c r="F2" t="n">
-        <v>4.00944</v>
+        <v>3.73075</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.78524</v>
+        <v>3.26292</v>
       </c>
       <c r="C3" t="n">
-        <v>4.55906</v>
+        <v>4.5212</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7362</v>
+        <v>6.06747</v>
       </c>
       <c r="E3" t="n">
-        <v>3.89453</v>
+        <v>3.48714</v>
       </c>
       <c r="F3" t="n">
-        <v>4.01049</v>
+        <v>3.75381</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.81309</v>
+        <v>3.30252</v>
       </c>
       <c r="C4" t="n">
-        <v>4.59621</v>
+        <v>4.55197</v>
       </c>
       <c r="D4" t="n">
-        <v>6.17019</v>
+        <v>6.39074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.91311</v>
+        <v>3.50506</v>
       </c>
       <c r="F4" t="n">
-        <v>4.04558</v>
+        <v>3.78388</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>2.83056</v>
+        <v>3.32078</v>
       </c>
       <c r="C5" t="n">
-        <v>4.64149</v>
+        <v>4.58517</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49925</v>
+        <v>6.64964</v>
       </c>
       <c r="E5" t="n">
-        <v>3.93975</v>
+        <v>3.45189</v>
       </c>
       <c r="F5" t="n">
-        <v>4.08654</v>
+        <v>3.78674</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>2.85869</v>
+        <v>3.35084</v>
       </c>
       <c r="C6" t="n">
-        <v>4.71375</v>
+        <v>4.63319</v>
       </c>
       <c r="D6" t="n">
-        <v>6.9429</v>
+        <v>7.12107</v>
       </c>
       <c r="E6" t="n">
-        <v>3.96152</v>
+        <v>3.4741</v>
       </c>
       <c r="F6" t="n">
-        <v>4.16083</v>
+        <v>3.79551</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>2.88229</v>
+        <v>3.38243</v>
       </c>
       <c r="C7" t="n">
-        <v>4.76535</v>
+        <v>4.70258</v>
       </c>
       <c r="D7" t="n">
-        <v>5.14033</v>
+        <v>5.40469</v>
       </c>
       <c r="E7" t="n">
-        <v>3.86374</v>
+        <v>3.5048</v>
       </c>
       <c r="F7" t="n">
-        <v>4.04947</v>
+        <v>3.83677</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>2.90896</v>
+        <v>3.41014</v>
       </c>
       <c r="C8" t="n">
-        <v>4.84528</v>
+        <v>4.64584</v>
       </c>
       <c r="D8" t="n">
-        <v>5.31581</v>
+        <v>5.55878</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8901</v>
+        <v>3.51185</v>
       </c>
       <c r="F8" t="n">
-        <v>4.07833</v>
+        <v>3.83242</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>2.9733</v>
+        <v>3.45809</v>
       </c>
       <c r="C9" t="n">
-        <v>4.83918</v>
+        <v>4.64213</v>
       </c>
       <c r="D9" t="n">
-        <v>5.53076</v>
+        <v>5.78438</v>
       </c>
       <c r="E9" t="n">
-        <v>3.91051</v>
+        <v>3.52373</v>
       </c>
       <c r="F9" t="n">
-        <v>4.10921</v>
+        <v>3.8389</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.40813</v>
+        <v>3.91783</v>
       </c>
       <c r="C10" t="n">
-        <v>4.86257</v>
+        <v>4.64897</v>
       </c>
       <c r="D10" t="n">
-        <v>5.79279</v>
+        <v>6.05207</v>
       </c>
       <c r="E10" t="n">
-        <v>3.93613</v>
+        <v>3.54217</v>
       </c>
       <c r="F10" t="n">
-        <v>4.15084</v>
+        <v>3.88615</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.42317</v>
+        <v>3.9342</v>
       </c>
       <c r="C11" t="n">
-        <v>4.84206</v>
+        <v>4.70464</v>
       </c>
       <c r="D11" t="n">
-        <v>6.01959</v>
+        <v>6.31623</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9278</v>
+        <v>3.57207</v>
       </c>
       <c r="F11" t="n">
-        <v>4.15128</v>
+        <v>3.92919</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.43705</v>
+        <v>4.06219</v>
       </c>
       <c r="C12" t="n">
-        <v>4.90423</v>
+        <v>4.67562</v>
       </c>
       <c r="D12" t="n">
-        <v>6.30423</v>
+        <v>6.5895</v>
       </c>
       <c r="E12" t="n">
-        <v>3.96455</v>
+        <v>3.59734</v>
       </c>
       <c r="F12" t="n">
-        <v>4.19024</v>
+        <v>3.94647</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.45571</v>
+        <v>3.97084</v>
       </c>
       <c r="C13" t="n">
-        <v>4.92098</v>
+        <v>4.69169</v>
       </c>
       <c r="D13" t="n">
-        <v>6.63004</v>
+        <v>6.88375</v>
       </c>
       <c r="E13" t="n">
-        <v>3.99154</v>
+        <v>3.63839</v>
       </c>
       <c r="F13" t="n">
-        <v>4.19279</v>
+        <v>3.99482</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4466</v>
+        <v>3.98899</v>
       </c>
       <c r="C14" t="n">
-        <v>4.88038</v>
+        <v>4.71404</v>
       </c>
       <c r="D14" t="n">
-        <v>6.90913</v>
+        <v>7.13635</v>
       </c>
       <c r="E14" t="n">
-        <v>4.00843</v>
+        <v>3.67475</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2327</v>
+        <v>3.99018</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.46629</v>
+        <v>4.01825</v>
       </c>
       <c r="C15" t="n">
-        <v>4.96189</v>
+        <v>4.75925</v>
       </c>
       <c r="D15" t="n">
-        <v>7.18141</v>
+        <v>7.43774</v>
       </c>
       <c r="E15" t="n">
-        <v>4.03184</v>
+        <v>3.69213</v>
       </c>
       <c r="F15" t="n">
-        <v>4.24432</v>
+        <v>4.01892</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.46969</v>
+        <v>4.02865</v>
       </c>
       <c r="C16" t="n">
-        <v>4.97441</v>
+        <v>4.78002</v>
       </c>
       <c r="D16" t="n">
-        <v>7.44195</v>
+        <v>7.68671</v>
       </c>
       <c r="E16" t="n">
-        <v>4.07945</v>
+        <v>3.72724</v>
       </c>
       <c r="F16" t="n">
-        <v>4.28883</v>
+        <v>4.046</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.51003</v>
+        <v>4.04566</v>
       </c>
       <c r="C17" t="n">
-        <v>5.00076</v>
+        <v>4.76855</v>
       </c>
       <c r="D17" t="n">
-        <v>7.70302</v>
+        <v>7.96923</v>
       </c>
       <c r="E17" t="n">
-        <v>4.09745</v>
+        <v>3.75342</v>
       </c>
       <c r="F17" t="n">
-        <v>4.30581</v>
+        <v>4.07312</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.52649</v>
+        <v>4.08223</v>
       </c>
       <c r="C18" t="n">
-        <v>5.04659</v>
+        <v>4.83262</v>
       </c>
       <c r="D18" t="n">
-        <v>7.98568</v>
+        <v>8.239599999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>4.13723</v>
+        <v>3.79416</v>
       </c>
       <c r="F18" t="n">
-        <v>4.35351</v>
+        <v>4.11497</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.56161</v>
+        <v>4.09651</v>
       </c>
       <c r="C19" t="n">
-        <v>5.06043</v>
+        <v>4.8816</v>
       </c>
       <c r="D19" t="n">
-        <v>8.28417</v>
+        <v>8.533709999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>4.17481</v>
+        <v>3.8284</v>
       </c>
       <c r="F19" t="n">
-        <v>4.39498</v>
+        <v>4.13745</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.59424</v>
+        <v>4.14995</v>
       </c>
       <c r="C20" t="n">
-        <v>5.13711</v>
+        <v>4.94049</v>
       </c>
       <c r="D20" t="n">
-        <v>8.49849</v>
+        <v>8.735580000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>4.24137</v>
+        <v>3.78542</v>
       </c>
       <c r="F20" t="n">
-        <v>4.48596</v>
+        <v>4.17983</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.62055</v>
+        <v>4.19727</v>
       </c>
       <c r="C21" t="n">
-        <v>5.20606</v>
+        <v>5.00512</v>
       </c>
       <c r="D21" t="n">
-        <v>6.28477</v>
+        <v>6.60004</v>
       </c>
       <c r="E21" t="n">
-        <v>4.13554</v>
+        <v>3.79653</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5068</v>
+        <v>4.19477</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.67162</v>
+        <v>4.26423</v>
       </c>
       <c r="C22" t="n">
-        <v>5.22019</v>
+        <v>4.99823</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53181</v>
+        <v>6.80985</v>
       </c>
       <c r="E22" t="n">
-        <v>4.19036</v>
+        <v>3.76732</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5417</v>
+        <v>4.20554</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.72625</v>
+        <v>4.35244</v>
       </c>
       <c r="C23" t="n">
-        <v>5.26461</v>
+        <v>4.96792</v>
       </c>
       <c r="D23" t="n">
-        <v>6.73189</v>
+        <v>7.02934</v>
       </c>
       <c r="E23" t="n">
-        <v>4.17088</v>
+        <v>3.81227</v>
       </c>
       <c r="F23" t="n">
-        <v>4.54387</v>
+        <v>4.2277</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.91438</v>
+        <v>4.50264</v>
       </c>
       <c r="C24" t="n">
-        <v>5.2256</v>
+        <v>5.07993</v>
       </c>
       <c r="D24" t="n">
-        <v>7.02569</v>
+        <v>7.26773</v>
       </c>
       <c r="E24" t="n">
-        <v>4.20188</v>
+        <v>3.83701</v>
       </c>
       <c r="F24" t="n">
-        <v>4.57395</v>
+        <v>4.26301</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.93787</v>
+        <v>4.52064</v>
       </c>
       <c r="C25" t="n">
-        <v>5.33655</v>
+        <v>4.9338</v>
       </c>
       <c r="D25" t="n">
-        <v>7.26107</v>
+        <v>7.52774</v>
       </c>
       <c r="E25" t="n">
-        <v>4.24844</v>
+        <v>3.87305</v>
       </c>
       <c r="F25" t="n">
-        <v>4.60225</v>
+        <v>4.30168</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.92704</v>
+        <v>4.50915</v>
       </c>
       <c r="C26" t="n">
-        <v>5.22624</v>
+        <v>5.01712</v>
       </c>
       <c r="D26" t="n">
-        <v>7.48242</v>
+        <v>7.73424</v>
       </c>
       <c r="E26" t="n">
-        <v>4.26125</v>
+        <v>3.93695</v>
       </c>
       <c r="F26" t="n">
-        <v>4.63442</v>
+        <v>4.32751</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.94555</v>
+        <v>4.53876</v>
       </c>
       <c r="C27" t="n">
-        <v>5.26405</v>
+        <v>4.99638</v>
       </c>
       <c r="D27" t="n">
-        <v>7.75742</v>
+        <v>7.99033</v>
       </c>
       <c r="E27" t="n">
-        <v>4.27942</v>
+        <v>3.9132</v>
       </c>
       <c r="F27" t="n">
-        <v>4.65824</v>
+        <v>4.3607</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.93537</v>
+        <v>4.55089</v>
       </c>
       <c r="C28" t="n">
-        <v>5.33618</v>
+        <v>5.06578</v>
       </c>
       <c r="D28" t="n">
-        <v>8.00337</v>
+        <v>8.24994</v>
       </c>
       <c r="E28" t="n">
-        <v>4.35499</v>
+        <v>3.94696</v>
       </c>
       <c r="F28" t="n">
-        <v>4.68304</v>
+        <v>4.37876</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.96495</v>
+        <v>4.53662</v>
       </c>
       <c r="C29" t="n">
-        <v>5.32442</v>
+        <v>5.0613</v>
       </c>
       <c r="D29" t="n">
-        <v>8.2667</v>
+        <v>8.532159999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>4.38851</v>
+        <v>3.99802</v>
       </c>
       <c r="F29" t="n">
-        <v>4.69565</v>
+        <v>4.42651</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.96886</v>
+        <v>4.57233</v>
       </c>
       <c r="C30" t="n">
-        <v>5.40935</v>
+        <v>5.14811</v>
       </c>
       <c r="D30" t="n">
-        <v>8.54987</v>
+        <v>8.751860000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>4.35598</v>
+        <v>4.05746</v>
       </c>
       <c r="F30" t="n">
-        <v>4.73712</v>
+        <v>4.45412</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.00135</v>
+        <v>4.59765</v>
       </c>
       <c r="C31" t="n">
-        <v>5.35808</v>
+        <v>5.06474</v>
       </c>
       <c r="D31" t="n">
-        <v>8.76878</v>
+        <v>9.00963</v>
       </c>
       <c r="E31" t="n">
-        <v>4.40079</v>
+        <v>4.07239</v>
       </c>
       <c r="F31" t="n">
-        <v>4.78346</v>
+        <v>4.50341</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.99849</v>
+        <v>4.60768</v>
       </c>
       <c r="C32" t="n">
-        <v>5.40429</v>
+        <v>5.16167</v>
       </c>
       <c r="D32" t="n">
-        <v>9.004160000000001</v>
+        <v>9.2379</v>
       </c>
       <c r="E32" t="n">
-        <v>4.43087</v>
+        <v>4.10007</v>
       </c>
       <c r="F32" t="n">
-        <v>4.82469</v>
+        <v>4.5373</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.05683</v>
+        <v>4.65468</v>
       </c>
       <c r="C33" t="n">
-        <v>5.52158</v>
+        <v>5.21752</v>
       </c>
       <c r="D33" t="n">
-        <v>9.247350000000001</v>
+        <v>9.522970000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>4.56743</v>
+        <v>4.17874</v>
       </c>
       <c r="F33" t="n">
-        <v>4.90198</v>
+        <v>4.59602</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.0811</v>
+        <v>4.7066</v>
       </c>
       <c r="C34" t="n">
-        <v>5.58255</v>
+        <v>5.26369</v>
       </c>
       <c r="D34" t="n">
-        <v>9.489269999999999</v>
+        <v>9.77624</v>
       </c>
       <c r="E34" t="n">
-        <v>4.60126</v>
+        <v>4.13792</v>
       </c>
       <c r="F34" t="n">
-        <v>4.99071</v>
+        <v>4.50924</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.13285</v>
+        <v>4.72909</v>
       </c>
       <c r="C35" t="n">
-        <v>5.64236</v>
+        <v>5.32258</v>
       </c>
       <c r="D35" t="n">
-        <v>6.84559</v>
+        <v>7.10687</v>
       </c>
       <c r="E35" t="n">
-        <v>4.43326</v>
+        <v>4.16096</v>
       </c>
       <c r="F35" t="n">
-        <v>4.83733</v>
+        <v>4.4957</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.22436</v>
+        <v>4.82569</v>
       </c>
       <c r="C36" t="n">
-        <v>5.7983</v>
+        <v>5.43566</v>
       </c>
       <c r="D36" t="n">
-        <v>7.01444</v>
+        <v>7.27043</v>
       </c>
       <c r="E36" t="n">
-        <v>4.40977</v>
+        <v>4.19712</v>
       </c>
       <c r="F36" t="n">
-        <v>4.88006</v>
+        <v>4.56047</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.41766</v>
+        <v>5.08389</v>
       </c>
       <c r="C37" t="n">
-        <v>5.57476</v>
+        <v>5.22077</v>
       </c>
       <c r="D37" t="n">
-        <v>7.20785</v>
+        <v>7.45712</v>
       </c>
       <c r="E37" t="n">
-        <v>4.49022</v>
+        <v>4.20341</v>
       </c>
       <c r="F37" t="n">
-        <v>4.89485</v>
+        <v>4.58795</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.20417</v>
+        <v>4.83519</v>
       </c>
       <c r="C38" t="n">
-        <v>5.5449</v>
+        <v>5.27501</v>
       </c>
       <c r="D38" t="n">
-        <v>7.4164</v>
+        <v>7.67941</v>
       </c>
       <c r="E38" t="n">
-        <v>4.5171</v>
+        <v>4.18742</v>
       </c>
       <c r="F38" t="n">
-        <v>4.89887</v>
+        <v>4.61952</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.1774</v>
+        <v>4.84304</v>
       </c>
       <c r="C39" t="n">
-        <v>5.5559</v>
+        <v>5.25055</v>
       </c>
       <c r="D39" t="n">
-        <v>7.64624</v>
+        <v>7.88898</v>
       </c>
       <c r="E39" t="n">
-        <v>4.54055</v>
+        <v>4.26991</v>
       </c>
       <c r="F39" t="n">
-        <v>4.89589</v>
+        <v>4.61256</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.24553</v>
+        <v>4.84394</v>
       </c>
       <c r="C40" t="n">
-        <v>5.61905</v>
+        <v>5.31083</v>
       </c>
       <c r="D40" t="n">
-        <v>7.89368</v>
+        <v>8.114240000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>4.59921</v>
+        <v>4.30583</v>
       </c>
       <c r="F40" t="n">
-        <v>4.9954</v>
+        <v>4.64785</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.19327</v>
+        <v>4.79544</v>
       </c>
       <c r="C41" t="n">
-        <v>5.63422</v>
+        <v>5.29258</v>
       </c>
       <c r="D41" t="n">
-        <v>8.143599999999999</v>
+        <v>8.37393</v>
       </c>
       <c r="E41" t="n">
-        <v>4.61189</v>
+        <v>4.32298</v>
       </c>
       <c r="F41" t="n">
-        <v>5.00281</v>
+        <v>4.70115</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.28032</v>
+        <v>4.86159</v>
       </c>
       <c r="C42" t="n">
-        <v>5.62503</v>
+        <v>5.34221</v>
       </c>
       <c r="D42" t="n">
-        <v>8.371040000000001</v>
+        <v>8.626099999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>4.66568</v>
+        <v>4.38266</v>
       </c>
       <c r="F42" t="n">
-        <v>5.03659</v>
+        <v>4.72212</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.23979</v>
+        <v>4.82737</v>
       </c>
       <c r="C43" t="n">
-        <v>5.66979</v>
+        <v>5.343</v>
       </c>
       <c r="D43" t="n">
-        <v>8.653230000000001</v>
+        <v>8.87552</v>
       </c>
       <c r="E43" t="n">
-        <v>4.70085</v>
+        <v>4.40351</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04972</v>
+        <v>4.77401</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.21991</v>
+        <v>4.84</v>
       </c>
       <c r="C44" t="n">
-        <v>5.68045</v>
+        <v>5.36574</v>
       </c>
       <c r="D44" t="n">
-        <v>8.9069</v>
+        <v>9.13725</v>
       </c>
       <c r="E44" t="n">
-        <v>4.71356</v>
+        <v>4.44773</v>
       </c>
       <c r="F44" t="n">
-        <v>5.10924</v>
+        <v>4.76554</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.27109</v>
+        <v>4.98641</v>
       </c>
       <c r="C45" t="n">
-        <v>5.69605</v>
+        <v>5.40405</v>
       </c>
       <c r="D45" t="n">
-        <v>9.15779</v>
+        <v>9.403919999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>4.79263</v>
+        <v>4.4866</v>
       </c>
       <c r="F45" t="n">
-        <v>5.15802</v>
+        <v>4.84374</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.29285</v>
+        <v>4.97434</v>
       </c>
       <c r="C46" t="n">
-        <v>5.75058</v>
+        <v>5.46412</v>
       </c>
       <c r="D46" t="n">
-        <v>9.36913</v>
+        <v>9.642429999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>4.8427</v>
+        <v>4.55944</v>
       </c>
       <c r="F46" t="n">
-        <v>5.21322</v>
+        <v>4.91551</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.32511</v>
+        <v>4.96477</v>
       </c>
       <c r="C47" t="n">
-        <v>5.83803</v>
+        <v>5.4951</v>
       </c>
       <c r="D47" t="n">
-        <v>9.62233</v>
+        <v>9.881320000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>4.9379</v>
+        <v>4.64271</v>
       </c>
       <c r="F47" t="n">
-        <v>5.34204</v>
+        <v>4.97014</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.37632</v>
+        <v>5.06741</v>
       </c>
       <c r="C48" t="n">
-        <v>5.8416</v>
+        <v>5.5769</v>
       </c>
       <c r="D48" t="n">
-        <v>9.882709999999999</v>
+        <v>10.1403</v>
       </c>
       <c r="E48" t="n">
-        <v>5.08012</v>
+        <v>4.50994</v>
       </c>
       <c r="F48" t="n">
-        <v>5.44474</v>
+        <v>4.83248</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.4032</v>
+        <v>5.02223</v>
       </c>
       <c r="C49" t="n">
-        <v>6.00206</v>
+        <v>5.65184</v>
       </c>
       <c r="D49" t="n">
-        <v>10.1162</v>
+        <v>10.3652</v>
       </c>
       <c r="E49" t="n">
-        <v>5.33</v>
+        <v>4.52703</v>
       </c>
       <c r="F49" t="n">
-        <v>5.73348</v>
+        <v>4.82071</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.5478</v>
+        <v>5.15497</v>
       </c>
       <c r="C50" t="n">
-        <v>6.11137</v>
+        <v>5.79801</v>
       </c>
       <c r="D50" t="n">
-        <v>7.14368</v>
+        <v>7.38827</v>
       </c>
       <c r="E50" t="n">
-        <v>4.80564</v>
+        <v>4.55658</v>
       </c>
       <c r="F50" t="n">
-        <v>5.14543</v>
+        <v>4.84535</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>4.74327</v>
+        <v>5.41169</v>
       </c>
       <c r="C51" t="n">
-        <v>5.94262</v>
+        <v>5.62886</v>
       </c>
       <c r="D51" t="n">
-        <v>7.32539</v>
+        <v>7.53533</v>
       </c>
       <c r="E51" t="n">
-        <v>4.83276</v>
+        <v>4.58802</v>
       </c>
       <c r="F51" t="n">
-        <v>5.16889</v>
+        <v>4.87154</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.08754</v>
+        <v>5.7987</v>
       </c>
       <c r="C52" t="n">
-        <v>5.99561</v>
+        <v>5.60972</v>
       </c>
       <c r="D52" t="n">
-        <v>7.504</v>
+        <v>7.72635</v>
       </c>
       <c r="E52" t="n">
-        <v>4.84938</v>
+        <v>4.61514</v>
       </c>
       <c r="F52" t="n">
-        <v>5.16571</v>
+        <v>4.89818</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>4.76938</v>
+        <v>5.47037</v>
       </c>
       <c r="C53" t="n">
-        <v>5.98844</v>
+        <v>5.66144</v>
       </c>
       <c r="D53" t="n">
-        <v>7.77121</v>
+        <v>7.97844</v>
       </c>
       <c r="E53" t="n">
-        <v>4.87676</v>
+        <v>4.63192</v>
       </c>
       <c r="F53" t="n">
-        <v>5.1657</v>
+        <v>4.93045</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>4.76662</v>
+        <v>5.44708</v>
       </c>
       <c r="C54" t="n">
-        <v>5.97762</v>
+        <v>5.67847</v>
       </c>
       <c r="D54" t="n">
-        <v>8.00389</v>
+        <v>8.18375</v>
       </c>
       <c r="E54" t="n">
-        <v>4.93212</v>
+        <v>4.6749</v>
       </c>
       <c r="F54" t="n">
-        <v>5.22857</v>
+        <v>4.949</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>4.74368</v>
+        <v>5.4549</v>
       </c>
       <c r="C55" t="n">
-        <v>6.03157</v>
+        <v>5.71628</v>
       </c>
       <c r="D55" t="n">
-        <v>8.239369999999999</v>
+        <v>8.45241</v>
       </c>
       <c r="E55" t="n">
-        <v>4.93493</v>
+        <v>4.67869</v>
       </c>
       <c r="F55" t="n">
-        <v>5.29365</v>
+        <v>4.98091</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>4.7941</v>
+        <v>5.49467</v>
       </c>
       <c r="C56" t="n">
-        <v>6.06145</v>
+        <v>5.71422</v>
       </c>
       <c r="D56" t="n">
-        <v>8.48611</v>
+        <v>8.716279999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>4.98817</v>
+        <v>4.73787</v>
       </c>
       <c r="F56" t="n">
-        <v>5.32506</v>
+        <v>5.02182</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.80819</v>
+        <v>5.45248</v>
       </c>
       <c r="C57" t="n">
-        <v>6.08068</v>
+        <v>5.75142</v>
       </c>
       <c r="D57" t="n">
-        <v>8.768079999999999</v>
+        <v>8.99966</v>
       </c>
       <c r="E57" t="n">
-        <v>5.05443</v>
+        <v>4.79908</v>
       </c>
       <c r="F57" t="n">
-        <v>5.36824</v>
+        <v>5.08476</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.77944</v>
+        <v>5.51331</v>
       </c>
       <c r="C58" t="n">
-        <v>6.11868</v>
+        <v>5.77596</v>
       </c>
       <c r="D58" t="n">
-        <v>9.045199999999999</v>
+        <v>9.258559999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>5.05923</v>
+        <v>4.82969</v>
       </c>
       <c r="F58" t="n">
-        <v>5.39494</v>
+        <v>5.10598</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.81816</v>
+        <v>5.50892</v>
       </c>
       <c r="C59" t="n">
-        <v>6.12808</v>
+        <v>5.81271</v>
       </c>
       <c r="D59" t="n">
-        <v>9.242419999999999</v>
+        <v>9.523440000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>5.14413</v>
+        <v>4.87254</v>
       </c>
       <c r="F59" t="n">
-        <v>5.47658</v>
+        <v>5.18256</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.84292</v>
+        <v>5.52234</v>
       </c>
       <c r="C60" t="n">
-        <v>6.1471</v>
+        <v>5.78966</v>
       </c>
       <c r="D60" t="n">
-        <v>9.487450000000001</v>
+        <v>9.737489999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>5.22879</v>
+        <v>4.95907</v>
       </c>
       <c r="F60" t="n">
-        <v>5.58914</v>
+        <v>5.25662</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.83284</v>
+        <v>5.5365</v>
       </c>
       <c r="C61" t="n">
-        <v>6.25833</v>
+        <v>5.85625</v>
       </c>
       <c r="D61" t="n">
-        <v>9.783379999999999</v>
+        <v>10.0278</v>
       </c>
       <c r="E61" t="n">
-        <v>5.36052</v>
+        <v>5.06863</v>
       </c>
       <c r="F61" t="n">
-        <v>5.70852</v>
+        <v>5.3637</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>4.92625</v>
+        <v>5.57832</v>
       </c>
       <c r="C62" t="n">
-        <v>6.31707</v>
+        <v>5.95371</v>
       </c>
       <c r="D62" t="n">
-        <v>10.0162</v>
+        <v>10.2842</v>
       </c>
       <c r="E62" t="n">
-        <v>5.50943</v>
+        <v>5.20437</v>
       </c>
       <c r="F62" t="n">
-        <v>5.89134</v>
+        <v>5.54199</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>4.95339</v>
+        <v>5.67587</v>
       </c>
       <c r="C63" t="n">
-        <v>6.41525</v>
+        <v>6.05376</v>
       </c>
       <c r="D63" t="n">
-        <v>10.2587</v>
+        <v>10.52</v>
       </c>
       <c r="E63" t="n">
-        <v>5.74494</v>
+        <v>4.8371</v>
       </c>
       <c r="F63" t="n">
-        <v>6.09161</v>
+        <v>5.08193</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.05091</v>
+        <v>5.8235</v>
       </c>
       <c r="C64" t="n">
-        <v>6.56677</v>
+        <v>6.18095</v>
       </c>
       <c r="D64" t="n">
-        <v>7.37446</v>
+        <v>7.55727</v>
       </c>
       <c r="E64" t="n">
-        <v>5.11412</v>
+        <v>4.8163</v>
       </c>
       <c r="F64" t="n">
-        <v>5.34094</v>
+        <v>5.07524</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.27946</v>
+        <v>6.02357</v>
       </c>
       <c r="C65" t="n">
-        <v>6.2914</v>
+        <v>5.90753</v>
       </c>
       <c r="D65" t="n">
-        <v>7.60869</v>
+        <v>7.78158</v>
       </c>
       <c r="E65" t="n">
-        <v>5.13946</v>
+        <v>4.87372</v>
       </c>
       <c r="F65" t="n">
-        <v>5.37675</v>
+        <v>5.11099</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>5.5984</v>
+        <v>6.34002</v>
       </c>
       <c r="C66" t="n">
-        <v>6.33606</v>
+        <v>5.92879</v>
       </c>
       <c r="D66" t="n">
-        <v>7.85155</v>
+        <v>8.009169999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>5.16681</v>
+        <v>4.87302</v>
       </c>
       <c r="F66" t="n">
-        <v>5.40176</v>
+        <v>5.11947</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>5.52099</v>
+        <v>6.3712</v>
       </c>
       <c r="C67" t="n">
-        <v>6.32449</v>
+        <v>5.94342</v>
       </c>
       <c r="D67" t="n">
-        <v>8.124980000000001</v>
+        <v>8.30673</v>
       </c>
       <c r="E67" t="n">
-        <v>5.16532</v>
+        <v>4.90185</v>
       </c>
       <c r="F67" t="n">
-        <v>5.40732</v>
+        <v>5.16801</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>5.59872</v>
+        <v>6.44722</v>
       </c>
       <c r="C68" t="n">
-        <v>6.3858</v>
+        <v>5.96329</v>
       </c>
       <c r="D68" t="n">
-        <v>8.447089999999999</v>
+        <v>8.625489999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>5.2128</v>
+        <v>4.93055</v>
       </c>
       <c r="F68" t="n">
-        <v>5.59304</v>
+        <v>5.22849</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>5.56679</v>
+        <v>6.43882</v>
       </c>
       <c r="C69" t="n">
-        <v>6.35879</v>
+        <v>5.95977</v>
       </c>
       <c r="D69" t="n">
-        <v>8.75836</v>
+        <v>8.93938</v>
       </c>
       <c r="E69" t="n">
-        <v>5.24209</v>
+        <v>4.97533</v>
       </c>
       <c r="F69" t="n">
-        <v>5.61902</v>
+        <v>5.35287</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>5.64783</v>
+        <v>6.43038</v>
       </c>
       <c r="C70" t="n">
-        <v>6.39462</v>
+        <v>6.04884</v>
       </c>
       <c r="D70" t="n">
-        <v>9.050280000000001</v>
+        <v>9.29368</v>
       </c>
       <c r="E70" t="n">
-        <v>5.26831</v>
+        <v>5.00863</v>
       </c>
       <c r="F70" t="n">
-        <v>5.77442</v>
+        <v>5.37302</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>5.55404</v>
+        <v>6.40784</v>
       </c>
       <c r="C71" t="n">
-        <v>6.40677</v>
+        <v>6.01158</v>
       </c>
       <c r="D71" t="n">
-        <v>9.371980000000001</v>
+        <v>9.60647</v>
       </c>
       <c r="E71" t="n">
-        <v>5.30995</v>
+        <v>5.03743</v>
       </c>
       <c r="F71" t="n">
-        <v>6.28842</v>
+        <v>5.68762</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>5.56922</v>
+        <v>6.47149</v>
       </c>
       <c r="C72" t="n">
-        <v>6.43838</v>
+        <v>6.04781</v>
       </c>
       <c r="D72" t="n">
-        <v>9.65649</v>
+        <v>9.95908</v>
       </c>
       <c r="E72" t="n">
-        <v>5.35354</v>
+        <v>5.11741</v>
       </c>
       <c r="F72" t="n">
-        <v>6.44913</v>
+        <v>6.2198</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.66683</v>
+        <v>6.45935</v>
       </c>
       <c r="C73" t="n">
-        <v>6.48381</v>
+        <v>6.04689</v>
       </c>
       <c r="D73" t="n">
-        <v>10.2565</v>
+        <v>10.5982</v>
       </c>
       <c r="E73" t="n">
-        <v>5.44083</v>
+        <v>5.1584</v>
       </c>
       <c r="F73" t="n">
-        <v>7.36467</v>
+        <v>7.0171</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.66649</v>
+        <v>6.48163</v>
       </c>
       <c r="C74" t="n">
-        <v>6.51271</v>
+        <v>6.12359</v>
       </c>
       <c r="D74" t="n">
-        <v>10.8058</v>
+        <v>11.1214</v>
       </c>
       <c r="E74" t="n">
-        <v>5.51269</v>
+        <v>5.21546</v>
       </c>
       <c r="F74" t="n">
-        <v>8.008839999999999</v>
+        <v>7.64068</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.65999</v>
+        <v>6.51058</v>
       </c>
       <c r="C75" t="n">
-        <v>6.55917</v>
+        <v>6.17839</v>
       </c>
       <c r="D75" t="n">
-        <v>11.4116</v>
+        <v>11.8847</v>
       </c>
       <c r="E75" t="n">
-        <v>5.61547</v>
+        <v>5.35019</v>
       </c>
       <c r="F75" t="n">
-        <v>8.89817</v>
+        <v>8.46275</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.68302</v>
+        <v>6.53731</v>
       </c>
       <c r="C76" t="n">
-        <v>6.63321</v>
+        <v>6.26682</v>
       </c>
       <c r="D76" t="n">
-        <v>12.0946</v>
+        <v>12.454</v>
       </c>
       <c r="E76" t="n">
-        <v>5.77202</v>
+        <v>5.4889</v>
       </c>
       <c r="F76" t="n">
-        <v>9.55917</v>
+        <v>9.1365</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>5.78347</v>
+        <v>6.64682</v>
       </c>
       <c r="C77" t="n">
-        <v>6.74035</v>
+        <v>6.35682</v>
       </c>
       <c r="D77" t="n">
-        <v>13.2006</v>
+        <v>13.4313</v>
       </c>
       <c r="E77" t="n">
-        <v>5.98177</v>
+        <v>5.85888</v>
       </c>
       <c r="F77" t="n">
-        <v>10.2634</v>
+        <v>11.1865</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>5.88944</v>
+        <v>6.77041</v>
       </c>
       <c r="C78" t="n">
-        <v>6.88434</v>
+        <v>6.48876</v>
       </c>
       <c r="D78" t="n">
-        <v>15.0916</v>
+        <v>16.0234</v>
       </c>
       <c r="E78" t="n">
-        <v>6.40215</v>
+        <v>6.04478</v>
       </c>
       <c r="F78" t="n">
-        <v>11.8</v>
+        <v>11.2626</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>6.03409</v>
+        <v>6.91822</v>
       </c>
       <c r="C79" t="n">
-        <v>13.8842</v>
+        <v>13.5825</v>
       </c>
       <c r="D79" t="n">
-        <v>15.7975</v>
+        <v>16.7682</v>
       </c>
       <c r="E79" t="n">
-        <v>6.56624</v>
+        <v>6.31394</v>
       </c>
       <c r="F79" t="n">
-        <v>11.884</v>
+        <v>11.3696</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>6.27199</v>
+        <v>7.20378</v>
       </c>
       <c r="C80" t="n">
-        <v>14.0655</v>
+        <v>13.6939</v>
       </c>
       <c r="D80" t="n">
-        <v>16.5331</v>
+        <v>17.5915</v>
       </c>
       <c r="E80" t="n">
-        <v>6.55735</v>
+        <v>6.52964</v>
       </c>
       <c r="F80" t="n">
-        <v>11.9451</v>
+        <v>11.3891</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>13.6596</v>
+        <v>14.9718</v>
       </c>
       <c r="C81" t="n">
-        <v>14.128</v>
+        <v>14.0115</v>
       </c>
       <c r="D81" t="n">
-        <v>17.2646</v>
+        <v>18.268</v>
       </c>
       <c r="E81" t="n">
-        <v>6.82306</v>
+        <v>6.58773</v>
       </c>
       <c r="F81" t="n">
-        <v>11.9125</v>
+        <v>11.6017</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.6514</v>
+        <v>15.0891</v>
       </c>
       <c r="C82" t="n">
-        <v>14.2417</v>
+        <v>14.1325</v>
       </c>
       <c r="D82" t="n">
-        <v>17.9128</v>
+        <v>19.1156</v>
       </c>
       <c r="E82" t="n">
-        <v>6.88466</v>
+        <v>6.62947</v>
       </c>
       <c r="F82" t="n">
-        <v>12.1348</v>
+        <v>11.6404</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.8818</v>
+        <v>15.2032</v>
       </c>
       <c r="C83" t="n">
-        <v>14.4407</v>
+        <v>14.252</v>
       </c>
       <c r="D83" t="n">
-        <v>18.6659</v>
+        <v>19.7231</v>
       </c>
       <c r="E83" t="n">
-        <v>7.16849</v>
+        <v>6.84997</v>
       </c>
       <c r="F83" t="n">
-        <v>12.1904</v>
+        <v>11.7614</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>13.9472</v>
+        <v>15.3497</v>
       </c>
       <c r="C84" t="n">
-        <v>14.317</v>
+        <v>14.2494</v>
       </c>
       <c r="D84" t="n">
-        <v>19.2976</v>
+        <v>20.5023</v>
       </c>
       <c r="E84" t="n">
-        <v>7.2822</v>
+        <v>6.91073</v>
       </c>
       <c r="F84" t="n">
-        <v>12.314</v>
+        <v>11.8076</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>14.0605</v>
+        <v>15.3829</v>
       </c>
       <c r="C85" t="n">
-        <v>14.581</v>
+        <v>14.4455</v>
       </c>
       <c r="D85" t="n">
-        <v>20.0046</v>
+        <v>21.158</v>
       </c>
       <c r="E85" t="n">
-        <v>7.50027</v>
+        <v>7.31768</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3396</v>
+        <v>11.8852</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>14.1248</v>
+        <v>15.4862</v>
       </c>
       <c r="C86" t="n">
-        <v>14.5038</v>
+        <v>14.2638</v>
       </c>
       <c r="D86" t="n">
-        <v>20.6627</v>
+        <v>21.7322</v>
       </c>
       <c r="E86" t="n">
-        <v>7.57652</v>
+        <v>7.02705</v>
       </c>
       <c r="F86" t="n">
-        <v>12.4681</v>
+        <v>12.0123</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.0488</v>
+        <v>15.5517</v>
       </c>
       <c r="C87" t="n">
-        <v>14.5822</v>
+        <v>14.4728</v>
       </c>
       <c r="D87" t="n">
-        <v>21.3247</v>
+        <v>22.4743</v>
       </c>
       <c r="E87" t="n">
-        <v>7.79324</v>
+        <v>7.46469</v>
       </c>
       <c r="F87" t="n">
-        <v>12.6692</v>
+        <v>12.1648</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>14.1991</v>
+        <v>15.4871</v>
       </c>
       <c r="C88" t="n">
-        <v>14.6284</v>
+        <v>14.3528</v>
       </c>
       <c r="D88" t="n">
-        <v>22.0005</v>
+        <v>23.048</v>
       </c>
       <c r="E88" t="n">
-        <v>7.95282</v>
+        <v>7.68786</v>
       </c>
       <c r="F88" t="n">
-        <v>12.6359</v>
+        <v>12.3038</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>14.2217</v>
+        <v>15.5371</v>
       </c>
       <c r="C89" t="n">
-        <v>14.6104</v>
+        <v>14.3654</v>
       </c>
       <c r="D89" t="n">
-        <v>22.6709</v>
+        <v>23.6679</v>
       </c>
       <c r="E89" t="n">
-        <v>8.27988</v>
+        <v>7.77841</v>
       </c>
       <c r="F89" t="n">
-        <v>12.9377</v>
+        <v>12.486</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>14.1883</v>
+        <v>15.5778</v>
       </c>
       <c r="C90" t="n">
-        <v>14.7245</v>
+        <v>14.2661</v>
       </c>
       <c r="D90" t="n">
-        <v>23.3849</v>
+        <v>24.4007</v>
       </c>
       <c r="E90" t="n">
-        <v>8.46233</v>
+        <v>8.087429999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>13.1305</v>
+        <v>12.6285</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>14.3897</v>
+        <v>15.665</v>
       </c>
       <c r="C91" t="n">
-        <v>14.7094</v>
+        <v>14.459</v>
       </c>
       <c r="D91" t="n">
-        <v>24.1096</v>
+        <v>25.1183</v>
       </c>
       <c r="E91" t="n">
-        <v>8.37809</v>
+        <v>14.9659</v>
       </c>
       <c r="F91" t="n">
-        <v>13.4082</v>
+        <v>18.137</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>14.4342</v>
+        <v>15.602</v>
       </c>
       <c r="C92" t="n">
-        <v>14.7847</v>
+        <v>14.5511</v>
       </c>
       <c r="D92" t="n">
-        <v>24.0064</v>
+        <v>25.2691</v>
       </c>
       <c r="E92" t="n">
-        <v>16.7159</v>
+        <v>15.1566</v>
       </c>
       <c r="F92" t="n">
-        <v>20.0151</v>
+        <v>18.1918</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.6278</v>
+        <v>15.72</v>
       </c>
       <c r="C93" t="n">
-        <v>14.8895</v>
+        <v>14.6826</v>
       </c>
       <c r="D93" t="n">
-        <v>24.4806</v>
+        <v>25.7531</v>
       </c>
       <c r="E93" t="n">
-        <v>16.8264</v>
+        <v>15.2951</v>
       </c>
       <c r="F93" t="n">
-        <v>20.0357</v>
+        <v>18.2523</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>14.7427</v>
+        <v>16.0635</v>
       </c>
       <c r="C94" t="n">
-        <v>23.5813</v>
+        <v>23.1963</v>
       </c>
       <c r="D94" t="n">
-        <v>25.0758</v>
+        <v>26.2422</v>
       </c>
       <c r="E94" t="n">
-        <v>17.0497</v>
+        <v>15.402</v>
       </c>
       <c r="F94" t="n">
-        <v>20.2206</v>
+        <v>18.3319</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>20.8041</v>
+        <v>23.2302</v>
       </c>
       <c r="C95" t="n">
-        <v>23.5834</v>
+        <v>23.155</v>
       </c>
       <c r="D95" t="n">
-        <v>25.646</v>
+        <v>26.6804</v>
       </c>
       <c r="E95" t="n">
-        <v>17.2328</v>
+        <v>15.5859</v>
       </c>
       <c r="F95" t="n">
-        <v>20.3332</v>
+        <v>18.4286</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>20.8851</v>
+        <v>23.2517</v>
       </c>
       <c r="C96" t="n">
-        <v>23.6335</v>
+        <v>23.2013</v>
       </c>
       <c r="D96" t="n">
-        <v>26.1023</v>
+        <v>27.3154</v>
       </c>
       <c r="E96" t="n">
-        <v>17.3832</v>
+        <v>15.754</v>
       </c>
       <c r="F96" t="n">
-        <v>20.3059</v>
+        <v>18.6014</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>20.931</v>
+        <v>23.2349</v>
       </c>
       <c r="C97" t="n">
-        <v>23.702</v>
+        <v>23.2263</v>
       </c>
       <c r="D97" t="n">
-        <v>26.637</v>
+        <v>27.837</v>
       </c>
       <c r="E97" t="n">
-        <v>17.5479</v>
+        <v>15.9762</v>
       </c>
       <c r="F97" t="n">
-        <v>20.4584</v>
+        <v>18.5676</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>20.9802</v>
+        <v>23.2315</v>
       </c>
       <c r="C98" t="n">
-        <v>23.7165</v>
+        <v>23.248</v>
       </c>
       <c r="D98" t="n">
-        <v>27.2112</v>
+        <v>28.5201</v>
       </c>
       <c r="E98" t="n">
-        <v>17.7182</v>
+        <v>16.098</v>
       </c>
       <c r="F98" t="n">
-        <v>20.5767</v>
+        <v>18.6852</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>20.9591</v>
+        <v>23.2591</v>
       </c>
       <c r="C99" t="n">
-        <v>23.7237</v>
+        <v>23.2981</v>
       </c>
       <c r="D99" t="n">
-        <v>27.8116</v>
+        <v>29.1016</v>
       </c>
       <c r="E99" t="n">
-        <v>17.8219</v>
+        <v>16.2464</v>
       </c>
       <c r="F99" t="n">
-        <v>20.6715</v>
+        <v>18.7561</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>20.9307</v>
+        <v>23.3085</v>
       </c>
       <c r="C100" t="n">
-        <v>23.679</v>
+        <v>23.3863</v>
       </c>
       <c r="D100" t="n">
-        <v>28.3994</v>
+        <v>29.6916</v>
       </c>
       <c r="E100" t="n">
-        <v>17.9866</v>
+        <v>16.4389</v>
       </c>
       <c r="F100" t="n">
-        <v>20.7421</v>
+        <v>18.9314</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8792</v>
+        <v>23.3257</v>
       </c>
       <c r="C101" t="n">
-        <v>23.8239</v>
+        <v>23.4027</v>
       </c>
       <c r="D101" t="n">
-        <v>29.219</v>
+        <v>30.4636</v>
       </c>
       <c r="E101" t="n">
-        <v>18.2627</v>
+        <v>16.6642</v>
       </c>
       <c r="F101" t="n">
-        <v>20.8673</v>
+        <v>19.0518</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.9967</v>
+        <v>23.239</v>
       </c>
       <c r="C102" t="n">
-        <v>23.8188</v>
+        <v>23.3564</v>
       </c>
       <c r="D102" t="n">
-        <v>29.887</v>
+        <v>31.0511</v>
       </c>
       <c r="E102" t="n">
-        <v>18.4009</v>
+        <v>16.8295</v>
       </c>
       <c r="F102" t="n">
-        <v>20.9254</v>
+        <v>19.2666</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.0691</v>
+        <v>23.2837</v>
       </c>
       <c r="C103" t="n">
-        <v>24.0348</v>
+        <v>23.4338</v>
       </c>
       <c r="D103" t="n">
-        <v>30.6492</v>
+        <v>31.8142</v>
       </c>
       <c r="E103" t="n">
-        <v>18.5941</v>
+        <v>17.0675</v>
       </c>
       <c r="F103" t="n">
-        <v>21.121</v>
+        <v>19.3228</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.0687</v>
+        <v>23.3112</v>
       </c>
       <c r="C104" t="n">
-        <v>23.997</v>
+        <v>23.5334</v>
       </c>
       <c r="D104" t="n">
-        <v>31.3173</v>
+        <v>32.5678</v>
       </c>
       <c r="E104" t="n">
-        <v>18.6904</v>
+        <v>17.1952</v>
       </c>
       <c r="F104" t="n">
-        <v>21.3369</v>
+        <v>19.5103</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.0929</v>
+        <v>23.328</v>
       </c>
       <c r="C105" t="n">
-        <v>24.0406</v>
+        <v>23.6388</v>
       </c>
       <c r="D105" t="n">
-        <v>32.1426</v>
+        <v>33.369</v>
       </c>
       <c r="E105" t="n">
-        <v>18.9795</v>
+        <v>20.1943</v>
       </c>
       <c r="F105" t="n">
-        <v>21.4792</v>
+        <v>22.9538</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.1117</v>
+        <v>23.3722</v>
       </c>
       <c r="C106" t="n">
-        <v>24.2898</v>
+        <v>23.6611</v>
       </c>
       <c r="D106" t="n">
-        <v>33.0657</v>
+        <v>34.143</v>
       </c>
       <c r="E106" t="n">
-        <v>19.2012</v>
+        <v>20.3199</v>
       </c>
       <c r="F106" t="n">
-        <v>21.8125</v>
+        <v>23.0685</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.2269</v>
+        <v>23.4626</v>
       </c>
       <c r="C107" t="n">
-        <v>24.4302</v>
+        <v>23.8572</v>
       </c>
       <c r="D107" t="n">
-        <v>28.7937</v>
+        <v>29.8894</v>
       </c>
       <c r="E107" t="n">
-        <v>22.6748</v>
+        <v>20.5199</v>
       </c>
       <c r="F107" t="n">
-        <v>25.5118</v>
+        <v>23.1383</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>21.4341</v>
+        <v>23.6587</v>
       </c>
       <c r="C108" t="n">
-        <v>27.9571</v>
+        <v>27.3817</v>
       </c>
       <c r="D108" t="n">
-        <v>29.2327</v>
+        <v>30.3706</v>
       </c>
       <c r="E108" t="n">
-        <v>22.8394</v>
+        <v>20.5859</v>
       </c>
       <c r="F108" t="n">
-        <v>25.6426</v>
+        <v>23.256</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.8092</v>
+        <v>24.0061</v>
       </c>
       <c r="C109" t="n">
-        <v>27.9611</v>
+        <v>27.4496</v>
       </c>
       <c r="D109" t="n">
-        <v>29.8525</v>
+        <v>30.7959</v>
       </c>
       <c r="E109" t="n">
-        <v>23.0373</v>
+        <v>20.7752</v>
       </c>
       <c r="F109" t="n">
-        <v>25.773</v>
+        <v>23.4116</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.6078</v>
+        <v>26.3404</v>
       </c>
       <c r="C110" t="n">
-        <v>27.9646</v>
+        <v>27.3823</v>
       </c>
       <c r="D110" t="n">
-        <v>30.2988</v>
+        <v>31.4144</v>
       </c>
       <c r="E110" t="n">
-        <v>23.2238</v>
+        <v>20.9487</v>
       </c>
       <c r="F110" t="n">
-        <v>25.8229</v>
+        <v>23.5484</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.5484</v>
+        <v>26.255</v>
       </c>
       <c r="C111" t="n">
-        <v>27.9992</v>
+        <v>27.4437</v>
       </c>
       <c r="D111" t="n">
-        <v>30.8236</v>
+        <v>32.0524</v>
       </c>
       <c r="E111" t="n">
-        <v>23.333</v>
+        <v>21.1543</v>
       </c>
       <c r="F111" t="n">
-        <v>25.962</v>
+        <v>23.6334</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.5886</v>
+        <v>26.3806</v>
       </c>
       <c r="C112" t="n">
-        <v>28.101</v>
+        <v>27.521</v>
       </c>
       <c r="D112" t="n">
-        <v>31.4848</v>
+        <v>32.5922</v>
       </c>
       <c r="E112" t="n">
-        <v>23.5096</v>
+        <v>21.2774</v>
       </c>
       <c r="F112" t="n">
-        <v>26.0415</v>
+        <v>23.8534</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.5079</v>
+        <v>26.3322</v>
       </c>
       <c r="C113" t="n">
-        <v>28.1023</v>
+        <v>27.4595</v>
       </c>
       <c r="D113" t="n">
-        <v>32.0425</v>
+        <v>33.2223</v>
       </c>
       <c r="E113" t="n">
-        <v>23.7162</v>
+        <v>21.5017</v>
       </c>
       <c r="F113" t="n">
-        <v>26.2848</v>
+        <v>23.988</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>23.6608</v>
+        <v>26.2747</v>
       </c>
       <c r="C114" t="n">
-        <v>28.1757</v>
+        <v>27.6117</v>
       </c>
       <c r="D114" t="n">
-        <v>32.7029</v>
+        <v>33.9052</v>
       </c>
       <c r="E114" t="n">
-        <v>23.848</v>
+        <v>21.6868</v>
       </c>
       <c r="F114" t="n">
-        <v>26.4457</v>
+        <v>24.0604</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>23.5408</v>
+        <v>26.3415</v>
       </c>
       <c r="C115" t="n">
-        <v>28.1869</v>
+        <v>27.6075</v>
       </c>
       <c r="D115" t="n">
-        <v>33.505</v>
+        <v>34.5466</v>
       </c>
       <c r="E115" t="n">
-        <v>24.1686</v>
+        <v>21.876</v>
       </c>
       <c r="F115" t="n">
-        <v>26.6014</v>
+        <v>24.3379</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.6419</v>
+        <v>26.3662</v>
       </c>
       <c r="C116" t="n">
-        <v>28.3794</v>
+        <v>27.6188</v>
       </c>
       <c r="D116" t="n">
-        <v>34.0844</v>
+        <v>35.3463</v>
       </c>
       <c r="E116" t="n">
-        <v>24.209</v>
+        <v>22.1252</v>
       </c>
       <c r="F116" t="n">
-        <v>26.9231</v>
+        <v>24.5169</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>23.5449</v>
+        <v>26.3483</v>
       </c>
       <c r="C117" t="n">
-        <v>28.4269</v>
+        <v>27.8758</v>
       </c>
       <c r="D117" t="n">
-        <v>34.9653</v>
+        <v>36.1564</v>
       </c>
       <c r="E117" t="n">
-        <v>24.3815</v>
+        <v>22.2751</v>
       </c>
       <c r="F117" t="n">
-        <v>27.0286</v>
+        <v>24.8253</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>23.5938</v>
+        <v>26.4663</v>
       </c>
       <c r="C118" t="n">
-        <v>28.5904</v>
+        <v>27.8859</v>
       </c>
       <c r="D118" t="n">
-        <v>35.7095</v>
+        <v>36.8341</v>
       </c>
       <c r="E118" t="n">
-        <v>24.5968</v>
+        <v>22.6427</v>
       </c>
       <c r="F118" t="n">
-        <v>27.3911</v>
+        <v>25.2039</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>23.6953</v>
+        <v>26.4454</v>
       </c>
       <c r="C119" t="n">
-        <v>28.7508</v>
+        <v>28.0545</v>
       </c>
       <c r="D119" t="n">
-        <v>36.5141</v>
+        <v>37.7518</v>
       </c>
       <c r="E119" t="n">
-        <v>24.9574</v>
+        <v>23.5732</v>
       </c>
       <c r="F119" t="n">
-        <v>27.663</v>
+        <v>26.8565</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>23.7039</v>
+        <v>26.5378</v>
       </c>
       <c r="C120" t="n">
-        <v>28.9205</v>
+        <v>28.2172</v>
       </c>
       <c r="D120" t="n">
-        <v>37.4513</v>
+        <v>38.4438</v>
       </c>
       <c r="E120" t="n">
-        <v>25.1611</v>
+        <v>23.7581</v>
       </c>
       <c r="F120" t="n">
-        <v>28.2581</v>
+        <v>27.0449</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>23.8795</v>
+        <v>26.7172</v>
       </c>
       <c r="C121" t="n">
-        <v>29.0549</v>
+        <v>28.4748</v>
       </c>
       <c r="D121" t="n">
-        <v>31.3979</v>
+        <v>32.4225</v>
       </c>
       <c r="E121" t="n">
-        <v>25.8814</v>
+        <v>23.8516</v>
       </c>
       <c r="F121" t="n">
-        <v>29.7061</v>
+        <v>27.0434</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>24.0289</v>
+        <v>26.8836</v>
       </c>
       <c r="C122" t="n">
-        <v>31.0216</v>
+        <v>29.9028</v>
       </c>
       <c r="D122" t="n">
-        <v>31.9428</v>
+        <v>32.8911</v>
       </c>
       <c r="E122" t="n">
-        <v>25.9811</v>
+        <v>24.0884</v>
       </c>
       <c r="F122" t="n">
-        <v>29.9717</v>
+        <v>27.1492</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.4527</v>
+        <v>27.1831</v>
       </c>
       <c r="C123" t="n">
-        <v>31.167</v>
+        <v>29.9483</v>
       </c>
       <c r="D123" t="n">
-        <v>32.5175</v>
+        <v>33.4071</v>
       </c>
       <c r="E123" t="n">
-        <v>26.3106</v>
+        <v>24.1107</v>
       </c>
       <c r="F123" t="n">
-        <v>29.9558</v>
+        <v>27.3582</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>29.8801</v>
+        <v>33.7281</v>
       </c>
       <c r="C124" t="n">
-        <v>31.2304</v>
+        <v>29.9178</v>
       </c>
       <c r="D124" t="n">
-        <v>32.8849</v>
+        <v>34.1604</v>
       </c>
       <c r="E124" t="n">
-        <v>26.3441</v>
+        <v>24.2743</v>
       </c>
       <c r="F124" t="n">
-        <v>30.1898</v>
+        <v>27.3776</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>29.7213</v>
+        <v>33.8466</v>
       </c>
       <c r="C125" t="n">
-        <v>31.2368</v>
+        <v>29.9974</v>
       </c>
       <c r="D125" t="n">
-        <v>33.5798</v>
+        <v>34.5374</v>
       </c>
       <c r="E125" t="n">
-        <v>26.4139</v>
+        <v>24.4912</v>
       </c>
       <c r="F125" t="n">
-        <v>30.2592</v>
+        <v>27.5893</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>29.8165</v>
+        <v>33.6827</v>
       </c>
       <c r="C126" t="n">
-        <v>31.3812</v>
+        <v>30.1877</v>
       </c>
       <c r="D126" t="n">
-        <v>34.0748</v>
+        <v>35.1247</v>
       </c>
       <c r="E126" t="n">
-        <v>26.7319</v>
+        <v>24.6777</v>
       </c>
       <c r="F126" t="n">
-        <v>30.4872</v>
+        <v>27.7645</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>29.7723</v>
+        <v>33.7135</v>
       </c>
       <c r="C127" t="n">
-        <v>31.4756</v>
+        <v>30.1568</v>
       </c>
       <c r="D127" t="n">
-        <v>34.7512</v>
+        <v>35.8883</v>
       </c>
       <c r="E127" t="n">
-        <v>26.8412</v>
+        <v>24.7559</v>
       </c>
       <c r="F127" t="n">
-        <v>30.7049</v>
+        <v>27.9353</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>29.7511</v>
+        <v>33.7438</v>
       </c>
       <c r="C128" t="n">
-        <v>31.6618</v>
+        <v>30.2315</v>
       </c>
       <c r="D128" t="n">
-        <v>35.3149</v>
+        <v>36.5154</v>
       </c>
       <c r="E128" t="n">
-        <v>26.9521</v>
+        <v>24.9432</v>
       </c>
       <c r="F128" t="n">
-        <v>30.9076</v>
+        <v>28.1211</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>29.7008</v>
+        <v>33.8136</v>
       </c>
       <c r="C129" t="n">
-        <v>31.6611</v>
+        <v>30.3786</v>
       </c>
       <c r="D129" t="n">
-        <v>35.9971</v>
+        <v>37.2386</v>
       </c>
       <c r="E129" t="n">
-        <v>27.1703</v>
+        <v>25.1867</v>
       </c>
       <c r="F129" t="n">
-        <v>31.0804</v>
+        <v>28.3361</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>29.8024</v>
+        <v>33.818</v>
       </c>
       <c r="C130" t="n">
-        <v>31.8418</v>
+        <v>30.5659</v>
       </c>
       <c r="D130" t="n">
-        <v>36.6811</v>
+        <v>37.9264</v>
       </c>
       <c r="E130" t="n">
-        <v>27.3666</v>
+        <v>25.3461</v>
       </c>
       <c r="F130" t="n">
-        <v>31.3934</v>
+        <v>28.674</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>29.7075</v>
+        <v>33.8148</v>
       </c>
       <c r="C131" t="n">
-        <v>32.0279</v>
+        <v>30.6574</v>
       </c>
       <c r="D131" t="n">
-        <v>37.5609</v>
+        <v>38.6901</v>
       </c>
       <c r="E131" t="n">
-        <v>27.6806</v>
+        <v>25.6952</v>
       </c>
       <c r="F131" t="n">
-        <v>31.6385</v>
+        <v>28.8648</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.8625</v>
+        <v>33.7409</v>
       </c>
       <c r="C132" t="n">
-        <v>32.1385</v>
+        <v>30.9325</v>
       </c>
       <c r="D132" t="n">
-        <v>38.1944</v>
+        <v>39.4497</v>
       </c>
       <c r="E132" t="n">
-        <v>27.9293</v>
+        <v>25.9361</v>
       </c>
       <c r="F132" t="n">
-        <v>32.0141</v>
+        <v>29.2496</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>29.8937</v>
+        <v>33.7633</v>
       </c>
       <c r="C133" t="n">
-        <v>32.4106</v>
+        <v>31.184</v>
       </c>
       <c r="D133" t="n">
-        <v>39.1734</v>
+        <v>40.4606</v>
       </c>
       <c r="E133" t="n">
-        <v>28.2431</v>
+        <v>26.2125</v>
       </c>
       <c r="F133" t="n">
-        <v>32.4472</v>
+        <v>29.7903</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>29.9283</v>
+        <v>33.7974</v>
       </c>
       <c r="C134" t="n">
-        <v>32.6252</v>
+        <v>31.5428</v>
       </c>
       <c r="D134" t="n">
-        <v>39.9302</v>
+        <v>41.1523</v>
       </c>
       <c r="E134" t="n">
-        <v>28.5039</v>
+        <v>26.6893</v>
       </c>
       <c r="F134" t="n">
-        <v>32.8753</v>
+        <v>29.4523</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>30.1125</v>
+        <v>33.9244</v>
       </c>
       <c r="C135" t="n">
-        <v>32.9787</v>
+        <v>31.8158</v>
       </c>
       <c r="D135" t="n">
-        <v>33.343</v>
+        <v>34.204</v>
       </c>
       <c r="E135" t="n">
-        <v>27.749</v>
+        <v>26.7101</v>
       </c>
       <c r="F135" t="n">
-        <v>32.129</v>
+        <v>29.6588</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>30.2263</v>
+        <v>34.064</v>
       </c>
       <c r="C136" t="n">
-        <v>34.2779</v>
+        <v>31.7442</v>
       </c>
       <c r="D136" t="n">
-        <v>33.657</v>
+        <v>34.6411</v>
       </c>
       <c r="E136" t="n">
-        <v>27.8152</v>
+        <v>26.8597</v>
       </c>
       <c r="F136" t="n">
-        <v>32.2906</v>
+        <v>29.6518</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>30.4353</v>
+        <v>34.264</v>
       </c>
       <c r="C137" t="n">
-        <v>34.3686</v>
+        <v>31.8719</v>
       </c>
       <c r="D137" t="n">
-        <v>34.1468</v>
+        <v>35.5412</v>
       </c>
       <c r="E137" t="n">
-        <v>28.0002</v>
+        <v>27.387</v>
       </c>
       <c r="F137" t="n">
-        <v>32.5</v>
+        <v>29.7607</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>34.9929</v>
+        <v>40.7776</v>
       </c>
       <c r="C138" t="n">
-        <v>34.3267</v>
+        <v>31.9991</v>
       </c>
       <c r="D138" t="n">
-        <v>34.5873</v>
+        <v>35.6323</v>
       </c>
       <c r="E138" t="n">
-        <v>28.0951</v>
+        <v>27.2062</v>
       </c>
       <c r="F138" t="n">
-        <v>32.7806</v>
+        <v>29.8621</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>35.1613</v>
+        <v>40.7761</v>
       </c>
       <c r="C139" t="n">
-        <v>34.5015</v>
+        <v>32.004</v>
       </c>
       <c r="D139" t="n">
-        <v>35.2163</v>
+        <v>36.2886</v>
       </c>
       <c r="E139" t="n">
-        <v>28.283</v>
+        <v>27.3531</v>
       </c>
       <c r="F139" t="n">
-        <v>33.037</v>
+        <v>30.1528</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>35.0463</v>
+        <v>40.79</v>
       </c>
       <c r="C140" t="n">
-        <v>34.6422</v>
+        <v>31.93</v>
       </c>
       <c r="D140" t="n">
-        <v>35.76</v>
+        <v>36.7833</v>
       </c>
       <c r="E140" t="n">
-        <v>28.5536</v>
+        <v>27.5216</v>
       </c>
       <c r="F140" t="n">
-        <v>32.8959</v>
+        <v>30.3291</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>35.15</v>
+        <v>40.8798</v>
       </c>
       <c r="C141" t="n">
-        <v>34.6201</v>
+        <v>32.1965</v>
       </c>
       <c r="D141" t="n">
-        <v>36.2902</v>
+        <v>37.5296</v>
       </c>
       <c r="E141" t="n">
-        <v>28.6867</v>
+        <v>27.6098</v>
       </c>
       <c r="F141" t="n">
-        <v>33.2585</v>
+        <v>30.499</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>35.1196</v>
+        <v>40.8457</v>
       </c>
       <c r="C142" t="n">
-        <v>34.9538</v>
+        <v>32.2673</v>
       </c>
       <c r="D142" t="n">
-        <v>37.0234</v>
+        <v>38.0515</v>
       </c>
       <c r="E142" t="n">
-        <v>28.9124</v>
+        <v>27.7125</v>
       </c>
       <c r="F142" t="n">
-        <v>33.4706</v>
+        <v>30.6783</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>35.2082</v>
+        <v>40.8298</v>
       </c>
       <c r="C143" t="n">
-        <v>34.9257</v>
+        <v>32.5308</v>
       </c>
       <c r="D143" t="n">
-        <v>37.7622</v>
+        <v>38.7787</v>
       </c>
       <c r="E143" t="n">
-        <v>29.0461</v>
+        <v>28.0389</v>
       </c>
       <c r="F143" t="n">
-        <v>33.7373</v>
+        <v>30.8782</v>
       </c>
     </row>
   </sheetData>
